--- a/data/TISG.MI.xlsx
+++ b/data/TISG.MI.xlsx
@@ -25718,6 +25718,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1103">
+      <c r="A1103" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B1103" t="n">
+        <v>247220</v>
+      </c>
+      <c r="C1103" t="n">
+        <v>1.14400005340576</v>
+      </c>
+      <c r="D1103" t="n">
+        <v>1.10000002384186</v>
+      </c>
+      <c r="E1103" t="n">
+        <v>1.13999998569489</v>
+      </c>
+      <c r="F1103" t="n">
+        <v>1.11199998855591</v>
+      </c>
+      <c r="G1103" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TISG.MI.xlsx
+++ b/data/TISG.MI.xlsx
@@ -25741,6 +25741,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1104">
+      <c r="A1104" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B1104" t="n">
+        <v>75868</v>
+      </c>
+      <c r="C1104" t="n">
+        <v>1.13999998569489</v>
+      </c>
+      <c r="D1104" t="n">
+        <v>1.11199998855591</v>
+      </c>
+      <c r="E1104" t="n">
+        <v>1.13199996948242</v>
+      </c>
+      <c r="F1104" t="n">
+        <v>1.12399995326996</v>
+      </c>
+      <c r="G1104" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TISG.MI.xlsx
+++ b/data/TISG.MI.xlsx
@@ -25764,6 +25764,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1105">
+      <c r="A1105" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B1105" t="n">
+        <v>943175</v>
+      </c>
+      <c r="C1105" t="n">
+        <v>1.27600002288818</v>
+      </c>
+      <c r="D1105" t="n">
+        <v>1.1599999666214</v>
+      </c>
+      <c r="E1105" t="n">
+        <v>1.2059999704361</v>
+      </c>
+      <c r="F1105" t="n">
+        <v>1.26199996471405</v>
+      </c>
+      <c r="G1105" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TISG.MI.xlsx
+++ b/data/TISG.MI.xlsx
@@ -25787,6 +25787,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1106">
+      <c r="A1106" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B1106" t="n">
+        <v>789082</v>
+      </c>
+      <c r="C1106" t="n">
+        <v>1.36000001430511</v>
+      </c>
+      <c r="D1106" t="n">
+        <v>1.21000003814697</v>
+      </c>
+      <c r="E1106" t="n">
+        <v>1.24000000953674</v>
+      </c>
+      <c r="F1106" t="n">
+        <v>1.30200004577637</v>
+      </c>
+      <c r="G1106" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TISG.MI.xlsx
+++ b/data/TISG.MI.xlsx
@@ -25628,22 +25628,22 @@
     </row>
     <row r="1099">
       <c r="A1099" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B1099" t="n">
-        <v>563860</v>
+        <v>149922</v>
       </c>
       <c r="C1099" t="n">
-        <v>1.3400000333786</v>
+        <v>1.29799997806549</v>
       </c>
       <c r="D1099" t="n">
-        <v>1.24800002574921</v>
+        <v>1.23199999332428</v>
       </c>
       <c r="E1099" t="n">
-        <v>1.29799997806549</v>
+        <v>1.25999999046326</v>
       </c>
       <c r="F1099" t="n">
-        <v>1.29200005531311</v>
+        <v>1.24199998378754</v>
       </c>
       <c r="G1099" t="s">
         <v>7</v>
@@ -25651,22 +25651,22 @@
     </row>
     <row r="1100">
       <c r="A1100" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B1100" t="n">
-        <v>578106</v>
+        <v>563860</v>
       </c>
       <c r="C1100" t="n">
-        <v>1.38399994373322</v>
+        <v>1.3400000333786</v>
       </c>
       <c r="D1100" t="n">
-        <v>1.25999999046326</v>
+        <v>1.24800002574921</v>
       </c>
       <c r="E1100" t="n">
-        <v>1.37000000476837</v>
+        <v>1.29799997806549</v>
       </c>
       <c r="F1100" t="n">
-        <v>1.25999999046326</v>
+        <v>1.29200005531311</v>
       </c>
       <c r="G1100" t="s">
         <v>7</v>
@@ -25674,22 +25674,22 @@
     </row>
     <row r="1101">
       <c r="A1101" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B1101" t="n">
-        <v>1155165</v>
+        <v>578106</v>
       </c>
       <c r="C1101" t="n">
-        <v>1.25</v>
+        <v>1.38399994373322</v>
       </c>
       <c r="D1101" t="n">
-        <v>1.08000004291534</v>
+        <v>1.25999999046326</v>
       </c>
       <c r="E1101" t="n">
-        <v>1.19400000572205</v>
+        <v>1.37000000476837</v>
       </c>
       <c r="F1101" t="n">
-        <v>1.10000002384186</v>
+        <v>1.25999999046326</v>
       </c>
       <c r="G1101" t="s">
         <v>7</v>
@@ -25697,22 +25697,22 @@
     </row>
     <row r="1102">
       <c r="A1102" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B1102" t="n">
-        <v>357099</v>
+        <v>1155165</v>
       </c>
       <c r="C1102" t="n">
-        <v>1.14800000190735</v>
+        <v>1.25</v>
       </c>
       <c r="D1102" t="n">
-        <v>1.07400000095367</v>
+        <v>1.08000004291534</v>
       </c>
       <c r="E1102" t="n">
-        <v>1.08000004291534</v>
+        <v>1.19400000572205</v>
       </c>
       <c r="F1102" t="n">
-        <v>1.13800001144409</v>
+        <v>1.10000002384186</v>
       </c>
       <c r="G1102" t="s">
         <v>7</v>
@@ -25720,22 +25720,22 @@
     </row>
     <row r="1103">
       <c r="A1103" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B1103" t="n">
-        <v>247220</v>
+        <v>357099</v>
       </c>
       <c r="C1103" t="n">
-        <v>1.14400005340576</v>
+        <v>1.14800000190735</v>
       </c>
       <c r="D1103" t="n">
-        <v>1.10000002384186</v>
+        <v>1.07400000095367</v>
       </c>
       <c r="E1103" t="n">
-        <v>1.13999998569489</v>
+        <v>1.08000004291534</v>
       </c>
       <c r="F1103" t="n">
-        <v>1.11199998855591</v>
+        <v>1.13800001144409</v>
       </c>
       <c r="G1103" t="s">
         <v>7</v>
@@ -25743,22 +25743,22 @@
     </row>
     <row r="1104">
       <c r="A1104" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B1104" t="n">
-        <v>75868</v>
+        <v>247220</v>
       </c>
       <c r="C1104" t="n">
+        <v>1.14400005340576</v>
+      </c>
+      <c r="D1104" t="n">
+        <v>1.10000002384186</v>
+      </c>
+      <c r="E1104" t="n">
         <v>1.13999998569489</v>
       </c>
-      <c r="D1104" t="n">
+      <c r="F1104" t="n">
         <v>1.11199998855591</v>
-      </c>
-      <c r="E1104" t="n">
-        <v>1.13199996948242</v>
-      </c>
-      <c r="F1104" t="n">
-        <v>1.12399995326996</v>
       </c>
       <c r="G1104" t="s">
         <v>7</v>
@@ -25766,22 +25766,22 @@
     </row>
     <row r="1105">
       <c r="A1105" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B1105" t="n">
-        <v>943175</v>
+        <v>75868</v>
       </c>
       <c r="C1105" t="n">
-        <v>1.27600002288818</v>
+        <v>1.13999998569489</v>
       </c>
       <c r="D1105" t="n">
-        <v>1.1599999666214</v>
+        <v>1.11199998855591</v>
       </c>
       <c r="E1105" t="n">
-        <v>1.2059999704361</v>
+        <v>1.13199996948242</v>
       </c>
       <c r="F1105" t="n">
-        <v>1.26199996471405</v>
+        <v>1.12399995326996</v>
       </c>
       <c r="G1105" t="s">
         <v>7</v>
@@ -25789,24 +25789,47 @@
     </row>
     <row r="1106">
       <c r="A1106" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B1106" t="n">
-        <v>789082</v>
+        <v>943175</v>
       </c>
       <c r="C1106" t="n">
-        <v>1.36000001430511</v>
+        <v>1.27600002288818</v>
       </c>
       <c r="D1106" t="n">
-        <v>1.21000003814697</v>
+        <v>1.1599999666214</v>
       </c>
       <c r="E1106" t="n">
-        <v>1.24000000953674</v>
+        <v>1.2059999704361</v>
       </c>
       <c r="F1106" t="n">
-        <v>1.30200004577637</v>
+        <v>1.26199996471405</v>
       </c>
       <c r="G1106" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1107">
+      <c r="A1107" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B1107" t="n">
+        <v>465669</v>
+      </c>
+      <c r="C1107" t="n">
+        <v>1.31400001049042</v>
+      </c>
+      <c r="D1107" t="n">
+        <v>1.2039999961853</v>
+      </c>
+      <c r="E1107" t="n">
+        <v>1.31400001049042</v>
+      </c>
+      <c r="F1107" t="n">
+        <v>1.21200001239777</v>
+      </c>
+      <c r="G1107" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/TISG.MI.xlsx
+++ b/data/TISG.MI.xlsx
@@ -421,7 +421,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G2" t="n">
-        <v>4.97171211242676</v>
+        <v>4.97171258926392</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G3" t="n">
-        <v>5.12372493743896</v>
+        <v>5.12372541427612</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G4" t="n">
-        <v>5.16843509674072</v>
+        <v>5.16843461990356</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G6" t="n">
-        <v>4.97171211242676</v>
+        <v>4.97171258926392</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G7" t="n">
-        <v>4.94488668441772</v>
+        <v>4.94488716125488</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G11" t="n">
-        <v>4.97171211242676</v>
+        <v>4.97171258926392</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>5.6100001335144</v>
       </c>
       <c r="G13" t="n">
-        <v>5.01642227172852</v>
+        <v>5.01642179489136</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G16" t="n">
-        <v>5.03430604934692</v>
+        <v>5.03430652618408</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G17" t="n">
-        <v>4.96277093887329</v>
+        <v>4.96277046203613</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G19" t="n">
-        <v>4.94488668441772</v>
+        <v>4.94488716125488</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>5.6100001335144</v>
       </c>
       <c r="G22" t="n">
-        <v>5.01642227172852</v>
+        <v>5.01642179489136</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G25" t="n">
-        <v>4.64086151123047</v>
+        <v>4.64086103439331</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G29" t="n">
-        <v>4.67662858963013</v>
+        <v>4.67662906646729</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G30" t="n">
-        <v>4.71239614486694</v>
+        <v>4.7123966217041</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G32" t="n">
-        <v>4.68557071685791</v>
+        <v>4.68557024002075</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G33" t="n">
-        <v>4.68557071685791</v>
+        <v>4.68557024002075</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G34" t="n">
-        <v>4.68557071685791</v>
+        <v>4.68557024002075</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G35" t="n">
-        <v>4.64086151123047</v>
+        <v>4.64086103439331</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>4.78499984741211</v>
       </c>
       <c r="G37" t="n">
-        <v>4.27871322631836</v>
+        <v>4.2787127494812</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>4.84499979019165</v>
       </c>
       <c r="G49" t="n">
-        <v>4.33236455917358</v>
+        <v>4.33236408233643</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>4.84499979019165</v>
       </c>
       <c r="G51" t="n">
-        <v>4.33236455917358</v>
+        <v>4.33236408233643</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G52" t="n">
-        <v>4.2921257019043</v>
+        <v>4.29212617874146</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G57" t="n">
-        <v>4.2921257019043</v>
+        <v>4.29212617874146</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G59" t="n">
-        <v>4.51567459106445</v>
+        <v>4.51567411422729</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G62" t="n">
-        <v>4.78393220901489</v>
+        <v>4.78393173217773</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G63" t="n">
-        <v>4.64980268478394</v>
+        <v>4.64980316162109</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G64" t="n">
-        <v>4.78393220901489</v>
+        <v>4.78393173217773</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G69" t="n">
-        <v>4.64980268478394</v>
+        <v>4.64980316162109</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>4.86499977111816</v>
       </c>
       <c r="G78" t="n">
-        <v>4.35024785995483</v>
+        <v>4.35024833679199</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G79" t="n">
-        <v>4.2921257019043</v>
+        <v>4.29212617874146</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G80" t="n">
-        <v>4.2921257019043</v>
+        <v>4.29212617874146</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G81" t="n">
-        <v>4.2921257019043</v>
+        <v>4.29212617874146</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>4.83500003814697</v>
       </c>
       <c r="G82" t="n">
-        <v>4.3234224319458</v>
+        <v>4.32342290878296</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G84" t="n">
-        <v>4.1579966545105</v>
+        <v>4.15799713134766</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G86" t="n">
-        <v>4.1579966545105</v>
+        <v>4.15799713134766</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G96" t="n">
-        <v>4.2921257019043</v>
+        <v>4.29212617874146</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G99" t="n">
-        <v>4.3547191619873</v>
+        <v>4.35471963882446</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G100" t="n">
-        <v>4.37260293960571</v>
+        <v>4.37260341644287</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G101" t="n">
-        <v>4.08646202087402</v>
+        <v>4.08646154403687</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>4.46500015258789</v>
       </c>
       <c r="G102" t="n">
-        <v>3.99257135391235</v>
+        <v>3.99257159233093</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G103" t="n">
-        <v>3.95233297348022</v>
+        <v>3.95233249664307</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G104" t="n">
-        <v>4.01492547988892</v>
+        <v>4.01492595672607</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G105" t="n">
-        <v>3.90762281417847</v>
+        <v>3.90762233734131</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G106" t="n">
-        <v>3.84502959251404</v>
+        <v>3.84502983093262</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G108" t="n">
-        <v>3.82714581489563</v>
+        <v>3.82714557647705</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>4.2649998664856</v>
       </c>
       <c r="G110" t="n">
-        <v>3.81373262405396</v>
+        <v>3.81373286247253</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G111" t="n">
-        <v>3.69301700592041</v>
+        <v>3.69301676750183</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G113" t="n">
-        <v>3.75560975074768</v>
+        <v>3.75561022758484</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>4.5</v>
       </c>
       <c r="G114" t="n">
-        <v>4.02386808395386</v>
+        <v>4.02386856079102</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G115" t="n">
-        <v>4.1579966545105</v>
+        <v>4.15799713134766</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>4.78499984741211</v>
       </c>
       <c r="G118" t="n">
-        <v>4.27871322631836</v>
+        <v>4.2787127494812</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>4.875</v>
       </c>
       <c r="G121" t="n">
-        <v>4.35919094085693</v>
+        <v>4.35919046401978</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G123" t="n">
-        <v>4.2921257019043</v>
+        <v>4.29212617874146</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G124" t="n">
-        <v>4.2921257019043</v>
+        <v>4.29212617874146</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G126" t="n">
-        <v>4.27424192428589</v>
+        <v>4.27424240112305</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>4.84499979019165</v>
       </c>
       <c r="G127" t="n">
-        <v>4.33236455917358</v>
+        <v>4.33236408233643</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G131" t="n">
-        <v>4.68557071685791</v>
+        <v>4.68557024002075</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G133" t="n">
-        <v>4.82864141464233</v>
+        <v>4.82864189147949</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G135" t="n">
-        <v>4.67662858963013</v>
+        <v>4.67662906646729</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G138" t="n">
-        <v>4.81075811386108</v>
+        <v>4.81075763702393</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G142" t="n">
-        <v>4.86440944671631</v>
+        <v>4.86440896987915</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G143" t="n">
-        <v>4.79287385940552</v>
+        <v>4.79287433624268</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G146" t="n">
-        <v>5.13266706466675</v>
+        <v>5.13266754150391</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G149" t="n">
-        <v>5.18631887435913</v>
+        <v>5.18631935119629</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G151" t="n">
-        <v>5.18631887435913</v>
+        <v>5.18631935119629</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G152" t="n">
-        <v>5.23102807998657</v>
+        <v>5.23102855682373</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G153" t="n">
-        <v>5.16843509674072</v>
+        <v>5.16843461990356</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G154" t="n">
-        <v>5.13266706466675</v>
+        <v>5.13266754150391</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>5.6100001335144</v>
       </c>
       <c r="G156" t="n">
-        <v>5.01642227172852</v>
+        <v>5.01642179489136</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G159" t="n">
-        <v>4.95382881164551</v>
+        <v>4.95382833480835</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G160" t="n">
-        <v>5.09689903259277</v>
+        <v>5.09689950942993</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G161" t="n">
-        <v>5.18631887435913</v>
+        <v>5.18631935119629</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G162" t="n">
-        <v>5.09689903259277</v>
+        <v>5.09689950942993</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>5.69000005722046</v>
       </c>
       <c r="G164" t="n">
-        <v>5.08795738220215</v>
+        <v>5.08795785903931</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>5.67000007629395</v>
       </c>
       <c r="G166" t="n">
-        <v>5.0700740814209</v>
+        <v>5.07007360458374</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G168" t="n">
-        <v>5.12372493743896</v>
+        <v>5.12372541427612</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G174" t="n">
-        <v>5.03430604934692</v>
+        <v>5.03430652618408</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G175" t="n">
-        <v>5.13266706466675</v>
+        <v>5.13266754150391</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G176" t="n">
-        <v>5.17737674713135</v>
+        <v>5.17737722396851</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G178" t="n">
-        <v>5.12372493743896</v>
+        <v>5.12372541427612</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G182" t="n">
-        <v>5.5261116027832</v>
+        <v>5.52611207962036</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G184" t="n">
-        <v>5.67812442779541</v>
+        <v>5.67812490463257</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G185" t="n">
-        <v>5.70495080947876</v>
+        <v>5.7049503326416</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G186" t="n">
-        <v>5.89273166656494</v>
+        <v>5.89273118972778</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G191" t="n">
-        <v>6.21464061737061</v>
+        <v>6.21464014053345</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G194" t="n">
-        <v>6.18781518936157</v>
+        <v>6.18781471252441</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>6.90999984741211</v>
       </c>
       <c r="G195" t="n">
-        <v>6.17887258529663</v>
+        <v>6.17887306213379</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G200" t="n">
-        <v>6.21464061737061</v>
+        <v>6.21464014053345</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>7.03999996185303</v>
       </c>
       <c r="G202" t="n">
-        <v>6.29511737823486</v>
+        <v>6.29511785507202</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G206" t="n">
-        <v>6.30406045913696</v>
+        <v>6.3040599822998</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G211" t="n">
-        <v>6.67067861557007</v>
+        <v>6.67067909240723</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G215" t="n">
-        <v>6.66173696517944</v>
+        <v>6.66173648834229</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G216" t="n">
-        <v>6.67067861557007</v>
+        <v>6.67067909240723</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G220" t="n">
-        <v>6.60808563232422</v>
+        <v>6.60808515548706</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G224" t="n">
-        <v>6.66173696517944</v>
+        <v>6.66173648834229</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>8.56999969482422</v>
       </c>
       <c r="G232" t="n">
-        <v>7.66323232650757</v>
+        <v>7.66323280334473</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G235" t="n">
-        <v>7.65429162979126</v>
+        <v>7.6542911529541</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G236" t="n">
-        <v>7.35920715332031</v>
+        <v>7.35920667648315</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G237" t="n">
-        <v>7.35920715332031</v>
+        <v>7.35920667648315</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G238" t="n">
-        <v>7.73476791381836</v>
+        <v>7.73476839065552</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>8.75</v>
       </c>
       <c r="G239" t="n">
-        <v>7.82418775558472</v>
+        <v>7.82418727874756</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G240" t="n">
-        <v>7.86889696121216</v>
+        <v>7.86889791488647</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G241" t="n">
-        <v>7.94043350219727</v>
+        <v>7.94043302536011</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G243" t="n">
-        <v>7.73476791381836</v>
+        <v>7.73476839065552</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>8.60999965667725</v>
       </c>
       <c r="G244" t="n">
-        <v>7.6990008354187</v>
+        <v>7.69899988174438</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>8.57999992370605</v>
       </c>
       <c r="G246" t="n">
-        <v>7.67217493057251</v>
+        <v>7.67217540740967</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G247" t="n">
-        <v>7.64534997940063</v>
+        <v>7.64534902572632</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>8.63000011444092</v>
       </c>
       <c r="G248" t="n">
-        <v>7.71688508987427</v>
+        <v>7.71688461303711</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G249" t="n">
-        <v>7.73476791381836</v>
+        <v>7.73476839065552</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G254" t="n">
-        <v>7.81047248840332</v>
+        <v>7.81047344207764</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>8.52999973297119</v>
       </c>
       <c r="G256" t="n">
-        <v>7.87509775161743</v>
+        <v>7.87509870529175</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>8.60999965667725</v>
       </c>
       <c r="G263" t="n">
-        <v>7.94895648956299</v>
+        <v>7.94895553588867</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>8.60999965667725</v>
       </c>
       <c r="G268" t="n">
-        <v>7.94895648956299</v>
+        <v>7.94895553588867</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G270" t="n">
-        <v>7.95818901062012</v>
+        <v>7.95818853378296</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G279" t="n">
-        <v>7.42271852493286</v>
+        <v>7.42271900177002</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G281" t="n">
-        <v>7.49657678604126</v>
+        <v>7.4965763092041</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>7.80999994277954</v>
       </c>
       <c r="G284" t="n">
-        <v>7.21037721633911</v>
+        <v>7.21037769317627</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>7.71000003814697</v>
       </c>
       <c r="G285" t="n">
-        <v>7.11805486679077</v>
+        <v>7.11805534362793</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G286" t="n">
-        <v>7.0534291267395</v>
+        <v>7.05342960357666</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G287" t="n">
-        <v>7.10882234573364</v>
+        <v>7.1088228225708</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G288" t="n">
-        <v>6.97033977508545</v>
+        <v>6.97033929824829</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G289" t="n">
-        <v>6.97033977508545</v>
+        <v>6.97033929824829</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G296" t="n">
-        <v>7.30270004272461</v>
+        <v>7.30269956588745</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G297" t="n">
-        <v>7.145751953125</v>
+        <v>7.14575147628784</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>7.78999996185303</v>
       </c>
       <c r="G300" t="n">
-        <v>7.19191312789917</v>
+        <v>7.19191265106201</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G309" t="n">
-        <v>6.93341016769409</v>
+        <v>6.93341064453125</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G310" t="n">
-        <v>6.97033977508545</v>
+        <v>6.97033929824829</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G311" t="n">
-        <v>6.87801694869995</v>
+        <v>6.87801647186279</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G312" t="n">
-        <v>7.03496503829956</v>
+        <v>7.0349645614624</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G316" t="n">
-        <v>6.97033977508545</v>
+        <v>6.97033929824829</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G318" t="n">
-        <v>7.42271852493286</v>
+        <v>7.42271900177002</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>7.78999996185303</v>
       </c>
       <c r="G321" t="n">
-        <v>7.19191312789917</v>
+        <v>7.19191265106201</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G326" t="n">
-        <v>7.10882234573364</v>
+        <v>7.1088228225708</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G327" t="n">
-        <v>6.97033977508545</v>
+        <v>6.97033929824829</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G328" t="n">
-        <v>7.13651990890503</v>
+        <v>7.13651943206787</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G329" t="n">
-        <v>7.0534291267395</v>
+        <v>7.05342960357666</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G332" t="n">
-        <v>6.93341016769409</v>
+        <v>6.93341064453125</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G333" t="n">
-        <v>7.0534291267395</v>
+        <v>7.05342960357666</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G335" t="n">
-        <v>7.0534291267395</v>
+        <v>7.05342960357666</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G344" t="n">
-        <v>6.97033977508545</v>
+        <v>6.97033929824829</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G346" t="n">
-        <v>7.145751953125</v>
+        <v>7.14575147628784</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G348" t="n">
-        <v>6.90571355819702</v>
+        <v>6.90571403503418</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>7.53999996185303</v>
       </c>
       <c r="G350" t="n">
-        <v>6.96110677719116</v>
+        <v>6.96110725402832</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G351" t="n">
-        <v>6.77646207809448</v>
+        <v>6.77646255493164</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G355" t="n">
-        <v>6.53642416000366</v>
+        <v>6.5364236831665</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>6.98999977111816</v>
       </c>
       <c r="G360" t="n">
-        <v>6.45333337783813</v>
+        <v>6.45333385467529</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G362" t="n">
-        <v>6.6472110748291</v>
+        <v>6.64721059799194</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G363" t="n">
-        <v>6.40717267990112</v>
+        <v>6.40717315673828</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G364" t="n">
-        <v>6.63797903060913</v>
+        <v>6.63797855377197</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G367" t="n">
-        <v>6.48103094100952</v>
+        <v>6.48103046417236</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>7.09000015258789</v>
       </c>
       <c r="G368" t="n">
-        <v>6.54565668106079</v>
+        <v>6.54565620422363</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>7.09000015258789</v>
       </c>
       <c r="G370" t="n">
-        <v>6.54565668106079</v>
+        <v>6.54565620422363</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G371" t="n">
-        <v>6.63797903060913</v>
+        <v>6.63797855377197</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G373" t="n">
-        <v>6.32408285140991</v>
+        <v>6.32408237457275</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>7</v>
       </c>
       <c r="G374" t="n">
-        <v>6.46256589889526</v>
+        <v>6.46256637573242</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>7.09000015258789</v>
       </c>
       <c r="G383" t="n">
-        <v>6.54565668106079</v>
+        <v>6.54565620422363</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G387" t="n">
-        <v>6.61028146743774</v>
+        <v>6.6102819442749</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G389" t="n">
-        <v>6.87801694869995</v>
+        <v>6.87801647186279</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G390" t="n">
-        <v>7.13651990890503</v>
+        <v>7.13651943206787</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G393" t="n">
-        <v>7.30270004272461</v>
+        <v>7.30269956588745</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G394" t="n">
-        <v>7.2011456489563</v>
+        <v>7.20114517211914</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>7.86999988555908</v>
       </c>
       <c r="G396" t="n">
-        <v>7.26577043533325</v>
+        <v>7.26577091217041</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G398" t="n">
-        <v>7.30270004272461</v>
+        <v>7.30269956588745</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G399" t="n">
-        <v>7.36732530593872</v>
+        <v>7.36732578277588</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G400" t="n">
-        <v>7.24730634689331</v>
+        <v>7.24730587005615</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G405" t="n">
-        <v>7.30270004272461</v>
+        <v>7.30269956588745</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G423" t="n">
-        <v>7.40425491333008</v>
+        <v>7.40425443649292</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>8.25</v>
       </c>
       <c r="G427" t="n">
-        <v>7.61659574508667</v>
+        <v>7.61659622192383</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G429" t="n">
-        <v>7.90279626846313</v>
+        <v>7.90279531478882</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G435" t="n">
-        <v>8.63214302062988</v>
+        <v>8.63214206695557</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>9.6899995803833</v>
       </c>
       <c r="G441" t="n">
-        <v>8.94603824615479</v>
+        <v>8.94603729248047</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G443" t="n">
-        <v>8.9921989440918</v>
+        <v>8.99219989776611</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G452" t="n">
-        <v>9.52766799926758</v>
+        <v>9.52766895294189</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G453" t="n">
-        <v>9.61999225616455</v>
+        <v>9.61999130249023</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G454" t="n">
-        <v>9.4168815612793</v>
+        <v>9.41688251495361</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G456" t="n">
-        <v>9.25070285797119</v>
+        <v>9.25070190429688</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G458" t="n">
-        <v>9.26916694641113</v>
+        <v>9.26916599273682</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G464" t="n">
-        <v>9.26916694641113</v>
+        <v>9.26916599273682</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>9.98999977111816</v>
       </c>
       <c r="G466" t="n">
-        <v>9.22300434112549</v>
+        <v>9.2230052947998</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G470" t="n">
-        <v>9.61999225616455</v>
+        <v>9.61999130249023</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>10.4799995422363</v>
       </c>
       <c r="G471" t="n">
-        <v>9.67538452148438</v>
+        <v>9.67538356781006</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G476" t="n">
-        <v>9.61999225616455</v>
+        <v>9.61999130249023</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G477" t="n">
-        <v>9.58306312561035</v>
+        <v>9.58306217193604</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G480" t="n">
-        <v>10.247784614563</v>
+        <v>10.2477836608887</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>11.1199998855591</v>
       </c>
       <c r="G481" t="n">
-        <v>10.2662487030029</v>
+        <v>10.2662477493286</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G482" t="n">
-        <v>8.93680667877197</v>
+        <v>8.93680572509766</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G483" t="n">
-        <v>9.28763198852539</v>
+        <v>9.28763103485107</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G484" t="n">
-        <v>9.21377182006836</v>
+        <v>9.21377277374268</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>9.63000011444092</v>
       </c>
       <c r="G488" t="n">
-        <v>8.89064407348633</v>
+        <v>8.89064502716064</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>9.28999996185303</v>
       </c>
       <c r="G494" t="n">
-        <v>8.57674884796143</v>
+        <v>8.57674789428711</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G495" t="n">
-        <v>8.48442554473877</v>
+        <v>8.48442649841309</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G499" t="n">
-        <v>8.62291049957275</v>
+        <v>8.62290954589844</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G501" t="n">
-        <v>8.62291049957275</v>
+        <v>8.62290954589844</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>9.6899995803833</v>
       </c>
       <c r="G503" t="n">
-        <v>8.94603824615479</v>
+        <v>8.94603729248047</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G504" t="n">
-        <v>8.86294746398926</v>
+        <v>8.86294841766357</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G511" t="n">
-        <v>8.78909015655518</v>
+        <v>8.78909111022949</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>9.8100004196167</v>
       </c>
       <c r="G513" t="n">
-        <v>9.05682563781738</v>
+        <v>9.05682468414307</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G516" t="n">
-        <v>8.95527076721191</v>
+        <v>8.9552698135376</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -29206,6 +29206,32 @@
         <v>1.24199998378754</v>
       </c>
       <c r="H1109" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1110">
+      <c r="A1110" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B1110" t="n">
+        <v>229179</v>
+      </c>
+      <c r="C1110" t="n">
+        <v>1.28600001335144</v>
+      </c>
+      <c r="D1110" t="n">
+        <v>1.22599995136261</v>
+      </c>
+      <c r="E1110" t="n">
+        <v>1.22599995136261</v>
+      </c>
+      <c r="F1110" t="n">
+        <v>1.23199999332428</v>
+      </c>
+      <c r="G1110" t="n">
+        <v>1.23199999332428</v>
+      </c>
+      <c r="H1110" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/TISG.MI.xlsx
+++ b/data/TISG.MI.xlsx
@@ -447,7 +447,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G3" t="n">
-        <v>5.12372541427612</v>
+        <v>5.12372589111328</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G4" t="n">
-        <v>5.16843461990356</v>
+        <v>5.16843509674072</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G7" t="n">
-        <v>4.94488716125488</v>
+        <v>4.94488668441772</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>5.6100001335144</v>
       </c>
       <c r="G13" t="n">
-        <v>5.01642179489136</v>
+        <v>5.01642227172852</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G16" t="n">
-        <v>5.03430652618408</v>
+        <v>5.03430604934692</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G17" t="n">
-        <v>4.96277046203613</v>
+        <v>4.96277093887329</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G18" t="n">
-        <v>4.9359450340271</v>
+        <v>4.93594455718994</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G19" t="n">
-        <v>4.94488716125488</v>
+        <v>4.94488668441772</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G21" t="n">
-        <v>5.02536392211914</v>
+        <v>5.0253643989563</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>5.6100001335144</v>
       </c>
       <c r="G22" t="n">
-        <v>5.01642179489136</v>
+        <v>5.01642227172852</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G25" t="n">
-        <v>4.64086103439331</v>
+        <v>4.64086151123047</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G31" t="n">
-        <v>4.65874481201172</v>
+        <v>4.65874528884888</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G32" t="n">
-        <v>4.68557024002075</v>
+        <v>4.68557071685791</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G33" t="n">
-        <v>4.68557024002075</v>
+        <v>4.68557071685791</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G34" t="n">
-        <v>4.68557024002075</v>
+        <v>4.68557071685791</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G35" t="n">
-        <v>4.64086103439331</v>
+        <v>4.64086151123047</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G40" t="n">
-        <v>4.3368353843689</v>
+        <v>4.33683586120605</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G42" t="n">
-        <v>4.40837097167969</v>
+        <v>4.40837049484253</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G45" t="n">
-        <v>4.39048671722412</v>
+        <v>4.39048719406128</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G47" t="n">
-        <v>4.3368353843689</v>
+        <v>4.33683586120605</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G48" t="n">
-        <v>4.25635862350464</v>
+        <v>4.25635814666748</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>4.84499979019165</v>
       </c>
       <c r="G49" t="n">
-        <v>4.33236408233643</v>
+        <v>4.33236455917358</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>4.84499979019165</v>
       </c>
       <c r="G51" t="n">
-        <v>4.33236408233643</v>
+        <v>4.33236455917358</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G52" t="n">
-        <v>4.29212617874146</v>
+        <v>4.2921257019043</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G53" t="n">
-        <v>4.32789373397827</v>
+        <v>4.32789421081543</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G57" t="n">
-        <v>4.29212617874146</v>
+        <v>4.2921257019043</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G58" t="n">
-        <v>4.32789373397827</v>
+        <v>4.32789421081543</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G61" t="n">
-        <v>4.9359450340271</v>
+        <v>4.93594455718994</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G65" t="n">
-        <v>4.65874481201172</v>
+        <v>4.65874528884888</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G66" t="n">
-        <v>4.65874481201172</v>
+        <v>4.65874528884888</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G70" t="n">
-        <v>4.56038379669189</v>
+        <v>4.56038331985474</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G71" t="n">
-        <v>4.61403512954712</v>
+        <v>4.61403465270996</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>4.9850001335144</v>
       </c>
       <c r="G75" t="n">
-        <v>4.45755195617676</v>
+        <v>4.4575514793396</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>4.85500001907349</v>
       </c>
       <c r="G76" t="n">
-        <v>4.34130620956421</v>
+        <v>4.34130668640137</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G77" t="n">
-        <v>4.31000995635986</v>
+        <v>4.31000947952271</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G79" t="n">
-        <v>4.29212617874146</v>
+        <v>4.2921257019043</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G80" t="n">
-        <v>4.29212617874146</v>
+        <v>4.2921257019043</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G81" t="n">
-        <v>4.29212617874146</v>
+        <v>4.2921257019043</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G87" t="n">
-        <v>4.23847389221191</v>
+        <v>4.23847436904907</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G88" t="n">
-        <v>4.49779033660889</v>
+        <v>4.49779081344604</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G90" t="n">
-        <v>4.4888482093811</v>
+        <v>4.48884868621826</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>4.85500001907349</v>
       </c>
       <c r="G91" t="n">
-        <v>4.34130620956421</v>
+        <v>4.34130668640137</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G92" t="n">
-        <v>4.40837097167969</v>
+        <v>4.40837049484253</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G96" t="n">
-        <v>4.29212617874146</v>
+        <v>4.2921257019043</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G99" t="n">
-        <v>4.35471963882446</v>
+        <v>4.3547191619873</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G105" t="n">
-        <v>3.90762233734131</v>
+        <v>3.90762281417847</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>4.39499998092651</v>
       </c>
       <c r="G107" t="n">
-        <v>3.92997789382935</v>
+        <v>3.92997741699219</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G108" t="n">
-        <v>3.82714557647705</v>
+        <v>3.82714605331421</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G109" t="n">
-        <v>3.80926203727722</v>
+        <v>3.80926156044006</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>4.2649998664856</v>
       </c>
       <c r="G110" t="n">
-        <v>3.81373286247253</v>
+        <v>3.81373238563538</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G113" t="n">
-        <v>3.75561022758484</v>
+        <v>3.75560975074768</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G116" t="n">
-        <v>4.17588090896606</v>
+        <v>4.17588138580322</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G122" t="n">
-        <v>4.25635862350464</v>
+        <v>4.25635814666748</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G123" t="n">
-        <v>4.29212617874146</v>
+        <v>4.2921257019043</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G124" t="n">
-        <v>4.29212617874146</v>
+        <v>4.2921257019043</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>4.84499979019165</v>
       </c>
       <c r="G127" t="n">
-        <v>4.33236408233643</v>
+        <v>4.33236455917358</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G131" t="n">
-        <v>4.68557024002075</v>
+        <v>4.68557071685791</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G138" t="n">
-        <v>4.81075763702393</v>
+        <v>4.81075811386108</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G141" t="n">
-        <v>4.9359450340271</v>
+        <v>4.93594455718994</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G142" t="n">
-        <v>4.86440896987915</v>
+        <v>4.86440944671631</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G143" t="n">
-        <v>4.79287433624268</v>
+        <v>4.79287385940552</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G147" t="n">
-        <v>5.02536392211914</v>
+        <v>5.0253643989563</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G149" t="n">
-        <v>5.18631935119629</v>
+        <v>5.18631887435913</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G151" t="n">
-        <v>5.18631935119629</v>
+        <v>5.18631887435913</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G153" t="n">
-        <v>5.16843461990356</v>
+        <v>5.16843509674072</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>5.6100001335144</v>
       </c>
       <c r="G156" t="n">
-        <v>5.01642179489136</v>
+        <v>5.01642227172852</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G158" t="n">
-        <v>5.02536392211914</v>
+        <v>5.0253643989563</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G160" t="n">
-        <v>5.09689950942993</v>
+        <v>5.09689903259277</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G161" t="n">
-        <v>5.18631935119629</v>
+        <v>5.18631887435913</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G162" t="n">
-        <v>5.09689950942993</v>
+        <v>5.09689903259277</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>5.69000005722046</v>
       </c>
       <c r="G164" t="n">
-        <v>5.08795785903931</v>
+        <v>5.08795738220215</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G165" t="n">
-        <v>5.04324817657471</v>
+        <v>5.04324769973755</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G168" t="n">
-        <v>5.12372541427612</v>
+        <v>5.12372589111328</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G174" t="n">
-        <v>5.03430652618408</v>
+        <v>5.03430604934692</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G178" t="n">
-        <v>5.12372541427612</v>
+        <v>5.12372589111328</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>5.90999984741211</v>
       </c>
       <c r="G179" t="n">
-        <v>5.28467988967896</v>
+        <v>5.28468036651611</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G185" t="n">
-        <v>5.7049503326416</v>
+        <v>5.70495080947876</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>6.80999994277954</v>
       </c>
       <c r="G192" t="n">
-        <v>6.08945369720459</v>
+        <v>6.08945322036743</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>7</v>
       </c>
       <c r="G193" t="n">
-        <v>6.25935029983521</v>
+        <v>6.25934982299805</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>7</v>
       </c>
       <c r="G197" t="n">
-        <v>6.25935029983521</v>
+        <v>6.25934982299805</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>7.03000020980835</v>
       </c>
       <c r="G199" t="n">
-        <v>6.2861762046814</v>
+        <v>6.28617668151855</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G201" t="n">
-        <v>6.27723407745361</v>
+        <v>6.27723455429077</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>7.09000015258789</v>
       </c>
       <c r="G204" t="n">
-        <v>6.33982753753662</v>
+        <v>6.33982801437378</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>7.03000020980835</v>
       </c>
       <c r="G205" t="n">
-        <v>6.2861762046814</v>
+        <v>6.28617668151855</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G215" t="n">
-        <v>6.66173648834229</v>
+        <v>6.66173696517944</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G220" t="n">
-        <v>6.60808515548706</v>
+        <v>6.60808563232422</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G224" t="n">
-        <v>6.66173648834229</v>
+        <v>6.66173696517944</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G231" t="n">
-        <v>7.3681492805481</v>
+        <v>7.36814880371094</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G235" t="n">
-        <v>7.6542911529541</v>
+        <v>7.65429210662842</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>8.75</v>
       </c>
       <c r="G239" t="n">
-        <v>7.82418727874756</v>
+        <v>7.82418823242188</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G240" t="n">
-        <v>7.86889791488647</v>
+        <v>7.86889696121216</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>8.60999965667725</v>
       </c>
       <c r="G244" t="n">
-        <v>7.69899988174438</v>
+        <v>7.6990008354187</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G247" t="n">
-        <v>7.64534902572632</v>
+        <v>7.64534997940063</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G254" t="n">
-        <v>7.81047344207764</v>
+        <v>7.81047248840332</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>8.52999973297119</v>
       </c>
       <c r="G256" t="n">
-        <v>7.87509870529175</v>
+        <v>7.87509775161743</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>8.60999965667725</v>
       </c>
       <c r="G263" t="n">
-        <v>7.94895553588867</v>
+        <v>7.94895648956299</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>8.60999965667725</v>
       </c>
       <c r="G268" t="n">
-        <v>7.94895553588867</v>
+        <v>7.94895648956299</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G270" t="n">
-        <v>7.95818853378296</v>
+        <v>7.95818901062012</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G279" t="n">
-        <v>7.42271900177002</v>
+        <v>7.42271852493286</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G281" t="n">
-        <v>7.4965763092041</v>
+        <v>7.49657678604126</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>7.80999994277954</v>
       </c>
       <c r="G284" t="n">
-        <v>7.21037769317627</v>
+        <v>7.21037721633911</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>7.71000003814697</v>
       </c>
       <c r="G285" t="n">
-        <v>7.11805534362793</v>
+        <v>7.11805486679077</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G286" t="n">
-        <v>7.05342960357666</v>
+        <v>7.0534291267395</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G287" t="n">
-        <v>7.1088228225708</v>
+        <v>7.10882234573364</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G288" t="n">
-        <v>6.97033929824829</v>
+        <v>6.97033977508545</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G289" t="n">
-        <v>6.97033929824829</v>
+        <v>6.97033977508545</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G296" t="n">
-        <v>7.30269956588745</v>
+        <v>7.30270004272461</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G297" t="n">
-        <v>7.14575147628784</v>
+        <v>7.145751953125</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>7.78999996185303</v>
       </c>
       <c r="G300" t="n">
-        <v>7.19191265106201</v>
+        <v>7.19191312789917</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G309" t="n">
-        <v>6.93341064453125</v>
+        <v>6.93341016769409</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G310" t="n">
-        <v>6.97033929824829</v>
+        <v>6.97033977508545</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G311" t="n">
-        <v>6.87801647186279</v>
+        <v>6.87801694869995</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G312" t="n">
-        <v>7.0349645614624</v>
+        <v>7.03496503829956</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G316" t="n">
-        <v>6.97033929824829</v>
+        <v>6.97033977508545</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G318" t="n">
-        <v>7.42271900177002</v>
+        <v>7.42271852493286</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>7.78999996185303</v>
       </c>
       <c r="G321" t="n">
-        <v>7.19191265106201</v>
+        <v>7.19191312789917</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G326" t="n">
-        <v>7.1088228225708</v>
+        <v>7.10882234573364</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G327" t="n">
-        <v>6.97033929824829</v>
+        <v>6.97033977508545</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G328" t="n">
-        <v>7.13651943206787</v>
+        <v>7.13651990890503</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G329" t="n">
-        <v>7.05342960357666</v>
+        <v>7.0534291267395</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G332" t="n">
-        <v>6.93341064453125</v>
+        <v>6.93341016769409</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G333" t="n">
-        <v>7.05342960357666</v>
+        <v>7.0534291267395</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G335" t="n">
-        <v>7.05342960357666</v>
+        <v>7.0534291267395</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G344" t="n">
-        <v>6.97033929824829</v>
+        <v>6.97033977508545</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G346" t="n">
-        <v>7.14575147628784</v>
+        <v>7.145751953125</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G348" t="n">
-        <v>6.90571403503418</v>
+        <v>6.90571355819702</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>7.53999996185303</v>
       </c>
       <c r="G350" t="n">
-        <v>6.96110725402832</v>
+        <v>6.96110677719116</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G351" t="n">
-        <v>6.77646255493164</v>
+        <v>6.77646207809448</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G355" t="n">
-        <v>6.5364236831665</v>
+        <v>6.53642416000366</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>6.98999977111816</v>
       </c>
       <c r="G360" t="n">
-        <v>6.45333385467529</v>
+        <v>6.45333337783813</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G362" t="n">
-        <v>6.64721059799194</v>
+        <v>6.6472110748291</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G363" t="n">
-        <v>6.40717315673828</v>
+        <v>6.40717267990112</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G364" t="n">
-        <v>6.63797855377197</v>
+        <v>6.63797903060913</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G367" t="n">
-        <v>6.48103046417236</v>
+        <v>6.48103094100952</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>7.09000015258789</v>
       </c>
       <c r="G368" t="n">
-        <v>6.54565620422363</v>
+        <v>6.54565668106079</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>7.09000015258789</v>
       </c>
       <c r="G370" t="n">
-        <v>6.54565620422363</v>
+        <v>6.54565668106079</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G371" t="n">
-        <v>6.63797855377197</v>
+        <v>6.63797903060913</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G373" t="n">
-        <v>6.32408237457275</v>
+        <v>6.32408285140991</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>7</v>
       </c>
       <c r="G374" t="n">
-        <v>6.46256637573242</v>
+        <v>6.46256589889526</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>7.09000015258789</v>
       </c>
       <c r="G383" t="n">
-        <v>6.54565620422363</v>
+        <v>6.54565668106079</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G387" t="n">
-        <v>6.6102819442749</v>
+        <v>6.61028146743774</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G389" t="n">
-        <v>6.87801647186279</v>
+        <v>6.87801694869995</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G390" t="n">
-        <v>7.13651943206787</v>
+        <v>7.13651990890503</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G393" t="n">
-        <v>7.30269956588745</v>
+        <v>7.30270004272461</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G394" t="n">
-        <v>7.20114517211914</v>
+        <v>7.2011456489563</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>7.86999988555908</v>
       </c>
       <c r="G396" t="n">
-        <v>7.26577091217041</v>
+        <v>7.26577043533325</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G398" t="n">
-        <v>7.30269956588745</v>
+        <v>7.30270004272461</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G399" t="n">
-        <v>7.36732578277588</v>
+        <v>7.36732530593872</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G400" t="n">
-        <v>7.24730587005615</v>
+        <v>7.24730634689331</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G405" t="n">
-        <v>7.30269956588745</v>
+        <v>7.30270004272461</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G423" t="n">
-        <v>7.40425443649292</v>
+        <v>7.40425491333008</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>8.25</v>
       </c>
       <c r="G427" t="n">
-        <v>7.61659622192383</v>
+        <v>7.61659574508667</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G429" t="n">
-        <v>7.90279531478882</v>
+        <v>7.90279626846313</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G435" t="n">
-        <v>8.63214206695557</v>
+        <v>8.63214302062988</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>9.6899995803833</v>
       </c>
       <c r="G441" t="n">
-        <v>8.94603729248047</v>
+        <v>8.94603824615479</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G443" t="n">
-        <v>8.99219989776611</v>
+        <v>8.9921989440918</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G452" t="n">
-        <v>9.52766895294189</v>
+        <v>9.52766799926758</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G453" t="n">
-        <v>9.61999130249023</v>
+        <v>9.61999225616455</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G454" t="n">
-        <v>9.41688251495361</v>
+        <v>9.4168815612793</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G456" t="n">
-        <v>9.25070190429688</v>
+        <v>9.25070285797119</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G458" t="n">
-        <v>9.26916599273682</v>
+        <v>9.26916694641113</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G464" t="n">
-        <v>9.26916599273682</v>
+        <v>9.26916694641113</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>9.98999977111816</v>
       </c>
       <c r="G466" t="n">
-        <v>9.2230052947998</v>
+        <v>9.22300434112549</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G470" t="n">
-        <v>9.61999130249023</v>
+        <v>9.61999225616455</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>10.4799995422363</v>
       </c>
       <c r="G471" t="n">
-        <v>9.67538356781006</v>
+        <v>9.67538452148438</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G476" t="n">
-        <v>9.61999130249023</v>
+        <v>9.61999225616455</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G477" t="n">
-        <v>9.58306217193604</v>
+        <v>9.58306312561035</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G480" t="n">
-        <v>10.2477836608887</v>
+        <v>10.247784614563</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>11.1199998855591</v>
       </c>
       <c r="G481" t="n">
-        <v>10.2662477493286</v>
+        <v>10.2662487030029</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G482" t="n">
-        <v>8.93680572509766</v>
+        <v>8.93680667877197</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G483" t="n">
-        <v>9.28763103485107</v>
+        <v>9.28763198852539</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G484" t="n">
-        <v>9.21377277374268</v>
+        <v>9.21377182006836</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>9.63000011444092</v>
       </c>
       <c r="G488" t="n">
-        <v>8.89064502716064</v>
+        <v>8.89064407348633</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>9.28999996185303</v>
       </c>
       <c r="G494" t="n">
-        <v>8.57674789428711</v>
+        <v>8.57674884796143</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G495" t="n">
-        <v>8.48442649841309</v>
+        <v>8.48442554473877</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G499" t="n">
-        <v>8.62290954589844</v>
+        <v>8.62291049957275</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G501" t="n">
-        <v>8.62290954589844</v>
+        <v>8.62291049957275</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>9.6899995803833</v>
       </c>
       <c r="G503" t="n">
-        <v>8.94603729248047</v>
+        <v>8.94603824615479</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G504" t="n">
-        <v>8.86294841766357</v>
+        <v>8.86294746398926</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G511" t="n">
-        <v>8.78909111022949</v>
+        <v>8.78909015655518</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>9.8100004196167</v>
       </c>
       <c r="G513" t="n">
-        <v>9.05682468414307</v>
+        <v>9.05682563781738</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G516" t="n">
-        <v>8.9552698135376</v>
+        <v>8.95527076721191</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -29232,6 +29232,32 @@
         <v>1.23199999332428</v>
       </c>
       <c r="H1110" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1111">
+      <c r="A1111" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B1111" t="n">
+        <v>213535</v>
+      </c>
+      <c r="C1111" t="n">
+        <v>1.24800002574921</v>
+      </c>
+      <c r="D1111" t="n">
+        <v>1.19400000572205</v>
+      </c>
+      <c r="E1111" t="n">
+        <v>1.24800002574921</v>
+      </c>
+      <c r="F1111" t="n">
+        <v>1.19000005722046</v>
+      </c>
+      <c r="G1111" t="n">
+        <v>1.19000005722046</v>
+      </c>
+      <c r="H1111" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/TISG.MI.xlsx
+++ b/data/TISG.MI.xlsx
@@ -421,7 +421,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G2" t="n">
-        <v>4.97171258926392</v>
+        <v>4.97171211242676</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G3" t="n">
-        <v>5.12372589111328</v>
+        <v>5.12372493743896</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G6" t="n">
-        <v>4.97171258926392</v>
+        <v>4.97171211242676</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G11" t="n">
-        <v>4.97171258926392</v>
+        <v>4.97171211242676</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G18" t="n">
-        <v>4.93594455718994</v>
+        <v>4.9359450340271</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G21" t="n">
-        <v>5.0253643989563</v>
+        <v>5.02536392211914</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G29" t="n">
-        <v>4.67662906646729</v>
+        <v>4.67662858963013</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G30" t="n">
-        <v>4.7123966217041</v>
+        <v>4.71239614486694</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G31" t="n">
-        <v>4.65874528884888</v>
+        <v>4.65874481201172</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>4.78499984741211</v>
       </c>
       <c r="G37" t="n">
-        <v>4.2787127494812</v>
+        <v>4.27871322631836</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G40" t="n">
-        <v>4.33683586120605</v>
+        <v>4.3368353843689</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G42" t="n">
-        <v>4.40837049484253</v>
+        <v>4.40837097167969</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G45" t="n">
-        <v>4.39048719406128</v>
+        <v>4.39048671722412</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G47" t="n">
-        <v>4.33683586120605</v>
+        <v>4.3368353843689</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G48" t="n">
-        <v>4.25635814666748</v>
+        <v>4.25635862350464</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G53" t="n">
-        <v>4.32789421081543</v>
+        <v>4.32789373397827</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G58" t="n">
-        <v>4.32789421081543</v>
+        <v>4.32789373397827</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G59" t="n">
-        <v>4.51567411422729</v>
+        <v>4.51567459106445</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G61" t="n">
-        <v>4.93594455718994</v>
+        <v>4.9359450340271</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G62" t="n">
-        <v>4.78393173217773</v>
+        <v>4.78393220901489</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G63" t="n">
-        <v>4.64980316162109</v>
+        <v>4.64980268478394</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G64" t="n">
-        <v>4.78393173217773</v>
+        <v>4.78393220901489</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G65" t="n">
-        <v>4.65874528884888</v>
+        <v>4.65874481201172</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G66" t="n">
-        <v>4.65874528884888</v>
+        <v>4.65874481201172</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G69" t="n">
-        <v>4.64980316162109</v>
+        <v>4.64980268478394</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G70" t="n">
-        <v>4.56038331985474</v>
+        <v>4.56038379669189</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G71" t="n">
-        <v>4.61403465270996</v>
+        <v>4.61403512954712</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>4.9850001335144</v>
       </c>
       <c r="G75" t="n">
-        <v>4.4575514793396</v>
+        <v>4.45755195617676</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>4.85500001907349</v>
       </c>
       <c r="G76" t="n">
-        <v>4.34130668640137</v>
+        <v>4.34130620956421</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G77" t="n">
-        <v>4.31000947952271</v>
+        <v>4.31000995635986</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>4.86499977111816</v>
       </c>
       <c r="G78" t="n">
-        <v>4.35024833679199</v>
+        <v>4.35024785995483</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>4.83500003814697</v>
       </c>
       <c r="G82" t="n">
-        <v>4.32342290878296</v>
+        <v>4.3234224319458</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G84" t="n">
-        <v>4.15799713134766</v>
+        <v>4.1579966545105</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G86" t="n">
-        <v>4.15799713134766</v>
+        <v>4.1579966545105</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G87" t="n">
-        <v>4.23847436904907</v>
+        <v>4.23847389221191</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G88" t="n">
-        <v>4.49779081344604</v>
+        <v>4.49779033660889</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G90" t="n">
-        <v>4.48884868621826</v>
+        <v>4.4888482093811</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>4.85500001907349</v>
       </c>
       <c r="G91" t="n">
-        <v>4.34130668640137</v>
+        <v>4.34130620956421</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G92" t="n">
-        <v>4.40837049484253</v>
+        <v>4.40837097167969</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G100" t="n">
-        <v>4.37260341644287</v>
+        <v>4.37260293960571</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G101" t="n">
-        <v>4.08646154403687</v>
+        <v>4.08646202087402</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>4.46500015258789</v>
       </c>
       <c r="G102" t="n">
-        <v>3.99257159233093</v>
+        <v>3.99257135391235</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G103" t="n">
-        <v>3.95233249664307</v>
+        <v>3.95233297348022</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G104" t="n">
-        <v>4.01492595672607</v>
+        <v>4.01492547988892</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G106" t="n">
-        <v>3.84502983093262</v>
+        <v>3.84502959251404</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>4.39499998092651</v>
       </c>
       <c r="G107" t="n">
-        <v>3.92997741699219</v>
+        <v>3.92997789382935</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G108" t="n">
-        <v>3.82714605331421</v>
+        <v>3.82714581489563</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G109" t="n">
-        <v>3.80926156044006</v>
+        <v>3.80926203727722</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>4.2649998664856</v>
       </c>
       <c r="G110" t="n">
-        <v>3.81373238563538</v>
+        <v>3.81373262405396</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G111" t="n">
-        <v>3.69301676750183</v>
+        <v>3.69301700592041</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>4.5</v>
       </c>
       <c r="G114" t="n">
-        <v>4.02386856079102</v>
+        <v>4.02386808395386</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G115" t="n">
-        <v>4.15799713134766</v>
+        <v>4.1579966545105</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G116" t="n">
-        <v>4.17588138580322</v>
+        <v>4.17588090896606</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>4.78499984741211</v>
       </c>
       <c r="G118" t="n">
-        <v>4.2787127494812</v>
+        <v>4.27871322631836</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>4.875</v>
       </c>
       <c r="G121" t="n">
-        <v>4.35919046401978</v>
+        <v>4.35919094085693</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G122" t="n">
-        <v>4.25635814666748</v>
+        <v>4.25635862350464</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G126" t="n">
-        <v>4.27424240112305</v>
+        <v>4.27424192428589</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G133" t="n">
-        <v>4.82864189147949</v>
+        <v>4.82864141464233</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G135" t="n">
-        <v>4.67662906646729</v>
+        <v>4.67662858963013</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G141" t="n">
-        <v>4.93594455718994</v>
+        <v>4.9359450340271</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G146" t="n">
-        <v>5.13266754150391</v>
+        <v>5.13266706466675</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G147" t="n">
-        <v>5.0253643989563</v>
+        <v>5.02536392211914</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G152" t="n">
-        <v>5.23102855682373</v>
+        <v>5.23102807998657</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G154" t="n">
-        <v>5.13266754150391</v>
+        <v>5.13266706466675</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G158" t="n">
-        <v>5.0253643989563</v>
+        <v>5.02536392211914</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G159" t="n">
-        <v>4.95382833480835</v>
+        <v>4.95382881164551</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G165" t="n">
-        <v>5.04324769973755</v>
+        <v>5.04324817657471</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>5.67000007629395</v>
       </c>
       <c r="G166" t="n">
-        <v>5.07007360458374</v>
+        <v>5.0700740814209</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G168" t="n">
-        <v>5.12372589111328</v>
+        <v>5.12372493743896</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G175" t="n">
-        <v>5.13266754150391</v>
+        <v>5.13266706466675</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G176" t="n">
-        <v>5.17737722396851</v>
+        <v>5.17737674713135</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G178" t="n">
-        <v>5.12372589111328</v>
+        <v>5.12372493743896</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>5.90999984741211</v>
       </c>
       <c r="G179" t="n">
-        <v>5.28468036651611</v>
+        <v>5.28467988967896</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G182" t="n">
-        <v>5.52611207962036</v>
+        <v>5.5261116027832</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G184" t="n">
-        <v>5.67812490463257</v>
+        <v>5.67812442779541</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G186" t="n">
-        <v>5.89273118972778</v>
+        <v>5.89273166656494</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G191" t="n">
-        <v>6.21464014053345</v>
+        <v>6.21464061737061</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>6.80999994277954</v>
       </c>
       <c r="G192" t="n">
-        <v>6.08945322036743</v>
+        <v>6.08945369720459</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>7</v>
       </c>
       <c r="G193" t="n">
-        <v>6.25934982299805</v>
+        <v>6.25935029983521</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G194" t="n">
-        <v>6.18781471252441</v>
+        <v>6.18781518936157</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>6.90999984741211</v>
       </c>
       <c r="G195" t="n">
-        <v>6.17887306213379</v>
+        <v>6.17887258529663</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>7</v>
       </c>
       <c r="G197" t="n">
-        <v>6.25934982299805</v>
+        <v>6.25935029983521</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>7.03000020980835</v>
       </c>
       <c r="G199" t="n">
-        <v>6.28617668151855</v>
+        <v>6.2861762046814</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G200" t="n">
-        <v>6.21464014053345</v>
+        <v>6.21464061737061</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G201" t="n">
-        <v>6.27723455429077</v>
+        <v>6.27723407745361</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>7.03999996185303</v>
       </c>
       <c r="G202" t="n">
-        <v>6.29511785507202</v>
+        <v>6.29511737823486</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>7.09000015258789</v>
       </c>
       <c r="G204" t="n">
-        <v>6.33982801437378</v>
+        <v>6.33982753753662</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>7.03000020980835</v>
       </c>
       <c r="G205" t="n">
-        <v>6.28617668151855</v>
+        <v>6.2861762046814</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G206" t="n">
-        <v>6.3040599822998</v>
+        <v>6.30406045913696</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G211" t="n">
-        <v>6.67067909240723</v>
+        <v>6.67067861557007</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G216" t="n">
-        <v>6.67067909240723</v>
+        <v>6.67067861557007</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G231" t="n">
-        <v>7.36814880371094</v>
+        <v>7.3681492805481</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>8.56999969482422</v>
       </c>
       <c r="G232" t="n">
-        <v>7.66323280334473</v>
+        <v>7.66323232650757</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G235" t="n">
-        <v>7.65429210662842</v>
+        <v>7.65429162979126</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G236" t="n">
-        <v>7.35920667648315</v>
+        <v>7.35920715332031</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G237" t="n">
-        <v>7.35920667648315</v>
+        <v>7.35920715332031</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G238" t="n">
-        <v>7.73476839065552</v>
+        <v>7.73476791381836</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>8.75</v>
       </c>
       <c r="G239" t="n">
-        <v>7.82418823242188</v>
+        <v>7.82418775558472</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G241" t="n">
-        <v>7.94043302536011</v>
+        <v>7.94043350219727</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G243" t="n">
-        <v>7.73476839065552</v>
+        <v>7.73476791381836</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>8.57999992370605</v>
       </c>
       <c r="G246" t="n">
-        <v>7.67217540740967</v>
+        <v>7.67217493057251</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>8.63000011444092</v>
       </c>
       <c r="G248" t="n">
-        <v>7.71688461303711</v>
+        <v>7.71688508987427</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G249" t="n">
-        <v>7.73476839065552</v>
+        <v>7.73476791381836</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -29246,7 +29246,7 @@
         <v>1.24800002574921</v>
       </c>
       <c r="D1111" t="n">
-        <v>1.19400000572205</v>
+        <v>1.19000005722046</v>
       </c>
       <c r="E1111" t="n">
         <v>1.24800002574921</v>
@@ -29258,6 +29258,32 @@
         <v>1.19000005722046</v>
       </c>
       <c r="H1111" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1112">
+      <c r="A1112" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B1112" t="n">
+        <v>106248</v>
+      </c>
+      <c r="C1112" t="n">
+        <v>1.23599994182587</v>
+      </c>
+      <c r="D1112" t="n">
+        <v>1.19000005722046</v>
+      </c>
+      <c r="E1112" t="n">
+        <v>1.23599994182587</v>
+      </c>
+      <c r="F1112" t="n">
+        <v>1.20200002193451</v>
+      </c>
+      <c r="G1112" t="n">
+        <v>1.20200002193451</v>
+      </c>
+      <c r="H1112" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/TISG.MI.xlsx
+++ b/data/TISG.MI.xlsx
@@ -421,7 +421,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G2" t="n">
-        <v>4.97171211242676</v>
+        <v>4.97171258926392</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G3" t="n">
-        <v>5.12372493743896</v>
+        <v>5.12372589111328</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G6" t="n">
-        <v>4.97171211242676</v>
+        <v>4.97171258926392</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G11" t="n">
-        <v>4.97171211242676</v>
+        <v>4.97171258926392</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G18" t="n">
-        <v>4.9359450340271</v>
+        <v>4.93594455718994</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G21" t="n">
-        <v>5.02536392211914</v>
+        <v>5.0253643989563</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G29" t="n">
-        <v>4.67662858963013</v>
+        <v>4.67662906646729</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G30" t="n">
-        <v>4.71239614486694</v>
+        <v>4.7123966217041</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G31" t="n">
-        <v>4.65874481201172</v>
+        <v>4.65874528884888</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>4.78499984741211</v>
       </c>
       <c r="G37" t="n">
-        <v>4.27871322631836</v>
+        <v>4.2787127494812</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G40" t="n">
-        <v>4.3368353843689</v>
+        <v>4.33683586120605</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G42" t="n">
-        <v>4.40837097167969</v>
+        <v>4.40837049484253</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G45" t="n">
-        <v>4.39048671722412</v>
+        <v>4.39048719406128</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G47" t="n">
-        <v>4.3368353843689</v>
+        <v>4.33683586120605</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G48" t="n">
-        <v>4.25635862350464</v>
+        <v>4.25635814666748</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G53" t="n">
-        <v>4.32789373397827</v>
+        <v>4.32789421081543</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G58" t="n">
-        <v>4.32789373397827</v>
+        <v>4.32789421081543</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G59" t="n">
-        <v>4.51567459106445</v>
+        <v>4.51567411422729</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G61" t="n">
-        <v>4.9359450340271</v>
+        <v>4.93594455718994</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G62" t="n">
-        <v>4.78393220901489</v>
+        <v>4.78393173217773</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G63" t="n">
-        <v>4.64980268478394</v>
+        <v>4.64980316162109</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G64" t="n">
-        <v>4.78393220901489</v>
+        <v>4.78393173217773</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G65" t="n">
-        <v>4.65874481201172</v>
+        <v>4.65874528884888</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G66" t="n">
-        <v>4.65874481201172</v>
+        <v>4.65874528884888</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G69" t="n">
-        <v>4.64980268478394</v>
+        <v>4.64980316162109</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G70" t="n">
-        <v>4.56038379669189</v>
+        <v>4.56038331985474</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G71" t="n">
-        <v>4.61403512954712</v>
+        <v>4.61403465270996</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>4.9850001335144</v>
       </c>
       <c r="G75" t="n">
-        <v>4.45755195617676</v>
+        <v>4.4575514793396</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>4.85500001907349</v>
       </c>
       <c r="G76" t="n">
-        <v>4.34130620956421</v>
+        <v>4.34130668640137</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G77" t="n">
-        <v>4.31000995635986</v>
+        <v>4.31000947952271</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>4.86499977111816</v>
       </c>
       <c r="G78" t="n">
-        <v>4.35024785995483</v>
+        <v>4.35024833679199</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>4.83500003814697</v>
       </c>
       <c r="G82" t="n">
-        <v>4.3234224319458</v>
+        <v>4.32342290878296</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G84" t="n">
-        <v>4.1579966545105</v>
+        <v>4.15799713134766</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G86" t="n">
-        <v>4.1579966545105</v>
+        <v>4.15799713134766</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G87" t="n">
-        <v>4.23847389221191</v>
+        <v>4.23847436904907</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G88" t="n">
-        <v>4.49779033660889</v>
+        <v>4.49779081344604</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G90" t="n">
-        <v>4.4888482093811</v>
+        <v>4.48884868621826</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>4.85500001907349</v>
       </c>
       <c r="G91" t="n">
-        <v>4.34130620956421</v>
+        <v>4.34130668640137</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G92" t="n">
-        <v>4.40837097167969</v>
+        <v>4.40837049484253</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G100" t="n">
-        <v>4.37260293960571</v>
+        <v>4.37260341644287</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G101" t="n">
-        <v>4.08646202087402</v>
+        <v>4.08646154403687</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>4.46500015258789</v>
       </c>
       <c r="G102" t="n">
-        <v>3.99257135391235</v>
+        <v>3.99257159233093</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G103" t="n">
-        <v>3.95233297348022</v>
+        <v>3.95233249664307</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G104" t="n">
-        <v>4.01492547988892</v>
+        <v>4.01492595672607</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G106" t="n">
-        <v>3.84502959251404</v>
+        <v>3.84502983093262</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>4.39499998092651</v>
       </c>
       <c r="G107" t="n">
-        <v>3.92997789382935</v>
+        <v>3.92997741699219</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G108" t="n">
-        <v>3.82714581489563</v>
+        <v>3.82714605331421</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G109" t="n">
-        <v>3.80926203727722</v>
+        <v>3.80926156044006</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>4.2649998664856</v>
       </c>
       <c r="G110" t="n">
-        <v>3.81373262405396</v>
+        <v>3.81373238563538</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G111" t="n">
-        <v>3.69301700592041</v>
+        <v>3.69301676750183</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>4.5</v>
       </c>
       <c r="G114" t="n">
-        <v>4.02386808395386</v>
+        <v>4.02386856079102</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G115" t="n">
-        <v>4.1579966545105</v>
+        <v>4.15799713134766</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G116" t="n">
-        <v>4.17588090896606</v>
+        <v>4.17588138580322</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>4.78499984741211</v>
       </c>
       <c r="G118" t="n">
-        <v>4.27871322631836</v>
+        <v>4.2787127494812</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>4.875</v>
       </c>
       <c r="G121" t="n">
-        <v>4.35919094085693</v>
+        <v>4.35919046401978</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G122" t="n">
-        <v>4.25635862350464</v>
+        <v>4.25635814666748</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G126" t="n">
-        <v>4.27424192428589</v>
+        <v>4.27424240112305</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G133" t="n">
-        <v>4.82864141464233</v>
+        <v>4.82864189147949</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G135" t="n">
-        <v>4.67662858963013</v>
+        <v>4.67662906646729</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G141" t="n">
-        <v>4.9359450340271</v>
+        <v>4.93594455718994</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G146" t="n">
-        <v>5.13266706466675</v>
+        <v>5.13266754150391</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G147" t="n">
-        <v>5.02536392211914</v>
+        <v>5.0253643989563</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G152" t="n">
-        <v>5.23102807998657</v>
+        <v>5.23102855682373</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G154" t="n">
-        <v>5.13266706466675</v>
+        <v>5.13266754150391</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G158" t="n">
-        <v>5.02536392211914</v>
+        <v>5.0253643989563</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G159" t="n">
-        <v>4.95382881164551</v>
+        <v>4.95382833480835</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G165" t="n">
-        <v>5.04324817657471</v>
+        <v>5.04324769973755</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>5.67000007629395</v>
       </c>
       <c r="G166" t="n">
-        <v>5.0700740814209</v>
+        <v>5.07007360458374</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G168" t="n">
-        <v>5.12372493743896</v>
+        <v>5.12372589111328</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G175" t="n">
-        <v>5.13266706466675</v>
+        <v>5.13266754150391</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G176" t="n">
-        <v>5.17737674713135</v>
+        <v>5.17737722396851</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G178" t="n">
-        <v>5.12372493743896</v>
+        <v>5.12372589111328</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>5.90999984741211</v>
       </c>
       <c r="G179" t="n">
-        <v>5.28467988967896</v>
+        <v>5.28468036651611</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G182" t="n">
-        <v>5.5261116027832</v>
+        <v>5.52611207962036</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G184" t="n">
-        <v>5.67812442779541</v>
+        <v>5.67812490463257</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G186" t="n">
-        <v>5.89273166656494</v>
+        <v>5.89273118972778</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G191" t="n">
-        <v>6.21464061737061</v>
+        <v>6.21464014053345</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>6.80999994277954</v>
       </c>
       <c r="G192" t="n">
-        <v>6.08945369720459</v>
+        <v>6.08945322036743</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>7</v>
       </c>
       <c r="G193" t="n">
-        <v>6.25935029983521</v>
+        <v>6.25934982299805</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G194" t="n">
-        <v>6.18781518936157</v>
+        <v>6.18781471252441</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>6.90999984741211</v>
       </c>
       <c r="G195" t="n">
-        <v>6.17887258529663</v>
+        <v>6.17887306213379</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>7</v>
       </c>
       <c r="G197" t="n">
-        <v>6.25935029983521</v>
+        <v>6.25934982299805</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>7.03000020980835</v>
       </c>
       <c r="G199" t="n">
-        <v>6.2861762046814</v>
+        <v>6.28617668151855</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G200" t="n">
-        <v>6.21464061737061</v>
+        <v>6.21464014053345</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G201" t="n">
-        <v>6.27723407745361</v>
+        <v>6.27723455429077</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>7.03999996185303</v>
       </c>
       <c r="G202" t="n">
-        <v>6.29511737823486</v>
+        <v>6.29511785507202</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>7.09000015258789</v>
       </c>
       <c r="G204" t="n">
-        <v>6.33982753753662</v>
+        <v>6.33982801437378</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>7.03000020980835</v>
       </c>
       <c r="G205" t="n">
-        <v>6.2861762046814</v>
+        <v>6.28617668151855</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G206" t="n">
-        <v>6.30406045913696</v>
+        <v>6.3040599822998</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G211" t="n">
-        <v>6.67067861557007</v>
+        <v>6.67067909240723</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G216" t="n">
-        <v>6.67067861557007</v>
+        <v>6.67067909240723</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G231" t="n">
-        <v>7.3681492805481</v>
+        <v>7.36814880371094</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>8.56999969482422</v>
       </c>
       <c r="G232" t="n">
-        <v>7.66323232650757</v>
+        <v>7.66323280334473</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G235" t="n">
-        <v>7.65429162979126</v>
+        <v>7.65429210662842</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G236" t="n">
-        <v>7.35920715332031</v>
+        <v>7.35920667648315</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G237" t="n">
-        <v>7.35920715332031</v>
+        <v>7.35920667648315</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G238" t="n">
-        <v>7.73476791381836</v>
+        <v>7.73476839065552</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>8.75</v>
       </c>
       <c r="G239" t="n">
-        <v>7.82418775558472</v>
+        <v>7.82418823242188</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G241" t="n">
-        <v>7.94043350219727</v>
+        <v>7.94043302536011</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G243" t="n">
-        <v>7.73476791381836</v>
+        <v>7.73476839065552</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>8.57999992370605</v>
       </c>
       <c r="G246" t="n">
-        <v>7.67217493057251</v>
+        <v>7.67217540740967</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>8.63000011444092</v>
       </c>
       <c r="G248" t="n">
-        <v>7.71688508987427</v>
+        <v>7.71688461303711</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G249" t="n">
-        <v>7.73476791381836</v>
+        <v>7.73476839065552</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -29284,6 +29284,32 @@
         <v>1.20200002193451</v>
       </c>
       <c r="H1112" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1113">
+      <c r="A1113" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B1113" t="n">
+        <v>163506</v>
+      </c>
+      <c r="C1113" t="n">
+        <v>1.22599995136261</v>
+      </c>
+      <c r="D1113" t="n">
+        <v>1.17200005054474</v>
+      </c>
+      <c r="E1113" t="n">
+        <v>1.19200003147125</v>
+      </c>
+      <c r="F1113" t="n">
+        <v>1.17799997329712</v>
+      </c>
+      <c r="G1113" t="n">
+        <v>1.17799997329712</v>
+      </c>
+      <c r="H1113" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/TISG.MI.xlsx
+++ b/data/TISG.MI.xlsx
@@ -447,7 +447,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G3" t="n">
-        <v>5.12372493743896</v>
+        <v>5.12372541427612</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G14" t="n">
-        <v>4.98959636688232</v>
+        <v>4.98959589004517</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G16" t="n">
-        <v>5.03430604934692</v>
+        <v>5.03430652618408</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G17" t="n">
-        <v>4.96277093887329</v>
+        <v>4.96277046203613</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G21" t="n">
-        <v>5.02536344528198</v>
+        <v>5.02536392211914</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G31" t="n">
-        <v>4.65874528884888</v>
+        <v>4.65874481201172</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G32" t="n">
-        <v>4.68557071685791</v>
+        <v>4.68557024002075</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G33" t="n">
-        <v>4.68557071685791</v>
+        <v>4.68557024002075</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G34" t="n">
-        <v>4.68557071685791</v>
+        <v>4.68557024002075</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>4.78499984741211</v>
       </c>
       <c r="G37" t="n">
-        <v>4.27871322631836</v>
+        <v>4.2787127494812</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G41" t="n">
-        <v>4.4262547492981</v>
+        <v>4.42625427246094</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G46" t="n">
-        <v>4.41731309890747</v>
+        <v>4.41731262207031</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G48" t="n">
-        <v>4.25635814666748</v>
+        <v>4.25635862350464</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>4.84499979019165</v>
       </c>
       <c r="G49" t="n">
-        <v>4.33236455917358</v>
+        <v>4.33236408233643</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>4.84499979019165</v>
       </c>
       <c r="G51" t="n">
-        <v>4.33236455917358</v>
+        <v>4.33236408233643</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G52" t="n">
-        <v>4.2921257019043</v>
+        <v>4.29212617874146</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G53" t="n">
-        <v>4.32789421081543</v>
+        <v>4.32789373397827</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G57" t="n">
-        <v>4.2921257019043</v>
+        <v>4.29212617874146</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G58" t="n">
-        <v>4.32789421081543</v>
+        <v>4.32789373397827</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G63" t="n">
-        <v>4.64980268478394</v>
+        <v>4.64980316162109</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G65" t="n">
-        <v>4.65874528884888</v>
+        <v>4.65874481201172</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G66" t="n">
-        <v>4.65874528884888</v>
+        <v>4.65874481201172</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G69" t="n">
-        <v>4.64980268478394</v>
+        <v>4.64980316162109</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G77" t="n">
-        <v>4.31000947952271</v>
+        <v>4.31000995635986</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G79" t="n">
-        <v>4.2921257019043</v>
+        <v>4.29212617874146</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G80" t="n">
-        <v>4.2921257019043</v>
+        <v>4.29212617874146</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G81" t="n">
-        <v>4.2921257019043</v>
+        <v>4.29212617874146</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G88" t="n">
-        <v>4.49779033660889</v>
+        <v>4.49779081344604</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G90" t="n">
-        <v>4.4888482093811</v>
+        <v>4.48884868621826</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G96" t="n">
-        <v>4.2921257019043</v>
+        <v>4.29212617874146</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G99" t="n">
-        <v>4.3547191619873</v>
+        <v>4.35471963882446</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G101" t="n">
-        <v>4.08646202087402</v>
+        <v>4.08646154403687</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G103" t="n">
-        <v>3.95233297348022</v>
+        <v>3.95233249664307</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G104" t="n">
-        <v>4.01492547988892</v>
+        <v>4.01492595672607</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G105" t="n">
-        <v>3.90762305259705</v>
+        <v>3.90762257575989</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G106" t="n">
-        <v>3.84502959251404</v>
+        <v>3.84502983093262</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>4.39499998092651</v>
       </c>
       <c r="G107" t="n">
-        <v>3.92997741699219</v>
+        <v>3.92997789382935</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>4.2649998664856</v>
       </c>
       <c r="G110" t="n">
-        <v>3.81373262405396</v>
+        <v>3.81373286247253</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G111" t="n">
-        <v>3.69301700592041</v>
+        <v>3.69301676750183</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G112" t="n">
-        <v>3.76455211639404</v>
+        <v>3.76455187797546</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G113" t="n">
-        <v>3.75560975074768</v>
+        <v>3.75561022758484</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>4.5</v>
       </c>
       <c r="G114" t="n">
-        <v>4.02386808395386</v>
+        <v>4.02386856079102</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G116" t="n">
-        <v>4.17588090896606</v>
+        <v>4.17588043212891</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>4.78499984741211</v>
       </c>
       <c r="G118" t="n">
-        <v>4.27871322631836</v>
+        <v>4.2787127494812</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G122" t="n">
-        <v>4.25635814666748</v>
+        <v>4.25635862350464</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G123" t="n">
-        <v>4.2921257019043</v>
+        <v>4.29212617874146</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G124" t="n">
-        <v>4.2921257019043</v>
+        <v>4.29212617874146</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>4.84499979019165</v>
       </c>
       <c r="G127" t="n">
-        <v>4.33236455917358</v>
+        <v>4.33236408233643</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G131" t="n">
-        <v>4.68557071685791</v>
+        <v>4.68557024002075</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G132" t="n">
-        <v>4.76604795455933</v>
+        <v>4.76604843139648</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G133" t="n">
-        <v>4.82864141464233</v>
+        <v>4.82864189147949</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G142" t="n">
-        <v>4.86440944671631</v>
+        <v>4.86440896987915</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G143" t="n">
-        <v>4.79287385940552</v>
+        <v>4.79287433624268</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G147" t="n">
-        <v>5.02536344528198</v>
+        <v>5.02536392211914</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G148" t="n">
-        <v>5.22208642959595</v>
+        <v>5.22208690643311</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G152" t="n">
-        <v>5.23102855682373</v>
+        <v>5.23102807998657</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G158" t="n">
-        <v>5.02536344528198</v>
+        <v>5.02536392211914</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G159" t="n">
-        <v>4.95382881164551</v>
+        <v>4.95382833480835</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>5.67000007629395</v>
       </c>
       <c r="G166" t="n">
-        <v>5.07007360458374</v>
+        <v>5.0700740814209</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G168" t="n">
-        <v>5.12372493743896</v>
+        <v>5.12372541427612</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>5.75</v>
       </c>
       <c r="G171" t="n">
-        <v>5.14160966873169</v>
+        <v>5.14160919189453</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>5.75</v>
       </c>
       <c r="G172" t="n">
-        <v>5.14160966873169</v>
+        <v>5.14160919189453</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G174" t="n">
-        <v>5.03430604934692</v>
+        <v>5.03430652618408</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G176" t="n">
-        <v>5.17737722396851</v>
+        <v>5.17737674713135</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G178" t="n">
-        <v>5.12372493743896</v>
+        <v>5.12372541427612</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G181" t="n">
-        <v>5.43669271469116</v>
+        <v>5.436692237854</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G185" t="n">
-        <v>5.70495080947876</v>
+        <v>5.7049503326416</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G194" t="n">
-        <v>6.18781518936157</v>
+        <v>6.18781471252441</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>7.03999996185303</v>
       </c>
       <c r="G202" t="n">
-        <v>6.29511785507202</v>
+        <v>6.29511833190918</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G203" t="n">
-        <v>6.5276083946228</v>
+        <v>6.52760791778564</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G207" t="n">
-        <v>6.65279483795166</v>
+        <v>6.65279531478882</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G214" t="n">
-        <v>6.79586553573608</v>
+        <v>6.79586601257324</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G215" t="n">
-        <v>6.66173696517944</v>
+        <v>6.66173648834229</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G224" t="n">
-        <v>6.66173696517944</v>
+        <v>6.66173648834229</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G231" t="n">
-        <v>7.36814880371094</v>
+        <v>7.3681492805481</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G234" t="n">
-        <v>7.77947854995728</v>
+        <v>7.77947759628296</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G238" t="n">
-        <v>7.73476791381836</v>
+        <v>7.73476886749268</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G240" t="n">
-        <v>7.86889696121216</v>
+        <v>7.86889791488647</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G242" t="n">
-        <v>7.77947854995728</v>
+        <v>7.77947759628296</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G243" t="n">
-        <v>7.73476791381836</v>
+        <v>7.73476886749268</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G245" t="n">
-        <v>7.77947854995728</v>
+        <v>7.77947759628296</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>8.57999992370605</v>
       </c>
       <c r="G246" t="n">
-        <v>7.67217445373535</v>
+        <v>7.67217493057251</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G247" t="n">
-        <v>7.64534950256348</v>
+        <v>7.64534902572632</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G249" t="n">
-        <v>7.73476791381836</v>
+        <v>7.73476886749268</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -29362,6 +29362,32 @@
         <v>1.12000000476837</v>
       </c>
       <c r="H1115" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1116">
+      <c r="A1116" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B1116" t="n">
+        <v>107609</v>
+      </c>
+      <c r="C1116" t="n">
+        <v>1.15600001811981</v>
+      </c>
+      <c r="D1116" t="n">
+        <v>1.12399995326996</v>
+      </c>
+      <c r="E1116" t="n">
+        <v>1.12399995326996</v>
+      </c>
+      <c r="F1116" t="n">
+        <v>1.14199995994568</v>
+      </c>
+      <c r="G1116" t="n">
+        <v>1.14199995994568</v>
+      </c>
+      <c r="H1116" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/TISG.MI.xlsx
+++ b/data/TISG.MI.xlsx
@@ -26102,8 +26102,31 @@
       <c r="E1119" t="n">
         <v>1.1139999628067</v>
       </c>
-      <c r="F1119"/>
+      <c r="F1119" t="n">
+        <v>1.11000001430511</v>
+      </c>
       <c r="G1119" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1120">
+      <c r="A1120" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B1120" t="n">
+        <v>155488</v>
+      </c>
+      <c r="C1120" t="n">
+        <v>1.13999998569489</v>
+      </c>
+      <c r="D1120" t="n">
+        <v>1.1139999628067</v>
+      </c>
+      <c r="E1120" t="n">
+        <v>1.13199996948242</v>
+      </c>
+      <c r="F1120"/>
+      <c r="G1120" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/TISG.MI.xlsx
+++ b/data/TISG.MI.xlsx
@@ -26125,8 +26125,31 @@
       <c r="E1120" t="n">
         <v>1.13199996948242</v>
       </c>
-      <c r="F1120"/>
+      <c r="F1120" t="n">
+        <v>1.12199997901917</v>
+      </c>
       <c r="G1120" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1121">
+      <c r="A1121" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B1121" t="n">
+        <v>125270</v>
+      </c>
+      <c r="C1121" t="n">
+        <v>1.13999998569489</v>
+      </c>
+      <c r="D1121" t="n">
+        <v>1.11000001430511</v>
+      </c>
+      <c r="E1121" t="n">
+        <v>1.11000001430511</v>
+      </c>
+      <c r="F1121"/>
+      <c r="G1121" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/TISG.MI.xlsx
+++ b/data/TISG.MI.xlsx
@@ -26148,8 +26148,31 @@
       <c r="E1121" t="n">
         <v>1.11000001430511</v>
       </c>
-      <c r="F1121"/>
+      <c r="F1121" t="n">
+        <v>1.11800003051758</v>
+      </c>
       <c r="G1121" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1122">
+      <c r="A1122" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B1122" t="n">
+        <v>75301</v>
+      </c>
+      <c r="C1122" t="n">
+        <v>1.12600004673004</v>
+      </c>
+      <c r="D1122" t="n">
+        <v>1.10199999809265</v>
+      </c>
+      <c r="E1122" t="n">
+        <v>1.11000001430511</v>
+      </c>
+      <c r="F1122"/>
+      <c r="G1122" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/TISG.MI.xlsx
+++ b/data/TISG.MI.xlsx
@@ -26171,8 +26171,31 @@
       <c r="E1122" t="n">
         <v>1.11000001430511</v>
       </c>
-      <c r="F1122"/>
+      <c r="F1122" t="n">
+        <v>1.11000001430511</v>
+      </c>
       <c r="G1122" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1123">
+      <c r="A1123" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B1123" t="n">
+        <v>125570</v>
+      </c>
+      <c r="C1123" t="n">
+        <v>1.12800002098083</v>
+      </c>
+      <c r="D1123" t="n">
+        <v>1.08000004291534</v>
+      </c>
+      <c r="E1123" t="n">
+        <v>1.08000004291534</v>
+      </c>
+      <c r="F1123"/>
+      <c r="G1123" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/TISG.MI.xlsx
+++ b/data/TISG.MI.xlsx
@@ -26201,6 +26201,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1124">
+      <c r="A1124" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B1124" t="n">
+        <v>266149</v>
+      </c>
+      <c r="C1124" t="n">
+        <v>1.14800000190735</v>
+      </c>
+      <c r="D1124" t="n">
+        <v>1.07200002670288</v>
+      </c>
+      <c r="E1124" t="n">
+        <v>1.10000002384186</v>
+      </c>
+      <c r="F1124" t="n">
+        <v>1.07200002670288</v>
+      </c>
+      <c r="G1124" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TISG.MI.xlsx
+++ b/data/TISG.MI.xlsx
@@ -473,7 +473,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G4" t="n">
-        <v>5.16843509674072</v>
+        <v>5.16843461990356</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G7" t="n">
-        <v>4.94488668441772</v>
+        <v>4.94488716125488</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>5.6100001335144</v>
       </c>
       <c r="G13" t="n">
-        <v>5.01642227172852</v>
+        <v>5.01642179489136</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G16" t="n">
-        <v>5.03430604934692</v>
+        <v>5.03430652618408</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G17" t="n">
-        <v>4.96277093887329</v>
+        <v>4.96277046203613</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G18" t="n">
-        <v>4.93594455718994</v>
+        <v>4.9359450340271</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G19" t="n">
-        <v>4.94488668441772</v>
+        <v>4.94488716125488</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>5.6100001335144</v>
       </c>
       <c r="G22" t="n">
-        <v>5.01642227172852</v>
+        <v>5.01642179489136</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G24" t="n">
-        <v>4.59615087509155</v>
+        <v>4.59615135192871</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G25" t="n">
-        <v>4.64086151123047</v>
+        <v>4.64086103439331</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G35" t="n">
-        <v>4.64086151123047</v>
+        <v>4.64086103439331</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>5</v>
       </c>
       <c r="G43" t="n">
-        <v>4.47096490859985</v>
+        <v>4.4709644317627</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>5</v>
       </c>
       <c r="G44" t="n">
-        <v>4.47096490859985</v>
+        <v>4.4709644317627</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>4.84499979019165</v>
       </c>
       <c r="G49" t="n">
-        <v>4.33236455917358</v>
+        <v>4.33236408233643</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>4.84499979019165</v>
       </c>
       <c r="G51" t="n">
-        <v>4.33236455917358</v>
+        <v>4.33236408233643</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G52" t="n">
-        <v>4.2921257019043</v>
+        <v>4.29212617874146</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G57" t="n">
-        <v>4.2921257019043</v>
+        <v>4.29212617874146</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G59" t="n">
-        <v>4.51567459106445</v>
+        <v>4.51567411422729</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G61" t="n">
-        <v>4.93594455718994</v>
+        <v>4.9359450340271</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G72" t="n">
-        <v>4.6676869392395</v>
+        <v>4.66768646240234</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>4.9850001335144</v>
       </c>
       <c r="G75" t="n">
-        <v>4.4575514793396</v>
+        <v>4.45755195617676</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>4.85500001907349</v>
       </c>
       <c r="G76" t="n">
-        <v>4.34130668640137</v>
+        <v>4.34130620956421</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G79" t="n">
-        <v>4.2921257019043</v>
+        <v>4.29212617874146</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G80" t="n">
-        <v>4.2921257019043</v>
+        <v>4.29212617874146</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G81" t="n">
-        <v>4.2921257019043</v>
+        <v>4.29212617874146</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>4.83500003814697</v>
       </c>
       <c r="G82" t="n">
-        <v>4.3234224319458</v>
+        <v>4.32342290878296</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G88" t="n">
-        <v>4.49779081344604</v>
+        <v>4.49779033660889</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>5</v>
       </c>
       <c r="G89" t="n">
-        <v>4.47096490859985</v>
+        <v>4.4709644317627</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G90" t="n">
-        <v>4.48884868621826</v>
+        <v>4.4888482093811</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>4.85500001907349</v>
       </c>
       <c r="G91" t="n">
-        <v>4.34130668640137</v>
+        <v>4.34130620956421</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G96" t="n">
-        <v>4.2921257019043</v>
+        <v>4.29212617874146</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G98" t="n">
-        <v>4.31895208358765</v>
+        <v>4.31895160675049</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G99" t="n">
-        <v>4.3547191619873</v>
+        <v>4.35471963882446</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>4.46500015258789</v>
       </c>
       <c r="G102" t="n">
-        <v>3.99257135391235</v>
+        <v>3.99257159233093</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G103" t="n">
-        <v>3.95233273506165</v>
+        <v>3.95233249664307</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G105" t="n">
-        <v>3.90762281417847</v>
+        <v>3.90762233734131</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G106" t="n">
-        <v>3.84502959251404</v>
+        <v>3.84502983093262</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G108" t="n">
-        <v>3.82714605331421</v>
+        <v>3.82714557647705</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G109" t="n">
-        <v>3.80926179885864</v>
+        <v>3.80926203727722</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>4.2649998664856</v>
       </c>
       <c r="G110" t="n">
-        <v>3.81373238563538</v>
+        <v>3.81373286247253</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G113" t="n">
-        <v>3.75560998916626</v>
+        <v>3.75561022758484</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>4.5</v>
       </c>
       <c r="G114" t="n">
-        <v>4.02386808395386</v>
+        <v>4.02386856079102</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G123" t="n">
-        <v>4.2921257019043</v>
+        <v>4.29212617874146</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G124" t="n">
-        <v>4.2921257019043</v>
+        <v>4.29212617874146</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G126" t="n">
-        <v>4.27424192428589</v>
+        <v>4.27424240112305</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>4.84499979019165</v>
       </c>
       <c r="G127" t="n">
-        <v>4.33236455917358</v>
+        <v>4.33236408233643</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G138" t="n">
-        <v>4.81075811386108</v>
+        <v>4.81075763702393</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G141" t="n">
-        <v>4.93594455718994</v>
+        <v>4.9359450340271</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G142" t="n">
-        <v>4.86440944671631</v>
+        <v>4.86440896987915</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G143" t="n">
-        <v>4.79287385940552</v>
+        <v>4.79287433624268</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G148" t="n">
-        <v>5.22208690643311</v>
+        <v>5.22208642959595</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G149" t="n">
-        <v>5.18631887435913</v>
+        <v>5.18631935119629</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G151" t="n">
-        <v>5.18631887435913</v>
+        <v>5.18631935119629</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G152" t="n">
-        <v>5.23102807998657</v>
+        <v>5.23102855682373</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G153" t="n">
-        <v>5.16843509674072</v>
+        <v>5.16843461990356</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>5.6100001335144</v>
       </c>
       <c r="G156" t="n">
-        <v>5.01642227172852</v>
+        <v>5.01642179489136</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G159" t="n">
-        <v>4.95382881164551</v>
+        <v>4.95382833480835</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G160" t="n">
-        <v>5.09689903259277</v>
+        <v>5.09689950942993</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G161" t="n">
-        <v>5.18631887435913</v>
+        <v>5.18631935119629</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G162" t="n">
-        <v>5.09689903259277</v>
+        <v>5.09689950942993</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>5.69000005722046</v>
       </c>
       <c r="G164" t="n">
-        <v>5.08795738220215</v>
+        <v>5.08795785903931</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>5.67000007629395</v>
       </c>
       <c r="G166" t="n">
-        <v>5.0700740814209</v>
+        <v>5.07007360458374</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G173" t="n">
-        <v>5.07901525497437</v>
+        <v>5.07901573181152</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G174" t="n">
-        <v>5.03430604934692</v>
+        <v>5.03430652618408</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G176" t="n">
-        <v>5.17737674713135</v>
+        <v>5.17737722396851</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>5.90999984741211</v>
       </c>
       <c r="G179" t="n">
-        <v>5.28468036651611</v>
+        <v>5.28467988967896</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G181" t="n">
-        <v>5.436692237854</v>
+        <v>5.43669271469116</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G184" t="n">
-        <v>5.67812442779541</v>
+        <v>5.67812490463257</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G185" t="n">
-        <v>5.70495080947876</v>
+        <v>5.7049503326416</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G191" t="n">
-        <v>6.21464061737061</v>
+        <v>6.21464014053345</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>6.80999994277954</v>
       </c>
       <c r="G192" t="n">
-        <v>6.08945322036743</v>
+        <v>6.08945369720459</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>7</v>
       </c>
       <c r="G193" t="n">
-        <v>6.25934982299805</v>
+        <v>6.25935029983521</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G194" t="n">
-        <v>6.18781518936157</v>
+        <v>6.18781471252441</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>6.90999984741211</v>
       </c>
       <c r="G195" t="n">
-        <v>6.17887258529663</v>
+        <v>6.17887306213379</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>7</v>
       </c>
       <c r="G197" t="n">
-        <v>6.25934982299805</v>
+        <v>6.25935029983521</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G200" t="n">
-        <v>6.21464061737061</v>
+        <v>6.21464014053345</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G201" t="n">
-        <v>6.27723455429077</v>
+        <v>6.27723407745361</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G203" t="n">
-        <v>6.52760791778564</v>
+        <v>6.5276083946228</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G206" t="n">
-        <v>6.30406045913696</v>
+        <v>6.3040599822998</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G215" t="n">
-        <v>6.66173696517944</v>
+        <v>6.66173648834229</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G217" t="n">
-        <v>6.4203052520752</v>
+        <v>6.42030477523804</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>7.53000020980835</v>
       </c>
       <c r="G218" t="n">
-        <v>6.73327207565308</v>
+        <v>6.73327255249023</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G220" t="n">
-        <v>6.60808563232422</v>
+        <v>6.60808515548706</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G221" t="n">
-        <v>6.45607280731201</v>
+        <v>6.45607233047485</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G224" t="n">
-        <v>6.66173696517944</v>
+        <v>6.66173648834229</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G226" t="n">
-        <v>6.50972461700439</v>
+        <v>6.50972414016724</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G227" t="n">
-        <v>6.58125925064087</v>
+        <v>6.58125972747803</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>7.53000020980835</v>
       </c>
       <c r="G228" t="n">
-        <v>6.73327207565308</v>
+        <v>6.73327255249023</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>7.98999977111816</v>
       </c>
       <c r="G230" t="n">
-        <v>7.14460134506226</v>
+        <v>7.1446008682251</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G231" t="n">
-        <v>7.36814880371094</v>
+        <v>7.3681492805481</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>8.56999969482422</v>
       </c>
       <c r="G232" t="n">
-        <v>7.66323328018188</v>
+        <v>7.66323280334473</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G233" t="n">
-        <v>7.63640642166138</v>
+        <v>7.63640689849854</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G235" t="n">
-        <v>7.65429210662842</v>
+        <v>7.6542911529541</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G236" t="n">
-        <v>7.35920715332031</v>
+        <v>7.35920667648315</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G237" t="n">
-        <v>7.35920715332031</v>
+        <v>7.35920667648315</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G238" t="n">
-        <v>7.73476886749268</v>
+        <v>7.73476839065552</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>8.75</v>
       </c>
       <c r="G239" t="n">
-        <v>7.82418775558472</v>
+        <v>7.82418727874756</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G240" t="n">
-        <v>7.86889696121216</v>
+        <v>7.86889791488647</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G241" t="n">
-        <v>7.94043254852295</v>
+        <v>7.94043302536011</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G243" t="n">
-        <v>7.73476886749268</v>
+        <v>7.73476839065552</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>8.60999965667725</v>
       </c>
       <c r="G244" t="n">
-        <v>7.6990008354187</v>
+        <v>7.69899988174438</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G247" t="n">
-        <v>7.64534997940063</v>
+        <v>7.64534902572632</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>8.63000011444092</v>
       </c>
       <c r="G248" t="n">
-        <v>7.71688508987427</v>
+        <v>7.71688461303711</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G249" t="n">
-        <v>7.73476886749268</v>
+        <v>7.73476839065552</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G254" t="n">
-        <v>7.81047248840332</v>
+        <v>7.81047344207764</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>8.52999973297119</v>
       </c>
       <c r="G256" t="n">
-        <v>7.87509775161743</v>
+        <v>7.87509870529175</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>8.60999965667725</v>
       </c>
       <c r="G263" t="n">
-        <v>7.94895648956299</v>
+        <v>7.94895553588867</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>8.60999965667725</v>
       </c>
       <c r="G268" t="n">
-        <v>7.94895648956299</v>
+        <v>7.94895553588867</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G270" t="n">
-        <v>7.95818901062012</v>
+        <v>7.95818853378296</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G279" t="n">
-        <v>7.42271852493286</v>
+        <v>7.42271900177002</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G281" t="n">
-        <v>7.49657678604126</v>
+        <v>7.4965763092041</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>7.80999994277954</v>
       </c>
       <c r="G284" t="n">
-        <v>7.21037721633911</v>
+        <v>7.21037769317627</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>7.71000003814697</v>
       </c>
       <c r="G285" t="n">
-        <v>7.11805486679077</v>
+        <v>7.11805534362793</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G286" t="n">
-        <v>7.0534291267395</v>
+        <v>7.05342960357666</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G287" t="n">
-        <v>7.10882234573364</v>
+        <v>7.1088228225708</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G288" t="n">
-        <v>6.97033977508545</v>
+        <v>6.97033929824829</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G289" t="n">
-        <v>6.97033977508545</v>
+        <v>6.97033929824829</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G296" t="n">
-        <v>7.30270004272461</v>
+        <v>7.30269956588745</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G297" t="n">
-        <v>7.145751953125</v>
+        <v>7.14575147628784</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>7.78999996185303</v>
       </c>
       <c r="G300" t="n">
-        <v>7.19191312789917</v>
+        <v>7.19191265106201</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G309" t="n">
-        <v>6.93341016769409</v>
+        <v>6.93341064453125</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G310" t="n">
-        <v>6.97033977508545</v>
+        <v>6.97033929824829</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G311" t="n">
-        <v>6.87801694869995</v>
+        <v>6.87801647186279</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G312" t="n">
-        <v>7.03496503829956</v>
+        <v>7.0349645614624</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G316" t="n">
-        <v>6.97033977508545</v>
+        <v>6.97033929824829</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G318" t="n">
-        <v>7.42271852493286</v>
+        <v>7.42271900177002</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>7.78999996185303</v>
       </c>
       <c r="G321" t="n">
-        <v>7.19191312789917</v>
+        <v>7.19191265106201</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G326" t="n">
-        <v>7.10882234573364</v>
+        <v>7.1088228225708</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G327" t="n">
-        <v>6.97033977508545</v>
+        <v>6.97033929824829</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G328" t="n">
-        <v>7.13651990890503</v>
+        <v>7.13651943206787</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G329" t="n">
-        <v>7.0534291267395</v>
+        <v>7.05342960357666</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G332" t="n">
-        <v>6.93341016769409</v>
+        <v>6.93341064453125</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G333" t="n">
-        <v>7.0534291267395</v>
+        <v>7.05342960357666</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G335" t="n">
-        <v>7.0534291267395</v>
+        <v>7.05342960357666</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G344" t="n">
-        <v>6.97033977508545</v>
+        <v>6.97033929824829</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G346" t="n">
-        <v>7.145751953125</v>
+        <v>7.14575147628784</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G348" t="n">
-        <v>6.90571355819702</v>
+        <v>6.90571403503418</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>7.53999996185303</v>
       </c>
       <c r="G350" t="n">
-        <v>6.96110677719116</v>
+        <v>6.96110725402832</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G351" t="n">
-        <v>6.77646207809448</v>
+        <v>6.77646255493164</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G355" t="n">
-        <v>6.53642416000366</v>
+        <v>6.5364236831665</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>6.98999977111816</v>
       </c>
       <c r="G360" t="n">
-        <v>6.45333337783813</v>
+        <v>6.45333385467529</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G362" t="n">
-        <v>6.6472110748291</v>
+        <v>6.64721059799194</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G363" t="n">
-        <v>6.40717267990112</v>
+        <v>6.40717315673828</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G364" t="n">
-        <v>6.63797903060913</v>
+        <v>6.63797855377197</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G367" t="n">
-        <v>6.48103094100952</v>
+        <v>6.48103046417236</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>7.09000015258789</v>
       </c>
       <c r="G368" t="n">
-        <v>6.54565668106079</v>
+        <v>6.54565620422363</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>7.09000015258789</v>
       </c>
       <c r="G370" t="n">
-        <v>6.54565668106079</v>
+        <v>6.54565620422363</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G371" t="n">
-        <v>6.63797903060913</v>
+        <v>6.63797855377197</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G373" t="n">
-        <v>6.32408285140991</v>
+        <v>6.32408237457275</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>7</v>
       </c>
       <c r="G374" t="n">
-        <v>6.46256589889526</v>
+        <v>6.46256637573242</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>7.09000015258789</v>
       </c>
       <c r="G383" t="n">
-        <v>6.54565668106079</v>
+        <v>6.54565620422363</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G387" t="n">
-        <v>6.61028146743774</v>
+        <v>6.6102819442749</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G389" t="n">
-        <v>6.87801694869995</v>
+        <v>6.87801647186279</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G390" t="n">
-        <v>7.13651990890503</v>
+        <v>7.13651943206787</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G393" t="n">
-        <v>7.30270004272461</v>
+        <v>7.30269956588745</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G394" t="n">
-        <v>7.2011456489563</v>
+        <v>7.20114517211914</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>7.86999988555908</v>
       </c>
       <c r="G396" t="n">
-        <v>7.26577043533325</v>
+        <v>7.26577091217041</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G398" t="n">
-        <v>7.30270004272461</v>
+        <v>7.30269956588745</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G399" t="n">
-        <v>7.36732530593872</v>
+        <v>7.36732578277588</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G400" t="n">
-        <v>7.24730634689331</v>
+        <v>7.24730587005615</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G405" t="n">
-        <v>7.30270004272461</v>
+        <v>7.30269956588745</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G423" t="n">
-        <v>7.40425491333008</v>
+        <v>7.40425443649292</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>8.25</v>
       </c>
       <c r="G427" t="n">
-        <v>7.61659574508667</v>
+        <v>7.61659622192383</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G429" t="n">
-        <v>7.90279626846313</v>
+        <v>7.90279531478882</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G435" t="n">
-        <v>8.63214302062988</v>
+        <v>8.63214206695557</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>9.6899995803833</v>
       </c>
       <c r="G441" t="n">
-        <v>8.94603824615479</v>
+        <v>8.94603729248047</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G443" t="n">
-        <v>8.9921989440918</v>
+        <v>8.99219989776611</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G452" t="n">
-        <v>9.52766799926758</v>
+        <v>9.52766895294189</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G453" t="n">
-        <v>9.61999225616455</v>
+        <v>9.61999130249023</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G454" t="n">
-        <v>9.4168815612793</v>
+        <v>9.41688251495361</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G456" t="n">
-        <v>9.25070285797119</v>
+        <v>9.25070190429688</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G458" t="n">
-        <v>9.26916694641113</v>
+        <v>9.26916599273682</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G464" t="n">
-        <v>9.26916694641113</v>
+        <v>9.26916599273682</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>9.98999977111816</v>
       </c>
       <c r="G466" t="n">
-        <v>9.22300434112549</v>
+        <v>9.2230052947998</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G470" t="n">
-        <v>9.61999225616455</v>
+        <v>9.61999130249023</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>10.4799995422363</v>
       </c>
       <c r="G471" t="n">
-        <v>9.67538452148438</v>
+        <v>9.67538356781006</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G476" t="n">
-        <v>9.61999225616455</v>
+        <v>9.61999130249023</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G477" t="n">
-        <v>9.58306312561035</v>
+        <v>9.58306217193604</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G480" t="n">
-        <v>10.247784614563</v>
+        <v>10.2477836608887</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>11.1199998855591</v>
       </c>
       <c r="G481" t="n">
-        <v>10.2662487030029</v>
+        <v>10.2662477493286</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G482" t="n">
-        <v>8.93680667877197</v>
+        <v>8.93680572509766</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G483" t="n">
-        <v>9.28763198852539</v>
+        <v>9.28763103485107</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G484" t="n">
-        <v>9.21377182006836</v>
+        <v>9.21377277374268</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>9.63000011444092</v>
       </c>
       <c r="G488" t="n">
-        <v>8.89064407348633</v>
+        <v>8.89064502716064</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>9.28999996185303</v>
       </c>
       <c r="G494" t="n">
-        <v>8.57674884796143</v>
+        <v>8.57674789428711</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G495" t="n">
-        <v>8.48442554473877</v>
+        <v>8.48442649841309</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G499" t="n">
-        <v>8.62291049957275</v>
+        <v>8.62290954589844</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G501" t="n">
-        <v>8.62291049957275</v>
+        <v>8.62290954589844</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>9.6899995803833</v>
       </c>
       <c r="G503" t="n">
-        <v>8.94603824615479</v>
+        <v>8.94603729248047</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G504" t="n">
-        <v>8.86294746398926</v>
+        <v>8.86294841766357</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G511" t="n">
-        <v>8.78909015655518</v>
+        <v>8.78909111022949</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>9.8100004196167</v>
       </c>
       <c r="G513" t="n">
-        <v>9.05682563781738</v>
+        <v>9.05682468414307</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G516" t="n">
-        <v>8.95527076721191</v>
+        <v>8.9552698135376</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -29648,6 +29648,32 @@
         <v>1.05200004577637</v>
       </c>
       <c r="H1126" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1127">
+      <c r="A1127" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B1127" t="n">
+        <v>106765</v>
+      </c>
+      <c r="C1127" t="n">
+        <v>1.07000005245209</v>
+      </c>
+      <c r="D1127" t="n">
+        <v>1.04799997806549</v>
+      </c>
+      <c r="E1127" t="n">
+        <v>1.04999995231628</v>
+      </c>
+      <c r="F1127" t="n">
+        <v>1.05400002002716</v>
+      </c>
+      <c r="G1127" t="n">
+        <v>1.05400002002716</v>
+      </c>
+      <c r="H1127" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/TISG.MI.xlsx
+++ b/data/TISG.MI.xlsx
@@ -29677,6 +29677,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1128">
+      <c r="A1128" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B1128" t="n">
+        <v>199826</v>
+      </c>
+      <c r="C1128" t="n">
+        <v>1.07400000095367</v>
+      </c>
+      <c r="D1128" t="n">
+        <v>1.01400005817413</v>
+      </c>
+      <c r="E1128" t="n">
+        <v>1.04999995231628</v>
+      </c>
+      <c r="F1128" t="n">
+        <v>1.01999998092651</v>
+      </c>
+      <c r="G1128" t="n">
+        <v>1.01999998092651</v>
+      </c>
+      <c r="H1128" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TISG.MI.xlsx
+++ b/data/TISG.MI.xlsx
@@ -485,7 +485,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G4" t="n">
-        <v>5.16843509674072</v>
+        <v>5.16843461990356</v>
       </c>
       <c r="H4" t="n">
         <v>13258</v>
@@ -572,7 +572,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G7" t="n">
-        <v>4.94488668441772</v>
+        <v>4.94488716125488</v>
       </c>
       <c r="H7" t="n">
         <v>13883</v>
@@ -746,7 +746,7 @@
         <v>5.6100001335144</v>
       </c>
       <c r="G13" t="n">
-        <v>5.01642227172852</v>
+        <v>5.01642179489136</v>
       </c>
       <c r="H13" t="n">
         <v>20247</v>
@@ -833,7 +833,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G16" t="n">
-        <v>5.03430604934692</v>
+        <v>5.03430652618408</v>
       </c>
       <c r="H16" t="n">
         <v>20391</v>
@@ -862,7 +862,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G17" t="n">
-        <v>4.96277093887329</v>
+        <v>4.96277046203613</v>
       </c>
       <c r="H17" t="n">
         <v>9297</v>
@@ -891,7 +891,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G18" t="n">
-        <v>4.93594455718994</v>
+        <v>4.9359450340271</v>
       </c>
       <c r="H18" t="n">
         <v>2331</v>
@@ -920,7 +920,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G19" t="n">
-        <v>4.94488668441772</v>
+        <v>4.94488716125488</v>
       </c>
       <c r="H19" t="n">
         <v>8685</v>
@@ -1007,7 +1007,7 @@
         <v>5.6100001335144</v>
       </c>
       <c r="G22" t="n">
-        <v>5.01642227172852</v>
+        <v>5.01642179489136</v>
       </c>
       <c r="H22" t="n">
         <v>57978</v>
@@ -1065,7 +1065,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G24" t="n">
-        <v>4.59615087509155</v>
+        <v>4.59615135192871</v>
       </c>
       <c r="H24" t="n">
         <v>122824</v>
@@ -1094,7 +1094,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G25" t="n">
-        <v>4.64086151123047</v>
+        <v>4.64086103439331</v>
       </c>
       <c r="H25" t="n">
         <v>38675</v>
@@ -1384,7 +1384,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G35" t="n">
-        <v>4.64086151123047</v>
+        <v>4.64086103439331</v>
       </c>
       <c r="H35" t="n">
         <v>71434</v>
@@ -1616,7 +1616,7 @@
         <v>5</v>
       </c>
       <c r="G43" t="n">
-        <v>4.47096490859985</v>
+        <v>4.4709644317627</v>
       </c>
       <c r="H43" t="n">
         <v>31060</v>
@@ -1645,7 +1645,7 @@
         <v>5</v>
       </c>
       <c r="G44" t="n">
-        <v>4.47096490859985</v>
+        <v>4.4709644317627</v>
       </c>
       <c r="H44" t="n">
         <v>19860</v>
@@ -1790,7 +1790,7 @@
         <v>4.84499979019165</v>
       </c>
       <c r="G49" t="n">
-        <v>4.33236455917358</v>
+        <v>4.33236408233643</v>
       </c>
       <c r="H49" t="n">
         <v>18567</v>
@@ -1848,7 +1848,7 @@
         <v>4.84499979019165</v>
       </c>
       <c r="G51" t="n">
-        <v>4.33236455917358</v>
+        <v>4.33236408233643</v>
       </c>
       <c r="H51" t="n">
         <v>13315</v>
@@ -1877,7 +1877,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G52" t="n">
-        <v>4.2921257019043</v>
+        <v>4.29212617874146</v>
       </c>
       <c r="H52" t="n">
         <v>24850</v>
@@ -2022,7 +2022,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G57" t="n">
-        <v>4.2921257019043</v>
+        <v>4.29212617874146</v>
       </c>
       <c r="H57" t="n">
         <v>9336</v>
@@ -2080,7 +2080,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G59" t="n">
-        <v>4.51567459106445</v>
+        <v>4.51567411422729</v>
       </c>
       <c r="H59" t="n">
         <v>22808</v>
@@ -2138,7 +2138,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G61" t="n">
-        <v>4.93594455718994</v>
+        <v>4.9359450340271</v>
       </c>
       <c r="H61" t="n">
         <v>80771</v>
@@ -2457,7 +2457,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G72" t="n">
-        <v>4.6676869392395</v>
+        <v>4.66768646240234</v>
       </c>
       <c r="H72" t="n">
         <v>17558</v>
@@ -2544,7 +2544,7 @@
         <v>4.9850001335144</v>
       </c>
       <c r="G75" t="n">
-        <v>4.4575514793396</v>
+        <v>4.45755195617676</v>
       </c>
       <c r="H75" t="n">
         <v>16465</v>
@@ -2573,7 +2573,7 @@
         <v>4.85500001907349</v>
       </c>
       <c r="G76" t="n">
-        <v>4.34130668640137</v>
+        <v>4.34130620956421</v>
       </c>
       <c r="H76" t="n">
         <v>21022</v>
@@ -2660,7 +2660,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G79" t="n">
-        <v>4.2921257019043</v>
+        <v>4.29212617874146</v>
       </c>
       <c r="H79" t="n">
         <v>26762</v>
@@ -2689,7 +2689,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G80" t="n">
-        <v>4.2921257019043</v>
+        <v>4.29212617874146</v>
       </c>
       <c r="H80" t="n">
         <v>10522</v>
@@ -2718,7 +2718,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G81" t="n">
-        <v>4.2921257019043</v>
+        <v>4.29212617874146</v>
       </c>
       <c r="H81" t="n">
         <v>38577</v>
@@ -2747,7 +2747,7 @@
         <v>4.83500003814697</v>
       </c>
       <c r="G82" t="n">
-        <v>4.3234224319458</v>
+        <v>4.32342290878296</v>
       </c>
       <c r="H82" t="n">
         <v>63420</v>
@@ -2921,7 +2921,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G88" t="n">
-        <v>4.49779081344604</v>
+        <v>4.49779033660889</v>
       </c>
       <c r="H88" t="n">
         <v>22654</v>
@@ -2950,7 +2950,7 @@
         <v>5</v>
       </c>
       <c r="G89" t="n">
-        <v>4.47096490859985</v>
+        <v>4.4709644317627</v>
       </c>
       <c r="H89" t="n">
         <v>83457</v>
@@ -2979,7 +2979,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G90" t="n">
-        <v>4.48884868621826</v>
+        <v>4.4888482093811</v>
       </c>
       <c r="H90" t="n">
         <v>27075</v>
@@ -3008,7 +3008,7 @@
         <v>4.85500001907349</v>
       </c>
       <c r="G91" t="n">
-        <v>4.34130668640137</v>
+        <v>4.34130620956421</v>
       </c>
       <c r="H91" t="n">
         <v>28795</v>
@@ -3153,7 +3153,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G96" t="n">
-        <v>4.2921257019043</v>
+        <v>4.29212617874146</v>
       </c>
       <c r="H96" t="n">
         <v>8412</v>
@@ -3211,7 +3211,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G98" t="n">
-        <v>4.31895208358765</v>
+        <v>4.31895160675049</v>
       </c>
       <c r="H98" t="n">
         <v>10092</v>
@@ -3240,7 +3240,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G99" t="n">
-        <v>4.3547191619873</v>
+        <v>4.35471963882446</v>
       </c>
       <c r="H99" t="n">
         <v>17935</v>
@@ -3327,7 +3327,7 @@
         <v>4.46500015258789</v>
       </c>
       <c r="G102" t="n">
-        <v>3.99257135391235</v>
+        <v>3.99257159233093</v>
       </c>
       <c r="H102" t="n">
         <v>73666</v>
@@ -3356,7 +3356,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G103" t="n">
-        <v>3.95233273506165</v>
+        <v>3.95233249664307</v>
       </c>
       <c r="H103" t="n">
         <v>122405</v>
@@ -3414,7 +3414,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G105" t="n">
-        <v>3.90762281417847</v>
+        <v>3.90762233734131</v>
       </c>
       <c r="H105" t="n">
         <v>8913</v>
@@ -3443,7 +3443,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G106" t="n">
-        <v>3.84502959251404</v>
+        <v>3.84502983093262</v>
       </c>
       <c r="H106" t="n">
         <v>39490</v>
@@ -3501,7 +3501,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G108" t="n">
-        <v>3.82714605331421</v>
+        <v>3.82714557647705</v>
       </c>
       <c r="H108" t="n">
         <v>26268</v>
@@ -3530,7 +3530,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G109" t="n">
-        <v>3.80926179885864</v>
+        <v>3.80926203727722</v>
       </c>
       <c r="H109" t="n">
         <v>5280</v>
@@ -3559,7 +3559,7 @@
         <v>4.2649998664856</v>
       </c>
       <c r="G110" t="n">
-        <v>3.81373238563538</v>
+        <v>3.81373286247253</v>
       </c>
       <c r="H110" t="n">
         <v>30391</v>
@@ -3646,7 +3646,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G113" t="n">
-        <v>3.75560998916626</v>
+        <v>3.75561022758484</v>
       </c>
       <c r="H113" t="n">
         <v>18855</v>
@@ -3675,7 +3675,7 @@
         <v>4.5</v>
       </c>
       <c r="G114" t="n">
-        <v>4.02386808395386</v>
+        <v>4.02386856079102</v>
       </c>
       <c r="H114" t="n">
         <v>51824</v>
@@ -3936,7 +3936,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G123" t="n">
-        <v>4.2921257019043</v>
+        <v>4.29212617874146</v>
       </c>
       <c r="H123" t="n">
         <v>9894</v>
@@ -3965,7 +3965,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G124" t="n">
-        <v>4.2921257019043</v>
+        <v>4.29212617874146</v>
       </c>
       <c r="H124" t="n">
         <v>5737</v>
@@ -4023,7 +4023,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G126" t="n">
-        <v>4.27424192428589</v>
+        <v>4.27424240112305</v>
       </c>
       <c r="H126" t="n">
         <v>14120</v>
@@ -4052,7 +4052,7 @@
         <v>4.84499979019165</v>
       </c>
       <c r="G127" t="n">
-        <v>4.33236455917358</v>
+        <v>4.33236408233643</v>
       </c>
       <c r="H127" t="n">
         <v>6687</v>
@@ -4371,7 +4371,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G138" t="n">
-        <v>4.81075811386108</v>
+        <v>4.81075763702393</v>
       </c>
       <c r="H138" t="n">
         <v>13168</v>
@@ -4458,7 +4458,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G141" t="n">
-        <v>4.93594455718994</v>
+        <v>4.9359450340271</v>
       </c>
       <c r="H141" t="n">
         <v>96218</v>
@@ -4487,7 +4487,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G142" t="n">
-        <v>4.86440944671631</v>
+        <v>4.86440896987915</v>
       </c>
       <c r="H142" t="n">
         <v>86543</v>
@@ -4516,7 +4516,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G143" t="n">
-        <v>4.79287385940552</v>
+        <v>4.79287433624268</v>
       </c>
       <c r="H143" t="n">
         <v>12914</v>
@@ -4661,7 +4661,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G148" t="n">
-        <v>5.22208690643311</v>
+        <v>5.22208642959595</v>
       </c>
       <c r="H148" t="n">
         <v>48197</v>
@@ -4690,7 +4690,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G149" t="n">
-        <v>5.18631887435913</v>
+        <v>5.18631935119629</v>
       </c>
       <c r="H149" t="n">
         <v>94640</v>
@@ -4748,7 +4748,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G151" t="n">
-        <v>5.18631887435913</v>
+        <v>5.18631935119629</v>
       </c>
       <c r="H151" t="n">
         <v>10180</v>
@@ -4777,7 +4777,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G152" t="n">
-        <v>5.23102807998657</v>
+        <v>5.23102855682373</v>
       </c>
       <c r="H152" t="n">
         <v>20268</v>
@@ -4806,7 +4806,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G153" t="n">
-        <v>5.16843509674072</v>
+        <v>5.16843461990356</v>
       </c>
       <c r="H153" t="n">
         <v>62349</v>
@@ -4893,7 +4893,7 @@
         <v>5.6100001335144</v>
       </c>
       <c r="G156" t="n">
-        <v>5.01642227172852</v>
+        <v>5.01642179489136</v>
       </c>
       <c r="H156" t="n">
         <v>19697</v>
@@ -4980,7 +4980,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G159" t="n">
-        <v>4.95382881164551</v>
+        <v>4.95382833480835</v>
       </c>
       <c r="H159" t="n">
         <v>26457</v>
@@ -5009,7 +5009,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G160" t="n">
-        <v>5.09689903259277</v>
+        <v>5.09689950942993</v>
       </c>
       <c r="H160" t="n">
         <v>13151</v>
@@ -5038,7 +5038,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G161" t="n">
-        <v>5.18631887435913</v>
+        <v>5.18631935119629</v>
       </c>
       <c r="H161" t="n">
         <v>25073</v>
@@ -5067,7 +5067,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G162" t="n">
-        <v>5.09689903259277</v>
+        <v>5.09689950942993</v>
       </c>
       <c r="H162" t="n">
         <v>60968</v>
@@ -5125,7 +5125,7 @@
         <v>5.69000005722046</v>
       </c>
       <c r="G164" t="n">
-        <v>5.08795738220215</v>
+        <v>5.08795785903931</v>
       </c>
       <c r="H164" t="n">
         <v>9415</v>
@@ -5183,7 +5183,7 @@
         <v>5.67000007629395</v>
       </c>
       <c r="G166" t="n">
-        <v>5.0700740814209</v>
+        <v>5.07007360458374</v>
       </c>
       <c r="H166" t="n">
         <v>8659</v>
@@ -5386,7 +5386,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G173" t="n">
-        <v>5.07901525497437</v>
+        <v>5.07901573181152</v>
       </c>
       <c r="H173" t="n">
         <v>8390</v>
@@ -5415,7 +5415,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G174" t="n">
-        <v>5.03430604934692</v>
+        <v>5.03430652618408</v>
       </c>
       <c r="H174" t="n">
         <v>11363</v>
@@ -5473,7 +5473,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G176" t="n">
-        <v>5.17737674713135</v>
+        <v>5.17737722396851</v>
       </c>
       <c r="H176" t="n">
         <v>15289</v>
@@ -5560,7 +5560,7 @@
         <v>5.90999984741211</v>
       </c>
       <c r="G179" t="n">
-        <v>5.28468036651611</v>
+        <v>5.28467988967896</v>
       </c>
       <c r="H179" t="n">
         <v>21763</v>
@@ -5618,7 +5618,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G181" t="n">
-        <v>5.436692237854</v>
+        <v>5.43669271469116</v>
       </c>
       <c r="H181" t="n">
         <v>65727</v>
@@ -5705,7 +5705,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G184" t="n">
-        <v>5.67812442779541</v>
+        <v>5.67812490463257</v>
       </c>
       <c r="H184" t="n">
         <v>135409</v>
@@ -5734,7 +5734,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G185" t="n">
-        <v>5.70495080947876</v>
+        <v>5.7049503326416</v>
       </c>
       <c r="H185" t="n">
         <v>70596</v>
@@ -5908,7 +5908,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G191" t="n">
-        <v>6.21464061737061</v>
+        <v>6.21464014053345</v>
       </c>
       <c r="H191" t="n">
         <v>39877</v>
@@ -5937,7 +5937,7 @@
         <v>6.80999994277954</v>
       </c>
       <c r="G192" t="n">
-        <v>6.08945322036743</v>
+        <v>6.08945369720459</v>
       </c>
       <c r="H192" t="n">
         <v>86712</v>
@@ -5966,7 +5966,7 @@
         <v>7</v>
       </c>
       <c r="G193" t="n">
-        <v>6.25934982299805</v>
+        <v>6.25935029983521</v>
       </c>
       <c r="H193" t="n">
         <v>64859</v>
@@ -5995,7 +5995,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G194" t="n">
-        <v>6.18781518936157</v>
+        <v>6.18781471252441</v>
       </c>
       <c r="H194" t="n">
         <v>195087</v>
@@ -6024,7 +6024,7 @@
         <v>6.90999984741211</v>
       </c>
       <c r="G195" t="n">
-        <v>6.17887258529663</v>
+        <v>6.17887306213379</v>
       </c>
       <c r="H195" t="n">
         <v>47173</v>
@@ -6082,7 +6082,7 @@
         <v>7</v>
       </c>
       <c r="G197" t="n">
-        <v>6.25934982299805</v>
+        <v>6.25935029983521</v>
       </c>
       <c r="H197" t="n">
         <v>92157</v>
@@ -6169,7 +6169,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G200" t="n">
-        <v>6.21464061737061</v>
+        <v>6.21464014053345</v>
       </c>
       <c r="H200" t="n">
         <v>49278</v>
@@ -6198,7 +6198,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G201" t="n">
-        <v>6.27723455429077</v>
+        <v>6.27723407745361</v>
       </c>
       <c r="H201" t="n">
         <v>56777</v>
@@ -6256,7 +6256,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G203" t="n">
-        <v>6.52760791778564</v>
+        <v>6.5276083946228</v>
       </c>
       <c r="H203" t="n">
         <v>138551</v>
@@ -6343,7 +6343,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G206" t="n">
-        <v>6.30406045913696</v>
+        <v>6.3040599822998</v>
       </c>
       <c r="H206" t="n">
         <v>51631</v>
@@ -6604,7 +6604,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G215" t="n">
-        <v>6.66173696517944</v>
+        <v>6.66173648834229</v>
       </c>
       <c r="H215" t="n">
         <v>95402</v>
@@ -6662,7 +6662,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G217" t="n">
-        <v>6.4203052520752</v>
+        <v>6.42030477523804</v>
       </c>
       <c r="H217" t="n">
         <v>143048</v>
@@ -6691,7 +6691,7 @@
         <v>7.53000020980835</v>
       </c>
       <c r="G218" t="n">
-        <v>6.73327207565308</v>
+        <v>6.73327255249023</v>
       </c>
       <c r="H218" t="n">
         <v>97258</v>
@@ -6749,7 +6749,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G220" t="n">
-        <v>6.60808563232422</v>
+        <v>6.60808515548706</v>
       </c>
       <c r="H220" t="n">
         <v>64845</v>
@@ -6778,7 +6778,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G221" t="n">
-        <v>6.45607280731201</v>
+        <v>6.45607233047485</v>
       </c>
       <c r="H221" t="n">
         <v>66909</v>
@@ -6865,7 +6865,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G224" t="n">
-        <v>6.66173696517944</v>
+        <v>6.66173648834229</v>
       </c>
       <c r="H224" t="n">
         <v>30693</v>
@@ -6923,7 +6923,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G226" t="n">
-        <v>6.50972461700439</v>
+        <v>6.50972414016724</v>
       </c>
       <c r="H226" t="n">
         <v>94459</v>
@@ -6952,7 +6952,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G227" t="n">
-        <v>6.58125925064087</v>
+        <v>6.58125972747803</v>
       </c>
       <c r="H227" t="n">
         <v>33666</v>
@@ -6981,7 +6981,7 @@
         <v>7.53000020980835</v>
       </c>
       <c r="G228" t="n">
-        <v>6.73327207565308</v>
+        <v>6.73327255249023</v>
       </c>
       <c r="H228" t="n">
         <v>150431</v>
@@ -7039,7 +7039,7 @@
         <v>7.98999977111816</v>
       </c>
       <c r="G230" t="n">
-        <v>7.14460134506226</v>
+        <v>7.1446008682251</v>
       </c>
       <c r="H230" t="n">
         <v>156690</v>
@@ -7068,7 +7068,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G231" t="n">
-        <v>7.36814880371094</v>
+        <v>7.3681492805481</v>
       </c>
       <c r="H231" t="n">
         <v>165049</v>
@@ -7097,7 +7097,7 @@
         <v>8.56999969482422</v>
       </c>
       <c r="G232" t="n">
-        <v>7.66323328018188</v>
+        <v>7.66323280334473</v>
       </c>
       <c r="H232" t="n">
         <v>214841</v>
@@ -7126,7 +7126,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G233" t="n">
-        <v>7.63640642166138</v>
+        <v>7.63640689849854</v>
       </c>
       <c r="H233" t="n">
         <v>144356</v>
@@ -7184,7 +7184,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G235" t="n">
-        <v>7.65429210662842</v>
+        <v>7.6542911529541</v>
       </c>
       <c r="H235" t="n">
         <v>82796</v>
@@ -7213,7 +7213,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G236" t="n">
-        <v>7.35920715332031</v>
+        <v>7.35920667648315</v>
       </c>
       <c r="H236" t="n">
         <v>253702</v>
@@ -7242,7 +7242,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G237" t="n">
-        <v>7.35920715332031</v>
+        <v>7.35920667648315</v>
       </c>
       <c r="H237" t="n">
         <v>172849</v>
@@ -7271,7 +7271,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G238" t="n">
-        <v>7.73476886749268</v>
+        <v>7.73476839065552</v>
       </c>
       <c r="H238" t="n">
         <v>113648</v>
@@ -7300,7 +7300,7 @@
         <v>8.75</v>
       </c>
       <c r="G239" t="n">
-        <v>7.82418775558472</v>
+        <v>7.82418727874756</v>
       </c>
       <c r="H239" t="n">
         <v>92729</v>
@@ -7329,7 +7329,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G240" t="n">
-        <v>7.86889696121216</v>
+        <v>7.86889791488647</v>
       </c>
       <c r="H240" t="n">
         <v>95722</v>
@@ -7358,7 +7358,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G241" t="n">
-        <v>7.94043254852295</v>
+        <v>7.94043302536011</v>
       </c>
       <c r="H241" t="n">
         <v>150011</v>
@@ -7416,7 +7416,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G243" t="n">
-        <v>7.73476886749268</v>
+        <v>7.73476839065552</v>
       </c>
       <c r="H243" t="n">
         <v>250001</v>
@@ -7445,7 +7445,7 @@
         <v>8.60999965667725</v>
       </c>
       <c r="G244" t="n">
-        <v>7.6990008354187</v>
+        <v>7.69899988174438</v>
       </c>
       <c r="H244" t="n">
         <v>102832</v>
@@ -7532,7 +7532,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G247" t="n">
-        <v>7.64534997940063</v>
+        <v>7.64534902572632</v>
       </c>
       <c r="H247" t="n">
         <v>105886</v>
@@ -7561,7 +7561,7 @@
         <v>8.63000011444092</v>
       </c>
       <c r="G248" t="n">
-        <v>7.71688508987427</v>
+        <v>7.71688461303711</v>
       </c>
       <c r="H248" t="n">
         <v>49730</v>
@@ -7590,7 +7590,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G249" t="n">
-        <v>7.73476886749268</v>
+        <v>7.73476839065552</v>
       </c>
       <c r="H249" t="n">
         <v>51008</v>
@@ -7735,7 +7735,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G254" t="n">
-        <v>7.81047248840332</v>
+        <v>7.81047344207764</v>
       </c>
       <c r="H254" t="n">
         <v>152971</v>
@@ -7793,7 +7793,7 @@
         <v>8.52999973297119</v>
       </c>
       <c r="G256" t="n">
-        <v>7.87509775161743</v>
+        <v>7.87509870529175</v>
       </c>
       <c r="H256" t="n">
         <v>99895</v>
@@ -7996,7 +7996,7 @@
         <v>8.60999965667725</v>
       </c>
       <c r="G263" t="n">
-        <v>7.94895648956299</v>
+        <v>7.94895553588867</v>
       </c>
       <c r="H263" t="n">
         <v>76537</v>
@@ -8141,7 +8141,7 @@
         <v>8.60999965667725</v>
       </c>
       <c r="G268" t="n">
-        <v>7.94895648956299</v>
+        <v>7.94895553588867</v>
       </c>
       <c r="H268" t="n">
         <v>61503</v>
@@ -8199,7 +8199,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G270" t="n">
-        <v>7.95818901062012</v>
+        <v>7.95818853378296</v>
       </c>
       <c r="H270" t="n">
         <v>77829</v>
@@ -8460,7 +8460,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G279" t="n">
-        <v>7.42271852493286</v>
+        <v>7.42271900177002</v>
       </c>
       <c r="H279" t="n">
         <v>56062</v>
@@ -8518,7 +8518,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G281" t="n">
-        <v>7.49657678604126</v>
+        <v>7.4965763092041</v>
       </c>
       <c r="H281" t="n">
         <v>39852</v>
@@ -8605,7 +8605,7 @@
         <v>7.80999994277954</v>
       </c>
       <c r="G284" t="n">
-        <v>7.21037721633911</v>
+        <v>7.21037769317627</v>
       </c>
       <c r="H284" t="n">
         <v>117674</v>
@@ -8634,7 +8634,7 @@
         <v>7.71000003814697</v>
       </c>
       <c r="G285" t="n">
-        <v>7.11805486679077</v>
+        <v>7.11805534362793</v>
       </c>
       <c r="H285" t="n">
         <v>57382</v>
@@ -8663,7 +8663,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G286" t="n">
-        <v>7.0534291267395</v>
+        <v>7.05342960357666</v>
       </c>
       <c r="H286" t="n">
         <v>74446</v>
@@ -8692,7 +8692,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G287" t="n">
-        <v>7.10882234573364</v>
+        <v>7.1088228225708</v>
       </c>
       <c r="H287" t="n">
         <v>108157</v>
@@ -8721,7 +8721,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G288" t="n">
-        <v>6.97033977508545</v>
+        <v>6.97033929824829</v>
       </c>
       <c r="H288" t="n">
         <v>37819</v>
@@ -8750,7 +8750,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G289" t="n">
-        <v>6.97033977508545</v>
+        <v>6.97033929824829</v>
       </c>
       <c r="H289" t="n">
         <v>41222</v>
@@ -8953,7 +8953,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G296" t="n">
-        <v>7.30270004272461</v>
+        <v>7.30269956588745</v>
       </c>
       <c r="H296" t="n">
         <v>83813</v>
@@ -8982,7 +8982,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G297" t="n">
-        <v>7.145751953125</v>
+        <v>7.14575147628784</v>
       </c>
       <c r="H297" t="n">
         <v>43493</v>
@@ -9069,7 +9069,7 @@
         <v>7.78999996185303</v>
       </c>
       <c r="G300" t="n">
-        <v>7.19191312789917</v>
+        <v>7.19191265106201</v>
       </c>
       <c r="H300" t="n">
         <v>50892</v>
@@ -9330,7 +9330,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G309" t="n">
-        <v>6.93341016769409</v>
+        <v>6.93341064453125</v>
       </c>
       <c r="H309" t="n">
         <v>19291</v>
@@ -9359,7 +9359,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G310" t="n">
-        <v>6.97033977508545</v>
+        <v>6.97033929824829</v>
       </c>
       <c r="H310" t="n">
         <v>22938</v>
@@ -9388,7 +9388,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G311" t="n">
-        <v>6.87801694869995</v>
+        <v>6.87801647186279</v>
       </c>
       <c r="H311" t="n">
         <v>39307</v>
@@ -9417,7 +9417,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G312" t="n">
-        <v>7.03496503829956</v>
+        <v>7.0349645614624</v>
       </c>
       <c r="H312" t="n">
         <v>19565</v>
@@ -9533,7 +9533,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G316" t="n">
-        <v>6.97033977508545</v>
+        <v>6.97033929824829</v>
       </c>
       <c r="H316" t="n">
         <v>31066</v>
@@ -9591,7 +9591,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G318" t="n">
-        <v>7.42271852493286</v>
+        <v>7.42271900177002</v>
       </c>
       <c r="H318" t="n">
         <v>77225</v>
@@ -9678,7 +9678,7 @@
         <v>7.78999996185303</v>
       </c>
       <c r="G321" t="n">
-        <v>7.19191312789917</v>
+        <v>7.19191265106201</v>
       </c>
       <c r="H321" t="n">
         <v>21141</v>
@@ -9823,7 +9823,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G326" t="n">
-        <v>7.10882234573364</v>
+        <v>7.1088228225708</v>
       </c>
       <c r="H326" t="n">
         <v>18088</v>
@@ -9852,7 +9852,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G327" t="n">
-        <v>6.97033977508545</v>
+        <v>6.97033929824829</v>
       </c>
       <c r="H327" t="n">
         <v>69708</v>
@@ -9881,7 +9881,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G328" t="n">
-        <v>7.13651990890503</v>
+        <v>7.13651943206787</v>
       </c>
       <c r="H328" t="n">
         <v>33278</v>
@@ -9910,7 +9910,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G329" t="n">
-        <v>7.0534291267395</v>
+        <v>7.05342960357666</v>
       </c>
       <c r="H329" t="n">
         <v>17493</v>
@@ -9997,7 +9997,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G332" t="n">
-        <v>6.93341016769409</v>
+        <v>6.93341064453125</v>
       </c>
       <c r="H332" t="n">
         <v>24732</v>
@@ -10026,7 +10026,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G333" t="n">
-        <v>7.0534291267395</v>
+        <v>7.05342960357666</v>
       </c>
       <c r="H333" t="n">
         <v>18353</v>
@@ -10084,7 +10084,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G335" t="n">
-        <v>7.0534291267395</v>
+        <v>7.05342960357666</v>
       </c>
       <c r="H335" t="n">
         <v>11054</v>
@@ -10345,7 +10345,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G344" t="n">
-        <v>6.97033977508545</v>
+        <v>6.97033929824829</v>
       </c>
       <c r="H344" t="n">
         <v>42139</v>
@@ -10403,7 +10403,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G346" t="n">
-        <v>7.145751953125</v>
+        <v>7.14575147628784</v>
       </c>
       <c r="H346" t="n">
         <v>47587</v>
@@ -10461,7 +10461,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G348" t="n">
-        <v>6.90571355819702</v>
+        <v>6.90571403503418</v>
       </c>
       <c r="H348" t="n">
         <v>60152</v>
@@ -10519,7 +10519,7 @@
         <v>7.53999996185303</v>
       </c>
       <c r="G350" t="n">
-        <v>6.96110677719116</v>
+        <v>6.96110725402832</v>
       </c>
       <c r="H350" t="n">
         <v>28852</v>
@@ -10548,7 +10548,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G351" t="n">
-        <v>6.77646207809448</v>
+        <v>6.77646255493164</v>
       </c>
       <c r="H351" t="n">
         <v>58129</v>
@@ -10664,7 +10664,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G355" t="n">
-        <v>6.53642416000366</v>
+        <v>6.5364236831665</v>
       </c>
       <c r="H355" t="n">
         <v>26264</v>
@@ -10809,7 +10809,7 @@
         <v>6.98999977111816</v>
       </c>
       <c r="G360" t="n">
-        <v>6.45333337783813</v>
+        <v>6.45333385467529</v>
       </c>
       <c r="H360" t="n">
         <v>50111</v>
@@ -10867,7 +10867,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G362" t="n">
-        <v>6.6472110748291</v>
+        <v>6.64721059799194</v>
       </c>
       <c r="H362" t="n">
         <v>58993</v>
@@ -10896,7 +10896,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G363" t="n">
-        <v>6.40717267990112</v>
+        <v>6.40717315673828</v>
       </c>
       <c r="H363" t="n">
         <v>39953</v>
@@ -10925,7 +10925,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G364" t="n">
-        <v>6.63797903060913</v>
+        <v>6.63797855377197</v>
       </c>
       <c r="H364" t="n">
         <v>33892</v>
@@ -11012,7 +11012,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G367" t="n">
-        <v>6.48103094100952</v>
+        <v>6.48103046417236</v>
       </c>
       <c r="H367" t="n">
         <v>37646</v>
@@ -11041,7 +11041,7 @@
         <v>7.09000015258789</v>
       </c>
       <c r="G368" t="n">
-        <v>6.54565668106079</v>
+        <v>6.54565620422363</v>
       </c>
       <c r="H368" t="n">
         <v>45957</v>
@@ -11099,7 +11099,7 @@
         <v>7.09000015258789</v>
       </c>
       <c r="G370" t="n">
-        <v>6.54565668106079</v>
+        <v>6.54565620422363</v>
       </c>
       <c r="H370" t="n">
         <v>28684</v>
@@ -11128,7 +11128,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G371" t="n">
-        <v>6.63797903060913</v>
+        <v>6.63797855377197</v>
       </c>
       <c r="H371" t="n">
         <v>24535</v>
@@ -11186,7 +11186,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G373" t="n">
-        <v>6.32408285140991</v>
+        <v>6.32408237457275</v>
       </c>
       <c r="H373" t="n">
         <v>47509</v>
@@ -11215,7 +11215,7 @@
         <v>7</v>
       </c>
       <c r="G374" t="n">
-        <v>6.46256589889526</v>
+        <v>6.46256637573242</v>
       </c>
       <c r="H374" t="n">
         <v>17115</v>
@@ -11476,7 +11476,7 @@
         <v>7.09000015258789</v>
       </c>
       <c r="G383" t="n">
-        <v>6.54565668106079</v>
+        <v>6.54565620422363</v>
       </c>
       <c r="H383" t="n">
         <v>39879</v>
@@ -11592,7 +11592,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G387" t="n">
-        <v>6.61028146743774</v>
+        <v>6.6102819442749</v>
       </c>
       <c r="H387" t="n">
         <v>59425</v>
@@ -11650,7 +11650,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G389" t="n">
-        <v>6.87801694869995</v>
+        <v>6.87801647186279</v>
       </c>
       <c r="H389" t="n">
         <v>91784</v>
@@ -11679,7 +11679,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G390" t="n">
-        <v>7.13651990890503</v>
+        <v>7.13651943206787</v>
       </c>
       <c r="H390" t="n">
         <v>203114</v>
@@ -11766,7 +11766,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G393" t="n">
-        <v>7.30270004272461</v>
+        <v>7.30269956588745</v>
       </c>
       <c r="H393" t="n">
         <v>167425</v>
@@ -11795,7 +11795,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G394" t="n">
-        <v>7.2011456489563</v>
+        <v>7.20114517211914</v>
       </c>
       <c r="H394" t="n">
         <v>191654</v>
@@ -11853,7 +11853,7 @@
         <v>7.86999988555908</v>
       </c>
       <c r="G396" t="n">
-        <v>7.26577043533325</v>
+        <v>7.26577091217041</v>
       </c>
       <c r="H396" t="n">
         <v>50620</v>
@@ -11911,7 +11911,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G398" t="n">
-        <v>7.30270004272461</v>
+        <v>7.30269956588745</v>
       </c>
       <c r="H398" t="n">
         <v>99717</v>
@@ -11940,7 +11940,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G399" t="n">
-        <v>7.36732530593872</v>
+        <v>7.36732578277588</v>
       </c>
       <c r="H399" t="n">
         <v>124059</v>
@@ -11969,7 +11969,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G400" t="n">
-        <v>7.24730634689331</v>
+        <v>7.24730587005615</v>
       </c>
       <c r="H400" t="n">
         <v>72121</v>
@@ -12114,7 +12114,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G405" t="n">
-        <v>7.30270004272461</v>
+        <v>7.30269956588745</v>
       </c>
       <c r="H405" t="n">
         <v>38438</v>
@@ -12636,7 +12636,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G423" t="n">
-        <v>7.40425491333008</v>
+        <v>7.40425443649292</v>
       </c>
       <c r="H423" t="n">
         <v>48656</v>
@@ -12752,7 +12752,7 @@
         <v>8.25</v>
       </c>
       <c r="G427" t="n">
-        <v>7.61659574508667</v>
+        <v>7.61659622192383</v>
       </c>
       <c r="H427" t="n">
         <v>55700</v>
@@ -12810,7 +12810,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G429" t="n">
-        <v>7.90279626846313</v>
+        <v>7.90279531478882</v>
       </c>
       <c r="H429" t="n">
         <v>122032</v>
@@ -12984,7 +12984,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G435" t="n">
-        <v>8.63214302062988</v>
+        <v>8.63214206695557</v>
       </c>
       <c r="H435" t="n">
         <v>236669</v>
@@ -13158,7 +13158,7 @@
         <v>9.6899995803833</v>
       </c>
       <c r="G441" t="n">
-        <v>8.94603824615479</v>
+        <v>8.94603729248047</v>
       </c>
       <c r="H441" t="n">
         <v>85296</v>
@@ -13216,7 +13216,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G443" t="n">
-        <v>8.9921989440918</v>
+        <v>8.99219989776611</v>
       </c>
       <c r="H443" t="n">
         <v>101160</v>
@@ -13477,7 +13477,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G452" t="n">
-        <v>9.52766799926758</v>
+        <v>9.52766895294189</v>
       </c>
       <c r="H452" t="n">
         <v>186778</v>
@@ -13506,7 +13506,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G453" t="n">
-        <v>9.61999225616455</v>
+        <v>9.61999130249023</v>
       </c>
       <c r="H453" t="n">
         <v>106036</v>
@@ -13535,7 +13535,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G454" t="n">
-        <v>9.4168815612793</v>
+        <v>9.41688251495361</v>
       </c>
       <c r="H454" t="n">
         <v>85544</v>
@@ -13593,7 +13593,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G456" t="n">
-        <v>9.25070285797119</v>
+        <v>9.25070190429688</v>
       </c>
       <c r="H456" t="n">
         <v>45013</v>
@@ -13651,7 +13651,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G458" t="n">
-        <v>9.26916694641113</v>
+        <v>9.26916599273682</v>
       </c>
       <c r="H458" t="n">
         <v>73523</v>
@@ -13825,7 +13825,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G464" t="n">
-        <v>9.26916694641113</v>
+        <v>9.26916599273682</v>
       </c>
       <c r="H464" t="n">
         <v>35262</v>
@@ -13883,7 +13883,7 @@
         <v>9.98999977111816</v>
       </c>
       <c r="G466" t="n">
-        <v>9.22300434112549</v>
+        <v>9.2230052947998</v>
       </c>
       <c r="H466" t="n">
         <v>90490</v>
@@ -13999,7 +13999,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G470" t="n">
-        <v>9.61999225616455</v>
+        <v>9.61999130249023</v>
       </c>
       <c r="H470" t="n">
         <v>91656</v>
@@ -14028,7 +14028,7 @@
         <v>10.4799995422363</v>
       </c>
       <c r="G471" t="n">
-        <v>9.67538452148438</v>
+        <v>9.67538356781006</v>
       </c>
       <c r="H471" t="n">
         <v>94908</v>
@@ -14173,7 +14173,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G476" t="n">
-        <v>9.61999225616455</v>
+        <v>9.61999130249023</v>
       </c>
       <c r="H476" t="n">
         <v>55619</v>
@@ -14202,7 +14202,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G477" t="n">
-        <v>9.58306312561035</v>
+        <v>9.58306217193604</v>
       </c>
       <c r="H477" t="n">
         <v>68414</v>
@@ -14289,7 +14289,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G480" t="n">
-        <v>10.247784614563</v>
+        <v>10.2477836608887</v>
       </c>
       <c r="H480" t="n">
         <v>121664</v>
@@ -14318,7 +14318,7 @@
         <v>11.1199998855591</v>
       </c>
       <c r="G481" t="n">
-        <v>10.2662487030029</v>
+        <v>10.2662477493286</v>
       </c>
       <c r="H481" t="n">
         <v>62344</v>
@@ -14347,7 +14347,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G482" t="n">
-        <v>8.93680667877197</v>
+        <v>8.93680572509766</v>
       </c>
       <c r="H482" t="n">
         <v>1087677</v>
@@ -14376,7 +14376,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G483" t="n">
-        <v>9.28763198852539</v>
+        <v>9.28763103485107</v>
       </c>
       <c r="H483" t="n">
         <v>332225</v>
@@ -14405,7 +14405,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G484" t="n">
-        <v>9.21377182006836</v>
+        <v>9.21377277374268</v>
       </c>
       <c r="H484" t="n">
         <v>153862</v>
@@ -14521,7 +14521,7 @@
         <v>9.63000011444092</v>
       </c>
       <c r="G488" t="n">
-        <v>8.89064407348633</v>
+        <v>8.89064502716064</v>
       </c>
       <c r="H488" t="n">
         <v>74178</v>
@@ -14695,7 +14695,7 @@
         <v>9.28999996185303</v>
       </c>
       <c r="G494" t="n">
-        <v>8.57674884796143</v>
+        <v>8.57674789428711</v>
       </c>
       <c r="H494" t="n">
         <v>136448</v>
@@ -14724,7 +14724,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G495" t="n">
-        <v>8.48442554473877</v>
+        <v>8.48442649841309</v>
       </c>
       <c r="H495" t="n">
         <v>37699</v>
@@ -14840,7 +14840,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G499" t="n">
-        <v>8.62291049957275</v>
+        <v>8.62290954589844</v>
       </c>
       <c r="H499" t="n">
         <v>120557</v>
@@ -14898,7 +14898,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G501" t="n">
-        <v>8.62291049957275</v>
+        <v>8.62290954589844</v>
       </c>
       <c r="H501" t="n">
         <v>49932</v>
@@ -14956,7 +14956,7 @@
         <v>9.6899995803833</v>
       </c>
       <c r="G503" t="n">
-        <v>8.94603824615479</v>
+        <v>8.94603729248047</v>
       </c>
       <c r="H503" t="n">
         <v>146163</v>
@@ -14985,7 +14985,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G504" t="n">
-        <v>8.86294746398926</v>
+        <v>8.86294841766357</v>
       </c>
       <c r="H504" t="n">
         <v>41942</v>
@@ -15188,7 +15188,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G511" t="n">
-        <v>8.78909015655518</v>
+        <v>8.78909111022949</v>
       </c>
       <c r="H511" t="n">
         <v>113583</v>
@@ -15246,7 +15246,7 @@
         <v>9.8100004196167</v>
       </c>
       <c r="G513" t="n">
-        <v>9.05682563781738</v>
+        <v>9.05682468414307</v>
       </c>
       <c r="H513" t="n">
         <v>107598</v>
@@ -15333,7 +15333,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G516" t="n">
-        <v>8.95527076721191</v>
+        <v>8.9552698135376</v>
       </c>
       <c r="H516" t="n">
         <v>76374</v>
@@ -33087,6 +33087,64 @@
         <v>199828</v>
       </c>
       <c r="I1128" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1129">
+      <c r="A1129" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1129" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C1129" t="n">
+        <v>1.02600002288818</v>
+      </c>
+      <c r="D1129" t="n">
+        <v>1.07799994945526</v>
+      </c>
+      <c r="E1129" t="n">
+        <v>1.02199995517731</v>
+      </c>
+      <c r="F1129" t="n">
+        <v>1.07000005245209</v>
+      </c>
+      <c r="G1129" t="n">
+        <v>1.07000005245209</v>
+      </c>
+      <c r="H1129" t="n">
+        <v>230300</v>
+      </c>
+      <c r="I1129" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1130">
+      <c r="A1130" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1130" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C1130" t="n">
+        <v>1.04999995231628</v>
+      </c>
+      <c r="D1130" t="n">
+        <v>1.04999995231628</v>
+      </c>
+      <c r="E1130" t="n">
+        <v>0.829999983310699</v>
+      </c>
+      <c r="F1130" t="n">
+        <v>0.910000026226044</v>
+      </c>
+      <c r="G1130" t="n">
+        <v>0.910000026226044</v>
+      </c>
+      <c r="H1130" t="n">
+        <v>1635379</v>
+      </c>
+      <c r="I1130" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/TISG.MI.xlsx
+++ b/data/TISG.MI.xlsx
@@ -427,7 +427,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G2" t="n">
-        <v>4.97171258926392</v>
+        <v>4.97171211242676</v>
       </c>
       <c r="H2" t="n">
         <v>20197</v>
@@ -456,7 +456,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G3" t="n">
-        <v>5.12372541427612</v>
+        <v>5.12372493743896</v>
       </c>
       <c r="H3" t="n">
         <v>28276</v>
@@ -485,7 +485,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G4" t="n">
-        <v>5.16843461990356</v>
+        <v>5.16843509674072</v>
       </c>
       <c r="H4" t="n">
         <v>13258</v>
@@ -543,7 +543,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G6" t="n">
-        <v>4.97171258926392</v>
+        <v>4.97171211242676</v>
       </c>
       <c r="H6" t="n">
         <v>18977</v>
@@ -572,7 +572,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G7" t="n">
-        <v>4.94488716125488</v>
+        <v>4.94488668441772</v>
       </c>
       <c r="H7" t="n">
         <v>13883</v>
@@ -688,7 +688,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G11" t="n">
-        <v>4.97171258926392</v>
+        <v>4.97171211242676</v>
       </c>
       <c r="H11" t="n">
         <v>12298</v>
@@ -746,7 +746,7 @@
         <v>5.6100001335144</v>
       </c>
       <c r="G13" t="n">
-        <v>5.01642179489136</v>
+        <v>5.01642227172852</v>
       </c>
       <c r="H13" t="n">
         <v>20247</v>
@@ -833,7 +833,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G16" t="n">
-        <v>5.03430652618408</v>
+        <v>5.03430604934692</v>
       </c>
       <c r="H16" t="n">
         <v>20391</v>
@@ -862,7 +862,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G17" t="n">
-        <v>4.96277046203613</v>
+        <v>4.96277093887329</v>
       </c>
       <c r="H17" t="n">
         <v>9297</v>
@@ -891,7 +891,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G18" t="n">
-        <v>4.9359450340271</v>
+        <v>4.93594455718994</v>
       </c>
       <c r="H18" t="n">
         <v>2331</v>
@@ -920,7 +920,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G19" t="n">
-        <v>4.94488716125488</v>
+        <v>4.94488668441772</v>
       </c>
       <c r="H19" t="n">
         <v>8685</v>
@@ -978,7 +978,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G21" t="n">
-        <v>5.02536392211914</v>
+        <v>5.02536344528198</v>
       </c>
       <c r="H21" t="n">
         <v>16980</v>
@@ -1007,7 +1007,7 @@
         <v>5.6100001335144</v>
       </c>
       <c r="G22" t="n">
-        <v>5.01642179489136</v>
+        <v>5.01642227172852</v>
       </c>
       <c r="H22" t="n">
         <v>57978</v>
@@ -1268,7 +1268,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G31" t="n">
-        <v>4.65874481201172</v>
+        <v>4.65874528884888</v>
       </c>
       <c r="H31" t="n">
         <v>18744</v>
@@ -1297,7 +1297,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G32" t="n">
-        <v>4.68557024002075</v>
+        <v>4.68557071685791</v>
       </c>
       <c r="H32" t="n">
         <v>47444</v>
@@ -1326,7 +1326,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G33" t="n">
-        <v>4.68557024002075</v>
+        <v>4.68557071685791</v>
       </c>
       <c r="H33" t="n">
         <v>11521</v>
@@ -1355,7 +1355,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G34" t="n">
-        <v>4.68557024002075</v>
+        <v>4.68557071685791</v>
       </c>
       <c r="H34" t="n">
         <v>15121</v>
@@ -1442,7 +1442,7 @@
         <v>4.78499984741211</v>
       </c>
       <c r="G37" t="n">
-        <v>4.2787127494812</v>
+        <v>4.27871322631836</v>
       </c>
       <c r="H37" t="n">
         <v>58880</v>
@@ -1703,7 +1703,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G46" t="n">
-        <v>4.41731262207031</v>
+        <v>4.41731309890747</v>
       </c>
       <c r="H46" t="n">
         <v>16689</v>
@@ -1761,7 +1761,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G48" t="n">
-        <v>4.25635862350464</v>
+        <v>4.25635814666748</v>
       </c>
       <c r="H48" t="n">
         <v>16777</v>
@@ -1790,7 +1790,7 @@
         <v>4.84499979019165</v>
       </c>
       <c r="G49" t="n">
-        <v>4.33236408233643</v>
+        <v>4.33236455917358</v>
       </c>
       <c r="H49" t="n">
         <v>18567</v>
@@ -1848,7 +1848,7 @@
         <v>4.84499979019165</v>
       </c>
       <c r="G51" t="n">
-        <v>4.33236408233643</v>
+        <v>4.33236455917358</v>
       </c>
       <c r="H51" t="n">
         <v>13315</v>
@@ -1877,7 +1877,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G52" t="n">
-        <v>4.29212617874146</v>
+        <v>4.2921257019043</v>
       </c>
       <c r="H52" t="n">
         <v>24850</v>
@@ -1906,7 +1906,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G53" t="n">
-        <v>4.32789373397827</v>
+        <v>4.32789421081543</v>
       </c>
       <c r="H53" t="n">
         <v>8833</v>
@@ -1935,7 +1935,7 @@
         <v>4.89499998092651</v>
       </c>
       <c r="G54" t="n">
-        <v>4.37707424163818</v>
+        <v>4.37707471847534</v>
       </c>
       <c r="H54" t="n">
         <v>13462</v>
@@ -2022,7 +2022,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G57" t="n">
-        <v>4.29212617874146</v>
+        <v>4.2921257019043</v>
       </c>
       <c r="H57" t="n">
         <v>9336</v>
@@ -2051,7 +2051,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G58" t="n">
-        <v>4.32789373397827</v>
+        <v>4.32789421081543</v>
       </c>
       <c r="H58" t="n">
         <v>17486</v>
@@ -2080,7 +2080,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G59" t="n">
-        <v>4.51567411422729</v>
+        <v>4.51567459106445</v>
       </c>
       <c r="H59" t="n">
         <v>22808</v>
@@ -2138,7 +2138,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G61" t="n">
-        <v>4.9359450340271</v>
+        <v>4.93594455718994</v>
       </c>
       <c r="H61" t="n">
         <v>80771</v>
@@ -2196,7 +2196,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G63" t="n">
-        <v>4.64980316162109</v>
+        <v>4.64980268478394</v>
       </c>
       <c r="H63" t="n">
         <v>36457</v>
@@ -2254,7 +2254,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G65" t="n">
-        <v>4.65874481201172</v>
+        <v>4.65874528884888</v>
       </c>
       <c r="H65" t="n">
         <v>15144</v>
@@ -2283,7 +2283,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G66" t="n">
-        <v>4.65874481201172</v>
+        <v>4.65874528884888</v>
       </c>
       <c r="H66" t="n">
         <v>14073</v>
@@ -2312,7 +2312,7 @@
         <v>5.25</v>
       </c>
       <c r="G67" t="n">
-        <v>4.69451284408569</v>
+        <v>4.69451236724854</v>
       </c>
       <c r="H67" t="n">
         <v>45084</v>
@@ -2341,7 +2341,7 @@
         <v>5.25</v>
       </c>
       <c r="G68" t="n">
-        <v>4.69451284408569</v>
+        <v>4.69451236724854</v>
       </c>
       <c r="H68" t="n">
         <v>32450</v>
@@ -2370,7 +2370,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G69" t="n">
-        <v>4.64980316162109</v>
+        <v>4.64980268478394</v>
       </c>
       <c r="H69" t="n">
         <v>10853</v>
@@ -2544,7 +2544,7 @@
         <v>4.9850001335144</v>
       </c>
       <c r="G75" t="n">
-        <v>4.45755195617676</v>
+        <v>4.4575514793396</v>
       </c>
       <c r="H75" t="n">
         <v>16465</v>
@@ -2602,7 +2602,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G77" t="n">
-        <v>4.31000995635986</v>
+        <v>4.31000947952271</v>
       </c>
       <c r="H77" t="n">
         <v>12944</v>
@@ -2660,7 +2660,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G79" t="n">
-        <v>4.29212617874146</v>
+        <v>4.2921257019043</v>
       </c>
       <c r="H79" t="n">
         <v>26762</v>
@@ -2689,7 +2689,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G80" t="n">
-        <v>4.29212617874146</v>
+        <v>4.2921257019043</v>
       </c>
       <c r="H80" t="n">
         <v>10522</v>
@@ -2718,7 +2718,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G81" t="n">
-        <v>4.29212617874146</v>
+        <v>4.2921257019043</v>
       </c>
       <c r="H81" t="n">
         <v>38577</v>
@@ -3095,7 +3095,7 @@
         <v>4.75</v>
       </c>
       <c r="G94" t="n">
-        <v>4.2474160194397</v>
+        <v>4.24741649627686</v>
       </c>
       <c r="H94" t="n">
         <v>25723</v>
@@ -3153,7 +3153,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G96" t="n">
-        <v>4.29212617874146</v>
+        <v>4.2921257019043</v>
       </c>
       <c r="H96" t="n">
         <v>8412</v>
@@ -3182,7 +3182,7 @@
         <v>4.89499998092651</v>
       </c>
       <c r="G97" t="n">
-        <v>4.37707424163818</v>
+        <v>4.37707471847534</v>
       </c>
       <c r="H97" t="n">
         <v>41065</v>
@@ -3240,7 +3240,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G99" t="n">
-        <v>4.35471963882446</v>
+        <v>4.3547191619873</v>
       </c>
       <c r="H99" t="n">
         <v>17935</v>
@@ -3269,7 +3269,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G100" t="n">
-        <v>4.37260341644287</v>
+        <v>4.37260293960571</v>
       </c>
       <c r="H100" t="n">
         <v>25467</v>
@@ -3298,7 +3298,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G101" t="n">
-        <v>4.08646154403687</v>
+        <v>4.08646202087402</v>
       </c>
       <c r="H101" t="n">
         <v>93157</v>
@@ -3356,7 +3356,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G103" t="n">
-        <v>3.95233249664307</v>
+        <v>3.95233297348022</v>
       </c>
       <c r="H103" t="n">
         <v>122405</v>
@@ -3385,7 +3385,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G104" t="n">
-        <v>4.01492595672607</v>
+        <v>4.01492547988892</v>
       </c>
       <c r="H104" t="n">
         <v>12994</v>
@@ -3414,7 +3414,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G105" t="n">
-        <v>3.90762233734131</v>
+        <v>3.90762305259705</v>
       </c>
       <c r="H105" t="n">
         <v>8913</v>
@@ -3443,7 +3443,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G106" t="n">
-        <v>3.84502983093262</v>
+        <v>3.84502959251404</v>
       </c>
       <c r="H106" t="n">
         <v>39490</v>
@@ -3472,7 +3472,7 @@
         <v>4.39499998092651</v>
       </c>
       <c r="G107" t="n">
-        <v>3.92997789382935</v>
+        <v>3.92997741699219</v>
       </c>
       <c r="H107" t="n">
         <v>9552</v>
@@ -3501,7 +3501,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G108" t="n">
-        <v>3.82714557647705</v>
+        <v>3.82714581489563</v>
       </c>
       <c r="H108" t="n">
         <v>26268</v>
@@ -3559,7 +3559,7 @@
         <v>4.2649998664856</v>
       </c>
       <c r="G110" t="n">
-        <v>3.81373286247253</v>
+        <v>3.81373262405396</v>
       </c>
       <c r="H110" t="n">
         <v>30391</v>
@@ -3588,7 +3588,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G111" t="n">
-        <v>3.69301676750183</v>
+        <v>3.69301700592041</v>
       </c>
       <c r="H111" t="n">
         <v>51138</v>
@@ -3646,7 +3646,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G113" t="n">
-        <v>3.75561022758484</v>
+        <v>3.75560975074768</v>
       </c>
       <c r="H113" t="n">
         <v>18855</v>
@@ -3675,7 +3675,7 @@
         <v>4.5</v>
       </c>
       <c r="G114" t="n">
-        <v>4.02386856079102</v>
+        <v>4.02386808395386</v>
       </c>
       <c r="H114" t="n">
         <v>51824</v>
@@ -3791,7 +3791,7 @@
         <v>4.78499984741211</v>
       </c>
       <c r="G118" t="n">
-        <v>4.2787127494812</v>
+        <v>4.27871322631836</v>
       </c>
       <c r="H118" t="n">
         <v>22444</v>
@@ -3820,7 +3820,7 @@
         <v>4.75</v>
       </c>
       <c r="G119" t="n">
-        <v>4.2474160194397</v>
+        <v>4.24741649627686</v>
       </c>
       <c r="H119" t="n">
         <v>12242</v>
@@ -3907,7 +3907,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G122" t="n">
-        <v>4.25635862350464</v>
+        <v>4.25635814666748</v>
       </c>
       <c r="H122" t="n">
         <v>6911</v>
@@ -3936,7 +3936,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G123" t="n">
-        <v>4.29212617874146</v>
+        <v>4.2921257019043</v>
       </c>
       <c r="H123" t="n">
         <v>9894</v>
@@ -3965,7 +3965,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G124" t="n">
-        <v>4.29212617874146</v>
+        <v>4.2921257019043</v>
       </c>
       <c r="H124" t="n">
         <v>5737</v>
@@ -3994,7 +3994,7 @@
         <v>4.70499992370605</v>
       </c>
       <c r="G125" t="n">
-        <v>4.20717763900757</v>
+        <v>4.20717716217041</v>
       </c>
       <c r="H125" t="n">
         <v>19005</v>
@@ -4052,7 +4052,7 @@
         <v>4.84499979019165</v>
       </c>
       <c r="G127" t="n">
-        <v>4.33236408233643</v>
+        <v>4.33236455917358</v>
       </c>
       <c r="H127" t="n">
         <v>6687</v>
@@ -4110,7 +4110,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G129" t="n">
-        <v>4.56932544708252</v>
+        <v>4.56932592391968</v>
       </c>
       <c r="H129" t="n">
         <v>34023</v>
@@ -4168,7 +4168,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G131" t="n">
-        <v>4.68557024002075</v>
+        <v>4.68557071685791</v>
       </c>
       <c r="H131" t="n">
         <v>35085</v>
@@ -4226,7 +4226,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G133" t="n">
-        <v>4.82864189147949</v>
+        <v>4.82864141464233</v>
       </c>
       <c r="H133" t="n">
         <v>33414</v>
@@ -4342,7 +4342,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G137" t="n">
-        <v>4.83758354187012</v>
+        <v>4.83758306503296</v>
       </c>
       <c r="H137" t="n">
         <v>18118</v>
@@ -4458,7 +4458,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G141" t="n">
-        <v>4.9359450340271</v>
+        <v>4.93594455718994</v>
       </c>
       <c r="H141" t="n">
         <v>96218</v>
@@ -4487,7 +4487,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G142" t="n">
-        <v>4.86440896987915</v>
+        <v>4.86440944671631</v>
       </c>
       <c r="H142" t="n">
         <v>86543</v>
@@ -4516,7 +4516,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G143" t="n">
-        <v>4.79287433624268</v>
+        <v>4.79287385940552</v>
       </c>
       <c r="H143" t="n">
         <v>12914</v>
@@ -4603,7 +4603,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G146" t="n">
-        <v>5.13266754150391</v>
+        <v>5.13266706466675</v>
       </c>
       <c r="H146" t="n">
         <v>31662</v>
@@ -4632,7 +4632,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G147" t="n">
-        <v>5.02536392211914</v>
+        <v>5.02536344528198</v>
       </c>
       <c r="H147" t="n">
         <v>22523</v>
@@ -4690,7 +4690,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G149" t="n">
-        <v>5.18631935119629</v>
+        <v>5.18631887435913</v>
       </c>
       <c r="H149" t="n">
         <v>94640</v>
@@ -4719,7 +4719,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G150" t="n">
-        <v>5.06113147735596</v>
+        <v>5.06113195419312</v>
       </c>
       <c r="H150" t="n">
         <v>44995</v>
@@ -4748,7 +4748,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G151" t="n">
-        <v>5.18631935119629</v>
+        <v>5.18631887435913</v>
       </c>
       <c r="H151" t="n">
         <v>10180</v>
@@ -4806,7 +4806,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G153" t="n">
-        <v>5.16843461990356</v>
+        <v>5.16843509674072</v>
       </c>
       <c r="H153" t="n">
         <v>62349</v>
@@ -4835,7 +4835,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G154" t="n">
-        <v>5.13266754150391</v>
+        <v>5.13266706466675</v>
       </c>
       <c r="H154" t="n">
         <v>24494</v>
@@ -4893,7 +4893,7 @@
         <v>5.6100001335144</v>
       </c>
       <c r="G156" t="n">
-        <v>5.01642179489136</v>
+        <v>5.01642227172852</v>
       </c>
       <c r="H156" t="n">
         <v>19697</v>
@@ -4951,7 +4951,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G158" t="n">
-        <v>5.02536392211914</v>
+        <v>5.02536344528198</v>
       </c>
       <c r="H158" t="n">
         <v>12170</v>
@@ -4980,7 +4980,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G159" t="n">
-        <v>4.95382833480835</v>
+        <v>4.95382881164551</v>
       </c>
       <c r="H159" t="n">
         <v>26457</v>
@@ -5038,7 +5038,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G161" t="n">
-        <v>5.18631935119629</v>
+        <v>5.18631887435913</v>
       </c>
       <c r="H161" t="n">
         <v>25073</v>
@@ -5241,7 +5241,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G168" t="n">
-        <v>5.12372541427612</v>
+        <v>5.12372493743896</v>
       </c>
       <c r="H168" t="n">
         <v>13445</v>
@@ -5328,7 +5328,7 @@
         <v>5.75</v>
       </c>
       <c r="G171" t="n">
-        <v>5.14160919189453</v>
+        <v>5.14160966873169</v>
       </c>
       <c r="H171" t="n">
         <v>1538</v>
@@ -5357,7 +5357,7 @@
         <v>5.75</v>
       </c>
       <c r="G172" t="n">
-        <v>5.14160919189453</v>
+        <v>5.14160966873169</v>
       </c>
       <c r="H172" t="n">
         <v>9719</v>
@@ -5386,7 +5386,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G173" t="n">
-        <v>5.07901573181152</v>
+        <v>5.07901525497437</v>
       </c>
       <c r="H173" t="n">
         <v>8390</v>
@@ -5415,7 +5415,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G174" t="n">
-        <v>5.03430652618408</v>
+        <v>5.03430604934692</v>
       </c>
       <c r="H174" t="n">
         <v>11363</v>
@@ -5444,7 +5444,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G175" t="n">
-        <v>5.13266754150391</v>
+        <v>5.13266706466675</v>
       </c>
       <c r="H175" t="n">
         <v>26260</v>
@@ -5531,7 +5531,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G178" t="n">
-        <v>5.12372541427612</v>
+        <v>5.12372493743896</v>
       </c>
       <c r="H178" t="n">
         <v>13789</v>
@@ -5705,7 +5705,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G184" t="n">
-        <v>5.67812490463257</v>
+        <v>5.67812442779541</v>
       </c>
       <c r="H184" t="n">
         <v>135409</v>
@@ -5734,7 +5734,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G185" t="n">
-        <v>5.7049503326416</v>
+        <v>5.70495080947876</v>
       </c>
       <c r="H185" t="n">
         <v>70596</v>
@@ -5995,7 +5995,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G194" t="n">
-        <v>6.18781471252441</v>
+        <v>6.18781518936157</v>
       </c>
       <c r="H194" t="n">
         <v>195087</v>
@@ -6140,7 +6140,7 @@
         <v>7.03000020980835</v>
       </c>
       <c r="G199" t="n">
-        <v>6.2861762046814</v>
+        <v>6.28617668151855</v>
       </c>
       <c r="H199" t="n">
         <v>56247</v>
@@ -6285,7 +6285,7 @@
         <v>7.09000015258789</v>
       </c>
       <c r="G204" t="n">
-        <v>6.33982753753662</v>
+        <v>6.33982801437378</v>
       </c>
       <c r="H204" t="n">
         <v>53372</v>
@@ -6314,7 +6314,7 @@
         <v>7.03000020980835</v>
       </c>
       <c r="G205" t="n">
-        <v>6.2861762046814</v>
+        <v>6.28617668151855</v>
       </c>
       <c r="H205" t="n">
         <v>111627</v>
@@ -6372,7 +6372,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G207" t="n">
-        <v>6.65279531478882</v>
+        <v>6.65279483795166</v>
       </c>
       <c r="H207" t="n">
         <v>179183</v>
@@ -6517,7 +6517,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G212" t="n">
-        <v>6.61702728271484</v>
+        <v>6.617027759552</v>
       </c>
       <c r="H212" t="n">
         <v>59738</v>
@@ -6575,7 +6575,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G214" t="n">
-        <v>6.79586601257324</v>
+        <v>6.79586553573608</v>
       </c>
       <c r="H214" t="n">
         <v>155309</v>
@@ -6604,7 +6604,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G215" t="n">
-        <v>6.66173648834229</v>
+        <v>6.66173696517944</v>
       </c>
       <c r="H215" t="n">
         <v>95402</v>
@@ -6865,7 +6865,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G224" t="n">
-        <v>6.66173648834229</v>
+        <v>6.66173696517944</v>
       </c>
       <c r="H224" t="n">
         <v>30693</v>
@@ -7068,7 +7068,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G231" t="n">
-        <v>7.3681492805481</v>
+        <v>7.36814880371094</v>
       </c>
       <c r="H231" t="n">
         <v>165049</v>
@@ -7155,7 +7155,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G234" t="n">
-        <v>7.77947807312012</v>
+        <v>7.77947854995728</v>
       </c>
       <c r="H234" t="n">
         <v>98556</v>
@@ -7184,7 +7184,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G235" t="n">
-        <v>7.6542911529541</v>
+        <v>7.65429162979126</v>
       </c>
       <c r="H235" t="n">
         <v>82796</v>
@@ -7213,7 +7213,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G236" t="n">
-        <v>7.35920667648315</v>
+        <v>7.35920715332031</v>
       </c>
       <c r="H236" t="n">
         <v>253702</v>
@@ -7242,7 +7242,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G237" t="n">
-        <v>7.35920667648315</v>
+        <v>7.35920715332031</v>
       </c>
       <c r="H237" t="n">
         <v>172849</v>
@@ -7271,7 +7271,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G238" t="n">
-        <v>7.73476839065552</v>
+        <v>7.73476791381836</v>
       </c>
       <c r="H238" t="n">
         <v>113648</v>
@@ -7300,7 +7300,7 @@
         <v>8.75</v>
       </c>
       <c r="G239" t="n">
-        <v>7.82418727874756</v>
+        <v>7.82418775558472</v>
       </c>
       <c r="H239" t="n">
         <v>92729</v>
@@ -7329,7 +7329,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G240" t="n">
-        <v>7.86889791488647</v>
+        <v>7.86889696121216</v>
       </c>
       <c r="H240" t="n">
         <v>95722</v>
@@ -7387,7 +7387,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G242" t="n">
-        <v>7.77947807312012</v>
+        <v>7.77947854995728</v>
       </c>
       <c r="H242" t="n">
         <v>118950</v>
@@ -7416,7 +7416,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G243" t="n">
-        <v>7.73476839065552</v>
+        <v>7.73476791381836</v>
       </c>
       <c r="H243" t="n">
         <v>250001</v>
@@ -7445,7 +7445,7 @@
         <v>8.60999965667725</v>
       </c>
       <c r="G244" t="n">
-        <v>7.69899988174438</v>
+        <v>7.69900035858154</v>
       </c>
       <c r="H244" t="n">
         <v>102832</v>
@@ -7474,7 +7474,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G245" t="n">
-        <v>7.77947807312012</v>
+        <v>7.77947854995728</v>
       </c>
       <c r="H245" t="n">
         <v>76403</v>
@@ -7503,7 +7503,7 @@
         <v>8.57999992370605</v>
       </c>
       <c r="G246" t="n">
-        <v>7.67217540740967</v>
+        <v>7.67217445373535</v>
       </c>
       <c r="H246" t="n">
         <v>44155</v>
@@ -7532,7 +7532,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G247" t="n">
-        <v>7.64534902572632</v>
+        <v>7.64534950256348</v>
       </c>
       <c r="H247" t="n">
         <v>105886</v>
@@ -7561,7 +7561,7 @@
         <v>8.63000011444092</v>
       </c>
       <c r="G248" t="n">
-        <v>7.71688461303711</v>
+        <v>7.71688508987427</v>
       </c>
       <c r="H248" t="n">
         <v>49730</v>
@@ -7590,7 +7590,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G249" t="n">
-        <v>7.73476839065552</v>
+        <v>7.73476791381836</v>
       </c>
       <c r="H249" t="n">
         <v>51008</v>
@@ -33145,6 +33145,35 @@
         <v>1635379</v>
       </c>
       <c r="I1130" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1131">
+      <c r="A1131" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1131" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C1131" t="n">
+        <v>0.949999988079071</v>
+      </c>
+      <c r="D1131" t="n">
+        <v>0.970000028610229</v>
+      </c>
+      <c r="E1131" t="n">
+        <v>0.89300000667572</v>
+      </c>
+      <c r="F1131" t="n">
+        <v>0.899999976158142</v>
+      </c>
+      <c r="G1131" t="n">
+        <v>0.899999976158142</v>
+      </c>
+      <c r="H1131" t="n">
+        <v>493789</v>
+      </c>
+      <c r="I1131" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/TISG.MI.xlsx
+++ b/data/TISG.MI.xlsx
@@ -891,7 +891,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G18" t="n">
-        <v>4.93594455718994</v>
+        <v>4.9359450340271</v>
       </c>
       <c r="H18" t="n">
         <v>2331</v>
@@ -978,7 +978,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G21" t="n">
-        <v>5.02536344528198</v>
+        <v>5.02536392211914</v>
       </c>
       <c r="H21" t="n">
         <v>16980</v>
@@ -1094,7 +1094,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G25" t="n">
-        <v>4.64086103439331</v>
+        <v>4.64086151123047</v>
       </c>
       <c r="H25" t="n">
         <v>38675</v>
@@ -1210,7 +1210,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G29" t="n">
-        <v>4.67662906646729</v>
+        <v>4.67662858963013</v>
       </c>
       <c r="H29" t="n">
         <v>41909</v>
@@ -1239,7 +1239,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G30" t="n">
-        <v>4.7123966217041</v>
+        <v>4.71239614486694</v>
       </c>
       <c r="H30" t="n">
         <v>40583</v>
@@ -1268,7 +1268,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G31" t="n">
-        <v>4.65874528884888</v>
+        <v>4.65874481201172</v>
       </c>
       <c r="H31" t="n">
         <v>18744</v>
@@ -1384,7 +1384,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G35" t="n">
-        <v>4.64086103439331</v>
+        <v>4.64086151123047</v>
       </c>
       <c r="H35" t="n">
         <v>71434</v>
@@ -1703,7 +1703,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G46" t="n">
-        <v>4.41731309890747</v>
+        <v>4.41731262207031</v>
       </c>
       <c r="H46" t="n">
         <v>16689</v>
@@ -1761,7 +1761,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G48" t="n">
-        <v>4.25635814666748</v>
+        <v>4.25635862350464</v>
       </c>
       <c r="H48" t="n">
         <v>16777</v>
@@ -1906,7 +1906,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G53" t="n">
-        <v>4.32789421081543</v>
+        <v>4.32789373397827</v>
       </c>
       <c r="H53" t="n">
         <v>8833</v>
@@ -1935,7 +1935,7 @@
         <v>4.89499998092651</v>
       </c>
       <c r="G54" t="n">
-        <v>4.37707471847534</v>
+        <v>4.37707424163818</v>
       </c>
       <c r="H54" t="n">
         <v>13462</v>
@@ -2051,7 +2051,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G58" t="n">
-        <v>4.32789421081543</v>
+        <v>4.32789373397827</v>
       </c>
       <c r="H58" t="n">
         <v>17486</v>
@@ -2138,7 +2138,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G61" t="n">
-        <v>4.93594455718994</v>
+        <v>4.9359450340271</v>
       </c>
       <c r="H61" t="n">
         <v>80771</v>
@@ -2167,7 +2167,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G62" t="n">
-        <v>4.78393173217773</v>
+        <v>4.78393220901489</v>
       </c>
       <c r="H62" t="n">
         <v>83045</v>
@@ -2225,7 +2225,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G64" t="n">
-        <v>4.78393173217773</v>
+        <v>4.78393220901489</v>
       </c>
       <c r="H64" t="n">
         <v>7440</v>
@@ -2254,7 +2254,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G65" t="n">
-        <v>4.65874528884888</v>
+        <v>4.65874481201172</v>
       </c>
       <c r="H65" t="n">
         <v>15144</v>
@@ -2283,7 +2283,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G66" t="n">
-        <v>4.65874528884888</v>
+        <v>4.65874481201172</v>
       </c>
       <c r="H66" t="n">
         <v>14073</v>
@@ -2312,7 +2312,7 @@
         <v>5.25</v>
       </c>
       <c r="G67" t="n">
-        <v>4.69451236724854</v>
+        <v>4.69451284408569</v>
       </c>
       <c r="H67" t="n">
         <v>45084</v>
@@ -2341,7 +2341,7 @@
         <v>5.25</v>
       </c>
       <c r="G68" t="n">
-        <v>4.69451236724854</v>
+        <v>4.69451284408569</v>
       </c>
       <c r="H68" t="n">
         <v>32450</v>
@@ -2544,7 +2544,7 @@
         <v>4.9850001335144</v>
       </c>
       <c r="G75" t="n">
-        <v>4.4575514793396</v>
+        <v>4.45755195617676</v>
       </c>
       <c r="H75" t="n">
         <v>16465</v>
@@ -2602,7 +2602,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G77" t="n">
-        <v>4.31000947952271</v>
+        <v>4.31000995635986</v>
       </c>
       <c r="H77" t="n">
         <v>12944</v>
@@ -2631,7 +2631,7 @@
         <v>4.86499977111816</v>
       </c>
       <c r="G78" t="n">
-        <v>4.35024833679199</v>
+        <v>4.35024785995483</v>
       </c>
       <c r="H78" t="n">
         <v>2266</v>
@@ -2747,7 +2747,7 @@
         <v>4.83500003814697</v>
       </c>
       <c r="G82" t="n">
-        <v>4.32342290878296</v>
+        <v>4.3234224319458</v>
       </c>
       <c r="H82" t="n">
         <v>63420</v>
@@ -2805,7 +2805,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G84" t="n">
-        <v>4.15799713134766</v>
+        <v>4.1579966545105</v>
       </c>
       <c r="H84" t="n">
         <v>33315</v>
@@ -2863,7 +2863,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G86" t="n">
-        <v>4.15799713134766</v>
+        <v>4.1579966545105</v>
       </c>
       <c r="H86" t="n">
         <v>50555</v>
@@ -3095,7 +3095,7 @@
         <v>4.75</v>
       </c>
       <c r="G94" t="n">
-        <v>4.24741649627686</v>
+        <v>4.2474160194397</v>
       </c>
       <c r="H94" t="n">
         <v>25723</v>
@@ -3182,7 +3182,7 @@
         <v>4.89499998092651</v>
       </c>
       <c r="G97" t="n">
-        <v>4.37707471847534</v>
+        <v>4.37707424163818</v>
       </c>
       <c r="H97" t="n">
         <v>41065</v>
@@ -3327,7 +3327,7 @@
         <v>4.46500015258789</v>
       </c>
       <c r="G102" t="n">
-        <v>3.99257159233093</v>
+        <v>3.99257135391235</v>
       </c>
       <c r="H102" t="n">
         <v>73666</v>
@@ -3414,7 +3414,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G105" t="n">
-        <v>3.90762305259705</v>
+        <v>3.90762281417847</v>
       </c>
       <c r="H105" t="n">
         <v>8913</v>
@@ -3472,7 +3472,7 @@
         <v>4.39499998092651</v>
       </c>
       <c r="G107" t="n">
-        <v>3.92997741699219</v>
+        <v>3.92997789382935</v>
       </c>
       <c r="H107" t="n">
         <v>9552</v>
@@ -3704,7 +3704,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G115" t="n">
-        <v>4.15799713134766</v>
+        <v>4.1579966545105</v>
       </c>
       <c r="H115" t="n">
         <v>25167</v>
@@ -3820,7 +3820,7 @@
         <v>4.75</v>
       </c>
       <c r="G119" t="n">
-        <v>4.24741649627686</v>
+        <v>4.2474160194397</v>
       </c>
       <c r="H119" t="n">
         <v>12242</v>
@@ -3878,7 +3878,7 @@
         <v>4.875</v>
       </c>
       <c r="G121" t="n">
-        <v>4.35919046401978</v>
+        <v>4.35919094085693</v>
       </c>
       <c r="H121" t="n">
         <v>12013</v>
@@ -3907,7 +3907,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G122" t="n">
-        <v>4.25635814666748</v>
+        <v>4.25635862350464</v>
       </c>
       <c r="H122" t="n">
         <v>6911</v>
@@ -3994,7 +3994,7 @@
         <v>4.70499992370605</v>
       </c>
       <c r="G125" t="n">
-        <v>4.20717716217041</v>
+        <v>4.20717763900757</v>
       </c>
       <c r="H125" t="n">
         <v>19005</v>
@@ -4023,7 +4023,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G126" t="n">
-        <v>4.27424240112305</v>
+        <v>4.27424192428589</v>
       </c>
       <c r="H126" t="n">
         <v>14120</v>
@@ -4110,7 +4110,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G129" t="n">
-        <v>4.56932592391968</v>
+        <v>4.56932544708252</v>
       </c>
       <c r="H129" t="n">
         <v>34023</v>
@@ -4284,7 +4284,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G135" t="n">
-        <v>4.67662906646729</v>
+        <v>4.67662858963013</v>
       </c>
       <c r="H135" t="n">
         <v>36423</v>
@@ -4342,7 +4342,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G137" t="n">
-        <v>4.83758306503296</v>
+        <v>4.83758354187012</v>
       </c>
       <c r="H137" t="n">
         <v>18118</v>
@@ -4371,7 +4371,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G138" t="n">
-        <v>4.81075763702393</v>
+        <v>4.81075811386108</v>
       </c>
       <c r="H138" t="n">
         <v>13168</v>
@@ -4458,7 +4458,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G141" t="n">
-        <v>4.93594455718994</v>
+        <v>4.9359450340271</v>
       </c>
       <c r="H141" t="n">
         <v>96218</v>
@@ -4632,7 +4632,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G147" t="n">
-        <v>5.02536344528198</v>
+        <v>5.02536392211914</v>
       </c>
       <c r="H147" t="n">
         <v>22523</v>
@@ -4719,7 +4719,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G150" t="n">
-        <v>5.06113195419312</v>
+        <v>5.06113147735596</v>
       </c>
       <c r="H150" t="n">
         <v>44995</v>
@@ -4777,7 +4777,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G152" t="n">
-        <v>5.23102855682373</v>
+        <v>5.23102807998657</v>
       </c>
       <c r="H152" t="n">
         <v>20268</v>
@@ -4951,7 +4951,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G158" t="n">
-        <v>5.02536344528198</v>
+        <v>5.02536392211914</v>
       </c>
       <c r="H158" t="n">
         <v>12170</v>
@@ -5009,7 +5009,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G160" t="n">
-        <v>5.09689950942993</v>
+        <v>5.09689903259277</v>
       </c>
       <c r="H160" t="n">
         <v>13151</v>
@@ -5067,7 +5067,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G162" t="n">
-        <v>5.09689950942993</v>
+        <v>5.09689903259277</v>
       </c>
       <c r="H162" t="n">
         <v>60968</v>
@@ -5125,7 +5125,7 @@
         <v>5.69000005722046</v>
       </c>
       <c r="G164" t="n">
-        <v>5.08795785903931</v>
+        <v>5.08795738220215</v>
       </c>
       <c r="H164" t="n">
         <v>9415</v>
@@ -5183,7 +5183,7 @@
         <v>5.67000007629395</v>
       </c>
       <c r="G166" t="n">
-        <v>5.07007360458374</v>
+        <v>5.0700740814209</v>
       </c>
       <c r="H166" t="n">
         <v>8659</v>
@@ -5328,7 +5328,7 @@
         <v>5.75</v>
       </c>
       <c r="G171" t="n">
-        <v>5.14160966873169</v>
+        <v>5.14160919189453</v>
       </c>
       <c r="H171" t="n">
         <v>1538</v>
@@ -5357,7 +5357,7 @@
         <v>5.75</v>
       </c>
       <c r="G172" t="n">
-        <v>5.14160966873169</v>
+        <v>5.14160919189453</v>
       </c>
       <c r="H172" t="n">
         <v>9719</v>
@@ -5386,7 +5386,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G173" t="n">
-        <v>5.07901525497437</v>
+        <v>5.07901573181152</v>
       </c>
       <c r="H173" t="n">
         <v>8390</v>
@@ -5473,7 +5473,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G176" t="n">
-        <v>5.17737722396851</v>
+        <v>5.17737674713135</v>
       </c>
       <c r="H176" t="n">
         <v>15289</v>
@@ -5647,7 +5647,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G182" t="n">
-        <v>5.52611207962036</v>
+        <v>5.5261116027832</v>
       </c>
       <c r="H182" t="n">
         <v>63401</v>
@@ -5763,7 +5763,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G186" t="n">
-        <v>5.89273118972778</v>
+        <v>5.89273166656494</v>
       </c>
       <c r="H186" t="n">
         <v>120525</v>
@@ -5908,7 +5908,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G191" t="n">
-        <v>6.21464014053345</v>
+        <v>6.21464061737061</v>
       </c>
       <c r="H191" t="n">
         <v>39877</v>
@@ -6024,7 +6024,7 @@
         <v>6.90999984741211</v>
       </c>
       <c r="G195" t="n">
-        <v>6.17887306213379</v>
+        <v>6.17887258529663</v>
       </c>
       <c r="H195" t="n">
         <v>47173</v>
@@ -6140,7 +6140,7 @@
         <v>7.03000020980835</v>
       </c>
       <c r="G199" t="n">
-        <v>6.28617668151855</v>
+        <v>6.2861762046814</v>
       </c>
       <c r="H199" t="n">
         <v>56247</v>
@@ -6169,7 +6169,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G200" t="n">
-        <v>6.21464014053345</v>
+        <v>6.21464061737061</v>
       </c>
       <c r="H200" t="n">
         <v>49278</v>
@@ -6227,7 +6227,7 @@
         <v>7.03999996185303</v>
       </c>
       <c r="G202" t="n">
-        <v>6.29511785507202</v>
+        <v>6.29511737823486</v>
       </c>
       <c r="H202" t="n">
         <v>53850</v>
@@ -6285,7 +6285,7 @@
         <v>7.09000015258789</v>
       </c>
       <c r="G204" t="n">
-        <v>6.33982801437378</v>
+        <v>6.33982753753662</v>
       </c>
       <c r="H204" t="n">
         <v>53372</v>
@@ -6314,7 +6314,7 @@
         <v>7.03000020980835</v>
       </c>
       <c r="G205" t="n">
-        <v>6.28617668151855</v>
+        <v>6.2861762046814</v>
       </c>
       <c r="H205" t="n">
         <v>111627</v>
@@ -6343,7 +6343,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G206" t="n">
-        <v>6.3040599822998</v>
+        <v>6.30406045913696</v>
       </c>
       <c r="H206" t="n">
         <v>51631</v>
@@ -6372,7 +6372,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G207" t="n">
-        <v>6.65279483795166</v>
+        <v>6.65279531478882</v>
       </c>
       <c r="H207" t="n">
         <v>179183</v>
@@ -6488,7 +6488,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G211" t="n">
-        <v>6.67067909240723</v>
+        <v>6.67067861557007</v>
       </c>
       <c r="H211" t="n">
         <v>36745</v>
@@ -6517,7 +6517,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G212" t="n">
-        <v>6.617027759552</v>
+        <v>6.61702728271484</v>
       </c>
       <c r="H212" t="n">
         <v>59738</v>
@@ -6575,7 +6575,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G214" t="n">
-        <v>6.79586553573608</v>
+        <v>6.79586601257324</v>
       </c>
       <c r="H214" t="n">
         <v>155309</v>
@@ -6633,7 +6633,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G216" t="n">
-        <v>6.67067909240723</v>
+        <v>6.67067861557007</v>
       </c>
       <c r="H216" t="n">
         <v>92126</v>
@@ -6749,7 +6749,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G220" t="n">
-        <v>6.60808515548706</v>
+        <v>6.60808563232422</v>
       </c>
       <c r="H220" t="n">
         <v>64845</v>
@@ -7068,7 +7068,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G231" t="n">
-        <v>7.36814880371094</v>
+        <v>7.3681492805481</v>
       </c>
       <c r="H231" t="n">
         <v>165049</v>
@@ -7097,7 +7097,7 @@
         <v>8.56999969482422</v>
       </c>
       <c r="G232" t="n">
-        <v>7.66323280334473</v>
+        <v>7.66323232650757</v>
       </c>
       <c r="H232" t="n">
         <v>214841</v>
@@ -7155,7 +7155,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G234" t="n">
-        <v>7.77947854995728</v>
+        <v>7.77947807312012</v>
       </c>
       <c r="H234" t="n">
         <v>98556</v>
@@ -7358,7 +7358,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G241" t="n">
-        <v>7.94043302536011</v>
+        <v>7.94043350219727</v>
       </c>
       <c r="H241" t="n">
         <v>150011</v>
@@ -7387,7 +7387,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G242" t="n">
-        <v>7.77947854995728</v>
+        <v>7.77947807312012</v>
       </c>
       <c r="H242" t="n">
         <v>118950</v>
@@ -7445,7 +7445,7 @@
         <v>8.60999965667725</v>
       </c>
       <c r="G244" t="n">
-        <v>7.69900035858154</v>
+        <v>7.6990008354187</v>
       </c>
       <c r="H244" t="n">
         <v>102832</v>
@@ -7474,7 +7474,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G245" t="n">
-        <v>7.77947854995728</v>
+        <v>7.77947807312012</v>
       </c>
       <c r="H245" t="n">
         <v>76403</v>
@@ -7503,7 +7503,7 @@
         <v>8.57999992370605</v>
       </c>
       <c r="G246" t="n">
-        <v>7.67217445373535</v>
+        <v>7.67217493057251</v>
       </c>
       <c r="H246" t="n">
         <v>44155</v>
@@ -7532,7 +7532,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G247" t="n">
-        <v>7.64534950256348</v>
+        <v>7.64534997940063</v>
       </c>
       <c r="H247" t="n">
         <v>105886</v>
@@ -7735,7 +7735,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G254" t="n">
-        <v>7.81047344207764</v>
+        <v>7.81047248840332</v>
       </c>
       <c r="H254" t="n">
         <v>152971</v>
@@ -7793,7 +7793,7 @@
         <v>8.52999973297119</v>
       </c>
       <c r="G256" t="n">
-        <v>7.87509870529175</v>
+        <v>7.87509775161743</v>
       </c>
       <c r="H256" t="n">
         <v>99895</v>
@@ -7996,7 +7996,7 @@
         <v>8.60999965667725</v>
       </c>
       <c r="G263" t="n">
-        <v>7.94895553588867</v>
+        <v>7.94895648956299</v>
       </c>
       <c r="H263" t="n">
         <v>76537</v>
@@ -8141,7 +8141,7 @@
         <v>8.60999965667725</v>
       </c>
       <c r="G268" t="n">
-        <v>7.94895553588867</v>
+        <v>7.94895648956299</v>
       </c>
       <c r="H268" t="n">
         <v>61503</v>
@@ -8199,7 +8199,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G270" t="n">
-        <v>7.95818853378296</v>
+        <v>7.95818901062012</v>
       </c>
       <c r="H270" t="n">
         <v>77829</v>
@@ -8460,7 +8460,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G279" t="n">
-        <v>7.42271900177002</v>
+        <v>7.42271852493286</v>
       </c>
       <c r="H279" t="n">
         <v>56062</v>
@@ -8518,7 +8518,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G281" t="n">
-        <v>7.4965763092041</v>
+        <v>7.49657678604126</v>
       </c>
       <c r="H281" t="n">
         <v>39852</v>
@@ -8605,7 +8605,7 @@
         <v>7.80999994277954</v>
       </c>
       <c r="G284" t="n">
-        <v>7.21037769317627</v>
+        <v>7.21037721633911</v>
       </c>
       <c r="H284" t="n">
         <v>117674</v>
@@ -8634,7 +8634,7 @@
         <v>7.71000003814697</v>
       </c>
       <c r="G285" t="n">
-        <v>7.11805534362793</v>
+        <v>7.11805486679077</v>
       </c>
       <c r="H285" t="n">
         <v>57382</v>
@@ -8663,7 +8663,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G286" t="n">
-        <v>7.05342960357666</v>
+        <v>7.0534291267395</v>
       </c>
       <c r="H286" t="n">
         <v>74446</v>
@@ -8692,7 +8692,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G287" t="n">
-        <v>7.1088228225708</v>
+        <v>7.10882234573364</v>
       </c>
       <c r="H287" t="n">
         <v>108157</v>
@@ -8721,7 +8721,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G288" t="n">
-        <v>6.97033929824829</v>
+        <v>6.97033977508545</v>
       </c>
       <c r="H288" t="n">
         <v>37819</v>
@@ -8750,7 +8750,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G289" t="n">
-        <v>6.97033929824829</v>
+        <v>6.97033977508545</v>
       </c>
       <c r="H289" t="n">
         <v>41222</v>
@@ -8953,7 +8953,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G296" t="n">
-        <v>7.30269956588745</v>
+        <v>7.30270004272461</v>
       </c>
       <c r="H296" t="n">
         <v>83813</v>
@@ -8982,7 +8982,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G297" t="n">
-        <v>7.14575147628784</v>
+        <v>7.145751953125</v>
       </c>
       <c r="H297" t="n">
         <v>43493</v>
@@ -9069,7 +9069,7 @@
         <v>7.78999996185303</v>
       </c>
       <c r="G300" t="n">
-        <v>7.19191265106201</v>
+        <v>7.19191312789917</v>
       </c>
       <c r="H300" t="n">
         <v>50892</v>
@@ -9330,7 +9330,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G309" t="n">
-        <v>6.93341064453125</v>
+        <v>6.93341016769409</v>
       </c>
       <c r="H309" t="n">
         <v>19291</v>
@@ -9359,7 +9359,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G310" t="n">
-        <v>6.97033929824829</v>
+        <v>6.97033977508545</v>
       </c>
       <c r="H310" t="n">
         <v>22938</v>
@@ -9388,7 +9388,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G311" t="n">
-        <v>6.87801647186279</v>
+        <v>6.87801694869995</v>
       </c>
       <c r="H311" t="n">
         <v>39307</v>
@@ -9417,7 +9417,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G312" t="n">
-        <v>7.0349645614624</v>
+        <v>7.03496503829956</v>
       </c>
       <c r="H312" t="n">
         <v>19565</v>
@@ -9533,7 +9533,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G316" t="n">
-        <v>6.97033929824829</v>
+        <v>6.97033977508545</v>
       </c>
       <c r="H316" t="n">
         <v>31066</v>
@@ -9591,7 +9591,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G318" t="n">
-        <v>7.42271900177002</v>
+        <v>7.42271852493286</v>
       </c>
       <c r="H318" t="n">
         <v>77225</v>
@@ -9678,7 +9678,7 @@
         <v>7.78999996185303</v>
       </c>
       <c r="G321" t="n">
-        <v>7.19191265106201</v>
+        <v>7.19191312789917</v>
       </c>
       <c r="H321" t="n">
         <v>21141</v>
@@ -9823,7 +9823,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G326" t="n">
-        <v>7.1088228225708</v>
+        <v>7.10882234573364</v>
       </c>
       <c r="H326" t="n">
         <v>18088</v>
@@ -9852,7 +9852,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G327" t="n">
-        <v>6.97033929824829</v>
+        <v>6.97033977508545</v>
       </c>
       <c r="H327" t="n">
         <v>69708</v>
@@ -9881,7 +9881,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G328" t="n">
-        <v>7.13651943206787</v>
+        <v>7.13651990890503</v>
       </c>
       <c r="H328" t="n">
         <v>33278</v>
@@ -9910,7 +9910,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G329" t="n">
-        <v>7.05342960357666</v>
+        <v>7.0534291267395</v>
       </c>
       <c r="H329" t="n">
         <v>17493</v>
@@ -9997,7 +9997,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G332" t="n">
-        <v>6.93341064453125</v>
+        <v>6.93341016769409</v>
       </c>
       <c r="H332" t="n">
         <v>24732</v>
@@ -10026,7 +10026,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G333" t="n">
-        <v>7.05342960357666</v>
+        <v>7.0534291267395</v>
       </c>
       <c r="H333" t="n">
         <v>18353</v>
@@ -10084,7 +10084,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G335" t="n">
-        <v>7.05342960357666</v>
+        <v>7.0534291267395</v>
       </c>
       <c r="H335" t="n">
         <v>11054</v>
@@ -10345,7 +10345,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G344" t="n">
-        <v>6.97033929824829</v>
+        <v>6.97033977508545</v>
       </c>
       <c r="H344" t="n">
         <v>42139</v>
@@ -10403,7 +10403,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G346" t="n">
-        <v>7.14575147628784</v>
+        <v>7.145751953125</v>
       </c>
       <c r="H346" t="n">
         <v>47587</v>
@@ -10461,7 +10461,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G348" t="n">
-        <v>6.90571403503418</v>
+        <v>6.90571355819702</v>
       </c>
       <c r="H348" t="n">
         <v>60152</v>
@@ -10519,7 +10519,7 @@
         <v>7.53999996185303</v>
       </c>
       <c r="G350" t="n">
-        <v>6.96110725402832</v>
+        <v>6.96110677719116</v>
       </c>
       <c r="H350" t="n">
         <v>28852</v>
@@ -10548,7 +10548,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G351" t="n">
-        <v>6.77646255493164</v>
+        <v>6.77646207809448</v>
       </c>
       <c r="H351" t="n">
         <v>58129</v>
@@ -10664,7 +10664,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G355" t="n">
-        <v>6.5364236831665</v>
+        <v>6.53642416000366</v>
       </c>
       <c r="H355" t="n">
         <v>26264</v>
@@ -10809,7 +10809,7 @@
         <v>6.98999977111816</v>
       </c>
       <c r="G360" t="n">
-        <v>6.45333385467529</v>
+        <v>6.45333337783813</v>
       </c>
       <c r="H360" t="n">
         <v>50111</v>
@@ -10867,7 +10867,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G362" t="n">
-        <v>6.64721059799194</v>
+        <v>6.6472110748291</v>
       </c>
       <c r="H362" t="n">
         <v>58993</v>
@@ -10896,7 +10896,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G363" t="n">
-        <v>6.40717315673828</v>
+        <v>6.40717267990112</v>
       </c>
       <c r="H363" t="n">
         <v>39953</v>
@@ -10925,7 +10925,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G364" t="n">
-        <v>6.63797855377197</v>
+        <v>6.63797903060913</v>
       </c>
       <c r="H364" t="n">
         <v>33892</v>
@@ -11012,7 +11012,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G367" t="n">
-        <v>6.48103046417236</v>
+        <v>6.48103094100952</v>
       </c>
       <c r="H367" t="n">
         <v>37646</v>
@@ -11041,7 +11041,7 @@
         <v>7.09000015258789</v>
       </c>
       <c r="G368" t="n">
-        <v>6.54565620422363</v>
+        <v>6.54565668106079</v>
       </c>
       <c r="H368" t="n">
         <v>45957</v>
@@ -11099,7 +11099,7 @@
         <v>7.09000015258789</v>
       </c>
       <c r="G370" t="n">
-        <v>6.54565620422363</v>
+        <v>6.54565668106079</v>
       </c>
       <c r="H370" t="n">
         <v>28684</v>
@@ -11128,7 +11128,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G371" t="n">
-        <v>6.63797855377197</v>
+        <v>6.63797903060913</v>
       </c>
       <c r="H371" t="n">
         <v>24535</v>
@@ -11186,7 +11186,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G373" t="n">
-        <v>6.32408237457275</v>
+        <v>6.32408285140991</v>
       </c>
       <c r="H373" t="n">
         <v>47509</v>
@@ -11215,7 +11215,7 @@
         <v>7</v>
       </c>
       <c r="G374" t="n">
-        <v>6.46256637573242</v>
+        <v>6.46256589889526</v>
       </c>
       <c r="H374" t="n">
         <v>17115</v>
@@ -11476,7 +11476,7 @@
         <v>7.09000015258789</v>
       </c>
       <c r="G383" t="n">
-        <v>6.54565620422363</v>
+        <v>6.54565668106079</v>
       </c>
       <c r="H383" t="n">
         <v>39879</v>
@@ -11592,7 +11592,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G387" t="n">
-        <v>6.6102819442749</v>
+        <v>6.61028146743774</v>
       </c>
       <c r="H387" t="n">
         <v>59425</v>
@@ -11650,7 +11650,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G389" t="n">
-        <v>6.87801647186279</v>
+        <v>6.87801694869995</v>
       </c>
       <c r="H389" t="n">
         <v>91784</v>
@@ -11679,7 +11679,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G390" t="n">
-        <v>7.13651943206787</v>
+        <v>7.13651990890503</v>
       </c>
       <c r="H390" t="n">
         <v>203114</v>
@@ -11766,7 +11766,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G393" t="n">
-        <v>7.30269956588745</v>
+        <v>7.30270004272461</v>
       </c>
       <c r="H393" t="n">
         <v>167425</v>
@@ -11795,7 +11795,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G394" t="n">
-        <v>7.20114517211914</v>
+        <v>7.2011456489563</v>
       </c>
       <c r="H394" t="n">
         <v>191654</v>
@@ -11853,7 +11853,7 @@
         <v>7.86999988555908</v>
       </c>
       <c r="G396" t="n">
-        <v>7.26577091217041</v>
+        <v>7.26577043533325</v>
       </c>
       <c r="H396" t="n">
         <v>50620</v>
@@ -11911,7 +11911,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G398" t="n">
-        <v>7.30269956588745</v>
+        <v>7.30270004272461</v>
       </c>
       <c r="H398" t="n">
         <v>99717</v>
@@ -11940,7 +11940,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G399" t="n">
-        <v>7.36732578277588</v>
+        <v>7.36732530593872</v>
       </c>
       <c r="H399" t="n">
         <v>124059</v>
@@ -11969,7 +11969,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G400" t="n">
-        <v>7.24730587005615</v>
+        <v>7.24730634689331</v>
       </c>
       <c r="H400" t="n">
         <v>72121</v>
@@ -12114,7 +12114,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G405" t="n">
-        <v>7.30269956588745</v>
+        <v>7.30270004272461</v>
       </c>
       <c r="H405" t="n">
         <v>38438</v>
@@ -12636,7 +12636,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G423" t="n">
-        <v>7.40425443649292</v>
+        <v>7.40425491333008</v>
       </c>
       <c r="H423" t="n">
         <v>48656</v>
@@ -12752,7 +12752,7 @@
         <v>8.25</v>
       </c>
       <c r="G427" t="n">
-        <v>7.61659622192383</v>
+        <v>7.61659574508667</v>
       </c>
       <c r="H427" t="n">
         <v>55700</v>
@@ -12810,7 +12810,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G429" t="n">
-        <v>7.90279531478882</v>
+        <v>7.90279626846313</v>
       </c>
       <c r="H429" t="n">
         <v>122032</v>
@@ -12984,7 +12984,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G435" t="n">
-        <v>8.63214206695557</v>
+        <v>8.63214302062988</v>
       </c>
       <c r="H435" t="n">
         <v>236669</v>
@@ -13158,7 +13158,7 @@
         <v>9.6899995803833</v>
       </c>
       <c r="G441" t="n">
-        <v>8.94603729248047</v>
+        <v>8.94603824615479</v>
       </c>
       <c r="H441" t="n">
         <v>85296</v>
@@ -13216,7 +13216,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G443" t="n">
-        <v>8.99219989776611</v>
+        <v>8.9921989440918</v>
       </c>
       <c r="H443" t="n">
         <v>101160</v>
@@ -13477,7 +13477,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G452" t="n">
-        <v>9.52766895294189</v>
+        <v>9.52766799926758</v>
       </c>
       <c r="H452" t="n">
         <v>186778</v>
@@ -13506,7 +13506,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G453" t="n">
-        <v>9.61999130249023</v>
+        <v>9.61999225616455</v>
       </c>
       <c r="H453" t="n">
         <v>106036</v>
@@ -13535,7 +13535,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G454" t="n">
-        <v>9.41688251495361</v>
+        <v>9.4168815612793</v>
       </c>
       <c r="H454" t="n">
         <v>85544</v>
@@ -13593,7 +13593,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G456" t="n">
-        <v>9.25070190429688</v>
+        <v>9.25070285797119</v>
       </c>
       <c r="H456" t="n">
         <v>45013</v>
@@ -13651,7 +13651,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G458" t="n">
-        <v>9.26916599273682</v>
+        <v>9.26916694641113</v>
       </c>
       <c r="H458" t="n">
         <v>73523</v>
@@ -13825,7 +13825,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G464" t="n">
-        <v>9.26916599273682</v>
+        <v>9.26916694641113</v>
       </c>
       <c r="H464" t="n">
         <v>35262</v>
@@ -13883,7 +13883,7 @@
         <v>9.98999977111816</v>
       </c>
       <c r="G466" t="n">
-        <v>9.2230052947998</v>
+        <v>9.22300434112549</v>
       </c>
       <c r="H466" t="n">
         <v>90490</v>
@@ -13999,7 +13999,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G470" t="n">
-        <v>9.61999130249023</v>
+        <v>9.61999225616455</v>
       </c>
       <c r="H470" t="n">
         <v>91656</v>
@@ -14028,7 +14028,7 @@
         <v>10.4799995422363</v>
       </c>
       <c r="G471" t="n">
-        <v>9.67538356781006</v>
+        <v>9.67538452148438</v>
       </c>
       <c r="H471" t="n">
         <v>94908</v>
@@ -14173,7 +14173,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G476" t="n">
-        <v>9.61999130249023</v>
+        <v>9.61999225616455</v>
       </c>
       <c r="H476" t="n">
         <v>55619</v>
@@ -14202,7 +14202,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G477" t="n">
-        <v>9.58306217193604</v>
+        <v>9.58306312561035</v>
       </c>
       <c r="H477" t="n">
         <v>68414</v>
@@ -14289,7 +14289,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G480" t="n">
-        <v>10.2477836608887</v>
+        <v>10.247784614563</v>
       </c>
       <c r="H480" t="n">
         <v>121664</v>
@@ -14318,7 +14318,7 @@
         <v>11.1199998855591</v>
       </c>
       <c r="G481" t="n">
-        <v>10.2662477493286</v>
+        <v>10.2662487030029</v>
       </c>
       <c r="H481" t="n">
         <v>62344</v>
@@ -14347,7 +14347,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G482" t="n">
-        <v>8.93680572509766</v>
+        <v>8.93680667877197</v>
       </c>
       <c r="H482" t="n">
         <v>1087677</v>
@@ -14376,7 +14376,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G483" t="n">
-        <v>9.28763103485107</v>
+        <v>9.28763198852539</v>
       </c>
       <c r="H483" t="n">
         <v>332225</v>
@@ -14405,7 +14405,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G484" t="n">
-        <v>9.21377277374268</v>
+        <v>9.21377182006836</v>
       </c>
       <c r="H484" t="n">
         <v>153862</v>
@@ -14521,7 +14521,7 @@
         <v>9.63000011444092</v>
       </c>
       <c r="G488" t="n">
-        <v>8.89064502716064</v>
+        <v>8.89064407348633</v>
       </c>
       <c r="H488" t="n">
         <v>74178</v>
@@ -14695,7 +14695,7 @@
         <v>9.28999996185303</v>
       </c>
       <c r="G494" t="n">
-        <v>8.57674789428711</v>
+        <v>8.57674884796143</v>
       </c>
       <c r="H494" t="n">
         <v>136448</v>
@@ -14724,7 +14724,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G495" t="n">
-        <v>8.48442649841309</v>
+        <v>8.48442554473877</v>
       </c>
       <c r="H495" t="n">
         <v>37699</v>
@@ -14840,7 +14840,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G499" t="n">
-        <v>8.62290954589844</v>
+        <v>8.62291049957275</v>
       </c>
       <c r="H499" t="n">
         <v>120557</v>
@@ -14898,7 +14898,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G501" t="n">
-        <v>8.62290954589844</v>
+        <v>8.62291049957275</v>
       </c>
       <c r="H501" t="n">
         <v>49932</v>
@@ -14956,7 +14956,7 @@
         <v>9.6899995803833</v>
       </c>
       <c r="G503" t="n">
-        <v>8.94603729248047</v>
+        <v>8.94603824615479</v>
       </c>
       <c r="H503" t="n">
         <v>146163</v>
@@ -14985,7 +14985,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G504" t="n">
-        <v>8.86294841766357</v>
+        <v>8.86294746398926</v>
       </c>
       <c r="H504" t="n">
         <v>41942</v>
@@ -15188,7 +15188,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G511" t="n">
-        <v>8.78909111022949</v>
+        <v>8.78909015655518</v>
       </c>
       <c r="H511" t="n">
         <v>113583</v>
@@ -15246,7 +15246,7 @@
         <v>9.8100004196167</v>
       </c>
       <c r="G513" t="n">
-        <v>9.05682468414307</v>
+        <v>9.05682563781738</v>
       </c>
       <c r="H513" t="n">
         <v>107598</v>
@@ -15333,7 +15333,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G516" t="n">
-        <v>8.9552698135376</v>
+        <v>8.95527076721191</v>
       </c>
       <c r="H516" t="n">
         <v>76374</v>
@@ -33174,6 +33174,35 @@
         <v>493789</v>
       </c>
       <c r="I1131" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1132">
+      <c r="A1132" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1132" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C1132" t="n">
+        <v>0.944999992847443</v>
+      </c>
+      <c r="D1132" t="n">
+        <v>0.944999992847443</v>
+      </c>
+      <c r="E1132" t="n">
+        <v>0.864000022411346</v>
+      </c>
+      <c r="F1132" t="n">
+        <v>0.867999970912933</v>
+      </c>
+      <c r="G1132" t="n">
+        <v>0.867999970912933</v>
+      </c>
+      <c r="H1132" t="n">
+        <v>320376</v>
+      </c>
+      <c r="I1132" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/TISG.MI.xlsx
+++ b/data/TISG.MI.xlsx
@@ -891,7 +891,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G18" t="n">
-        <v>4.9359450340271</v>
+        <v>4.93594455718994</v>
       </c>
       <c r="H18" t="n">
         <v>2331</v>
@@ -978,7 +978,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G21" t="n">
-        <v>5.02536392211914</v>
+        <v>5.02536344528198</v>
       </c>
       <c r="H21" t="n">
         <v>16980</v>
@@ -1094,7 +1094,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G25" t="n">
-        <v>4.64086151123047</v>
+        <v>4.64086103439331</v>
       </c>
       <c r="H25" t="n">
         <v>38675</v>
@@ -1210,7 +1210,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G29" t="n">
-        <v>4.67662858963013</v>
+        <v>4.67662906646729</v>
       </c>
       <c r="H29" t="n">
         <v>41909</v>
@@ -1239,7 +1239,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G30" t="n">
-        <v>4.71239614486694</v>
+        <v>4.7123966217041</v>
       </c>
       <c r="H30" t="n">
         <v>40583</v>
@@ -1268,7 +1268,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G31" t="n">
-        <v>4.65874481201172</v>
+        <v>4.65874528884888</v>
       </c>
       <c r="H31" t="n">
         <v>18744</v>
@@ -1384,7 +1384,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G35" t="n">
-        <v>4.64086151123047</v>
+        <v>4.64086103439331</v>
       </c>
       <c r="H35" t="n">
         <v>71434</v>
@@ -1703,7 +1703,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G46" t="n">
-        <v>4.41731262207031</v>
+        <v>4.41731309890747</v>
       </c>
       <c r="H46" t="n">
         <v>16689</v>
@@ -1761,7 +1761,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G48" t="n">
-        <v>4.25635862350464</v>
+        <v>4.25635814666748</v>
       </c>
       <c r="H48" t="n">
         <v>16777</v>
@@ -1906,7 +1906,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G53" t="n">
-        <v>4.32789373397827</v>
+        <v>4.32789421081543</v>
       </c>
       <c r="H53" t="n">
         <v>8833</v>
@@ -1935,7 +1935,7 @@
         <v>4.89499998092651</v>
       </c>
       <c r="G54" t="n">
-        <v>4.37707424163818</v>
+        <v>4.37707471847534</v>
       </c>
       <c r="H54" t="n">
         <v>13462</v>
@@ -2051,7 +2051,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G58" t="n">
-        <v>4.32789373397827</v>
+        <v>4.32789421081543</v>
       </c>
       <c r="H58" t="n">
         <v>17486</v>
@@ -2138,7 +2138,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G61" t="n">
-        <v>4.9359450340271</v>
+        <v>4.93594455718994</v>
       </c>
       <c r="H61" t="n">
         <v>80771</v>
@@ -2167,7 +2167,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G62" t="n">
-        <v>4.78393220901489</v>
+        <v>4.78393173217773</v>
       </c>
       <c r="H62" t="n">
         <v>83045</v>
@@ -2225,7 +2225,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G64" t="n">
-        <v>4.78393220901489</v>
+        <v>4.78393173217773</v>
       </c>
       <c r="H64" t="n">
         <v>7440</v>
@@ -2254,7 +2254,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G65" t="n">
-        <v>4.65874481201172</v>
+        <v>4.65874528884888</v>
       </c>
       <c r="H65" t="n">
         <v>15144</v>
@@ -2283,7 +2283,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G66" t="n">
-        <v>4.65874481201172</v>
+        <v>4.65874528884888</v>
       </c>
       <c r="H66" t="n">
         <v>14073</v>
@@ -2312,7 +2312,7 @@
         <v>5.25</v>
       </c>
       <c r="G67" t="n">
-        <v>4.69451284408569</v>
+        <v>4.69451236724854</v>
       </c>
       <c r="H67" t="n">
         <v>45084</v>
@@ -2341,7 +2341,7 @@
         <v>5.25</v>
       </c>
       <c r="G68" t="n">
-        <v>4.69451284408569</v>
+        <v>4.69451236724854</v>
       </c>
       <c r="H68" t="n">
         <v>32450</v>
@@ -2544,7 +2544,7 @@
         <v>4.9850001335144</v>
       </c>
       <c r="G75" t="n">
-        <v>4.45755195617676</v>
+        <v>4.4575514793396</v>
       </c>
       <c r="H75" t="n">
         <v>16465</v>
@@ -2602,7 +2602,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G77" t="n">
-        <v>4.31000995635986</v>
+        <v>4.31000947952271</v>
       </c>
       <c r="H77" t="n">
         <v>12944</v>
@@ -2631,7 +2631,7 @@
         <v>4.86499977111816</v>
       </c>
       <c r="G78" t="n">
-        <v>4.35024785995483</v>
+        <v>4.35024833679199</v>
       </c>
       <c r="H78" t="n">
         <v>2266</v>
@@ -2747,7 +2747,7 @@
         <v>4.83500003814697</v>
       </c>
       <c r="G82" t="n">
-        <v>4.3234224319458</v>
+        <v>4.32342290878296</v>
       </c>
       <c r="H82" t="n">
         <v>63420</v>
@@ -2805,7 +2805,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G84" t="n">
-        <v>4.1579966545105</v>
+        <v>4.15799713134766</v>
       </c>
       <c r="H84" t="n">
         <v>33315</v>
@@ -2863,7 +2863,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G86" t="n">
-        <v>4.1579966545105</v>
+        <v>4.15799713134766</v>
       </c>
       <c r="H86" t="n">
         <v>50555</v>
@@ -3095,7 +3095,7 @@
         <v>4.75</v>
       </c>
       <c r="G94" t="n">
-        <v>4.2474160194397</v>
+        <v>4.24741649627686</v>
       </c>
       <c r="H94" t="n">
         <v>25723</v>
@@ -3182,7 +3182,7 @@
         <v>4.89499998092651</v>
       </c>
       <c r="G97" t="n">
-        <v>4.37707424163818</v>
+        <v>4.37707471847534</v>
       </c>
       <c r="H97" t="n">
         <v>41065</v>
@@ -3327,7 +3327,7 @@
         <v>4.46500015258789</v>
       </c>
       <c r="G102" t="n">
-        <v>3.99257135391235</v>
+        <v>3.99257159233093</v>
       </c>
       <c r="H102" t="n">
         <v>73666</v>
@@ -3414,7 +3414,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G105" t="n">
-        <v>3.90762281417847</v>
+        <v>3.90762305259705</v>
       </c>
       <c r="H105" t="n">
         <v>8913</v>
@@ -3472,7 +3472,7 @@
         <v>4.39499998092651</v>
       </c>
       <c r="G107" t="n">
-        <v>3.92997789382935</v>
+        <v>3.92997741699219</v>
       </c>
       <c r="H107" t="n">
         <v>9552</v>
@@ -3704,7 +3704,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G115" t="n">
-        <v>4.1579966545105</v>
+        <v>4.15799713134766</v>
       </c>
       <c r="H115" t="n">
         <v>25167</v>
@@ -3820,7 +3820,7 @@
         <v>4.75</v>
       </c>
       <c r="G119" t="n">
-        <v>4.2474160194397</v>
+        <v>4.24741649627686</v>
       </c>
       <c r="H119" t="n">
         <v>12242</v>
@@ -3878,7 +3878,7 @@
         <v>4.875</v>
       </c>
       <c r="G121" t="n">
-        <v>4.35919094085693</v>
+        <v>4.35919046401978</v>
       </c>
       <c r="H121" t="n">
         <v>12013</v>
@@ -3907,7 +3907,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G122" t="n">
-        <v>4.25635862350464</v>
+        <v>4.25635814666748</v>
       </c>
       <c r="H122" t="n">
         <v>6911</v>
@@ -3994,7 +3994,7 @@
         <v>4.70499992370605</v>
       </c>
       <c r="G125" t="n">
-        <v>4.20717763900757</v>
+        <v>4.20717716217041</v>
       </c>
       <c r="H125" t="n">
         <v>19005</v>
@@ -4023,7 +4023,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G126" t="n">
-        <v>4.27424192428589</v>
+        <v>4.27424240112305</v>
       </c>
       <c r="H126" t="n">
         <v>14120</v>
@@ -4110,7 +4110,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G129" t="n">
-        <v>4.56932544708252</v>
+        <v>4.56932592391968</v>
       </c>
       <c r="H129" t="n">
         <v>34023</v>
@@ -4284,7 +4284,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G135" t="n">
-        <v>4.67662858963013</v>
+        <v>4.67662906646729</v>
       </c>
       <c r="H135" t="n">
         <v>36423</v>
@@ -4342,7 +4342,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G137" t="n">
-        <v>4.83758354187012</v>
+        <v>4.83758306503296</v>
       </c>
       <c r="H137" t="n">
         <v>18118</v>
@@ -4371,7 +4371,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G138" t="n">
-        <v>4.81075811386108</v>
+        <v>4.81075763702393</v>
       </c>
       <c r="H138" t="n">
         <v>13168</v>
@@ -4458,7 +4458,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G141" t="n">
-        <v>4.9359450340271</v>
+        <v>4.93594455718994</v>
       </c>
       <c r="H141" t="n">
         <v>96218</v>
@@ -4632,7 +4632,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G147" t="n">
-        <v>5.02536392211914</v>
+        <v>5.02536344528198</v>
       </c>
       <c r="H147" t="n">
         <v>22523</v>
@@ -4719,7 +4719,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G150" t="n">
-        <v>5.06113147735596</v>
+        <v>5.06113195419312</v>
       </c>
       <c r="H150" t="n">
         <v>44995</v>
@@ -4777,7 +4777,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G152" t="n">
-        <v>5.23102807998657</v>
+        <v>5.23102855682373</v>
       </c>
       <c r="H152" t="n">
         <v>20268</v>
@@ -4951,7 +4951,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G158" t="n">
-        <v>5.02536392211914</v>
+        <v>5.02536344528198</v>
       </c>
       <c r="H158" t="n">
         <v>12170</v>
@@ -5009,7 +5009,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G160" t="n">
-        <v>5.09689903259277</v>
+        <v>5.09689950942993</v>
       </c>
       <c r="H160" t="n">
         <v>13151</v>
@@ -5067,7 +5067,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G162" t="n">
-        <v>5.09689903259277</v>
+        <v>5.09689950942993</v>
       </c>
       <c r="H162" t="n">
         <v>60968</v>
@@ -5125,7 +5125,7 @@
         <v>5.69000005722046</v>
       </c>
       <c r="G164" t="n">
-        <v>5.08795738220215</v>
+        <v>5.08795785903931</v>
       </c>
       <c r="H164" t="n">
         <v>9415</v>
@@ -5183,7 +5183,7 @@
         <v>5.67000007629395</v>
       </c>
       <c r="G166" t="n">
-        <v>5.0700740814209</v>
+        <v>5.07007360458374</v>
       </c>
       <c r="H166" t="n">
         <v>8659</v>
@@ -5328,7 +5328,7 @@
         <v>5.75</v>
       </c>
       <c r="G171" t="n">
-        <v>5.14160919189453</v>
+        <v>5.14160966873169</v>
       </c>
       <c r="H171" t="n">
         <v>1538</v>
@@ -5357,7 +5357,7 @@
         <v>5.75</v>
       </c>
       <c r="G172" t="n">
-        <v>5.14160919189453</v>
+        <v>5.14160966873169</v>
       </c>
       <c r="H172" t="n">
         <v>9719</v>
@@ -5386,7 +5386,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G173" t="n">
-        <v>5.07901573181152</v>
+        <v>5.07901525497437</v>
       </c>
       <c r="H173" t="n">
         <v>8390</v>
@@ -5473,7 +5473,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G176" t="n">
-        <v>5.17737674713135</v>
+        <v>5.17737722396851</v>
       </c>
       <c r="H176" t="n">
         <v>15289</v>
@@ -5647,7 +5647,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G182" t="n">
-        <v>5.5261116027832</v>
+        <v>5.52611207962036</v>
       </c>
       <c r="H182" t="n">
         <v>63401</v>
@@ -5763,7 +5763,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G186" t="n">
-        <v>5.89273166656494</v>
+        <v>5.89273118972778</v>
       </c>
       <c r="H186" t="n">
         <v>120525</v>
@@ -5908,7 +5908,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G191" t="n">
-        <v>6.21464061737061</v>
+        <v>6.21464014053345</v>
       </c>
       <c r="H191" t="n">
         <v>39877</v>
@@ -6024,7 +6024,7 @@
         <v>6.90999984741211</v>
       </c>
       <c r="G195" t="n">
-        <v>6.17887258529663</v>
+        <v>6.17887306213379</v>
       </c>
       <c r="H195" t="n">
         <v>47173</v>
@@ -6140,7 +6140,7 @@
         <v>7.03000020980835</v>
       </c>
       <c r="G199" t="n">
-        <v>6.2861762046814</v>
+        <v>6.28617668151855</v>
       </c>
       <c r="H199" t="n">
         <v>56247</v>
@@ -6169,7 +6169,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G200" t="n">
-        <v>6.21464061737061</v>
+        <v>6.21464014053345</v>
       </c>
       <c r="H200" t="n">
         <v>49278</v>
@@ -6227,7 +6227,7 @@
         <v>7.03999996185303</v>
       </c>
       <c r="G202" t="n">
-        <v>6.29511737823486</v>
+        <v>6.29511785507202</v>
       </c>
       <c r="H202" t="n">
         <v>53850</v>
@@ -6285,7 +6285,7 @@
         <v>7.09000015258789</v>
       </c>
       <c r="G204" t="n">
-        <v>6.33982753753662</v>
+        <v>6.33982801437378</v>
       </c>
       <c r="H204" t="n">
         <v>53372</v>
@@ -6314,7 +6314,7 @@
         <v>7.03000020980835</v>
       </c>
       <c r="G205" t="n">
-        <v>6.2861762046814</v>
+        <v>6.28617668151855</v>
       </c>
       <c r="H205" t="n">
         <v>111627</v>
@@ -6343,7 +6343,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G206" t="n">
-        <v>6.30406045913696</v>
+        <v>6.3040599822998</v>
       </c>
       <c r="H206" t="n">
         <v>51631</v>
@@ -6372,7 +6372,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G207" t="n">
-        <v>6.65279531478882</v>
+        <v>6.65279483795166</v>
       </c>
       <c r="H207" t="n">
         <v>179183</v>
@@ -6488,7 +6488,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G211" t="n">
-        <v>6.67067861557007</v>
+        <v>6.67067909240723</v>
       </c>
       <c r="H211" t="n">
         <v>36745</v>
@@ -6517,7 +6517,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G212" t="n">
-        <v>6.61702728271484</v>
+        <v>6.617027759552</v>
       </c>
       <c r="H212" t="n">
         <v>59738</v>
@@ -6575,7 +6575,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G214" t="n">
-        <v>6.79586601257324</v>
+        <v>6.79586553573608</v>
       </c>
       <c r="H214" t="n">
         <v>155309</v>
@@ -6633,7 +6633,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G216" t="n">
-        <v>6.67067861557007</v>
+        <v>6.67067909240723</v>
       </c>
       <c r="H216" t="n">
         <v>92126</v>
@@ -6749,7 +6749,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G220" t="n">
-        <v>6.60808563232422</v>
+        <v>6.60808515548706</v>
       </c>
       <c r="H220" t="n">
         <v>64845</v>
@@ -7068,7 +7068,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G231" t="n">
-        <v>7.3681492805481</v>
+        <v>7.36814880371094</v>
       </c>
       <c r="H231" t="n">
         <v>165049</v>
@@ -7097,7 +7097,7 @@
         <v>8.56999969482422</v>
       </c>
       <c r="G232" t="n">
-        <v>7.66323232650757</v>
+        <v>7.66323280334473</v>
       </c>
       <c r="H232" t="n">
         <v>214841</v>
@@ -7155,7 +7155,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G234" t="n">
-        <v>7.77947807312012</v>
+        <v>7.77947854995728</v>
       </c>
       <c r="H234" t="n">
         <v>98556</v>
@@ -7358,7 +7358,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G241" t="n">
-        <v>7.94043350219727</v>
+        <v>7.94043302536011</v>
       </c>
       <c r="H241" t="n">
         <v>150011</v>
@@ -7387,7 +7387,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G242" t="n">
-        <v>7.77947807312012</v>
+        <v>7.77947854995728</v>
       </c>
       <c r="H242" t="n">
         <v>118950</v>
@@ -7445,7 +7445,7 @@
         <v>8.60999965667725</v>
       </c>
       <c r="G244" t="n">
-        <v>7.6990008354187</v>
+        <v>7.69900035858154</v>
       </c>
       <c r="H244" t="n">
         <v>102832</v>
@@ -7474,7 +7474,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G245" t="n">
-        <v>7.77947807312012</v>
+        <v>7.77947854995728</v>
       </c>
       <c r="H245" t="n">
         <v>76403</v>
@@ -7503,7 +7503,7 @@
         <v>8.57999992370605</v>
       </c>
       <c r="G246" t="n">
-        <v>7.67217493057251</v>
+        <v>7.67217445373535</v>
       </c>
       <c r="H246" t="n">
         <v>44155</v>
@@ -7532,7 +7532,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G247" t="n">
-        <v>7.64534997940063</v>
+        <v>7.64534950256348</v>
       </c>
       <c r="H247" t="n">
         <v>105886</v>
@@ -7735,7 +7735,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G254" t="n">
-        <v>7.81047248840332</v>
+        <v>7.81047344207764</v>
       </c>
       <c r="H254" t="n">
         <v>152971</v>
@@ -7793,7 +7793,7 @@
         <v>8.52999973297119</v>
       </c>
       <c r="G256" t="n">
-        <v>7.87509775161743</v>
+        <v>7.87509870529175</v>
       </c>
       <c r="H256" t="n">
         <v>99895</v>
@@ -7996,7 +7996,7 @@
         <v>8.60999965667725</v>
       </c>
       <c r="G263" t="n">
-        <v>7.94895648956299</v>
+        <v>7.94895553588867</v>
       </c>
       <c r="H263" t="n">
         <v>76537</v>
@@ -8141,7 +8141,7 @@
         <v>8.60999965667725</v>
       </c>
       <c r="G268" t="n">
-        <v>7.94895648956299</v>
+        <v>7.94895553588867</v>
       </c>
       <c r="H268" t="n">
         <v>61503</v>
@@ -8199,7 +8199,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G270" t="n">
-        <v>7.95818901062012</v>
+        <v>7.95818853378296</v>
       </c>
       <c r="H270" t="n">
         <v>77829</v>
@@ -8460,7 +8460,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G279" t="n">
-        <v>7.42271852493286</v>
+        <v>7.42271900177002</v>
       </c>
       <c r="H279" t="n">
         <v>56062</v>
@@ -8518,7 +8518,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G281" t="n">
-        <v>7.49657678604126</v>
+        <v>7.4965763092041</v>
       </c>
       <c r="H281" t="n">
         <v>39852</v>
@@ -8605,7 +8605,7 @@
         <v>7.80999994277954</v>
       </c>
       <c r="G284" t="n">
-        <v>7.21037721633911</v>
+        <v>7.21037769317627</v>
       </c>
       <c r="H284" t="n">
         <v>117674</v>
@@ -8634,7 +8634,7 @@
         <v>7.71000003814697</v>
       </c>
       <c r="G285" t="n">
-        <v>7.11805486679077</v>
+        <v>7.11805534362793</v>
       </c>
       <c r="H285" t="n">
         <v>57382</v>
@@ -8663,7 +8663,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G286" t="n">
-        <v>7.0534291267395</v>
+        <v>7.05342960357666</v>
       </c>
       <c r="H286" t="n">
         <v>74446</v>
@@ -8692,7 +8692,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G287" t="n">
-        <v>7.10882234573364</v>
+        <v>7.1088228225708</v>
       </c>
       <c r="H287" t="n">
         <v>108157</v>
@@ -8721,7 +8721,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G288" t="n">
-        <v>6.97033977508545</v>
+        <v>6.97033929824829</v>
       </c>
       <c r="H288" t="n">
         <v>37819</v>
@@ -8750,7 +8750,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G289" t="n">
-        <v>6.97033977508545</v>
+        <v>6.97033929824829</v>
       </c>
       <c r="H289" t="n">
         <v>41222</v>
@@ -8953,7 +8953,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G296" t="n">
-        <v>7.30270004272461</v>
+        <v>7.30269956588745</v>
       </c>
       <c r="H296" t="n">
         <v>83813</v>
@@ -8982,7 +8982,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G297" t="n">
-        <v>7.145751953125</v>
+        <v>7.14575147628784</v>
       </c>
       <c r="H297" t="n">
         <v>43493</v>
@@ -9069,7 +9069,7 @@
         <v>7.78999996185303</v>
       </c>
       <c r="G300" t="n">
-        <v>7.19191312789917</v>
+        <v>7.19191265106201</v>
       </c>
       <c r="H300" t="n">
         <v>50892</v>
@@ -9330,7 +9330,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G309" t="n">
-        <v>6.93341016769409</v>
+        <v>6.93341064453125</v>
       </c>
       <c r="H309" t="n">
         <v>19291</v>
@@ -9359,7 +9359,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G310" t="n">
-        <v>6.97033977508545</v>
+        <v>6.97033929824829</v>
       </c>
       <c r="H310" t="n">
         <v>22938</v>
@@ -9388,7 +9388,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G311" t="n">
-        <v>6.87801694869995</v>
+        <v>6.87801647186279</v>
       </c>
       <c r="H311" t="n">
         <v>39307</v>
@@ -9417,7 +9417,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G312" t="n">
-        <v>7.03496503829956</v>
+        <v>7.0349645614624</v>
       </c>
       <c r="H312" t="n">
         <v>19565</v>
@@ -9533,7 +9533,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G316" t="n">
-        <v>6.97033977508545</v>
+        <v>6.97033929824829</v>
       </c>
       <c r="H316" t="n">
         <v>31066</v>
@@ -9591,7 +9591,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G318" t="n">
-        <v>7.42271852493286</v>
+        <v>7.42271900177002</v>
       </c>
       <c r="H318" t="n">
         <v>77225</v>
@@ -9678,7 +9678,7 @@
         <v>7.78999996185303</v>
       </c>
       <c r="G321" t="n">
-        <v>7.19191312789917</v>
+        <v>7.19191265106201</v>
       </c>
       <c r="H321" t="n">
         <v>21141</v>
@@ -9823,7 +9823,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G326" t="n">
-        <v>7.10882234573364</v>
+        <v>7.1088228225708</v>
       </c>
       <c r="H326" t="n">
         <v>18088</v>
@@ -9852,7 +9852,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G327" t="n">
-        <v>6.97033977508545</v>
+        <v>6.97033929824829</v>
       </c>
       <c r="H327" t="n">
         <v>69708</v>
@@ -9881,7 +9881,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G328" t="n">
-        <v>7.13651990890503</v>
+        <v>7.13651943206787</v>
       </c>
       <c r="H328" t="n">
         <v>33278</v>
@@ -9910,7 +9910,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G329" t="n">
-        <v>7.0534291267395</v>
+        <v>7.05342960357666</v>
       </c>
       <c r="H329" t="n">
         <v>17493</v>
@@ -9997,7 +9997,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G332" t="n">
-        <v>6.93341016769409</v>
+        <v>6.93341064453125</v>
       </c>
       <c r="H332" t="n">
         <v>24732</v>
@@ -10026,7 +10026,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G333" t="n">
-        <v>7.0534291267395</v>
+        <v>7.05342960357666</v>
       </c>
       <c r="H333" t="n">
         <v>18353</v>
@@ -10084,7 +10084,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G335" t="n">
-        <v>7.0534291267395</v>
+        <v>7.05342960357666</v>
       </c>
       <c r="H335" t="n">
         <v>11054</v>
@@ -10345,7 +10345,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G344" t="n">
-        <v>6.97033977508545</v>
+        <v>6.97033929824829</v>
       </c>
       <c r="H344" t="n">
         <v>42139</v>
@@ -10403,7 +10403,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G346" t="n">
-        <v>7.145751953125</v>
+        <v>7.14575147628784</v>
       </c>
       <c r="H346" t="n">
         <v>47587</v>
@@ -10461,7 +10461,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G348" t="n">
-        <v>6.90571355819702</v>
+        <v>6.90571403503418</v>
       </c>
       <c r="H348" t="n">
         <v>60152</v>
@@ -10519,7 +10519,7 @@
         <v>7.53999996185303</v>
       </c>
       <c r="G350" t="n">
-        <v>6.96110677719116</v>
+        <v>6.96110725402832</v>
       </c>
       <c r="H350" t="n">
         <v>28852</v>
@@ -10548,7 +10548,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G351" t="n">
-        <v>6.77646207809448</v>
+        <v>6.77646255493164</v>
       </c>
       <c r="H351" t="n">
         <v>58129</v>
@@ -10664,7 +10664,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G355" t="n">
-        <v>6.53642416000366</v>
+        <v>6.5364236831665</v>
       </c>
       <c r="H355" t="n">
         <v>26264</v>
@@ -10809,7 +10809,7 @@
         <v>6.98999977111816</v>
       </c>
       <c r="G360" t="n">
-        <v>6.45333337783813</v>
+        <v>6.45333385467529</v>
       </c>
       <c r="H360" t="n">
         <v>50111</v>
@@ -10867,7 +10867,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G362" t="n">
-        <v>6.6472110748291</v>
+        <v>6.64721059799194</v>
       </c>
       <c r="H362" t="n">
         <v>58993</v>
@@ -10896,7 +10896,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G363" t="n">
-        <v>6.40717267990112</v>
+        <v>6.40717315673828</v>
       </c>
       <c r="H363" t="n">
         <v>39953</v>
@@ -10925,7 +10925,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G364" t="n">
-        <v>6.63797903060913</v>
+        <v>6.63797855377197</v>
       </c>
       <c r="H364" t="n">
         <v>33892</v>
@@ -11012,7 +11012,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G367" t="n">
-        <v>6.48103094100952</v>
+        <v>6.48103046417236</v>
       </c>
       <c r="H367" t="n">
         <v>37646</v>
@@ -11041,7 +11041,7 @@
         <v>7.09000015258789</v>
       </c>
       <c r="G368" t="n">
-        <v>6.54565668106079</v>
+        <v>6.54565620422363</v>
       </c>
       <c r="H368" t="n">
         <v>45957</v>
@@ -11099,7 +11099,7 @@
         <v>7.09000015258789</v>
       </c>
       <c r="G370" t="n">
-        <v>6.54565668106079</v>
+        <v>6.54565620422363</v>
       </c>
       <c r="H370" t="n">
         <v>28684</v>
@@ -11128,7 +11128,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G371" t="n">
-        <v>6.63797903060913</v>
+        <v>6.63797855377197</v>
       </c>
       <c r="H371" t="n">
         <v>24535</v>
@@ -11186,7 +11186,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G373" t="n">
-        <v>6.32408285140991</v>
+        <v>6.32408237457275</v>
       </c>
       <c r="H373" t="n">
         <v>47509</v>
@@ -11215,7 +11215,7 @@
         <v>7</v>
       </c>
       <c r="G374" t="n">
-        <v>6.46256589889526</v>
+        <v>6.46256637573242</v>
       </c>
       <c r="H374" t="n">
         <v>17115</v>
@@ -11476,7 +11476,7 @@
         <v>7.09000015258789</v>
       </c>
       <c r="G383" t="n">
-        <v>6.54565668106079</v>
+        <v>6.54565620422363</v>
       </c>
       <c r="H383" t="n">
         <v>39879</v>
@@ -11592,7 +11592,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G387" t="n">
-        <v>6.61028146743774</v>
+        <v>6.6102819442749</v>
       </c>
       <c r="H387" t="n">
         <v>59425</v>
@@ -11650,7 +11650,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G389" t="n">
-        <v>6.87801694869995</v>
+        <v>6.87801647186279</v>
       </c>
       <c r="H389" t="n">
         <v>91784</v>
@@ -11679,7 +11679,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G390" t="n">
-        <v>7.13651990890503</v>
+        <v>7.13651943206787</v>
       </c>
       <c r="H390" t="n">
         <v>203114</v>
@@ -11766,7 +11766,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G393" t="n">
-        <v>7.30270004272461</v>
+        <v>7.30269956588745</v>
       </c>
       <c r="H393" t="n">
         <v>167425</v>
@@ -11795,7 +11795,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G394" t="n">
-        <v>7.2011456489563</v>
+        <v>7.20114517211914</v>
       </c>
       <c r="H394" t="n">
         <v>191654</v>
@@ -11853,7 +11853,7 @@
         <v>7.86999988555908</v>
       </c>
       <c r="G396" t="n">
-        <v>7.26577043533325</v>
+        <v>7.26577091217041</v>
       </c>
       <c r="H396" t="n">
         <v>50620</v>
@@ -11911,7 +11911,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G398" t="n">
-        <v>7.30270004272461</v>
+        <v>7.30269956588745</v>
       </c>
       <c r="H398" t="n">
         <v>99717</v>
@@ -11940,7 +11940,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G399" t="n">
-        <v>7.36732530593872</v>
+        <v>7.36732578277588</v>
       </c>
       <c r="H399" t="n">
         <v>124059</v>
@@ -11969,7 +11969,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G400" t="n">
-        <v>7.24730634689331</v>
+        <v>7.24730587005615</v>
       </c>
       <c r="H400" t="n">
         <v>72121</v>
@@ -12114,7 +12114,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G405" t="n">
-        <v>7.30270004272461</v>
+        <v>7.30269956588745</v>
       </c>
       <c r="H405" t="n">
         <v>38438</v>
@@ -12636,7 +12636,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G423" t="n">
-        <v>7.40425491333008</v>
+        <v>7.40425443649292</v>
       </c>
       <c r="H423" t="n">
         <v>48656</v>
@@ -12752,7 +12752,7 @@
         <v>8.25</v>
       </c>
       <c r="G427" t="n">
-        <v>7.61659574508667</v>
+        <v>7.61659622192383</v>
       </c>
       <c r="H427" t="n">
         <v>55700</v>
@@ -12810,7 +12810,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G429" t="n">
-        <v>7.90279626846313</v>
+        <v>7.90279531478882</v>
       </c>
       <c r="H429" t="n">
         <v>122032</v>
@@ -12984,7 +12984,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G435" t="n">
-        <v>8.63214302062988</v>
+        <v>8.63214206695557</v>
       </c>
       <c r="H435" t="n">
         <v>236669</v>
@@ -13158,7 +13158,7 @@
         <v>9.6899995803833</v>
       </c>
       <c r="G441" t="n">
-        <v>8.94603824615479</v>
+        <v>8.94603729248047</v>
       </c>
       <c r="H441" t="n">
         <v>85296</v>
@@ -13216,7 +13216,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G443" t="n">
-        <v>8.9921989440918</v>
+        <v>8.99219989776611</v>
       </c>
       <c r="H443" t="n">
         <v>101160</v>
@@ -13477,7 +13477,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G452" t="n">
-        <v>9.52766799926758</v>
+        <v>9.52766895294189</v>
       </c>
       <c r="H452" t="n">
         <v>186778</v>
@@ -13506,7 +13506,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G453" t="n">
-        <v>9.61999225616455</v>
+        <v>9.61999130249023</v>
       </c>
       <c r="H453" t="n">
         <v>106036</v>
@@ -13535,7 +13535,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G454" t="n">
-        <v>9.4168815612793</v>
+        <v>9.41688251495361</v>
       </c>
       <c r="H454" t="n">
         <v>85544</v>
@@ -13593,7 +13593,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G456" t="n">
-        <v>9.25070285797119</v>
+        <v>9.25070190429688</v>
       </c>
       <c r="H456" t="n">
         <v>45013</v>
@@ -13651,7 +13651,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G458" t="n">
-        <v>9.26916694641113</v>
+        <v>9.26916599273682</v>
       </c>
       <c r="H458" t="n">
         <v>73523</v>
@@ -13825,7 +13825,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G464" t="n">
-        <v>9.26916694641113</v>
+        <v>9.26916599273682</v>
       </c>
       <c r="H464" t="n">
         <v>35262</v>
@@ -13883,7 +13883,7 @@
         <v>9.98999977111816</v>
       </c>
       <c r="G466" t="n">
-        <v>9.22300434112549</v>
+        <v>9.2230052947998</v>
       </c>
       <c r="H466" t="n">
         <v>90490</v>
@@ -13999,7 +13999,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G470" t="n">
-        <v>9.61999225616455</v>
+        <v>9.61999130249023</v>
       </c>
       <c r="H470" t="n">
         <v>91656</v>
@@ -14028,7 +14028,7 @@
         <v>10.4799995422363</v>
       </c>
       <c r="G471" t="n">
-        <v>9.67538452148438</v>
+        <v>9.67538356781006</v>
       </c>
       <c r="H471" t="n">
         <v>94908</v>
@@ -14173,7 +14173,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G476" t="n">
-        <v>9.61999225616455</v>
+        <v>9.61999130249023</v>
       </c>
       <c r="H476" t="n">
         <v>55619</v>
@@ -14202,7 +14202,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G477" t="n">
-        <v>9.58306312561035</v>
+        <v>9.58306217193604</v>
       </c>
       <c r="H477" t="n">
         <v>68414</v>
@@ -14289,7 +14289,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G480" t="n">
-        <v>10.247784614563</v>
+        <v>10.2477836608887</v>
       </c>
       <c r="H480" t="n">
         <v>121664</v>
@@ -14318,7 +14318,7 @@
         <v>11.1199998855591</v>
       </c>
       <c r="G481" t="n">
-        <v>10.2662487030029</v>
+        <v>10.2662477493286</v>
       </c>
       <c r="H481" t="n">
         <v>62344</v>
@@ -14347,7 +14347,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G482" t="n">
-        <v>8.93680667877197</v>
+        <v>8.93680572509766</v>
       </c>
       <c r="H482" t="n">
         <v>1087677</v>
@@ -14376,7 +14376,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G483" t="n">
-        <v>9.28763198852539</v>
+        <v>9.28763103485107</v>
       </c>
       <c r="H483" t="n">
         <v>332225</v>
@@ -14405,7 +14405,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G484" t="n">
-        <v>9.21377182006836</v>
+        <v>9.21377277374268</v>
       </c>
       <c r="H484" t="n">
         <v>153862</v>
@@ -14521,7 +14521,7 @@
         <v>9.63000011444092</v>
       </c>
       <c r="G488" t="n">
-        <v>8.89064407348633</v>
+        <v>8.89064502716064</v>
       </c>
       <c r="H488" t="n">
         <v>74178</v>
@@ -14695,7 +14695,7 @@
         <v>9.28999996185303</v>
       </c>
       <c r="G494" t="n">
-        <v>8.57674884796143</v>
+        <v>8.57674789428711</v>
       </c>
       <c r="H494" t="n">
         <v>136448</v>
@@ -14724,7 +14724,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G495" t="n">
-        <v>8.48442554473877</v>
+        <v>8.48442649841309</v>
       </c>
       <c r="H495" t="n">
         <v>37699</v>
@@ -14840,7 +14840,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G499" t="n">
-        <v>8.62291049957275</v>
+        <v>8.62290954589844</v>
       </c>
       <c r="H499" t="n">
         <v>120557</v>
@@ -14898,7 +14898,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G501" t="n">
-        <v>8.62291049957275</v>
+        <v>8.62290954589844</v>
       </c>
       <c r="H501" t="n">
         <v>49932</v>
@@ -14956,7 +14956,7 @@
         <v>9.6899995803833</v>
       </c>
       <c r="G503" t="n">
-        <v>8.94603824615479</v>
+        <v>8.94603729248047</v>
       </c>
       <c r="H503" t="n">
         <v>146163</v>
@@ -14985,7 +14985,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G504" t="n">
-        <v>8.86294746398926</v>
+        <v>8.86294841766357</v>
       </c>
       <c r="H504" t="n">
         <v>41942</v>
@@ -15188,7 +15188,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G511" t="n">
-        <v>8.78909015655518</v>
+        <v>8.78909111022949</v>
       </c>
       <c r="H511" t="n">
         <v>113583</v>
@@ -15246,7 +15246,7 @@
         <v>9.8100004196167</v>
       </c>
       <c r="G513" t="n">
-        <v>9.05682563781738</v>
+        <v>9.05682468414307</v>
       </c>
       <c r="H513" t="n">
         <v>107598</v>
@@ -15333,7 +15333,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G516" t="n">
-        <v>8.95527076721191</v>
+        <v>8.9552698135376</v>
       </c>
       <c r="H516" t="n">
         <v>76374</v>
@@ -33203,6 +33203,35 @@
         <v>320376</v>
       </c>
       <c r="I1132" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1133">
+      <c r="A1133" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1133" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C1133" t="n">
+        <v>0.851999998092651</v>
+      </c>
+      <c r="D1133" t="n">
+        <v>0.870000004768372</v>
+      </c>
+      <c r="E1133" t="n">
+        <v>0.649999976158142</v>
+      </c>
+      <c r="F1133" t="n">
+        <v>0.649999976158142</v>
+      </c>
+      <c r="G1133" t="n">
+        <v>0.649999976158142</v>
+      </c>
+      <c r="H1133" t="n">
+        <v>973262</v>
+      </c>
+      <c r="I1133" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/TISG.MI.xlsx
+++ b/data/TISG.MI.xlsx
@@ -427,7 +427,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G2" t="n">
-        <v>4.97171211242676</v>
+        <v>4.97171258926392</v>
       </c>
       <c r="H2" t="n">
         <v>20197</v>
@@ -456,7 +456,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G3" t="n">
-        <v>5.12372493743896</v>
+        <v>5.12372541427612</v>
       </c>
       <c r="H3" t="n">
         <v>28276</v>
@@ -543,7 +543,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G6" t="n">
-        <v>4.97171211242676</v>
+        <v>4.97171258926392</v>
       </c>
       <c r="H6" t="n">
         <v>18977</v>
@@ -688,7 +688,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G11" t="n">
-        <v>4.97171211242676</v>
+        <v>4.97171258926392</v>
       </c>
       <c r="H11" t="n">
         <v>12298</v>
@@ -978,7 +978,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G21" t="n">
-        <v>5.02536344528198</v>
+        <v>5.02536392211914</v>
       </c>
       <c r="H21" t="n">
         <v>16980</v>
@@ -1065,7 +1065,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G24" t="n">
-        <v>4.59615135192871</v>
+        <v>4.59615087509155</v>
       </c>
       <c r="H24" t="n">
         <v>122824</v>
@@ -1094,7 +1094,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G25" t="n">
-        <v>4.64086103439331</v>
+        <v>4.64086151123047</v>
       </c>
       <c r="H25" t="n">
         <v>38675</v>
@@ -1268,7 +1268,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G31" t="n">
-        <v>4.65874528884888</v>
+        <v>4.65874481201172</v>
       </c>
       <c r="H31" t="n">
         <v>18744</v>
@@ -1297,7 +1297,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G32" t="n">
-        <v>4.68557071685791</v>
+        <v>4.68557024002075</v>
       </c>
       <c r="H32" t="n">
         <v>47444</v>
@@ -1326,7 +1326,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G33" t="n">
-        <v>4.68557071685791</v>
+        <v>4.68557024002075</v>
       </c>
       <c r="H33" t="n">
         <v>11521</v>
@@ -1355,7 +1355,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G34" t="n">
-        <v>4.68557071685791</v>
+        <v>4.68557024002075</v>
       </c>
       <c r="H34" t="n">
         <v>15121</v>
@@ -1384,7 +1384,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G35" t="n">
-        <v>4.64086103439331</v>
+        <v>4.64086151123047</v>
       </c>
       <c r="H35" t="n">
         <v>71434</v>
@@ -1442,7 +1442,7 @@
         <v>4.78499984741211</v>
       </c>
       <c r="G37" t="n">
-        <v>4.27871322631836</v>
+        <v>4.2787127494812</v>
       </c>
       <c r="H37" t="n">
         <v>58880</v>
@@ -1616,7 +1616,7 @@
         <v>5</v>
       </c>
       <c r="G43" t="n">
-        <v>4.4709644317627</v>
+        <v>4.47096490859985</v>
       </c>
       <c r="H43" t="n">
         <v>31060</v>
@@ -1645,7 +1645,7 @@
         <v>5</v>
       </c>
       <c r="G44" t="n">
-        <v>4.4709644317627</v>
+        <v>4.47096490859985</v>
       </c>
       <c r="H44" t="n">
         <v>19860</v>
@@ -1703,7 +1703,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G46" t="n">
-        <v>4.41731309890747</v>
+        <v>4.41731262207031</v>
       </c>
       <c r="H46" t="n">
         <v>16689</v>
@@ -1761,7 +1761,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G48" t="n">
-        <v>4.25635814666748</v>
+        <v>4.25635862350464</v>
       </c>
       <c r="H48" t="n">
         <v>16777</v>
@@ -1906,7 +1906,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G53" t="n">
-        <v>4.32789421081543</v>
+        <v>4.32789373397827</v>
       </c>
       <c r="H53" t="n">
         <v>8833</v>
@@ -1935,7 +1935,7 @@
         <v>4.89499998092651</v>
       </c>
       <c r="G54" t="n">
-        <v>4.37707471847534</v>
+        <v>4.37707424163818</v>
       </c>
       <c r="H54" t="n">
         <v>13462</v>
@@ -2051,7 +2051,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G58" t="n">
-        <v>4.32789421081543</v>
+        <v>4.32789373397827</v>
       </c>
       <c r="H58" t="n">
         <v>17486</v>
@@ -2196,7 +2196,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G63" t="n">
-        <v>4.64980268478394</v>
+        <v>4.64980316162109</v>
       </c>
       <c r="H63" t="n">
         <v>36457</v>
@@ -2254,7 +2254,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G65" t="n">
-        <v>4.65874528884888</v>
+        <v>4.65874481201172</v>
       </c>
       <c r="H65" t="n">
         <v>15144</v>
@@ -2283,7 +2283,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G66" t="n">
-        <v>4.65874528884888</v>
+        <v>4.65874481201172</v>
       </c>
       <c r="H66" t="n">
         <v>14073</v>
@@ -2312,7 +2312,7 @@
         <v>5.25</v>
       </c>
       <c r="G67" t="n">
-        <v>4.69451236724854</v>
+        <v>4.69451284408569</v>
       </c>
       <c r="H67" t="n">
         <v>45084</v>
@@ -2341,7 +2341,7 @@
         <v>5.25</v>
       </c>
       <c r="G68" t="n">
-        <v>4.69451236724854</v>
+        <v>4.69451284408569</v>
       </c>
       <c r="H68" t="n">
         <v>32450</v>
@@ -2370,7 +2370,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G69" t="n">
-        <v>4.64980268478394</v>
+        <v>4.64980316162109</v>
       </c>
       <c r="H69" t="n">
         <v>10853</v>
@@ -2457,7 +2457,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G72" t="n">
-        <v>4.66768646240234</v>
+        <v>4.6676869392395</v>
       </c>
       <c r="H72" t="n">
         <v>17558</v>
@@ -2573,7 +2573,7 @@
         <v>4.85500001907349</v>
       </c>
       <c r="G76" t="n">
-        <v>4.34130620956421</v>
+        <v>4.34130668640137</v>
       </c>
       <c r="H76" t="n">
         <v>21022</v>
@@ -2602,7 +2602,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G77" t="n">
-        <v>4.31000947952271</v>
+        <v>4.31000995635986</v>
       </c>
       <c r="H77" t="n">
         <v>12944</v>
@@ -2747,7 +2747,7 @@
         <v>4.83500003814697</v>
       </c>
       <c r="G82" t="n">
-        <v>4.32342290878296</v>
+        <v>4.3234224319458</v>
       </c>
       <c r="H82" t="n">
         <v>63420</v>
@@ -2921,7 +2921,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G88" t="n">
-        <v>4.49779033660889</v>
+        <v>4.49779081344604</v>
       </c>
       <c r="H88" t="n">
         <v>22654</v>
@@ -2950,7 +2950,7 @@
         <v>5</v>
       </c>
       <c r="G89" t="n">
-        <v>4.4709644317627</v>
+        <v>4.47096490859985</v>
       </c>
       <c r="H89" t="n">
         <v>83457</v>
@@ -2979,7 +2979,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G90" t="n">
-        <v>4.4888482093811</v>
+        <v>4.48884868621826</v>
       </c>
       <c r="H90" t="n">
         <v>27075</v>
@@ -3008,7 +3008,7 @@
         <v>4.85500001907349</v>
       </c>
       <c r="G91" t="n">
-        <v>4.34130620956421</v>
+        <v>4.34130668640137</v>
       </c>
       <c r="H91" t="n">
         <v>28795</v>
@@ -3095,7 +3095,7 @@
         <v>4.75</v>
       </c>
       <c r="G94" t="n">
-        <v>4.24741649627686</v>
+        <v>4.2474160194397</v>
       </c>
       <c r="H94" t="n">
         <v>25723</v>
@@ -3182,7 +3182,7 @@
         <v>4.89499998092651</v>
       </c>
       <c r="G97" t="n">
-        <v>4.37707471847534</v>
+        <v>4.37707424163818</v>
       </c>
       <c r="H97" t="n">
         <v>41065</v>
@@ -3211,7 +3211,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G98" t="n">
-        <v>4.31895160675049</v>
+        <v>4.31895208358765</v>
       </c>
       <c r="H98" t="n">
         <v>10092</v>
@@ -3269,7 +3269,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G100" t="n">
-        <v>4.37260293960571</v>
+        <v>4.37260341644287</v>
       </c>
       <c r="H100" t="n">
         <v>25467</v>
@@ -3298,7 +3298,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G101" t="n">
-        <v>4.08646202087402</v>
+        <v>4.08646154403687</v>
       </c>
       <c r="H101" t="n">
         <v>93157</v>
@@ -3327,7 +3327,7 @@
         <v>4.46500015258789</v>
       </c>
       <c r="G102" t="n">
-        <v>3.99257159233093</v>
+        <v>3.99257135391235</v>
       </c>
       <c r="H102" t="n">
         <v>73666</v>
@@ -3356,7 +3356,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G103" t="n">
-        <v>3.95233297348022</v>
+        <v>3.95233273506165</v>
       </c>
       <c r="H103" t="n">
         <v>122405</v>
@@ -3385,7 +3385,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G104" t="n">
-        <v>4.01492547988892</v>
+        <v>4.01492595672607</v>
       </c>
       <c r="H104" t="n">
         <v>12994</v>
@@ -3414,7 +3414,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G105" t="n">
-        <v>3.90762305259705</v>
+        <v>3.90762281417847</v>
       </c>
       <c r="H105" t="n">
         <v>8913</v>
@@ -3472,7 +3472,7 @@
         <v>4.39499998092651</v>
       </c>
       <c r="G107" t="n">
-        <v>3.92997741699219</v>
+        <v>3.92997789382935</v>
       </c>
       <c r="H107" t="n">
         <v>9552</v>
@@ -3501,7 +3501,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G108" t="n">
-        <v>3.82714581489563</v>
+        <v>3.82714605331421</v>
       </c>
       <c r="H108" t="n">
         <v>26268</v>
@@ -3530,7 +3530,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G109" t="n">
-        <v>3.80926203727722</v>
+        <v>3.80926179885864</v>
       </c>
       <c r="H109" t="n">
         <v>5280</v>
@@ -3559,7 +3559,7 @@
         <v>4.2649998664856</v>
       </c>
       <c r="G110" t="n">
-        <v>3.81373262405396</v>
+        <v>3.81373238563538</v>
       </c>
       <c r="H110" t="n">
         <v>30391</v>
@@ -3588,7 +3588,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G111" t="n">
-        <v>3.69301700592041</v>
+        <v>3.69301676750183</v>
       </c>
       <c r="H111" t="n">
         <v>51138</v>
@@ -3646,7 +3646,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G113" t="n">
-        <v>3.75560975074768</v>
+        <v>3.75560998916626</v>
       </c>
       <c r="H113" t="n">
         <v>18855</v>
@@ -3791,7 +3791,7 @@
         <v>4.78499984741211</v>
       </c>
       <c r="G118" t="n">
-        <v>4.27871322631836</v>
+        <v>4.2787127494812</v>
       </c>
       <c r="H118" t="n">
         <v>22444</v>
@@ -3820,7 +3820,7 @@
         <v>4.75</v>
       </c>
       <c r="G119" t="n">
-        <v>4.24741649627686</v>
+        <v>4.2474160194397</v>
       </c>
       <c r="H119" t="n">
         <v>12242</v>
@@ -3907,7 +3907,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G122" t="n">
-        <v>4.25635814666748</v>
+        <v>4.25635862350464</v>
       </c>
       <c r="H122" t="n">
         <v>6911</v>
@@ -3994,7 +3994,7 @@
         <v>4.70499992370605</v>
       </c>
       <c r="G125" t="n">
-        <v>4.20717716217041</v>
+        <v>4.20717763900757</v>
       </c>
       <c r="H125" t="n">
         <v>19005</v>
@@ -4023,7 +4023,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G126" t="n">
-        <v>4.27424240112305</v>
+        <v>4.27424192428589</v>
       </c>
       <c r="H126" t="n">
         <v>14120</v>
@@ -4110,7 +4110,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G129" t="n">
-        <v>4.56932592391968</v>
+        <v>4.56932544708252</v>
       </c>
       <c r="H129" t="n">
         <v>34023</v>
@@ -4168,7 +4168,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G131" t="n">
-        <v>4.68557071685791</v>
+        <v>4.68557024002075</v>
       </c>
       <c r="H131" t="n">
         <v>35085</v>
@@ -4226,7 +4226,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G133" t="n">
-        <v>4.82864141464233</v>
+        <v>4.82864189147949</v>
       </c>
       <c r="H133" t="n">
         <v>33414</v>
@@ -4342,7 +4342,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G137" t="n">
-        <v>4.83758306503296</v>
+        <v>4.83758354187012</v>
       </c>
       <c r="H137" t="n">
         <v>18118</v>
@@ -4371,7 +4371,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G138" t="n">
-        <v>4.81075763702393</v>
+        <v>4.81075811386108</v>
       </c>
       <c r="H138" t="n">
         <v>13168</v>
@@ -4603,7 +4603,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G146" t="n">
-        <v>5.13266706466675</v>
+        <v>5.13266754150391</v>
       </c>
       <c r="H146" t="n">
         <v>31662</v>
@@ -4632,7 +4632,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G147" t="n">
-        <v>5.02536344528198</v>
+        <v>5.02536392211914</v>
       </c>
       <c r="H147" t="n">
         <v>22523</v>
@@ -4661,7 +4661,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G148" t="n">
-        <v>5.22208642959595</v>
+        <v>5.22208690643311</v>
       </c>
       <c r="H148" t="n">
         <v>48197</v>
@@ -4719,7 +4719,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G150" t="n">
-        <v>5.06113195419312</v>
+        <v>5.06113147735596</v>
       </c>
       <c r="H150" t="n">
         <v>44995</v>
@@ -4777,7 +4777,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G152" t="n">
-        <v>5.23102855682373</v>
+        <v>5.23102807998657</v>
       </c>
       <c r="H152" t="n">
         <v>20268</v>
@@ -4835,7 +4835,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G154" t="n">
-        <v>5.13266706466675</v>
+        <v>5.13266754150391</v>
       </c>
       <c r="H154" t="n">
         <v>24494</v>
@@ -4951,7 +4951,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G158" t="n">
-        <v>5.02536344528198</v>
+        <v>5.02536392211914</v>
       </c>
       <c r="H158" t="n">
         <v>12170</v>
@@ -5009,7 +5009,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G160" t="n">
-        <v>5.09689950942993</v>
+        <v>5.09689903259277</v>
       </c>
       <c r="H160" t="n">
         <v>13151</v>
@@ -5067,7 +5067,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G162" t="n">
-        <v>5.09689950942993</v>
+        <v>5.09689903259277</v>
       </c>
       <c r="H162" t="n">
         <v>60968</v>
@@ -5125,7 +5125,7 @@
         <v>5.69000005722046</v>
       </c>
       <c r="G164" t="n">
-        <v>5.08795785903931</v>
+        <v>5.08795738220215</v>
       </c>
       <c r="H164" t="n">
         <v>9415</v>
@@ -5183,7 +5183,7 @@
         <v>5.67000007629395</v>
       </c>
       <c r="G166" t="n">
-        <v>5.07007360458374</v>
+        <v>5.0700740814209</v>
       </c>
       <c r="H166" t="n">
         <v>8659</v>
@@ -5241,7 +5241,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G168" t="n">
-        <v>5.12372493743896</v>
+        <v>5.12372541427612</v>
       </c>
       <c r="H168" t="n">
         <v>13445</v>
@@ -5328,7 +5328,7 @@
         <v>5.75</v>
       </c>
       <c r="G171" t="n">
-        <v>5.14160966873169</v>
+        <v>5.14160919189453</v>
       </c>
       <c r="H171" t="n">
         <v>1538</v>
@@ -5357,7 +5357,7 @@
         <v>5.75</v>
       </c>
       <c r="G172" t="n">
-        <v>5.14160966873169</v>
+        <v>5.14160919189453</v>
       </c>
       <c r="H172" t="n">
         <v>9719</v>
@@ -5444,7 +5444,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G175" t="n">
-        <v>5.13266706466675</v>
+        <v>5.13266754150391</v>
       </c>
       <c r="H175" t="n">
         <v>26260</v>
@@ -5473,7 +5473,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G176" t="n">
-        <v>5.17737722396851</v>
+        <v>5.17737674713135</v>
       </c>
       <c r="H176" t="n">
         <v>15289</v>
@@ -5531,7 +5531,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G178" t="n">
-        <v>5.12372493743896</v>
+        <v>5.12372541427612</v>
       </c>
       <c r="H178" t="n">
         <v>13789</v>
@@ -5560,7 +5560,7 @@
         <v>5.90999984741211</v>
       </c>
       <c r="G179" t="n">
-        <v>5.28467988967896</v>
+        <v>5.28468036651611</v>
       </c>
       <c r="H179" t="n">
         <v>21763</v>
@@ -5618,7 +5618,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G181" t="n">
-        <v>5.43669271469116</v>
+        <v>5.436692237854</v>
       </c>
       <c r="H181" t="n">
         <v>65727</v>
@@ -5908,7 +5908,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G191" t="n">
-        <v>6.21464014053345</v>
+        <v>6.21464061737061</v>
       </c>
       <c r="H191" t="n">
         <v>39877</v>
@@ -5937,7 +5937,7 @@
         <v>6.80999994277954</v>
       </c>
       <c r="G192" t="n">
-        <v>6.08945369720459</v>
+        <v>6.08945322036743</v>
       </c>
       <c r="H192" t="n">
         <v>86712</v>
@@ -5966,7 +5966,7 @@
         <v>7</v>
       </c>
       <c r="G193" t="n">
-        <v>6.25935029983521</v>
+        <v>6.25934982299805</v>
       </c>
       <c r="H193" t="n">
         <v>64859</v>
@@ -6024,7 +6024,7 @@
         <v>6.90999984741211</v>
       </c>
       <c r="G195" t="n">
-        <v>6.17887306213379</v>
+        <v>6.17887258529663</v>
       </c>
       <c r="H195" t="n">
         <v>47173</v>
@@ -6082,7 +6082,7 @@
         <v>7</v>
       </c>
       <c r="G197" t="n">
-        <v>6.25935029983521</v>
+        <v>6.25934982299805</v>
       </c>
       <c r="H197" t="n">
         <v>92157</v>
@@ -6140,7 +6140,7 @@
         <v>7.03000020980835</v>
       </c>
       <c r="G199" t="n">
-        <v>6.28617668151855</v>
+        <v>6.2861762046814</v>
       </c>
       <c r="H199" t="n">
         <v>56247</v>
@@ -6169,7 +6169,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G200" t="n">
-        <v>6.21464014053345</v>
+        <v>6.21464061737061</v>
       </c>
       <c r="H200" t="n">
         <v>49278</v>
@@ -6198,7 +6198,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G201" t="n">
-        <v>6.27723407745361</v>
+        <v>6.27723455429077</v>
       </c>
       <c r="H201" t="n">
         <v>56777</v>
@@ -6256,7 +6256,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G203" t="n">
-        <v>6.5276083946228</v>
+        <v>6.52760791778564</v>
       </c>
       <c r="H203" t="n">
         <v>138551</v>
@@ -6285,7 +6285,7 @@
         <v>7.09000015258789</v>
       </c>
       <c r="G204" t="n">
-        <v>6.33982801437378</v>
+        <v>6.33982753753662</v>
       </c>
       <c r="H204" t="n">
         <v>53372</v>
@@ -6314,7 +6314,7 @@
         <v>7.03000020980835</v>
       </c>
       <c r="G205" t="n">
-        <v>6.28617668151855</v>
+        <v>6.2861762046814</v>
       </c>
       <c r="H205" t="n">
         <v>111627</v>
@@ -6343,7 +6343,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G206" t="n">
-        <v>6.3040599822998</v>
+        <v>6.30406045913696</v>
       </c>
       <c r="H206" t="n">
         <v>51631</v>
@@ -6372,7 +6372,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G207" t="n">
-        <v>6.65279483795166</v>
+        <v>6.65279531478882</v>
       </c>
       <c r="H207" t="n">
         <v>179183</v>
@@ -6517,7 +6517,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G212" t="n">
-        <v>6.617027759552</v>
+        <v>6.61702728271484</v>
       </c>
       <c r="H212" t="n">
         <v>59738</v>
@@ -6575,7 +6575,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G214" t="n">
-        <v>6.79586553573608</v>
+        <v>6.79586601257324</v>
       </c>
       <c r="H214" t="n">
         <v>155309</v>
@@ -6662,7 +6662,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G217" t="n">
-        <v>6.42030477523804</v>
+        <v>6.4203052520752</v>
       </c>
       <c r="H217" t="n">
         <v>143048</v>
@@ -6691,7 +6691,7 @@
         <v>7.53000020980835</v>
       </c>
       <c r="G218" t="n">
-        <v>6.73327255249023</v>
+        <v>6.73327207565308</v>
       </c>
       <c r="H218" t="n">
         <v>97258</v>
@@ -6749,7 +6749,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G220" t="n">
-        <v>6.60808515548706</v>
+        <v>6.60808563232422</v>
       </c>
       <c r="H220" t="n">
         <v>64845</v>
@@ -6778,7 +6778,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G221" t="n">
-        <v>6.45607233047485</v>
+        <v>6.45607280731201</v>
       </c>
       <c r="H221" t="n">
         <v>66909</v>
@@ -6923,7 +6923,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G226" t="n">
-        <v>6.50972414016724</v>
+        <v>6.50972461700439</v>
       </c>
       <c r="H226" t="n">
         <v>94459</v>
@@ -6952,7 +6952,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G227" t="n">
-        <v>6.58125972747803</v>
+        <v>6.58125925064087</v>
       </c>
       <c r="H227" t="n">
         <v>33666</v>
@@ -6981,7 +6981,7 @@
         <v>7.53000020980835</v>
       </c>
       <c r="G228" t="n">
-        <v>6.73327255249023</v>
+        <v>6.73327207565308</v>
       </c>
       <c r="H228" t="n">
         <v>150431</v>
@@ -7039,7 +7039,7 @@
         <v>7.98999977111816</v>
       </c>
       <c r="G230" t="n">
-        <v>7.1446008682251</v>
+        <v>7.14460134506226</v>
       </c>
       <c r="H230" t="n">
         <v>156690</v>
@@ -7097,7 +7097,7 @@
         <v>8.56999969482422</v>
       </c>
       <c r="G232" t="n">
-        <v>7.66323280334473</v>
+        <v>7.66323328018188</v>
       </c>
       <c r="H232" t="n">
         <v>214841</v>
@@ -7126,7 +7126,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G233" t="n">
-        <v>7.63640689849854</v>
+        <v>7.63640642166138</v>
       </c>
       <c r="H233" t="n">
         <v>144356</v>
@@ -7155,7 +7155,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G234" t="n">
-        <v>7.77947854995728</v>
+        <v>7.77947807312012</v>
       </c>
       <c r="H234" t="n">
         <v>98556</v>
@@ -7184,7 +7184,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G235" t="n">
-        <v>7.65429162979126</v>
+        <v>7.65429210662842</v>
       </c>
       <c r="H235" t="n">
         <v>82796</v>
@@ -7271,7 +7271,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G238" t="n">
-        <v>7.73476791381836</v>
+        <v>7.73476886749268</v>
       </c>
       <c r="H238" t="n">
         <v>113648</v>
@@ -7358,7 +7358,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G241" t="n">
-        <v>7.94043302536011</v>
+        <v>7.94043254852295</v>
       </c>
       <c r="H241" t="n">
         <v>150011</v>
@@ -7387,7 +7387,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G242" t="n">
-        <v>7.77947854995728</v>
+        <v>7.77947807312012</v>
       </c>
       <c r="H242" t="n">
         <v>118950</v>
@@ -7416,7 +7416,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G243" t="n">
-        <v>7.73476791381836</v>
+        <v>7.73476886749268</v>
       </c>
       <c r="H243" t="n">
         <v>250001</v>
@@ -7445,7 +7445,7 @@
         <v>8.60999965667725</v>
       </c>
       <c r="G244" t="n">
-        <v>7.69900035858154</v>
+        <v>7.6990008354187</v>
       </c>
       <c r="H244" t="n">
         <v>102832</v>
@@ -7474,7 +7474,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G245" t="n">
-        <v>7.77947854995728</v>
+        <v>7.77947807312012</v>
       </c>
       <c r="H245" t="n">
         <v>76403</v>
@@ -7503,7 +7503,7 @@
         <v>8.57999992370605</v>
       </c>
       <c r="G246" t="n">
-        <v>7.67217445373535</v>
+        <v>7.67217540740967</v>
       </c>
       <c r="H246" t="n">
         <v>44155</v>
@@ -7532,7 +7532,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G247" t="n">
-        <v>7.64534950256348</v>
+        <v>7.64534997940063</v>
       </c>
       <c r="H247" t="n">
         <v>105886</v>
@@ -7590,7 +7590,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G249" t="n">
-        <v>7.73476791381836</v>
+        <v>7.73476886749268</v>
       </c>
       <c r="H249" t="n">
         <v>51008</v>
@@ -7735,7 +7735,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G254" t="n">
-        <v>7.81047344207764</v>
+        <v>7.81047248840332</v>
       </c>
       <c r="H254" t="n">
         <v>152971</v>
@@ -7793,7 +7793,7 @@
         <v>8.52999973297119</v>
       </c>
       <c r="G256" t="n">
-        <v>7.87509870529175</v>
+        <v>7.87509775161743</v>
       </c>
       <c r="H256" t="n">
         <v>99895</v>
@@ -7996,7 +7996,7 @@
         <v>8.60999965667725</v>
       </c>
       <c r="G263" t="n">
-        <v>7.94895553588867</v>
+        <v>7.94895648956299</v>
       </c>
       <c r="H263" t="n">
         <v>76537</v>
@@ -8141,7 +8141,7 @@
         <v>8.60999965667725</v>
       </c>
       <c r="G268" t="n">
-        <v>7.94895553588867</v>
+        <v>7.94895648956299</v>
       </c>
       <c r="H268" t="n">
         <v>61503</v>
@@ -8199,7 +8199,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G270" t="n">
-        <v>7.95818853378296</v>
+        <v>7.95818901062012</v>
       </c>
       <c r="H270" t="n">
         <v>77829</v>
@@ -8460,7 +8460,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G279" t="n">
-        <v>7.42271900177002</v>
+        <v>7.42271852493286</v>
       </c>
       <c r="H279" t="n">
         <v>56062</v>
@@ -8518,7 +8518,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G281" t="n">
-        <v>7.4965763092041</v>
+        <v>7.49657678604126</v>
       </c>
       <c r="H281" t="n">
         <v>39852</v>
@@ -8605,7 +8605,7 @@
         <v>7.80999994277954</v>
       </c>
       <c r="G284" t="n">
-        <v>7.21037769317627</v>
+        <v>7.21037721633911</v>
       </c>
       <c r="H284" t="n">
         <v>117674</v>
@@ -8634,7 +8634,7 @@
         <v>7.71000003814697</v>
       </c>
       <c r="G285" t="n">
-        <v>7.11805534362793</v>
+        <v>7.11805486679077</v>
       </c>
       <c r="H285" t="n">
         <v>57382</v>
@@ -8663,7 +8663,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G286" t="n">
-        <v>7.05342960357666</v>
+        <v>7.0534291267395</v>
       </c>
       <c r="H286" t="n">
         <v>74446</v>
@@ -8692,7 +8692,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G287" t="n">
-        <v>7.1088228225708</v>
+        <v>7.10882234573364</v>
       </c>
       <c r="H287" t="n">
         <v>108157</v>
@@ -8721,7 +8721,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G288" t="n">
-        <v>6.97033929824829</v>
+        <v>6.97033977508545</v>
       </c>
       <c r="H288" t="n">
         <v>37819</v>
@@ -8750,7 +8750,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G289" t="n">
-        <v>6.97033929824829</v>
+        <v>6.97033977508545</v>
       </c>
       <c r="H289" t="n">
         <v>41222</v>
@@ -8953,7 +8953,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G296" t="n">
-        <v>7.30269956588745</v>
+        <v>7.30270004272461</v>
       </c>
       <c r="H296" t="n">
         <v>83813</v>
@@ -8982,7 +8982,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G297" t="n">
-        <v>7.14575147628784</v>
+        <v>7.145751953125</v>
       </c>
       <c r="H297" t="n">
         <v>43493</v>
@@ -9069,7 +9069,7 @@
         <v>7.78999996185303</v>
       </c>
       <c r="G300" t="n">
-        <v>7.19191265106201</v>
+        <v>7.19191312789917</v>
       </c>
       <c r="H300" t="n">
         <v>50892</v>
@@ -9330,7 +9330,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G309" t="n">
-        <v>6.93341064453125</v>
+        <v>6.93341016769409</v>
       </c>
       <c r="H309" t="n">
         <v>19291</v>
@@ -9359,7 +9359,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G310" t="n">
-        <v>6.97033929824829</v>
+        <v>6.97033977508545</v>
       </c>
       <c r="H310" t="n">
         <v>22938</v>
@@ -9388,7 +9388,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G311" t="n">
-        <v>6.87801647186279</v>
+        <v>6.87801694869995</v>
       </c>
       <c r="H311" t="n">
         <v>39307</v>
@@ -9417,7 +9417,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G312" t="n">
-        <v>7.0349645614624</v>
+        <v>7.03496503829956</v>
       </c>
       <c r="H312" t="n">
         <v>19565</v>
@@ -9533,7 +9533,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G316" t="n">
-        <v>6.97033929824829</v>
+        <v>6.97033977508545</v>
       </c>
       <c r="H316" t="n">
         <v>31066</v>
@@ -9591,7 +9591,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G318" t="n">
-        <v>7.42271900177002</v>
+        <v>7.42271852493286</v>
       </c>
       <c r="H318" t="n">
         <v>77225</v>
@@ -9678,7 +9678,7 @@
         <v>7.78999996185303</v>
       </c>
       <c r="G321" t="n">
-        <v>7.19191265106201</v>
+        <v>7.19191312789917</v>
       </c>
       <c r="H321" t="n">
         <v>21141</v>
@@ -9823,7 +9823,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G326" t="n">
-        <v>7.1088228225708</v>
+        <v>7.10882234573364</v>
       </c>
       <c r="H326" t="n">
         <v>18088</v>
@@ -9852,7 +9852,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G327" t="n">
-        <v>6.97033929824829</v>
+        <v>6.97033977508545</v>
       </c>
       <c r="H327" t="n">
         <v>69708</v>
@@ -9881,7 +9881,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G328" t="n">
-        <v>7.13651943206787</v>
+        <v>7.13651990890503</v>
       </c>
       <c r="H328" t="n">
         <v>33278</v>
@@ -9910,7 +9910,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G329" t="n">
-        <v>7.05342960357666</v>
+        <v>7.0534291267395</v>
       </c>
       <c r="H329" t="n">
         <v>17493</v>
@@ -9997,7 +9997,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G332" t="n">
-        <v>6.93341064453125</v>
+        <v>6.93341016769409</v>
       </c>
       <c r="H332" t="n">
         <v>24732</v>
@@ -10026,7 +10026,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G333" t="n">
-        <v>7.05342960357666</v>
+        <v>7.0534291267395</v>
       </c>
       <c r="H333" t="n">
         <v>18353</v>
@@ -10084,7 +10084,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G335" t="n">
-        <v>7.05342960357666</v>
+        <v>7.0534291267395</v>
       </c>
       <c r="H335" t="n">
         <v>11054</v>
@@ -10345,7 +10345,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G344" t="n">
-        <v>6.97033929824829</v>
+        <v>6.97033977508545</v>
       </c>
       <c r="H344" t="n">
         <v>42139</v>
@@ -10403,7 +10403,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G346" t="n">
-        <v>7.14575147628784</v>
+        <v>7.145751953125</v>
       </c>
       <c r="H346" t="n">
         <v>47587</v>
@@ -10461,7 +10461,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G348" t="n">
-        <v>6.90571403503418</v>
+        <v>6.90571355819702</v>
       </c>
       <c r="H348" t="n">
         <v>60152</v>
@@ -10519,7 +10519,7 @@
         <v>7.53999996185303</v>
       </c>
       <c r="G350" t="n">
-        <v>6.96110725402832</v>
+        <v>6.96110677719116</v>
       </c>
       <c r="H350" t="n">
         <v>28852</v>
@@ -10548,7 +10548,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G351" t="n">
-        <v>6.77646255493164</v>
+        <v>6.77646207809448</v>
       </c>
       <c r="H351" t="n">
         <v>58129</v>
@@ -10664,7 +10664,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G355" t="n">
-        <v>6.5364236831665</v>
+        <v>6.53642416000366</v>
       </c>
       <c r="H355" t="n">
         <v>26264</v>
@@ -10809,7 +10809,7 @@
         <v>6.98999977111816</v>
       </c>
       <c r="G360" t="n">
-        <v>6.45333385467529</v>
+        <v>6.45333337783813</v>
       </c>
       <c r="H360" t="n">
         <v>50111</v>
@@ -10867,7 +10867,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G362" t="n">
-        <v>6.64721059799194</v>
+        <v>6.6472110748291</v>
       </c>
       <c r="H362" t="n">
         <v>58993</v>
@@ -10896,7 +10896,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G363" t="n">
-        <v>6.40717315673828</v>
+        <v>6.40717267990112</v>
       </c>
       <c r="H363" t="n">
         <v>39953</v>
@@ -10925,7 +10925,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G364" t="n">
-        <v>6.63797855377197</v>
+        <v>6.63797903060913</v>
       </c>
       <c r="H364" t="n">
         <v>33892</v>
@@ -11012,7 +11012,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G367" t="n">
-        <v>6.48103046417236</v>
+        <v>6.48103094100952</v>
       </c>
       <c r="H367" t="n">
         <v>37646</v>
@@ -11041,7 +11041,7 @@
         <v>7.09000015258789</v>
       </c>
       <c r="G368" t="n">
-        <v>6.54565620422363</v>
+        <v>6.54565668106079</v>
       </c>
       <c r="H368" t="n">
         <v>45957</v>
@@ -11099,7 +11099,7 @@
         <v>7.09000015258789</v>
       </c>
       <c r="G370" t="n">
-        <v>6.54565620422363</v>
+        <v>6.54565668106079</v>
       </c>
       <c r="H370" t="n">
         <v>28684</v>
@@ -11128,7 +11128,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G371" t="n">
-        <v>6.63797855377197</v>
+        <v>6.63797903060913</v>
       </c>
       <c r="H371" t="n">
         <v>24535</v>
@@ -11186,7 +11186,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G373" t="n">
-        <v>6.32408237457275</v>
+        <v>6.32408285140991</v>
       </c>
       <c r="H373" t="n">
         <v>47509</v>
@@ -11215,7 +11215,7 @@
         <v>7</v>
       </c>
       <c r="G374" t="n">
-        <v>6.46256637573242</v>
+        <v>6.46256589889526</v>
       </c>
       <c r="H374" t="n">
         <v>17115</v>
@@ -11476,7 +11476,7 @@
         <v>7.09000015258789</v>
       </c>
       <c r="G383" t="n">
-        <v>6.54565620422363</v>
+        <v>6.54565668106079</v>
       </c>
       <c r="H383" t="n">
         <v>39879</v>
@@ -11592,7 +11592,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G387" t="n">
-        <v>6.6102819442749</v>
+        <v>6.61028146743774</v>
       </c>
       <c r="H387" t="n">
         <v>59425</v>
@@ -11650,7 +11650,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G389" t="n">
-        <v>6.87801647186279</v>
+        <v>6.87801694869995</v>
       </c>
       <c r="H389" t="n">
         <v>91784</v>
@@ -11679,7 +11679,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G390" t="n">
-        <v>7.13651943206787</v>
+        <v>7.13651990890503</v>
       </c>
       <c r="H390" t="n">
         <v>203114</v>
@@ -11766,7 +11766,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G393" t="n">
-        <v>7.30269956588745</v>
+        <v>7.30270004272461</v>
       </c>
       <c r="H393" t="n">
         <v>167425</v>
@@ -11795,7 +11795,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G394" t="n">
-        <v>7.20114517211914</v>
+        <v>7.2011456489563</v>
       </c>
       <c r="H394" t="n">
         <v>191654</v>
@@ -11853,7 +11853,7 @@
         <v>7.86999988555908</v>
       </c>
       <c r="G396" t="n">
-        <v>7.26577091217041</v>
+        <v>7.26577043533325</v>
       </c>
       <c r="H396" t="n">
         <v>50620</v>
@@ -11911,7 +11911,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G398" t="n">
-        <v>7.30269956588745</v>
+        <v>7.30270004272461</v>
       </c>
       <c r="H398" t="n">
         <v>99717</v>
@@ -11940,7 +11940,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G399" t="n">
-        <v>7.36732578277588</v>
+        <v>7.36732530593872</v>
       </c>
       <c r="H399" t="n">
         <v>124059</v>
@@ -11969,7 +11969,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G400" t="n">
-        <v>7.24730587005615</v>
+        <v>7.24730634689331</v>
       </c>
       <c r="H400" t="n">
         <v>72121</v>
@@ -12114,7 +12114,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G405" t="n">
-        <v>7.30269956588745</v>
+        <v>7.30270004272461</v>
       </c>
       <c r="H405" t="n">
         <v>38438</v>
@@ -12636,7 +12636,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G423" t="n">
-        <v>7.40425443649292</v>
+        <v>7.40425491333008</v>
       </c>
       <c r="H423" t="n">
         <v>48656</v>
@@ -12752,7 +12752,7 @@
         <v>8.25</v>
       </c>
       <c r="G427" t="n">
-        <v>7.61659622192383</v>
+        <v>7.61659574508667</v>
       </c>
       <c r="H427" t="n">
         <v>55700</v>
@@ -12810,7 +12810,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G429" t="n">
-        <v>7.90279531478882</v>
+        <v>7.90279626846313</v>
       </c>
       <c r="H429" t="n">
         <v>122032</v>
@@ -12984,7 +12984,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G435" t="n">
-        <v>8.63214206695557</v>
+        <v>8.63214302062988</v>
       </c>
       <c r="H435" t="n">
         <v>236669</v>
@@ -13158,7 +13158,7 @@
         <v>9.6899995803833</v>
       </c>
       <c r="G441" t="n">
-        <v>8.94603729248047</v>
+        <v>8.94603824615479</v>
       </c>
       <c r="H441" t="n">
         <v>85296</v>
@@ -13216,7 +13216,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G443" t="n">
-        <v>8.99219989776611</v>
+        <v>8.9921989440918</v>
       </c>
       <c r="H443" t="n">
         <v>101160</v>
@@ -13477,7 +13477,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G452" t="n">
-        <v>9.52766895294189</v>
+        <v>9.52766799926758</v>
       </c>
       <c r="H452" t="n">
         <v>186778</v>
@@ -13506,7 +13506,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G453" t="n">
-        <v>9.61999130249023</v>
+        <v>9.61999225616455</v>
       </c>
       <c r="H453" t="n">
         <v>106036</v>
@@ -13535,7 +13535,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G454" t="n">
-        <v>9.41688251495361</v>
+        <v>9.4168815612793</v>
       </c>
       <c r="H454" t="n">
         <v>85544</v>
@@ -13593,7 +13593,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G456" t="n">
-        <v>9.25070190429688</v>
+        <v>9.25070285797119</v>
       </c>
       <c r="H456" t="n">
         <v>45013</v>
@@ -13651,7 +13651,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G458" t="n">
-        <v>9.26916599273682</v>
+        <v>9.26916694641113</v>
       </c>
       <c r="H458" t="n">
         <v>73523</v>
@@ -13825,7 +13825,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G464" t="n">
-        <v>9.26916599273682</v>
+        <v>9.26916694641113</v>
       </c>
       <c r="H464" t="n">
         <v>35262</v>
@@ -13883,7 +13883,7 @@
         <v>9.98999977111816</v>
       </c>
       <c r="G466" t="n">
-        <v>9.2230052947998</v>
+        <v>9.22300434112549</v>
       </c>
       <c r="H466" t="n">
         <v>90490</v>
@@ -13999,7 +13999,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G470" t="n">
-        <v>9.61999130249023</v>
+        <v>9.61999225616455</v>
       </c>
       <c r="H470" t="n">
         <v>91656</v>
@@ -14028,7 +14028,7 @@
         <v>10.4799995422363</v>
       </c>
       <c r="G471" t="n">
-        <v>9.67538356781006</v>
+        <v>9.67538452148438</v>
       </c>
       <c r="H471" t="n">
         <v>94908</v>
@@ -14173,7 +14173,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G476" t="n">
-        <v>9.61999130249023</v>
+        <v>9.61999225616455</v>
       </c>
       <c r="H476" t="n">
         <v>55619</v>
@@ -14202,7 +14202,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G477" t="n">
-        <v>9.58306217193604</v>
+        <v>9.58306312561035</v>
       </c>
       <c r="H477" t="n">
         <v>68414</v>
@@ -14289,7 +14289,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G480" t="n">
-        <v>10.2477836608887</v>
+        <v>10.247784614563</v>
       </c>
       <c r="H480" t="n">
         <v>121664</v>
@@ -14318,7 +14318,7 @@
         <v>11.1199998855591</v>
       </c>
       <c r="G481" t="n">
-        <v>10.2662477493286</v>
+        <v>10.2662487030029</v>
       </c>
       <c r="H481" t="n">
         <v>62344</v>
@@ -14347,7 +14347,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G482" t="n">
-        <v>8.93680572509766</v>
+        <v>8.93680667877197</v>
       </c>
       <c r="H482" t="n">
         <v>1087677</v>
@@ -14376,7 +14376,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G483" t="n">
-        <v>9.28763103485107</v>
+        <v>9.28763198852539</v>
       </c>
       <c r="H483" t="n">
         <v>332225</v>
@@ -14405,7 +14405,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G484" t="n">
-        <v>9.21377277374268</v>
+        <v>9.21377182006836</v>
       </c>
       <c r="H484" t="n">
         <v>153862</v>
@@ -14521,7 +14521,7 @@
         <v>9.63000011444092</v>
       </c>
       <c r="G488" t="n">
-        <v>8.89064502716064</v>
+        <v>8.89064407348633</v>
       </c>
       <c r="H488" t="n">
         <v>74178</v>
@@ -14695,7 +14695,7 @@
         <v>9.28999996185303</v>
       </c>
       <c r="G494" t="n">
-        <v>8.57674789428711</v>
+        <v>8.57674884796143</v>
       </c>
       <c r="H494" t="n">
         <v>136448</v>
@@ -14724,7 +14724,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G495" t="n">
-        <v>8.48442649841309</v>
+        <v>8.48442554473877</v>
       </c>
       <c r="H495" t="n">
         <v>37699</v>
@@ -14840,7 +14840,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G499" t="n">
-        <v>8.62290954589844</v>
+        <v>8.62291049957275</v>
       </c>
       <c r="H499" t="n">
         <v>120557</v>
@@ -14898,7 +14898,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G501" t="n">
-        <v>8.62290954589844</v>
+        <v>8.62291049957275</v>
       </c>
       <c r="H501" t="n">
         <v>49932</v>
@@ -14956,7 +14956,7 @@
         <v>9.6899995803833</v>
       </c>
       <c r="G503" t="n">
-        <v>8.94603729248047</v>
+        <v>8.94603824615479</v>
       </c>
       <c r="H503" t="n">
         <v>146163</v>
@@ -14985,7 +14985,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G504" t="n">
-        <v>8.86294841766357</v>
+        <v>8.86294746398926</v>
       </c>
       <c r="H504" t="n">
         <v>41942</v>
@@ -15188,7 +15188,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G511" t="n">
-        <v>8.78909111022949</v>
+        <v>8.78909015655518</v>
       </c>
       <c r="H511" t="n">
         <v>113583</v>
@@ -15246,7 +15246,7 @@
         <v>9.8100004196167</v>
       </c>
       <c r="G513" t="n">
-        <v>9.05682468414307</v>
+        <v>9.05682563781738</v>
       </c>
       <c r="H513" t="n">
         <v>107598</v>
@@ -15333,7 +15333,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G516" t="n">
-        <v>8.9552698135376</v>
+        <v>8.95527076721191</v>
       </c>
       <c r="H516" t="n">
         <v>76374</v>
@@ -33232,6 +33232,35 @@
         <v>973262</v>
       </c>
       <c r="I1133" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1134">
+      <c r="A1134" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1134" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C1134" t="n">
+        <v>0.651000022888184</v>
+      </c>
+      <c r="D1134" t="n">
+        <v>0.739000022411346</v>
+      </c>
+      <c r="E1134" t="n">
+        <v>0.635999977588654</v>
+      </c>
+      <c r="F1134" t="n">
+        <v>0.684000015258789</v>
+      </c>
+      <c r="G1134" t="n">
+        <v>0.684000015258789</v>
+      </c>
+      <c r="H1134" t="n">
+        <v>1428658</v>
+      </c>
+      <c r="I1134" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/TISG.MI.xlsx
+++ b/data/TISG.MI.xlsx
@@ -485,7 +485,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G4" t="n">
-        <v>5.16843509674072</v>
+        <v>5.16843461990356</v>
       </c>
       <c r="H4" t="n">
         <v>13258</v>
@@ -572,7 +572,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G7" t="n">
-        <v>4.94488668441772</v>
+        <v>4.94488716125488</v>
       </c>
       <c r="H7" t="n">
         <v>13883</v>
@@ -746,7 +746,7 @@
         <v>5.6100001335144</v>
       </c>
       <c r="G13" t="n">
-        <v>5.01642227172852</v>
+        <v>5.01642179489136</v>
       </c>
       <c r="H13" t="n">
         <v>20247</v>
@@ -833,7 +833,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G16" t="n">
-        <v>5.03430604934692</v>
+        <v>5.03430652618408</v>
       </c>
       <c r="H16" t="n">
         <v>20391</v>
@@ -862,7 +862,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G17" t="n">
-        <v>4.96277093887329</v>
+        <v>4.96277046203613</v>
       </c>
       <c r="H17" t="n">
         <v>9297</v>
@@ -891,7 +891,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G18" t="n">
-        <v>4.93594455718994</v>
+        <v>4.9359450340271</v>
       </c>
       <c r="H18" t="n">
         <v>2331</v>
@@ -920,7 +920,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G19" t="n">
-        <v>4.94488668441772</v>
+        <v>4.94488716125488</v>
       </c>
       <c r="H19" t="n">
         <v>8685</v>
@@ -1007,7 +1007,7 @@
         <v>5.6100001335144</v>
       </c>
       <c r="G22" t="n">
-        <v>5.01642227172852</v>
+        <v>5.01642179489136</v>
       </c>
       <c r="H22" t="n">
         <v>57978</v>
@@ -1065,7 +1065,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G24" t="n">
-        <v>4.59615087509155</v>
+        <v>4.59615135192871</v>
       </c>
       <c r="H24" t="n">
         <v>122824</v>
@@ -1094,7 +1094,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G25" t="n">
-        <v>4.64086151123047</v>
+        <v>4.64086103439331</v>
       </c>
       <c r="H25" t="n">
         <v>38675</v>
@@ -1384,7 +1384,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G35" t="n">
-        <v>4.64086151123047</v>
+        <v>4.64086103439331</v>
       </c>
       <c r="H35" t="n">
         <v>71434</v>
@@ -1616,7 +1616,7 @@
         <v>5</v>
       </c>
       <c r="G43" t="n">
-        <v>4.47096490859985</v>
+        <v>4.4709644317627</v>
       </c>
       <c r="H43" t="n">
         <v>31060</v>
@@ -1645,7 +1645,7 @@
         <v>5</v>
       </c>
       <c r="G44" t="n">
-        <v>4.47096490859985</v>
+        <v>4.4709644317627</v>
       </c>
       <c r="H44" t="n">
         <v>19860</v>
@@ -1790,7 +1790,7 @@
         <v>4.84499979019165</v>
       </c>
       <c r="G49" t="n">
-        <v>4.33236455917358</v>
+        <v>4.33236408233643</v>
       </c>
       <c r="H49" t="n">
         <v>18567</v>
@@ -1848,7 +1848,7 @@
         <v>4.84499979019165</v>
       </c>
       <c r="G51" t="n">
-        <v>4.33236455917358</v>
+        <v>4.33236408233643</v>
       </c>
       <c r="H51" t="n">
         <v>13315</v>
@@ -1877,7 +1877,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G52" t="n">
-        <v>4.2921257019043</v>
+        <v>4.29212617874146</v>
       </c>
       <c r="H52" t="n">
         <v>24850</v>
@@ -2022,7 +2022,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G57" t="n">
-        <v>4.2921257019043</v>
+        <v>4.29212617874146</v>
       </c>
       <c r="H57" t="n">
         <v>9336</v>
@@ -2080,7 +2080,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G59" t="n">
-        <v>4.51567459106445</v>
+        <v>4.51567411422729</v>
       </c>
       <c r="H59" t="n">
         <v>22808</v>
@@ -2138,7 +2138,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G61" t="n">
-        <v>4.93594455718994</v>
+        <v>4.9359450340271</v>
       </c>
       <c r="H61" t="n">
         <v>80771</v>
@@ -2457,7 +2457,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G72" t="n">
-        <v>4.6676869392395</v>
+        <v>4.66768646240234</v>
       </c>
       <c r="H72" t="n">
         <v>17558</v>
@@ -2544,7 +2544,7 @@
         <v>4.9850001335144</v>
       </c>
       <c r="G75" t="n">
-        <v>4.4575514793396</v>
+        <v>4.45755195617676</v>
       </c>
       <c r="H75" t="n">
         <v>16465</v>
@@ -2573,7 +2573,7 @@
         <v>4.85500001907349</v>
       </c>
       <c r="G76" t="n">
-        <v>4.34130668640137</v>
+        <v>4.34130620956421</v>
       </c>
       <c r="H76" t="n">
         <v>21022</v>
@@ -2660,7 +2660,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G79" t="n">
-        <v>4.2921257019043</v>
+        <v>4.29212617874146</v>
       </c>
       <c r="H79" t="n">
         <v>26762</v>
@@ -2689,7 +2689,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G80" t="n">
-        <v>4.2921257019043</v>
+        <v>4.29212617874146</v>
       </c>
       <c r="H80" t="n">
         <v>10522</v>
@@ -2718,7 +2718,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G81" t="n">
-        <v>4.2921257019043</v>
+        <v>4.29212617874146</v>
       </c>
       <c r="H81" t="n">
         <v>38577</v>
@@ -2747,7 +2747,7 @@
         <v>4.83500003814697</v>
       </c>
       <c r="G82" t="n">
-        <v>4.3234224319458</v>
+        <v>4.32342290878296</v>
       </c>
       <c r="H82" t="n">
         <v>63420</v>
@@ -2921,7 +2921,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G88" t="n">
-        <v>4.49779081344604</v>
+        <v>4.49779033660889</v>
       </c>
       <c r="H88" t="n">
         <v>22654</v>
@@ -2950,7 +2950,7 @@
         <v>5</v>
       </c>
       <c r="G89" t="n">
-        <v>4.47096490859985</v>
+        <v>4.4709644317627</v>
       </c>
       <c r="H89" t="n">
         <v>83457</v>
@@ -2979,7 +2979,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G90" t="n">
-        <v>4.48884868621826</v>
+        <v>4.4888482093811</v>
       </c>
       <c r="H90" t="n">
         <v>27075</v>
@@ -3008,7 +3008,7 @@
         <v>4.85500001907349</v>
       </c>
       <c r="G91" t="n">
-        <v>4.34130668640137</v>
+        <v>4.34130620956421</v>
       </c>
       <c r="H91" t="n">
         <v>28795</v>
@@ -3153,7 +3153,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G96" t="n">
-        <v>4.2921257019043</v>
+        <v>4.29212617874146</v>
       </c>
       <c r="H96" t="n">
         <v>8412</v>
@@ -3211,7 +3211,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G98" t="n">
-        <v>4.31895208358765</v>
+        <v>4.31895160675049</v>
       </c>
       <c r="H98" t="n">
         <v>10092</v>
@@ -3240,7 +3240,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G99" t="n">
-        <v>4.3547191619873</v>
+        <v>4.35471963882446</v>
       </c>
       <c r="H99" t="n">
         <v>17935</v>
@@ -3327,7 +3327,7 @@
         <v>4.46500015258789</v>
       </c>
       <c r="G102" t="n">
-        <v>3.99257135391235</v>
+        <v>3.99257159233093</v>
       </c>
       <c r="H102" t="n">
         <v>73666</v>
@@ -3356,7 +3356,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G103" t="n">
-        <v>3.95233273506165</v>
+        <v>3.95233249664307</v>
       </c>
       <c r="H103" t="n">
         <v>122405</v>
@@ -3414,7 +3414,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G105" t="n">
-        <v>3.90762281417847</v>
+        <v>3.90762233734131</v>
       </c>
       <c r="H105" t="n">
         <v>8913</v>
@@ -3443,7 +3443,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G106" t="n">
-        <v>3.84502959251404</v>
+        <v>3.84502983093262</v>
       </c>
       <c r="H106" t="n">
         <v>39490</v>
@@ -3501,7 +3501,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G108" t="n">
-        <v>3.82714605331421</v>
+        <v>3.82714557647705</v>
       </c>
       <c r="H108" t="n">
         <v>26268</v>
@@ -3530,7 +3530,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G109" t="n">
-        <v>3.80926179885864</v>
+        <v>3.80926203727722</v>
       </c>
       <c r="H109" t="n">
         <v>5280</v>
@@ -3559,7 +3559,7 @@
         <v>4.2649998664856</v>
       </c>
       <c r="G110" t="n">
-        <v>3.81373238563538</v>
+        <v>3.81373286247253</v>
       </c>
       <c r="H110" t="n">
         <v>30391</v>
@@ -3646,7 +3646,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G113" t="n">
-        <v>3.75560998916626</v>
+        <v>3.75561022758484</v>
       </c>
       <c r="H113" t="n">
         <v>18855</v>
@@ -3675,7 +3675,7 @@
         <v>4.5</v>
       </c>
       <c r="G114" t="n">
-        <v>4.02386808395386</v>
+        <v>4.02386856079102</v>
       </c>
       <c r="H114" t="n">
         <v>51824</v>
@@ -3936,7 +3936,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G123" t="n">
-        <v>4.2921257019043</v>
+        <v>4.29212617874146</v>
       </c>
       <c r="H123" t="n">
         <v>9894</v>
@@ -3965,7 +3965,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G124" t="n">
-        <v>4.2921257019043</v>
+        <v>4.29212617874146</v>
       </c>
       <c r="H124" t="n">
         <v>5737</v>
@@ -4023,7 +4023,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G126" t="n">
-        <v>4.27424192428589</v>
+        <v>4.27424240112305</v>
       </c>
       <c r="H126" t="n">
         <v>14120</v>
@@ -4052,7 +4052,7 @@
         <v>4.84499979019165</v>
       </c>
       <c r="G127" t="n">
-        <v>4.33236455917358</v>
+        <v>4.33236408233643</v>
       </c>
       <c r="H127" t="n">
         <v>6687</v>
@@ -4371,7 +4371,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G138" t="n">
-        <v>4.81075811386108</v>
+        <v>4.81075763702393</v>
       </c>
       <c r="H138" t="n">
         <v>13168</v>
@@ -4458,7 +4458,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G141" t="n">
-        <v>4.93594455718994</v>
+        <v>4.9359450340271</v>
       </c>
       <c r="H141" t="n">
         <v>96218</v>
@@ -4487,7 +4487,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G142" t="n">
-        <v>4.86440944671631</v>
+        <v>4.86440896987915</v>
       </c>
       <c r="H142" t="n">
         <v>86543</v>
@@ -4516,7 +4516,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G143" t="n">
-        <v>4.79287385940552</v>
+        <v>4.79287433624268</v>
       </c>
       <c r="H143" t="n">
         <v>12914</v>
@@ -4661,7 +4661,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G148" t="n">
-        <v>5.22208690643311</v>
+        <v>5.22208642959595</v>
       </c>
       <c r="H148" t="n">
         <v>48197</v>
@@ -4690,7 +4690,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G149" t="n">
-        <v>5.18631887435913</v>
+        <v>5.18631935119629</v>
       </c>
       <c r="H149" t="n">
         <v>94640</v>
@@ -4748,7 +4748,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G151" t="n">
-        <v>5.18631887435913</v>
+        <v>5.18631935119629</v>
       </c>
       <c r="H151" t="n">
         <v>10180</v>
@@ -4777,7 +4777,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G152" t="n">
-        <v>5.23102807998657</v>
+        <v>5.23102855682373</v>
       </c>
       <c r="H152" t="n">
         <v>20268</v>
@@ -4806,7 +4806,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G153" t="n">
-        <v>5.16843509674072</v>
+        <v>5.16843461990356</v>
       </c>
       <c r="H153" t="n">
         <v>62349</v>
@@ -4893,7 +4893,7 @@
         <v>5.6100001335144</v>
       </c>
       <c r="G156" t="n">
-        <v>5.01642227172852</v>
+        <v>5.01642179489136</v>
       </c>
       <c r="H156" t="n">
         <v>19697</v>
@@ -4980,7 +4980,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G159" t="n">
-        <v>4.95382881164551</v>
+        <v>4.95382833480835</v>
       </c>
       <c r="H159" t="n">
         <v>26457</v>
@@ -5009,7 +5009,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G160" t="n">
-        <v>5.09689903259277</v>
+        <v>5.09689950942993</v>
       </c>
       <c r="H160" t="n">
         <v>13151</v>
@@ -5038,7 +5038,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G161" t="n">
-        <v>5.18631887435913</v>
+        <v>5.18631935119629</v>
       </c>
       <c r="H161" t="n">
         <v>25073</v>
@@ -5067,7 +5067,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G162" t="n">
-        <v>5.09689903259277</v>
+        <v>5.09689950942993</v>
       </c>
       <c r="H162" t="n">
         <v>60968</v>
@@ -5125,7 +5125,7 @@
         <v>5.69000005722046</v>
       </c>
       <c r="G164" t="n">
-        <v>5.08795738220215</v>
+        <v>5.08795785903931</v>
       </c>
       <c r="H164" t="n">
         <v>9415</v>
@@ -5183,7 +5183,7 @@
         <v>5.67000007629395</v>
       </c>
       <c r="G166" t="n">
-        <v>5.0700740814209</v>
+        <v>5.07007360458374</v>
       </c>
       <c r="H166" t="n">
         <v>8659</v>
@@ -5386,7 +5386,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G173" t="n">
-        <v>5.07901525497437</v>
+        <v>5.07901573181152</v>
       </c>
       <c r="H173" t="n">
         <v>8390</v>
@@ -5415,7 +5415,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G174" t="n">
-        <v>5.03430604934692</v>
+        <v>5.03430652618408</v>
       </c>
       <c r="H174" t="n">
         <v>11363</v>
@@ -5473,7 +5473,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G176" t="n">
-        <v>5.17737674713135</v>
+        <v>5.17737722396851</v>
       </c>
       <c r="H176" t="n">
         <v>15289</v>
@@ -5560,7 +5560,7 @@
         <v>5.90999984741211</v>
       </c>
       <c r="G179" t="n">
-        <v>5.28468036651611</v>
+        <v>5.28467988967896</v>
       </c>
       <c r="H179" t="n">
         <v>21763</v>
@@ -5618,7 +5618,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G181" t="n">
-        <v>5.436692237854</v>
+        <v>5.43669271469116</v>
       </c>
       <c r="H181" t="n">
         <v>65727</v>
@@ -5705,7 +5705,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G184" t="n">
-        <v>5.67812442779541</v>
+        <v>5.67812490463257</v>
       </c>
       <c r="H184" t="n">
         <v>135409</v>
@@ -5734,7 +5734,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G185" t="n">
-        <v>5.70495080947876</v>
+        <v>5.7049503326416</v>
       </c>
       <c r="H185" t="n">
         <v>70596</v>
@@ -5908,7 +5908,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G191" t="n">
-        <v>6.21464061737061</v>
+        <v>6.21464014053345</v>
       </c>
       <c r="H191" t="n">
         <v>39877</v>
@@ -5937,7 +5937,7 @@
         <v>6.80999994277954</v>
       </c>
       <c r="G192" t="n">
-        <v>6.08945322036743</v>
+        <v>6.08945369720459</v>
       </c>
       <c r="H192" t="n">
         <v>86712</v>
@@ -5966,7 +5966,7 @@
         <v>7</v>
       </c>
       <c r="G193" t="n">
-        <v>6.25934982299805</v>
+        <v>6.25935029983521</v>
       </c>
       <c r="H193" t="n">
         <v>64859</v>
@@ -5995,7 +5995,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G194" t="n">
-        <v>6.18781518936157</v>
+        <v>6.18781471252441</v>
       </c>
       <c r="H194" t="n">
         <v>195087</v>
@@ -6024,7 +6024,7 @@
         <v>6.90999984741211</v>
       </c>
       <c r="G195" t="n">
-        <v>6.17887258529663</v>
+        <v>6.17887306213379</v>
       </c>
       <c r="H195" t="n">
         <v>47173</v>
@@ -6082,7 +6082,7 @@
         <v>7</v>
       </c>
       <c r="G197" t="n">
-        <v>6.25934982299805</v>
+        <v>6.25935029983521</v>
       </c>
       <c r="H197" t="n">
         <v>92157</v>
@@ -6169,7 +6169,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G200" t="n">
-        <v>6.21464061737061</v>
+        <v>6.21464014053345</v>
       </c>
       <c r="H200" t="n">
         <v>49278</v>
@@ -6198,7 +6198,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G201" t="n">
-        <v>6.27723455429077</v>
+        <v>6.27723407745361</v>
       </c>
       <c r="H201" t="n">
         <v>56777</v>
@@ -6256,7 +6256,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G203" t="n">
-        <v>6.52760791778564</v>
+        <v>6.5276083946228</v>
       </c>
       <c r="H203" t="n">
         <v>138551</v>
@@ -6343,7 +6343,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G206" t="n">
-        <v>6.30406045913696</v>
+        <v>6.3040599822998</v>
       </c>
       <c r="H206" t="n">
         <v>51631</v>
@@ -6604,7 +6604,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G215" t="n">
-        <v>6.66173696517944</v>
+        <v>6.66173648834229</v>
       </c>
       <c r="H215" t="n">
         <v>95402</v>
@@ -6662,7 +6662,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G217" t="n">
-        <v>6.4203052520752</v>
+        <v>6.42030477523804</v>
       </c>
       <c r="H217" t="n">
         <v>143048</v>
@@ -6691,7 +6691,7 @@
         <v>7.53000020980835</v>
       </c>
       <c r="G218" t="n">
-        <v>6.73327207565308</v>
+        <v>6.73327255249023</v>
       </c>
       <c r="H218" t="n">
         <v>97258</v>
@@ -6749,7 +6749,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G220" t="n">
-        <v>6.60808563232422</v>
+        <v>6.60808515548706</v>
       </c>
       <c r="H220" t="n">
         <v>64845</v>
@@ -6778,7 +6778,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G221" t="n">
-        <v>6.45607280731201</v>
+        <v>6.45607233047485</v>
       </c>
       <c r="H221" t="n">
         <v>66909</v>
@@ -6865,7 +6865,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G224" t="n">
-        <v>6.66173696517944</v>
+        <v>6.66173648834229</v>
       </c>
       <c r="H224" t="n">
         <v>30693</v>
@@ -6923,7 +6923,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G226" t="n">
-        <v>6.50972461700439</v>
+        <v>6.50972414016724</v>
       </c>
       <c r="H226" t="n">
         <v>94459</v>
@@ -6952,7 +6952,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G227" t="n">
-        <v>6.58125925064087</v>
+        <v>6.58125972747803</v>
       </c>
       <c r="H227" t="n">
         <v>33666</v>
@@ -6981,7 +6981,7 @@
         <v>7.53000020980835</v>
       </c>
       <c r="G228" t="n">
-        <v>6.73327207565308</v>
+        <v>6.73327255249023</v>
       </c>
       <c r="H228" t="n">
         <v>150431</v>
@@ -7039,7 +7039,7 @@
         <v>7.98999977111816</v>
       </c>
       <c r="G230" t="n">
-        <v>7.14460134506226</v>
+        <v>7.1446008682251</v>
       </c>
       <c r="H230" t="n">
         <v>156690</v>
@@ -7068,7 +7068,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G231" t="n">
-        <v>7.36814880371094</v>
+        <v>7.3681492805481</v>
       </c>
       <c r="H231" t="n">
         <v>165049</v>
@@ -7097,7 +7097,7 @@
         <v>8.56999969482422</v>
       </c>
       <c r="G232" t="n">
-        <v>7.66323328018188</v>
+        <v>7.66323280334473</v>
       </c>
       <c r="H232" t="n">
         <v>214841</v>
@@ -7126,7 +7126,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G233" t="n">
-        <v>7.63640642166138</v>
+        <v>7.63640689849854</v>
       </c>
       <c r="H233" t="n">
         <v>144356</v>
@@ -7184,7 +7184,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G235" t="n">
-        <v>7.65429210662842</v>
+        <v>7.6542911529541</v>
       </c>
       <c r="H235" t="n">
         <v>82796</v>
@@ -7213,7 +7213,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G236" t="n">
-        <v>7.35920715332031</v>
+        <v>7.35920667648315</v>
       </c>
       <c r="H236" t="n">
         <v>253702</v>
@@ -7242,7 +7242,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G237" t="n">
-        <v>7.35920715332031</v>
+        <v>7.35920667648315</v>
       </c>
       <c r="H237" t="n">
         <v>172849</v>
@@ -7271,7 +7271,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G238" t="n">
-        <v>7.73476886749268</v>
+        <v>7.73476839065552</v>
       </c>
       <c r="H238" t="n">
         <v>113648</v>
@@ -7300,7 +7300,7 @@
         <v>8.75</v>
       </c>
       <c r="G239" t="n">
-        <v>7.82418775558472</v>
+        <v>7.82418727874756</v>
       </c>
       <c r="H239" t="n">
         <v>92729</v>
@@ -7329,7 +7329,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G240" t="n">
-        <v>7.86889696121216</v>
+        <v>7.86889791488647</v>
       </c>
       <c r="H240" t="n">
         <v>95722</v>
@@ -7358,7 +7358,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G241" t="n">
-        <v>7.94043254852295</v>
+        <v>7.94043302536011</v>
       </c>
       <c r="H241" t="n">
         <v>150011</v>
@@ -7416,7 +7416,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G243" t="n">
-        <v>7.73476886749268</v>
+        <v>7.73476839065552</v>
       </c>
       <c r="H243" t="n">
         <v>250001</v>
@@ -7445,7 +7445,7 @@
         <v>8.60999965667725</v>
       </c>
       <c r="G244" t="n">
-        <v>7.6990008354187</v>
+        <v>7.69899988174438</v>
       </c>
       <c r="H244" t="n">
         <v>102832</v>
@@ -7532,7 +7532,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G247" t="n">
-        <v>7.64534997940063</v>
+        <v>7.64534902572632</v>
       </c>
       <c r="H247" t="n">
         <v>105886</v>
@@ -7561,7 +7561,7 @@
         <v>8.63000011444092</v>
       </c>
       <c r="G248" t="n">
-        <v>7.71688508987427</v>
+        <v>7.71688461303711</v>
       </c>
       <c r="H248" t="n">
         <v>49730</v>
@@ -7590,7 +7590,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G249" t="n">
-        <v>7.73476886749268</v>
+        <v>7.73476839065552</v>
       </c>
       <c r="H249" t="n">
         <v>51008</v>
@@ -7735,7 +7735,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G254" t="n">
-        <v>7.81047248840332</v>
+        <v>7.81047344207764</v>
       </c>
       <c r="H254" t="n">
         <v>152971</v>
@@ -7793,7 +7793,7 @@
         <v>8.52999973297119</v>
       </c>
       <c r="G256" t="n">
-        <v>7.87509775161743</v>
+        <v>7.87509870529175</v>
       </c>
       <c r="H256" t="n">
         <v>99895</v>
@@ -7996,7 +7996,7 @@
         <v>8.60999965667725</v>
       </c>
       <c r="G263" t="n">
-        <v>7.94895648956299</v>
+        <v>7.94895553588867</v>
       </c>
       <c r="H263" t="n">
         <v>76537</v>
@@ -8141,7 +8141,7 @@
         <v>8.60999965667725</v>
       </c>
       <c r="G268" t="n">
-        <v>7.94895648956299</v>
+        <v>7.94895553588867</v>
       </c>
       <c r="H268" t="n">
         <v>61503</v>
@@ -8199,7 +8199,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G270" t="n">
-        <v>7.95818901062012</v>
+        <v>7.95818853378296</v>
       </c>
       <c r="H270" t="n">
         <v>77829</v>
@@ -8460,7 +8460,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G279" t="n">
-        <v>7.42271852493286</v>
+        <v>7.42271900177002</v>
       </c>
       <c r="H279" t="n">
         <v>56062</v>
@@ -8518,7 +8518,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G281" t="n">
-        <v>7.49657678604126</v>
+        <v>7.4965763092041</v>
       </c>
       <c r="H281" t="n">
         <v>39852</v>
@@ -8605,7 +8605,7 @@
         <v>7.80999994277954</v>
       </c>
       <c r="G284" t="n">
-        <v>7.21037721633911</v>
+        <v>7.21037769317627</v>
       </c>
       <c r="H284" t="n">
         <v>117674</v>
@@ -8634,7 +8634,7 @@
         <v>7.71000003814697</v>
       </c>
       <c r="G285" t="n">
-        <v>7.11805486679077</v>
+        <v>7.11805534362793</v>
       </c>
       <c r="H285" t="n">
         <v>57382</v>
@@ -8663,7 +8663,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G286" t="n">
-        <v>7.0534291267395</v>
+        <v>7.05342960357666</v>
       </c>
       <c r="H286" t="n">
         <v>74446</v>
@@ -8692,7 +8692,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G287" t="n">
-        <v>7.10882234573364</v>
+        <v>7.1088228225708</v>
       </c>
       <c r="H287" t="n">
         <v>108157</v>
@@ -8721,7 +8721,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G288" t="n">
-        <v>6.97033977508545</v>
+        <v>6.97033929824829</v>
       </c>
       <c r="H288" t="n">
         <v>37819</v>
@@ -8750,7 +8750,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G289" t="n">
-        <v>6.97033977508545</v>
+        <v>6.97033929824829</v>
       </c>
       <c r="H289" t="n">
         <v>41222</v>
@@ -8953,7 +8953,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G296" t="n">
-        <v>7.30270004272461</v>
+        <v>7.30269956588745</v>
       </c>
       <c r="H296" t="n">
         <v>83813</v>
@@ -8982,7 +8982,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G297" t="n">
-        <v>7.145751953125</v>
+        <v>7.14575147628784</v>
       </c>
       <c r="H297" t="n">
         <v>43493</v>
@@ -9069,7 +9069,7 @@
         <v>7.78999996185303</v>
       </c>
       <c r="G300" t="n">
-        <v>7.19191312789917</v>
+        <v>7.19191265106201</v>
       </c>
       <c r="H300" t="n">
         <v>50892</v>
@@ -9330,7 +9330,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G309" t="n">
-        <v>6.93341016769409</v>
+        <v>6.93341064453125</v>
       </c>
       <c r="H309" t="n">
         <v>19291</v>
@@ -9359,7 +9359,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G310" t="n">
-        <v>6.97033977508545</v>
+        <v>6.97033929824829</v>
       </c>
       <c r="H310" t="n">
         <v>22938</v>
@@ -9388,7 +9388,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G311" t="n">
-        <v>6.87801694869995</v>
+        <v>6.87801647186279</v>
       </c>
       <c r="H311" t="n">
         <v>39307</v>
@@ -9417,7 +9417,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G312" t="n">
-        <v>7.03496503829956</v>
+        <v>7.0349645614624</v>
       </c>
       <c r="H312" t="n">
         <v>19565</v>
@@ -9533,7 +9533,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G316" t="n">
-        <v>6.97033977508545</v>
+        <v>6.97033929824829</v>
       </c>
       <c r="H316" t="n">
         <v>31066</v>
@@ -9591,7 +9591,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G318" t="n">
-        <v>7.42271852493286</v>
+        <v>7.42271900177002</v>
       </c>
       <c r="H318" t="n">
         <v>77225</v>
@@ -9678,7 +9678,7 @@
         <v>7.78999996185303</v>
       </c>
       <c r="G321" t="n">
-        <v>7.19191312789917</v>
+        <v>7.19191265106201</v>
       </c>
       <c r="H321" t="n">
         <v>21141</v>
@@ -9823,7 +9823,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G326" t="n">
-        <v>7.10882234573364</v>
+        <v>7.1088228225708</v>
       </c>
       <c r="H326" t="n">
         <v>18088</v>
@@ -9852,7 +9852,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G327" t="n">
-        <v>6.97033977508545</v>
+        <v>6.97033929824829</v>
       </c>
       <c r="H327" t="n">
         <v>69708</v>
@@ -9881,7 +9881,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G328" t="n">
-        <v>7.13651990890503</v>
+        <v>7.13651943206787</v>
       </c>
       <c r="H328" t="n">
         <v>33278</v>
@@ -9910,7 +9910,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G329" t="n">
-        <v>7.0534291267395</v>
+        <v>7.05342960357666</v>
       </c>
       <c r="H329" t="n">
         <v>17493</v>
@@ -9997,7 +9997,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G332" t="n">
-        <v>6.93341016769409</v>
+        <v>6.93341064453125</v>
       </c>
       <c r="H332" t="n">
         <v>24732</v>
@@ -10026,7 +10026,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G333" t="n">
-        <v>7.0534291267395</v>
+        <v>7.05342960357666</v>
       </c>
       <c r="H333" t="n">
         <v>18353</v>
@@ -10084,7 +10084,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G335" t="n">
-        <v>7.0534291267395</v>
+        <v>7.05342960357666</v>
       </c>
       <c r="H335" t="n">
         <v>11054</v>
@@ -10345,7 +10345,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G344" t="n">
-        <v>6.97033977508545</v>
+        <v>6.97033929824829</v>
       </c>
       <c r="H344" t="n">
         <v>42139</v>
@@ -10403,7 +10403,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G346" t="n">
-        <v>7.145751953125</v>
+        <v>7.14575147628784</v>
       </c>
       <c r="H346" t="n">
         <v>47587</v>
@@ -10461,7 +10461,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G348" t="n">
-        <v>6.90571355819702</v>
+        <v>6.90571403503418</v>
       </c>
       <c r="H348" t="n">
         <v>60152</v>
@@ -10519,7 +10519,7 @@
         <v>7.53999996185303</v>
       </c>
       <c r="G350" t="n">
-        <v>6.96110677719116</v>
+        <v>6.96110725402832</v>
       </c>
       <c r="H350" t="n">
         <v>28852</v>
@@ -10548,7 +10548,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G351" t="n">
-        <v>6.77646207809448</v>
+        <v>6.77646255493164</v>
       </c>
       <c r="H351" t="n">
         <v>58129</v>
@@ -10664,7 +10664,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G355" t="n">
-        <v>6.53642416000366</v>
+        <v>6.5364236831665</v>
       </c>
       <c r="H355" t="n">
         <v>26264</v>
@@ -10809,7 +10809,7 @@
         <v>6.98999977111816</v>
       </c>
       <c r="G360" t="n">
-        <v>6.45333337783813</v>
+        <v>6.45333385467529</v>
       </c>
       <c r="H360" t="n">
         <v>50111</v>
@@ -10867,7 +10867,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G362" t="n">
-        <v>6.6472110748291</v>
+        <v>6.64721059799194</v>
       </c>
       <c r="H362" t="n">
         <v>58993</v>
@@ -10896,7 +10896,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G363" t="n">
-        <v>6.40717267990112</v>
+        <v>6.40717315673828</v>
       </c>
       <c r="H363" t="n">
         <v>39953</v>
@@ -10925,7 +10925,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G364" t="n">
-        <v>6.63797903060913</v>
+        <v>6.63797855377197</v>
       </c>
       <c r="H364" t="n">
         <v>33892</v>
@@ -11012,7 +11012,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G367" t="n">
-        <v>6.48103094100952</v>
+        <v>6.48103046417236</v>
       </c>
       <c r="H367" t="n">
         <v>37646</v>
@@ -11041,7 +11041,7 @@
         <v>7.09000015258789</v>
       </c>
       <c r="G368" t="n">
-        <v>6.54565668106079</v>
+        <v>6.54565620422363</v>
       </c>
       <c r="H368" t="n">
         <v>45957</v>
@@ -11099,7 +11099,7 @@
         <v>7.09000015258789</v>
       </c>
       <c r="G370" t="n">
-        <v>6.54565668106079</v>
+        <v>6.54565620422363</v>
       </c>
       <c r="H370" t="n">
         <v>28684</v>
@@ -11128,7 +11128,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G371" t="n">
-        <v>6.63797903060913</v>
+        <v>6.63797855377197</v>
       </c>
       <c r="H371" t="n">
         <v>24535</v>
@@ -11186,7 +11186,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G373" t="n">
-        <v>6.32408285140991</v>
+        <v>6.32408237457275</v>
       </c>
       <c r="H373" t="n">
         <v>47509</v>
@@ -11215,7 +11215,7 @@
         <v>7</v>
       </c>
       <c r="G374" t="n">
-        <v>6.46256589889526</v>
+        <v>6.46256637573242</v>
       </c>
       <c r="H374" t="n">
         <v>17115</v>
@@ -11476,7 +11476,7 @@
         <v>7.09000015258789</v>
       </c>
       <c r="G383" t="n">
-        <v>6.54565668106079</v>
+        <v>6.54565620422363</v>
       </c>
       <c r="H383" t="n">
         <v>39879</v>
@@ -11592,7 +11592,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G387" t="n">
-        <v>6.61028146743774</v>
+        <v>6.6102819442749</v>
       </c>
       <c r="H387" t="n">
         <v>59425</v>
@@ -11650,7 +11650,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G389" t="n">
-        <v>6.87801694869995</v>
+        <v>6.87801647186279</v>
       </c>
       <c r="H389" t="n">
         <v>91784</v>
@@ -11679,7 +11679,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G390" t="n">
-        <v>7.13651990890503</v>
+        <v>7.13651943206787</v>
       </c>
       <c r="H390" t="n">
         <v>203114</v>
@@ -11766,7 +11766,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G393" t="n">
-        <v>7.30270004272461</v>
+        <v>7.30269956588745</v>
       </c>
       <c r="H393" t="n">
         <v>167425</v>
@@ -11795,7 +11795,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G394" t="n">
-        <v>7.2011456489563</v>
+        <v>7.20114517211914</v>
       </c>
       <c r="H394" t="n">
         <v>191654</v>
@@ -11853,7 +11853,7 @@
         <v>7.86999988555908</v>
       </c>
       <c r="G396" t="n">
-        <v>7.26577043533325</v>
+        <v>7.26577091217041</v>
       </c>
       <c r="H396" t="n">
         <v>50620</v>
@@ -11911,7 +11911,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G398" t="n">
-        <v>7.30270004272461</v>
+        <v>7.30269956588745</v>
       </c>
       <c r="H398" t="n">
         <v>99717</v>
@@ -11940,7 +11940,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G399" t="n">
-        <v>7.36732530593872</v>
+        <v>7.36732578277588</v>
       </c>
       <c r="H399" t="n">
         <v>124059</v>
@@ -11969,7 +11969,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G400" t="n">
-        <v>7.24730634689331</v>
+        <v>7.24730587005615</v>
       </c>
       <c r="H400" t="n">
         <v>72121</v>
@@ -12114,7 +12114,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G405" t="n">
-        <v>7.30270004272461</v>
+        <v>7.30269956588745</v>
       </c>
       <c r="H405" t="n">
         <v>38438</v>
@@ -12636,7 +12636,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G423" t="n">
-        <v>7.40425491333008</v>
+        <v>7.40425443649292</v>
       </c>
       <c r="H423" t="n">
         <v>48656</v>
@@ -12752,7 +12752,7 @@
         <v>8.25</v>
       </c>
       <c r="G427" t="n">
-        <v>7.61659574508667</v>
+        <v>7.61659622192383</v>
       </c>
       <c r="H427" t="n">
         <v>55700</v>
@@ -12810,7 +12810,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G429" t="n">
-        <v>7.90279626846313</v>
+        <v>7.90279531478882</v>
       </c>
       <c r="H429" t="n">
         <v>122032</v>
@@ -12984,7 +12984,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G435" t="n">
-        <v>8.63214302062988</v>
+        <v>8.63214206695557</v>
       </c>
       <c r="H435" t="n">
         <v>236669</v>
@@ -13158,7 +13158,7 @@
         <v>9.6899995803833</v>
       </c>
       <c r="G441" t="n">
-        <v>8.94603824615479</v>
+        <v>8.94603729248047</v>
       </c>
       <c r="H441" t="n">
         <v>85296</v>
@@ -13216,7 +13216,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G443" t="n">
-        <v>8.9921989440918</v>
+        <v>8.99219989776611</v>
       </c>
       <c r="H443" t="n">
         <v>101160</v>
@@ -13477,7 +13477,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G452" t="n">
-        <v>9.52766799926758</v>
+        <v>9.52766895294189</v>
       </c>
       <c r="H452" t="n">
         <v>186778</v>
@@ -13506,7 +13506,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G453" t="n">
-        <v>9.61999225616455</v>
+        <v>9.61999130249023</v>
       </c>
       <c r="H453" t="n">
         <v>106036</v>
@@ -13535,7 +13535,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G454" t="n">
-        <v>9.4168815612793</v>
+        <v>9.41688251495361</v>
       </c>
       <c r="H454" t="n">
         <v>85544</v>
@@ -13593,7 +13593,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G456" t="n">
-        <v>9.25070285797119</v>
+        <v>9.25070190429688</v>
       </c>
       <c r="H456" t="n">
         <v>45013</v>
@@ -13651,7 +13651,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G458" t="n">
-        <v>9.26916694641113</v>
+        <v>9.26916599273682</v>
       </c>
       <c r="H458" t="n">
         <v>73523</v>
@@ -13825,7 +13825,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G464" t="n">
-        <v>9.26916694641113</v>
+        <v>9.26916599273682</v>
       </c>
       <c r="H464" t="n">
         <v>35262</v>
@@ -13883,7 +13883,7 @@
         <v>9.98999977111816</v>
       </c>
       <c r="G466" t="n">
-        <v>9.22300434112549</v>
+        <v>9.2230052947998</v>
       </c>
       <c r="H466" t="n">
         <v>90490</v>
@@ -13999,7 +13999,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G470" t="n">
-        <v>9.61999225616455</v>
+        <v>9.61999130249023</v>
       </c>
       <c r="H470" t="n">
         <v>91656</v>
@@ -14028,7 +14028,7 @@
         <v>10.4799995422363</v>
       </c>
       <c r="G471" t="n">
-        <v>9.67538452148438</v>
+        <v>9.67538356781006</v>
       </c>
       <c r="H471" t="n">
         <v>94908</v>
@@ -14173,7 +14173,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G476" t="n">
-        <v>9.61999225616455</v>
+        <v>9.61999130249023</v>
       </c>
       <c r="H476" t="n">
         <v>55619</v>
@@ -14202,7 +14202,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G477" t="n">
-        <v>9.58306312561035</v>
+        <v>9.58306217193604</v>
       </c>
       <c r="H477" t="n">
         <v>68414</v>
@@ -14289,7 +14289,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G480" t="n">
-        <v>10.247784614563</v>
+        <v>10.2477836608887</v>
       </c>
       <c r="H480" t="n">
         <v>121664</v>
@@ -14318,7 +14318,7 @@
         <v>11.1199998855591</v>
       </c>
       <c r="G481" t="n">
-        <v>10.2662487030029</v>
+        <v>10.2662477493286</v>
       </c>
       <c r="H481" t="n">
         <v>62344</v>
@@ -14347,7 +14347,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G482" t="n">
-        <v>8.93680667877197</v>
+        <v>8.93680572509766</v>
       </c>
       <c r="H482" t="n">
         <v>1087677</v>
@@ -14376,7 +14376,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G483" t="n">
-        <v>9.28763198852539</v>
+        <v>9.28763103485107</v>
       </c>
       <c r="H483" t="n">
         <v>332225</v>
@@ -14405,7 +14405,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G484" t="n">
-        <v>9.21377182006836</v>
+        <v>9.21377277374268</v>
       </c>
       <c r="H484" t="n">
         <v>153862</v>
@@ -14521,7 +14521,7 @@
         <v>9.63000011444092</v>
       </c>
       <c r="G488" t="n">
-        <v>8.89064407348633</v>
+        <v>8.89064502716064</v>
       </c>
       <c r="H488" t="n">
         <v>74178</v>
@@ -14695,7 +14695,7 @@
         <v>9.28999996185303</v>
       </c>
       <c r="G494" t="n">
-        <v>8.57674884796143</v>
+        <v>8.57674789428711</v>
       </c>
       <c r="H494" t="n">
         <v>136448</v>
@@ -14724,7 +14724,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G495" t="n">
-        <v>8.48442554473877</v>
+        <v>8.48442649841309</v>
       </c>
       <c r="H495" t="n">
         <v>37699</v>
@@ -14840,7 +14840,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G499" t="n">
-        <v>8.62291049957275</v>
+        <v>8.62290954589844</v>
       </c>
       <c r="H499" t="n">
         <v>120557</v>
@@ -14898,7 +14898,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G501" t="n">
-        <v>8.62291049957275</v>
+        <v>8.62290954589844</v>
       </c>
       <c r="H501" t="n">
         <v>49932</v>
@@ -14956,7 +14956,7 @@
         <v>9.6899995803833</v>
       </c>
       <c r="G503" t="n">
-        <v>8.94603824615479</v>
+        <v>8.94603729248047</v>
       </c>
       <c r="H503" t="n">
         <v>146163</v>
@@ -14985,7 +14985,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G504" t="n">
-        <v>8.86294746398926</v>
+        <v>8.86294841766357</v>
       </c>
       <c r="H504" t="n">
         <v>41942</v>
@@ -15188,7 +15188,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G511" t="n">
-        <v>8.78909015655518</v>
+        <v>8.78909111022949</v>
       </c>
       <c r="H511" t="n">
         <v>113583</v>
@@ -15246,7 +15246,7 @@
         <v>9.8100004196167</v>
       </c>
       <c r="G513" t="n">
-        <v>9.05682563781738</v>
+        <v>9.05682468414307</v>
       </c>
       <c r="H513" t="n">
         <v>107598</v>
@@ -15333,7 +15333,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G516" t="n">
-        <v>8.95527076721191</v>
+        <v>8.9552698135376</v>
       </c>
       <c r="H516" t="n">
         <v>76374</v>
@@ -33261,6 +33261,35 @@
         <v>1428658</v>
       </c>
       <c r="I1134" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1135">
+      <c r="A1135" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1135" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C1135" t="n">
+        <v>0.677999973297119</v>
+      </c>
+      <c r="D1135" t="n">
+        <v>0.680000007152557</v>
+      </c>
+      <c r="E1135" t="n">
+        <v>0.589999973773956</v>
+      </c>
+      <c r="F1135" t="n">
+        <v>0.660000026226044</v>
+      </c>
+      <c r="G1135" t="n">
+        <v>0.660000026226044</v>
+      </c>
+      <c r="H1135" t="n">
+        <v>1061843</v>
+      </c>
+      <c r="I1135" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/TISG.MI.xlsx
+++ b/data/TISG.MI.xlsx
@@ -456,7 +456,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G3" t="n">
-        <v>5.12372541427612</v>
+        <v>5.12372589111328</v>
       </c>
       <c r="H3" t="n">
         <v>28276</v>
@@ -485,7 +485,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G4" t="n">
-        <v>5.16843461990356</v>
+        <v>5.16843509674072</v>
       </c>
       <c r="H4" t="n">
         <v>13258</v>
@@ -572,7 +572,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G7" t="n">
-        <v>4.94488716125488</v>
+        <v>4.94488668441772</v>
       </c>
       <c r="H7" t="n">
         <v>13883</v>
@@ -746,7 +746,7 @@
         <v>5.6100001335144</v>
       </c>
       <c r="G13" t="n">
-        <v>5.01642179489136</v>
+        <v>5.01642227172852</v>
       </c>
       <c r="H13" t="n">
         <v>20247</v>
@@ -833,7 +833,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G16" t="n">
-        <v>5.03430652618408</v>
+        <v>5.03430604934692</v>
       </c>
       <c r="H16" t="n">
         <v>20391</v>
@@ -862,7 +862,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G17" t="n">
-        <v>4.96277046203613</v>
+        <v>4.96277093887329</v>
       </c>
       <c r="H17" t="n">
         <v>9297</v>
@@ -891,7 +891,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G18" t="n">
-        <v>4.9359450340271</v>
+        <v>4.93594455718994</v>
       </c>
       <c r="H18" t="n">
         <v>2331</v>
@@ -920,7 +920,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G19" t="n">
-        <v>4.94488716125488</v>
+        <v>4.94488668441772</v>
       </c>
       <c r="H19" t="n">
         <v>8685</v>
@@ -978,7 +978,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G21" t="n">
-        <v>5.02536392211914</v>
+        <v>5.0253643989563</v>
       </c>
       <c r="H21" t="n">
         <v>16980</v>
@@ -1007,7 +1007,7 @@
         <v>5.6100001335144</v>
       </c>
       <c r="G22" t="n">
-        <v>5.01642179489136</v>
+        <v>5.01642227172852</v>
       </c>
       <c r="H22" t="n">
         <v>57978</v>
@@ -1094,7 +1094,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G25" t="n">
-        <v>4.64086103439331</v>
+        <v>4.64086151123047</v>
       </c>
       <c r="H25" t="n">
         <v>38675</v>
@@ -1268,7 +1268,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G31" t="n">
-        <v>4.65874481201172</v>
+        <v>4.65874528884888</v>
       </c>
       <c r="H31" t="n">
         <v>18744</v>
@@ -1297,7 +1297,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G32" t="n">
-        <v>4.68557024002075</v>
+        <v>4.68557071685791</v>
       </c>
       <c r="H32" t="n">
         <v>47444</v>
@@ -1326,7 +1326,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G33" t="n">
-        <v>4.68557024002075</v>
+        <v>4.68557071685791</v>
       </c>
       <c r="H33" t="n">
         <v>11521</v>
@@ -1355,7 +1355,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G34" t="n">
-        <v>4.68557024002075</v>
+        <v>4.68557071685791</v>
       </c>
       <c r="H34" t="n">
         <v>15121</v>
@@ -1384,7 +1384,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G35" t="n">
-        <v>4.64086103439331</v>
+        <v>4.64086151123047</v>
       </c>
       <c r="H35" t="n">
         <v>71434</v>
@@ -1529,7 +1529,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G40" t="n">
-        <v>4.3368353843689</v>
+        <v>4.33683586120605</v>
       </c>
       <c r="H40" t="n">
         <v>82262</v>
@@ -1587,7 +1587,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G42" t="n">
-        <v>4.40837097167969</v>
+        <v>4.40837049484253</v>
       </c>
       <c r="H42" t="n">
         <v>18554</v>
@@ -1674,7 +1674,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G45" t="n">
-        <v>4.39048671722412</v>
+        <v>4.39048719406128</v>
       </c>
       <c r="H45" t="n">
         <v>25487</v>
@@ -1732,7 +1732,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G47" t="n">
-        <v>4.3368353843689</v>
+        <v>4.33683586120605</v>
       </c>
       <c r="H47" t="n">
         <v>57150</v>
@@ -1761,7 +1761,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G48" t="n">
-        <v>4.25635862350464</v>
+        <v>4.25635814666748</v>
       </c>
       <c r="H48" t="n">
         <v>16777</v>
@@ -1790,7 +1790,7 @@
         <v>4.84499979019165</v>
       </c>
       <c r="G49" t="n">
-        <v>4.33236408233643</v>
+        <v>4.33236455917358</v>
       </c>
       <c r="H49" t="n">
         <v>18567</v>
@@ -1848,7 +1848,7 @@
         <v>4.84499979019165</v>
       </c>
       <c r="G51" t="n">
-        <v>4.33236408233643</v>
+        <v>4.33236455917358</v>
       </c>
       <c r="H51" t="n">
         <v>13315</v>
@@ -1877,7 +1877,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G52" t="n">
-        <v>4.29212617874146</v>
+        <v>4.2921257019043</v>
       </c>
       <c r="H52" t="n">
         <v>24850</v>
@@ -1906,7 +1906,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G53" t="n">
-        <v>4.32789373397827</v>
+        <v>4.32789421081543</v>
       </c>
       <c r="H53" t="n">
         <v>8833</v>
@@ -2022,7 +2022,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G57" t="n">
-        <v>4.29212617874146</v>
+        <v>4.2921257019043</v>
       </c>
       <c r="H57" t="n">
         <v>9336</v>
@@ -2051,7 +2051,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G58" t="n">
-        <v>4.32789373397827</v>
+        <v>4.32789421081543</v>
       </c>
       <c r="H58" t="n">
         <v>17486</v>
@@ -2138,7 +2138,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G61" t="n">
-        <v>4.9359450340271</v>
+        <v>4.93594455718994</v>
       </c>
       <c r="H61" t="n">
         <v>80771</v>
@@ -2254,7 +2254,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G65" t="n">
-        <v>4.65874481201172</v>
+        <v>4.65874528884888</v>
       </c>
       <c r="H65" t="n">
         <v>15144</v>
@@ -2283,7 +2283,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G66" t="n">
-        <v>4.65874481201172</v>
+        <v>4.65874528884888</v>
       </c>
       <c r="H66" t="n">
         <v>14073</v>
@@ -2399,7 +2399,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G70" t="n">
-        <v>4.56038379669189</v>
+        <v>4.56038331985474</v>
       </c>
       <c r="H70" t="n">
         <v>18662</v>
@@ -2428,7 +2428,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G71" t="n">
-        <v>4.61403512954712</v>
+        <v>4.61403465270996</v>
       </c>
       <c r="H71" t="n">
         <v>5955</v>
@@ -2544,7 +2544,7 @@
         <v>4.9850001335144</v>
       </c>
       <c r="G75" t="n">
-        <v>4.45755195617676</v>
+        <v>4.4575514793396</v>
       </c>
       <c r="H75" t="n">
         <v>16465</v>
@@ -2573,7 +2573,7 @@
         <v>4.85500001907349</v>
       </c>
       <c r="G76" t="n">
-        <v>4.34130620956421</v>
+        <v>4.34130668640137</v>
       </c>
       <c r="H76" t="n">
         <v>21022</v>
@@ -2602,7 +2602,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G77" t="n">
-        <v>4.31000995635986</v>
+        <v>4.31000947952271</v>
       </c>
       <c r="H77" t="n">
         <v>12944</v>
@@ -2660,7 +2660,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G79" t="n">
-        <v>4.29212617874146</v>
+        <v>4.2921257019043</v>
       </c>
       <c r="H79" t="n">
         <v>26762</v>
@@ -2689,7 +2689,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G80" t="n">
-        <v>4.29212617874146</v>
+        <v>4.2921257019043</v>
       </c>
       <c r="H80" t="n">
         <v>10522</v>
@@ -2718,7 +2718,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G81" t="n">
-        <v>4.29212617874146</v>
+        <v>4.2921257019043</v>
       </c>
       <c r="H81" t="n">
         <v>38577</v>
@@ -2892,7 +2892,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G87" t="n">
-        <v>4.23847389221191</v>
+        <v>4.23847436904907</v>
       </c>
       <c r="H87" t="n">
         <v>24828</v>
@@ -2921,7 +2921,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G88" t="n">
-        <v>4.49779033660889</v>
+        <v>4.49779081344604</v>
       </c>
       <c r="H88" t="n">
         <v>22654</v>
@@ -2979,7 +2979,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G90" t="n">
-        <v>4.4888482093811</v>
+        <v>4.48884868621826</v>
       </c>
       <c r="H90" t="n">
         <v>27075</v>
@@ -3008,7 +3008,7 @@
         <v>4.85500001907349</v>
       </c>
       <c r="G91" t="n">
-        <v>4.34130620956421</v>
+        <v>4.34130668640137</v>
       </c>
       <c r="H91" t="n">
         <v>28795</v>
@@ -3037,7 +3037,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G92" t="n">
-        <v>4.40837097167969</v>
+        <v>4.40837049484253</v>
       </c>
       <c r="H92" t="n">
         <v>28839</v>
@@ -3153,7 +3153,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G96" t="n">
-        <v>4.29212617874146</v>
+        <v>4.2921257019043</v>
       </c>
       <c r="H96" t="n">
         <v>8412</v>
@@ -3240,7 +3240,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G99" t="n">
-        <v>4.35471963882446</v>
+        <v>4.3547191619873</v>
       </c>
       <c r="H99" t="n">
         <v>17935</v>
@@ -3414,7 +3414,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G105" t="n">
-        <v>3.90762233734131</v>
+        <v>3.90762281417847</v>
       </c>
       <c r="H105" t="n">
         <v>8913</v>
@@ -3472,7 +3472,7 @@
         <v>4.39499998092651</v>
       </c>
       <c r="G107" t="n">
-        <v>3.92997789382935</v>
+        <v>3.92997741699219</v>
       </c>
       <c r="H107" t="n">
         <v>9552</v>
@@ -3501,7 +3501,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G108" t="n">
-        <v>3.82714557647705</v>
+        <v>3.82714605331421</v>
       </c>
       <c r="H108" t="n">
         <v>26268</v>
@@ -3530,7 +3530,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G109" t="n">
-        <v>3.80926203727722</v>
+        <v>3.80926156044006</v>
       </c>
       <c r="H109" t="n">
         <v>5280</v>
@@ -3559,7 +3559,7 @@
         <v>4.2649998664856</v>
       </c>
       <c r="G110" t="n">
-        <v>3.81373286247253</v>
+        <v>3.81373238563538</v>
       </c>
       <c r="H110" t="n">
         <v>30391</v>
@@ -3646,7 +3646,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G113" t="n">
-        <v>3.75561022758484</v>
+        <v>3.75560975074768</v>
       </c>
       <c r="H113" t="n">
         <v>18855</v>
@@ -3733,7 +3733,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G116" t="n">
-        <v>4.17588090896606</v>
+        <v>4.17588138580322</v>
       </c>
       <c r="H116" t="n">
         <v>27523</v>
@@ -3907,7 +3907,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G122" t="n">
-        <v>4.25635862350464</v>
+        <v>4.25635814666748</v>
       </c>
       <c r="H122" t="n">
         <v>6911</v>
@@ -3936,7 +3936,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G123" t="n">
-        <v>4.29212617874146</v>
+        <v>4.2921257019043</v>
       </c>
       <c r="H123" t="n">
         <v>9894</v>
@@ -3965,7 +3965,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G124" t="n">
-        <v>4.29212617874146</v>
+        <v>4.2921257019043</v>
       </c>
       <c r="H124" t="n">
         <v>5737</v>
@@ -4052,7 +4052,7 @@
         <v>4.84499979019165</v>
       </c>
       <c r="G127" t="n">
-        <v>4.33236408233643</v>
+        <v>4.33236455917358</v>
       </c>
       <c r="H127" t="n">
         <v>6687</v>
@@ -4168,7 +4168,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G131" t="n">
-        <v>4.68557024002075</v>
+        <v>4.68557071685791</v>
       </c>
       <c r="H131" t="n">
         <v>35085</v>
@@ -4371,7 +4371,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G138" t="n">
-        <v>4.81075763702393</v>
+        <v>4.81075811386108</v>
       </c>
       <c r="H138" t="n">
         <v>13168</v>
@@ -4458,7 +4458,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G141" t="n">
-        <v>4.9359450340271</v>
+        <v>4.93594455718994</v>
       </c>
       <c r="H141" t="n">
         <v>96218</v>
@@ -4487,7 +4487,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G142" t="n">
-        <v>4.86440896987915</v>
+        <v>4.86440944671631</v>
       </c>
       <c r="H142" t="n">
         <v>86543</v>
@@ -4516,7 +4516,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G143" t="n">
-        <v>4.79287433624268</v>
+        <v>4.79287385940552</v>
       </c>
       <c r="H143" t="n">
         <v>12914</v>
@@ -4632,7 +4632,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G147" t="n">
-        <v>5.02536392211914</v>
+        <v>5.0253643989563</v>
       </c>
       <c r="H147" t="n">
         <v>22523</v>
@@ -4690,7 +4690,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G149" t="n">
-        <v>5.18631935119629</v>
+        <v>5.18631887435913</v>
       </c>
       <c r="H149" t="n">
         <v>94640</v>
@@ -4748,7 +4748,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G151" t="n">
-        <v>5.18631935119629</v>
+        <v>5.18631887435913</v>
       </c>
       <c r="H151" t="n">
         <v>10180</v>
@@ -4806,7 +4806,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G153" t="n">
-        <v>5.16843461990356</v>
+        <v>5.16843509674072</v>
       </c>
       <c r="H153" t="n">
         <v>62349</v>
@@ -4893,7 +4893,7 @@
         <v>5.6100001335144</v>
       </c>
       <c r="G156" t="n">
-        <v>5.01642179489136</v>
+        <v>5.01642227172852</v>
       </c>
       <c r="H156" t="n">
         <v>19697</v>
@@ -4951,7 +4951,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G158" t="n">
-        <v>5.02536392211914</v>
+        <v>5.0253643989563</v>
       </c>
       <c r="H158" t="n">
         <v>12170</v>
@@ -5009,7 +5009,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G160" t="n">
-        <v>5.09689950942993</v>
+        <v>5.09689903259277</v>
       </c>
       <c r="H160" t="n">
         <v>13151</v>
@@ -5038,7 +5038,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G161" t="n">
-        <v>5.18631935119629</v>
+        <v>5.18631887435913</v>
       </c>
       <c r="H161" t="n">
         <v>25073</v>
@@ -5067,7 +5067,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G162" t="n">
-        <v>5.09689950942993</v>
+        <v>5.09689903259277</v>
       </c>
       <c r="H162" t="n">
         <v>60968</v>
@@ -5125,7 +5125,7 @@
         <v>5.69000005722046</v>
       </c>
       <c r="G164" t="n">
-        <v>5.08795785903931</v>
+        <v>5.08795738220215</v>
       </c>
       <c r="H164" t="n">
         <v>9415</v>
@@ -5154,7 +5154,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G165" t="n">
-        <v>5.04324817657471</v>
+        <v>5.04324769973755</v>
       </c>
       <c r="H165" t="n">
         <v>16099</v>
@@ -5241,7 +5241,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G168" t="n">
-        <v>5.12372541427612</v>
+        <v>5.12372589111328</v>
       </c>
       <c r="H168" t="n">
         <v>13445</v>
@@ -5415,7 +5415,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G174" t="n">
-        <v>5.03430652618408</v>
+        <v>5.03430604934692</v>
       </c>
       <c r="H174" t="n">
         <v>11363</v>
@@ -5531,7 +5531,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G178" t="n">
-        <v>5.12372541427612</v>
+        <v>5.12372589111328</v>
       </c>
       <c r="H178" t="n">
         <v>13789</v>
@@ -5560,7 +5560,7 @@
         <v>5.90999984741211</v>
       </c>
       <c r="G179" t="n">
-        <v>5.28467988967896</v>
+        <v>5.28468036651611</v>
       </c>
       <c r="H179" t="n">
         <v>21763</v>
@@ -5734,7 +5734,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G185" t="n">
-        <v>5.7049503326416</v>
+        <v>5.70495080947876</v>
       </c>
       <c r="H185" t="n">
         <v>70596</v>
@@ -5937,7 +5937,7 @@
         <v>6.80999994277954</v>
       </c>
       <c r="G192" t="n">
-        <v>6.08945369720459</v>
+        <v>6.08945322036743</v>
       </c>
       <c r="H192" t="n">
         <v>86712</v>
@@ -5966,7 +5966,7 @@
         <v>7</v>
       </c>
       <c r="G193" t="n">
-        <v>6.25935029983521</v>
+        <v>6.25934982299805</v>
       </c>
       <c r="H193" t="n">
         <v>64859</v>
@@ -6082,7 +6082,7 @@
         <v>7</v>
       </c>
       <c r="G197" t="n">
-        <v>6.25935029983521</v>
+        <v>6.25934982299805</v>
       </c>
       <c r="H197" t="n">
         <v>92157</v>
@@ -6140,7 +6140,7 @@
         <v>7.03000020980835</v>
       </c>
       <c r="G199" t="n">
-        <v>6.2861762046814</v>
+        <v>6.28617668151855</v>
       </c>
       <c r="H199" t="n">
         <v>56247</v>
@@ -6198,7 +6198,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G201" t="n">
-        <v>6.27723407745361</v>
+        <v>6.27723455429077</v>
       </c>
       <c r="H201" t="n">
         <v>56777</v>
@@ -6285,7 +6285,7 @@
         <v>7.09000015258789</v>
       </c>
       <c r="G204" t="n">
-        <v>6.33982753753662</v>
+        <v>6.33982801437378</v>
       </c>
       <c r="H204" t="n">
         <v>53372</v>
@@ -6314,7 +6314,7 @@
         <v>7.03000020980835</v>
       </c>
       <c r="G205" t="n">
-        <v>6.2861762046814</v>
+        <v>6.28617668151855</v>
       </c>
       <c r="H205" t="n">
         <v>111627</v>
@@ -6604,7 +6604,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G215" t="n">
-        <v>6.66173648834229</v>
+        <v>6.66173696517944</v>
       </c>
       <c r="H215" t="n">
         <v>95402</v>
@@ -6749,7 +6749,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G220" t="n">
-        <v>6.60808515548706</v>
+        <v>6.60808563232422</v>
       </c>
       <c r="H220" t="n">
         <v>64845</v>
@@ -6865,7 +6865,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G224" t="n">
-        <v>6.66173648834229</v>
+        <v>6.66173696517944</v>
       </c>
       <c r="H224" t="n">
         <v>30693</v>
@@ -7068,7 +7068,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G231" t="n">
-        <v>7.3681492805481</v>
+        <v>7.36814880371094</v>
       </c>
       <c r="H231" t="n">
         <v>165049</v>
@@ -7184,7 +7184,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G235" t="n">
-        <v>7.6542911529541</v>
+        <v>7.65429210662842</v>
       </c>
       <c r="H235" t="n">
         <v>82796</v>
@@ -7300,7 +7300,7 @@
         <v>8.75</v>
       </c>
       <c r="G239" t="n">
-        <v>7.82418727874756</v>
+        <v>7.82418823242188</v>
       </c>
       <c r="H239" t="n">
         <v>92729</v>
@@ -7329,7 +7329,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G240" t="n">
-        <v>7.86889791488647</v>
+        <v>7.86889696121216</v>
       </c>
       <c r="H240" t="n">
         <v>95722</v>
@@ -7445,7 +7445,7 @@
         <v>8.60999965667725</v>
       </c>
       <c r="G244" t="n">
-        <v>7.69899988174438</v>
+        <v>7.6990008354187</v>
       </c>
       <c r="H244" t="n">
         <v>102832</v>
@@ -7532,7 +7532,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G247" t="n">
-        <v>7.64534902572632</v>
+        <v>7.64534997940063</v>
       </c>
       <c r="H247" t="n">
         <v>105886</v>
@@ -7735,7 +7735,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G254" t="n">
-        <v>7.81047344207764</v>
+        <v>7.81047248840332</v>
       </c>
       <c r="H254" t="n">
         <v>152971</v>
@@ -7793,7 +7793,7 @@
         <v>8.52999973297119</v>
       </c>
       <c r="G256" t="n">
-        <v>7.87509870529175</v>
+        <v>7.87509775161743</v>
       </c>
       <c r="H256" t="n">
         <v>99895</v>
@@ -7996,7 +7996,7 @@
         <v>8.60999965667725</v>
       </c>
       <c r="G263" t="n">
-        <v>7.94895553588867</v>
+        <v>7.94895648956299</v>
       </c>
       <c r="H263" t="n">
         <v>76537</v>
@@ -8141,7 +8141,7 @@
         <v>8.60999965667725</v>
       </c>
       <c r="G268" t="n">
-        <v>7.94895553588867</v>
+        <v>7.94895648956299</v>
       </c>
       <c r="H268" t="n">
         <v>61503</v>
@@ -8199,7 +8199,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G270" t="n">
-        <v>7.95818853378296</v>
+        <v>7.95818901062012</v>
       </c>
       <c r="H270" t="n">
         <v>77829</v>
@@ -8460,7 +8460,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G279" t="n">
-        <v>7.42271900177002</v>
+        <v>7.42271852493286</v>
       </c>
       <c r="H279" t="n">
         <v>56062</v>
@@ -8518,7 +8518,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G281" t="n">
-        <v>7.4965763092041</v>
+        <v>7.49657678604126</v>
       </c>
       <c r="H281" t="n">
         <v>39852</v>
@@ -8605,7 +8605,7 @@
         <v>7.80999994277954</v>
       </c>
       <c r="G284" t="n">
-        <v>7.21037769317627</v>
+        <v>7.21037721633911</v>
       </c>
       <c r="H284" t="n">
         <v>117674</v>
@@ -8634,7 +8634,7 @@
         <v>7.71000003814697</v>
       </c>
       <c r="G285" t="n">
-        <v>7.11805534362793</v>
+        <v>7.11805486679077</v>
       </c>
       <c r="H285" t="n">
         <v>57382</v>
@@ -8663,7 +8663,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G286" t="n">
-        <v>7.05342960357666</v>
+        <v>7.0534291267395</v>
       </c>
       <c r="H286" t="n">
         <v>74446</v>
@@ -8692,7 +8692,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G287" t="n">
-        <v>7.1088228225708</v>
+        <v>7.10882234573364</v>
       </c>
       <c r="H287" t="n">
         <v>108157</v>
@@ -8721,7 +8721,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G288" t="n">
-        <v>6.97033929824829</v>
+        <v>6.97033977508545</v>
       </c>
       <c r="H288" t="n">
         <v>37819</v>
@@ -8750,7 +8750,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G289" t="n">
-        <v>6.97033929824829</v>
+        <v>6.97033977508545</v>
       </c>
       <c r="H289" t="n">
         <v>41222</v>
@@ -8953,7 +8953,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G296" t="n">
-        <v>7.30269956588745</v>
+        <v>7.30270004272461</v>
       </c>
       <c r="H296" t="n">
         <v>83813</v>
@@ -8982,7 +8982,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G297" t="n">
-        <v>7.14575147628784</v>
+        <v>7.145751953125</v>
       </c>
       <c r="H297" t="n">
         <v>43493</v>
@@ -9069,7 +9069,7 @@
         <v>7.78999996185303</v>
       </c>
       <c r="G300" t="n">
-        <v>7.19191265106201</v>
+        <v>7.19191312789917</v>
       </c>
       <c r="H300" t="n">
         <v>50892</v>
@@ -9330,7 +9330,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G309" t="n">
-        <v>6.93341064453125</v>
+        <v>6.93341016769409</v>
       </c>
       <c r="H309" t="n">
         <v>19291</v>
@@ -9359,7 +9359,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G310" t="n">
-        <v>6.97033929824829</v>
+        <v>6.97033977508545</v>
       </c>
       <c r="H310" t="n">
         <v>22938</v>
@@ -9388,7 +9388,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G311" t="n">
-        <v>6.87801647186279</v>
+        <v>6.87801694869995</v>
       </c>
       <c r="H311" t="n">
         <v>39307</v>
@@ -9417,7 +9417,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G312" t="n">
-        <v>7.0349645614624</v>
+        <v>7.03496503829956</v>
       </c>
       <c r="H312" t="n">
         <v>19565</v>
@@ -9533,7 +9533,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G316" t="n">
-        <v>6.97033929824829</v>
+        <v>6.97033977508545</v>
       </c>
       <c r="H316" t="n">
         <v>31066</v>
@@ -9591,7 +9591,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G318" t="n">
-        <v>7.42271900177002</v>
+        <v>7.42271852493286</v>
       </c>
       <c r="H318" t="n">
         <v>77225</v>
@@ -9678,7 +9678,7 @@
         <v>7.78999996185303</v>
       </c>
       <c r="G321" t="n">
-        <v>7.19191265106201</v>
+        <v>7.19191312789917</v>
       </c>
       <c r="H321" t="n">
         <v>21141</v>
@@ -9823,7 +9823,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G326" t="n">
-        <v>7.1088228225708</v>
+        <v>7.10882234573364</v>
       </c>
       <c r="H326" t="n">
         <v>18088</v>
@@ -9852,7 +9852,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G327" t="n">
-        <v>6.97033929824829</v>
+        <v>6.97033977508545</v>
       </c>
       <c r="H327" t="n">
         <v>69708</v>
@@ -9881,7 +9881,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G328" t="n">
-        <v>7.13651943206787</v>
+        <v>7.13651990890503</v>
       </c>
       <c r="H328" t="n">
         <v>33278</v>
@@ -9910,7 +9910,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G329" t="n">
-        <v>7.05342960357666</v>
+        <v>7.0534291267395</v>
       </c>
       <c r="H329" t="n">
         <v>17493</v>
@@ -9997,7 +9997,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G332" t="n">
-        <v>6.93341064453125</v>
+        <v>6.93341016769409</v>
       </c>
       <c r="H332" t="n">
         <v>24732</v>
@@ -10026,7 +10026,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G333" t="n">
-        <v>7.05342960357666</v>
+        <v>7.0534291267395</v>
       </c>
       <c r="H333" t="n">
         <v>18353</v>
@@ -10084,7 +10084,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G335" t="n">
-        <v>7.05342960357666</v>
+        <v>7.0534291267395</v>
       </c>
       <c r="H335" t="n">
         <v>11054</v>
@@ -10345,7 +10345,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G344" t="n">
-        <v>6.97033929824829</v>
+        <v>6.97033977508545</v>
       </c>
       <c r="H344" t="n">
         <v>42139</v>
@@ -10403,7 +10403,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G346" t="n">
-        <v>7.14575147628784</v>
+        <v>7.145751953125</v>
       </c>
       <c r="H346" t="n">
         <v>47587</v>
@@ -10461,7 +10461,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G348" t="n">
-        <v>6.90571403503418</v>
+        <v>6.90571355819702</v>
       </c>
       <c r="H348" t="n">
         <v>60152</v>
@@ -10519,7 +10519,7 @@
         <v>7.53999996185303</v>
       </c>
       <c r="G350" t="n">
-        <v>6.96110725402832</v>
+        <v>6.96110677719116</v>
       </c>
       <c r="H350" t="n">
         <v>28852</v>
@@ -10548,7 +10548,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G351" t="n">
-        <v>6.77646255493164</v>
+        <v>6.77646207809448</v>
       </c>
       <c r="H351" t="n">
         <v>58129</v>
@@ -10664,7 +10664,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G355" t="n">
-        <v>6.5364236831665</v>
+        <v>6.53642416000366</v>
       </c>
       <c r="H355" t="n">
         <v>26264</v>
@@ -10809,7 +10809,7 @@
         <v>6.98999977111816</v>
       </c>
       <c r="G360" t="n">
-        <v>6.45333385467529</v>
+        <v>6.45333337783813</v>
       </c>
       <c r="H360" t="n">
         <v>50111</v>
@@ -10867,7 +10867,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G362" t="n">
-        <v>6.64721059799194</v>
+        <v>6.6472110748291</v>
       </c>
       <c r="H362" t="n">
         <v>58993</v>
@@ -10896,7 +10896,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G363" t="n">
-        <v>6.40717315673828</v>
+        <v>6.40717267990112</v>
       </c>
       <c r="H363" t="n">
         <v>39953</v>
@@ -10925,7 +10925,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G364" t="n">
-        <v>6.63797855377197</v>
+        <v>6.63797903060913</v>
       </c>
       <c r="H364" t="n">
         <v>33892</v>
@@ -11012,7 +11012,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G367" t="n">
-        <v>6.48103046417236</v>
+        <v>6.48103094100952</v>
       </c>
       <c r="H367" t="n">
         <v>37646</v>
@@ -11041,7 +11041,7 @@
         <v>7.09000015258789</v>
       </c>
       <c r="G368" t="n">
-        <v>6.54565620422363</v>
+        <v>6.54565668106079</v>
       </c>
       <c r="H368" t="n">
         <v>45957</v>
@@ -11099,7 +11099,7 @@
         <v>7.09000015258789</v>
       </c>
       <c r="G370" t="n">
-        <v>6.54565620422363</v>
+        <v>6.54565668106079</v>
       </c>
       <c r="H370" t="n">
         <v>28684</v>
@@ -11128,7 +11128,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G371" t="n">
-        <v>6.63797855377197</v>
+        <v>6.63797903060913</v>
       </c>
       <c r="H371" t="n">
         <v>24535</v>
@@ -11186,7 +11186,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G373" t="n">
-        <v>6.32408237457275</v>
+        <v>6.32408285140991</v>
       </c>
       <c r="H373" t="n">
         <v>47509</v>
@@ -11215,7 +11215,7 @@
         <v>7</v>
       </c>
       <c r="G374" t="n">
-        <v>6.46256637573242</v>
+        <v>6.46256589889526</v>
       </c>
       <c r="H374" t="n">
         <v>17115</v>
@@ -11476,7 +11476,7 @@
         <v>7.09000015258789</v>
       </c>
       <c r="G383" t="n">
-        <v>6.54565620422363</v>
+        <v>6.54565668106079</v>
       </c>
       <c r="H383" t="n">
         <v>39879</v>
@@ -11592,7 +11592,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G387" t="n">
-        <v>6.6102819442749</v>
+        <v>6.61028146743774</v>
       </c>
       <c r="H387" t="n">
         <v>59425</v>
@@ -11650,7 +11650,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G389" t="n">
-        <v>6.87801647186279</v>
+        <v>6.87801694869995</v>
       </c>
       <c r="H389" t="n">
         <v>91784</v>
@@ -11679,7 +11679,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G390" t="n">
-        <v>7.13651943206787</v>
+        <v>7.13651990890503</v>
       </c>
       <c r="H390" t="n">
         <v>203114</v>
@@ -11766,7 +11766,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G393" t="n">
-        <v>7.30269956588745</v>
+        <v>7.30270004272461</v>
       </c>
       <c r="H393" t="n">
         <v>167425</v>
@@ -11795,7 +11795,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G394" t="n">
-        <v>7.20114517211914</v>
+        <v>7.2011456489563</v>
       </c>
       <c r="H394" t="n">
         <v>191654</v>
@@ -11853,7 +11853,7 @@
         <v>7.86999988555908</v>
       </c>
       <c r="G396" t="n">
-        <v>7.26577091217041</v>
+        <v>7.26577043533325</v>
       </c>
       <c r="H396" t="n">
         <v>50620</v>
@@ -11911,7 +11911,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G398" t="n">
-        <v>7.30269956588745</v>
+        <v>7.30270004272461</v>
       </c>
       <c r="H398" t="n">
         <v>99717</v>
@@ -11940,7 +11940,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G399" t="n">
-        <v>7.36732578277588</v>
+        <v>7.36732530593872</v>
       </c>
       <c r="H399" t="n">
         <v>124059</v>
@@ -11969,7 +11969,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G400" t="n">
-        <v>7.24730587005615</v>
+        <v>7.24730634689331</v>
       </c>
       <c r="H400" t="n">
         <v>72121</v>
@@ -12114,7 +12114,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G405" t="n">
-        <v>7.30269956588745</v>
+        <v>7.30270004272461</v>
       </c>
       <c r="H405" t="n">
         <v>38438</v>
@@ -12636,7 +12636,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G423" t="n">
-        <v>7.40425443649292</v>
+        <v>7.40425491333008</v>
       </c>
       <c r="H423" t="n">
         <v>48656</v>
@@ -12752,7 +12752,7 @@
         <v>8.25</v>
       </c>
       <c r="G427" t="n">
-        <v>7.61659622192383</v>
+        <v>7.61659574508667</v>
       </c>
       <c r="H427" t="n">
         <v>55700</v>
@@ -12810,7 +12810,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G429" t="n">
-        <v>7.90279531478882</v>
+        <v>7.90279626846313</v>
       </c>
       <c r="H429" t="n">
         <v>122032</v>
@@ -12984,7 +12984,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G435" t="n">
-        <v>8.63214206695557</v>
+        <v>8.63214302062988</v>
       </c>
       <c r="H435" t="n">
         <v>236669</v>
@@ -13158,7 +13158,7 @@
         <v>9.6899995803833</v>
       </c>
       <c r="G441" t="n">
-        <v>8.94603729248047</v>
+        <v>8.94603824615479</v>
       </c>
       <c r="H441" t="n">
         <v>85296</v>
@@ -13216,7 +13216,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G443" t="n">
-        <v>8.99219989776611</v>
+        <v>8.9921989440918</v>
       </c>
       <c r="H443" t="n">
         <v>101160</v>
@@ -13477,7 +13477,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G452" t="n">
-        <v>9.52766895294189</v>
+        <v>9.52766799926758</v>
       </c>
       <c r="H452" t="n">
         <v>186778</v>
@@ -13506,7 +13506,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G453" t="n">
-        <v>9.61999130249023</v>
+        <v>9.61999225616455</v>
       </c>
       <c r="H453" t="n">
         <v>106036</v>
@@ -13535,7 +13535,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G454" t="n">
-        <v>9.41688251495361</v>
+        <v>9.4168815612793</v>
       </c>
       <c r="H454" t="n">
         <v>85544</v>
@@ -13593,7 +13593,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G456" t="n">
-        <v>9.25070190429688</v>
+        <v>9.25070285797119</v>
       </c>
       <c r="H456" t="n">
         <v>45013</v>
@@ -13651,7 +13651,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G458" t="n">
-        <v>9.26916599273682</v>
+        <v>9.26916694641113</v>
       </c>
       <c r="H458" t="n">
         <v>73523</v>
@@ -13825,7 +13825,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G464" t="n">
-        <v>9.26916599273682</v>
+        <v>9.26916694641113</v>
       </c>
       <c r="H464" t="n">
         <v>35262</v>
@@ -13883,7 +13883,7 @@
         <v>9.98999977111816</v>
       </c>
       <c r="G466" t="n">
-        <v>9.2230052947998</v>
+        <v>9.22300434112549</v>
       </c>
       <c r="H466" t="n">
         <v>90490</v>
@@ -13999,7 +13999,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G470" t="n">
-        <v>9.61999130249023</v>
+        <v>9.61999225616455</v>
       </c>
       <c r="H470" t="n">
         <v>91656</v>
@@ -14028,7 +14028,7 @@
         <v>10.4799995422363</v>
       </c>
       <c r="G471" t="n">
-        <v>9.67538356781006</v>
+        <v>9.67538452148438</v>
       </c>
       <c r="H471" t="n">
         <v>94908</v>
@@ -14173,7 +14173,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G476" t="n">
-        <v>9.61999130249023</v>
+        <v>9.61999225616455</v>
       </c>
       <c r="H476" t="n">
         <v>55619</v>
@@ -14202,7 +14202,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G477" t="n">
-        <v>9.58306217193604</v>
+        <v>9.58306312561035</v>
       </c>
       <c r="H477" t="n">
         <v>68414</v>
@@ -14289,7 +14289,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G480" t="n">
-        <v>10.2477836608887</v>
+        <v>10.247784614563</v>
       </c>
       <c r="H480" t="n">
         <v>121664</v>
@@ -14318,7 +14318,7 @@
         <v>11.1199998855591</v>
       </c>
       <c r="G481" t="n">
-        <v>10.2662477493286</v>
+        <v>10.2662487030029</v>
       </c>
       <c r="H481" t="n">
         <v>62344</v>
@@ -14347,7 +14347,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G482" t="n">
-        <v>8.93680572509766</v>
+        <v>8.93680667877197</v>
       </c>
       <c r="H482" t="n">
         <v>1087677</v>
@@ -14376,7 +14376,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G483" t="n">
-        <v>9.28763103485107</v>
+        <v>9.28763198852539</v>
       </c>
       <c r="H483" t="n">
         <v>332225</v>
@@ -14405,7 +14405,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G484" t="n">
-        <v>9.21377277374268</v>
+        <v>9.21377182006836</v>
       </c>
       <c r="H484" t="n">
         <v>153862</v>
@@ -14521,7 +14521,7 @@
         <v>9.63000011444092</v>
       </c>
       <c r="G488" t="n">
-        <v>8.89064502716064</v>
+        <v>8.89064407348633</v>
       </c>
       <c r="H488" t="n">
         <v>74178</v>
@@ -14695,7 +14695,7 @@
         <v>9.28999996185303</v>
       </c>
       <c r="G494" t="n">
-        <v>8.57674789428711</v>
+        <v>8.57674884796143</v>
       </c>
       <c r="H494" t="n">
         <v>136448</v>
@@ -14724,7 +14724,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G495" t="n">
-        <v>8.48442649841309</v>
+        <v>8.48442554473877</v>
       </c>
       <c r="H495" t="n">
         <v>37699</v>
@@ -14840,7 +14840,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G499" t="n">
-        <v>8.62290954589844</v>
+        <v>8.62291049957275</v>
       </c>
       <c r="H499" t="n">
         <v>120557</v>
@@ -14898,7 +14898,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G501" t="n">
-        <v>8.62290954589844</v>
+        <v>8.62291049957275</v>
       </c>
       <c r="H501" t="n">
         <v>49932</v>
@@ -14956,7 +14956,7 @@
         <v>9.6899995803833</v>
       </c>
       <c r="G503" t="n">
-        <v>8.94603729248047</v>
+        <v>8.94603824615479</v>
       </c>
       <c r="H503" t="n">
         <v>146163</v>
@@ -14985,7 +14985,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G504" t="n">
-        <v>8.86294841766357</v>
+        <v>8.86294746398926</v>
       </c>
       <c r="H504" t="n">
         <v>41942</v>
@@ -15188,7 +15188,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G511" t="n">
-        <v>8.78909111022949</v>
+        <v>8.78909015655518</v>
       </c>
       <c r="H511" t="n">
         <v>113583</v>
@@ -15246,7 +15246,7 @@
         <v>9.8100004196167</v>
       </c>
       <c r="G513" t="n">
-        <v>9.05682468414307</v>
+        <v>9.05682563781738</v>
       </c>
       <c r="H513" t="n">
         <v>107598</v>
@@ -15333,7 +15333,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G516" t="n">
-        <v>8.9552698135376</v>
+        <v>8.95527076721191</v>
       </c>
       <c r="H516" t="n">
         <v>76374</v>
@@ -33287,9 +33287,38 @@
         <v>0.660000026226044</v>
       </c>
       <c r="H1135" t="n">
-        <v>1061843</v>
+        <v>1063712</v>
       </c>
       <c r="I1135" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1136">
+      <c r="A1136" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1136" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C1136" t="n">
+        <v>0.632000029087067</v>
+      </c>
+      <c r="D1136" t="n">
+        <v>0.725000023841858</v>
+      </c>
+      <c r="E1136" t="n">
+        <v>0.629999995231628</v>
+      </c>
+      <c r="F1136" t="n">
+        <v>0.694999992847443</v>
+      </c>
+      <c r="G1136" t="n">
+        <v>0.694999992847443</v>
+      </c>
+      <c r="H1136" t="n">
+        <v>534033</v>
+      </c>
+      <c r="I1136" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/TISG.MI.xlsx
+++ b/data/TISG.MI.xlsx
@@ -427,7 +427,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G2" t="n">
-        <v>4.97171258926392</v>
+        <v>4.97171211242676</v>
       </c>
       <c r="H2" t="n">
         <v>20197</v>
@@ -456,7 +456,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G3" t="n">
-        <v>5.12372589111328</v>
+        <v>5.12372493743896</v>
       </c>
       <c r="H3" t="n">
         <v>28276</v>
@@ -543,7 +543,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G6" t="n">
-        <v>4.97171258926392</v>
+        <v>4.97171211242676</v>
       </c>
       <c r="H6" t="n">
         <v>18977</v>
@@ -688,7 +688,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G11" t="n">
-        <v>4.97171258926392</v>
+        <v>4.97171211242676</v>
       </c>
       <c r="H11" t="n">
         <v>12298</v>
@@ -978,7 +978,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G21" t="n">
-        <v>5.0253643989563</v>
+        <v>5.02536344528198</v>
       </c>
       <c r="H21" t="n">
         <v>16980</v>
@@ -1094,7 +1094,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G25" t="n">
-        <v>4.64086151123047</v>
+        <v>4.64086103439331</v>
       </c>
       <c r="H25" t="n">
         <v>38675</v>
@@ -1384,7 +1384,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G35" t="n">
-        <v>4.64086151123047</v>
+        <v>4.64086103439331</v>
       </c>
       <c r="H35" t="n">
         <v>71434</v>
@@ -1442,7 +1442,7 @@
         <v>4.78499984741211</v>
       </c>
       <c r="G37" t="n">
-        <v>4.2787127494812</v>
+        <v>4.27871322631836</v>
       </c>
       <c r="H37" t="n">
         <v>58880</v>
@@ -1529,7 +1529,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G40" t="n">
-        <v>4.33683586120605</v>
+        <v>4.3368353843689</v>
       </c>
       <c r="H40" t="n">
         <v>82262</v>
@@ -1587,7 +1587,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G42" t="n">
-        <v>4.40837049484253</v>
+        <v>4.40837097167969</v>
       </c>
       <c r="H42" t="n">
         <v>18554</v>
@@ -1674,7 +1674,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G45" t="n">
-        <v>4.39048719406128</v>
+        <v>4.39048671722412</v>
       </c>
       <c r="H45" t="n">
         <v>25487</v>
@@ -1703,7 +1703,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G46" t="n">
-        <v>4.41731262207031</v>
+        <v>4.41731309890747</v>
       </c>
       <c r="H46" t="n">
         <v>16689</v>
@@ -1732,7 +1732,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G47" t="n">
-        <v>4.33683586120605</v>
+        <v>4.3368353843689</v>
       </c>
       <c r="H47" t="n">
         <v>57150</v>
@@ -1935,7 +1935,7 @@
         <v>4.89499998092651</v>
       </c>
       <c r="G54" t="n">
-        <v>4.37707424163818</v>
+        <v>4.37707471847534</v>
       </c>
       <c r="H54" t="n">
         <v>13462</v>
@@ -2080,7 +2080,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G59" t="n">
-        <v>4.51567411422729</v>
+        <v>4.51567459106445</v>
       </c>
       <c r="H59" t="n">
         <v>22808</v>
@@ -2196,7 +2196,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G63" t="n">
-        <v>4.64980316162109</v>
+        <v>4.64980268478394</v>
       </c>
       <c r="H63" t="n">
         <v>36457</v>
@@ -2312,7 +2312,7 @@
         <v>5.25</v>
       </c>
       <c r="G67" t="n">
-        <v>4.69451284408569</v>
+        <v>4.69451236724854</v>
       </c>
       <c r="H67" t="n">
         <v>45084</v>
@@ -2341,7 +2341,7 @@
         <v>5.25</v>
       </c>
       <c r="G68" t="n">
-        <v>4.69451284408569</v>
+        <v>4.69451236724854</v>
       </c>
       <c r="H68" t="n">
         <v>32450</v>
@@ -2370,7 +2370,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G69" t="n">
-        <v>4.64980316162109</v>
+        <v>4.64980268478394</v>
       </c>
       <c r="H69" t="n">
         <v>10853</v>
@@ -2399,7 +2399,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G70" t="n">
-        <v>4.56038331985474</v>
+        <v>4.56038379669189</v>
       </c>
       <c r="H70" t="n">
         <v>18662</v>
@@ -2428,7 +2428,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G71" t="n">
-        <v>4.61403465270996</v>
+        <v>4.61403512954712</v>
       </c>
       <c r="H71" t="n">
         <v>5955</v>
@@ -2573,7 +2573,7 @@
         <v>4.85500001907349</v>
       </c>
       <c r="G76" t="n">
-        <v>4.34130668640137</v>
+        <v>4.34130620956421</v>
       </c>
       <c r="H76" t="n">
         <v>21022</v>
@@ -2892,7 +2892,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G87" t="n">
-        <v>4.23847436904907</v>
+        <v>4.23847389221191</v>
       </c>
       <c r="H87" t="n">
         <v>24828</v>
@@ -2921,7 +2921,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G88" t="n">
-        <v>4.49779081344604</v>
+        <v>4.49779033660889</v>
       </c>
       <c r="H88" t="n">
         <v>22654</v>
@@ -2979,7 +2979,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G90" t="n">
-        <v>4.48884868621826</v>
+        <v>4.4888482093811</v>
       </c>
       <c r="H90" t="n">
         <v>27075</v>
@@ -3008,7 +3008,7 @@
         <v>4.85500001907349</v>
       </c>
       <c r="G91" t="n">
-        <v>4.34130668640137</v>
+        <v>4.34130620956421</v>
       </c>
       <c r="H91" t="n">
         <v>28795</v>
@@ -3037,7 +3037,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G92" t="n">
-        <v>4.40837049484253</v>
+        <v>4.40837097167969</v>
       </c>
       <c r="H92" t="n">
         <v>28839</v>
@@ -3095,7 +3095,7 @@
         <v>4.75</v>
       </c>
       <c r="G94" t="n">
-        <v>4.2474160194397</v>
+        <v>4.24741649627686</v>
       </c>
       <c r="H94" t="n">
         <v>25723</v>
@@ -3182,7 +3182,7 @@
         <v>4.89499998092651</v>
       </c>
       <c r="G97" t="n">
-        <v>4.37707424163818</v>
+        <v>4.37707471847534</v>
       </c>
       <c r="H97" t="n">
         <v>41065</v>
@@ -3269,7 +3269,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G100" t="n">
-        <v>4.37260341644287</v>
+        <v>4.37260293960571</v>
       </c>
       <c r="H100" t="n">
         <v>25467</v>
@@ -3298,7 +3298,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G101" t="n">
-        <v>4.08646154403687</v>
+        <v>4.08646202087402</v>
       </c>
       <c r="H101" t="n">
         <v>93157</v>
@@ -3356,7 +3356,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G103" t="n">
-        <v>3.95233249664307</v>
+        <v>3.95233297348022</v>
       </c>
       <c r="H103" t="n">
         <v>122405</v>
@@ -3385,7 +3385,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G104" t="n">
-        <v>4.01492595672607</v>
+        <v>4.01492547988892</v>
       </c>
       <c r="H104" t="n">
         <v>12994</v>
@@ -3414,7 +3414,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G105" t="n">
-        <v>3.90762281417847</v>
+        <v>3.90762305259705</v>
       </c>
       <c r="H105" t="n">
         <v>8913</v>
@@ -3443,7 +3443,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G106" t="n">
-        <v>3.84502983093262</v>
+        <v>3.84502959251404</v>
       </c>
       <c r="H106" t="n">
         <v>39490</v>
@@ -3501,7 +3501,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G108" t="n">
-        <v>3.82714605331421</v>
+        <v>3.82714581489563</v>
       </c>
       <c r="H108" t="n">
         <v>26268</v>
@@ -3530,7 +3530,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G109" t="n">
-        <v>3.80926156044006</v>
+        <v>3.80926203727722</v>
       </c>
       <c r="H109" t="n">
         <v>5280</v>
@@ -3559,7 +3559,7 @@
         <v>4.2649998664856</v>
       </c>
       <c r="G110" t="n">
-        <v>3.81373238563538</v>
+        <v>3.81373262405396</v>
       </c>
       <c r="H110" t="n">
         <v>30391</v>
@@ -3588,7 +3588,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G111" t="n">
-        <v>3.69301676750183</v>
+        <v>3.69301700592041</v>
       </c>
       <c r="H111" t="n">
         <v>51138</v>
@@ -3675,7 +3675,7 @@
         <v>4.5</v>
       </c>
       <c r="G114" t="n">
-        <v>4.02386856079102</v>
+        <v>4.02386808395386</v>
       </c>
       <c r="H114" t="n">
         <v>51824</v>
@@ -3733,7 +3733,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G116" t="n">
-        <v>4.17588138580322</v>
+        <v>4.17588090896606</v>
       </c>
       <c r="H116" t="n">
         <v>27523</v>
@@ -3791,7 +3791,7 @@
         <v>4.78499984741211</v>
       </c>
       <c r="G118" t="n">
-        <v>4.2787127494812</v>
+        <v>4.27871322631836</v>
       </c>
       <c r="H118" t="n">
         <v>22444</v>
@@ -3820,7 +3820,7 @@
         <v>4.75</v>
       </c>
       <c r="G119" t="n">
-        <v>4.2474160194397</v>
+        <v>4.24741649627686</v>
       </c>
       <c r="H119" t="n">
         <v>12242</v>
@@ -3994,7 +3994,7 @@
         <v>4.70499992370605</v>
       </c>
       <c r="G125" t="n">
-        <v>4.20717763900757</v>
+        <v>4.20717716217041</v>
       </c>
       <c r="H125" t="n">
         <v>19005</v>
@@ -4110,7 +4110,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G129" t="n">
-        <v>4.56932544708252</v>
+        <v>4.56932592391968</v>
       </c>
       <c r="H129" t="n">
         <v>34023</v>
@@ -4226,7 +4226,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G133" t="n">
-        <v>4.82864189147949</v>
+        <v>4.82864141464233</v>
       </c>
       <c r="H133" t="n">
         <v>33414</v>
@@ -4342,7 +4342,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G137" t="n">
-        <v>4.83758354187012</v>
+        <v>4.83758306503296</v>
       </c>
       <c r="H137" t="n">
         <v>18118</v>
@@ -4371,7 +4371,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G138" t="n">
-        <v>4.81075811386108</v>
+        <v>4.81075763702393</v>
       </c>
       <c r="H138" t="n">
         <v>13168</v>
@@ -4603,7 +4603,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G146" t="n">
-        <v>5.13266754150391</v>
+        <v>5.13266706466675</v>
       </c>
       <c r="H146" t="n">
         <v>31662</v>
@@ -4632,7 +4632,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G147" t="n">
-        <v>5.0253643989563</v>
+        <v>5.02536344528198</v>
       </c>
       <c r="H147" t="n">
         <v>22523</v>
@@ -4719,7 +4719,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G150" t="n">
-        <v>5.06113147735596</v>
+        <v>5.06113195419312</v>
       </c>
       <c r="H150" t="n">
         <v>44995</v>
@@ -4835,7 +4835,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G154" t="n">
-        <v>5.13266754150391</v>
+        <v>5.13266706466675</v>
       </c>
       <c r="H154" t="n">
         <v>24494</v>
@@ -4951,7 +4951,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G158" t="n">
-        <v>5.0253643989563</v>
+        <v>5.02536344528198</v>
       </c>
       <c r="H158" t="n">
         <v>12170</v>
@@ -4980,7 +4980,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G159" t="n">
-        <v>4.95382833480835</v>
+        <v>4.95382881164551</v>
       </c>
       <c r="H159" t="n">
         <v>26457</v>
@@ -5009,7 +5009,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G160" t="n">
-        <v>5.09689903259277</v>
+        <v>5.09689950942993</v>
       </c>
       <c r="H160" t="n">
         <v>13151</v>
@@ -5067,7 +5067,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G162" t="n">
-        <v>5.09689903259277</v>
+        <v>5.09689950942993</v>
       </c>
       <c r="H162" t="n">
         <v>60968</v>
@@ -5125,7 +5125,7 @@
         <v>5.69000005722046</v>
       </c>
       <c r="G164" t="n">
-        <v>5.08795738220215</v>
+        <v>5.08795785903931</v>
       </c>
       <c r="H164" t="n">
         <v>9415</v>
@@ -5154,7 +5154,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G165" t="n">
-        <v>5.04324769973755</v>
+        <v>5.04324817657471</v>
       </c>
       <c r="H165" t="n">
         <v>16099</v>
@@ -5241,7 +5241,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G168" t="n">
-        <v>5.12372589111328</v>
+        <v>5.12372493743896</v>
       </c>
       <c r="H168" t="n">
         <v>13445</v>
@@ -5328,7 +5328,7 @@
         <v>5.75</v>
       </c>
       <c r="G171" t="n">
-        <v>5.14160919189453</v>
+        <v>5.14160966873169</v>
       </c>
       <c r="H171" t="n">
         <v>1538</v>
@@ -5357,7 +5357,7 @@
         <v>5.75</v>
       </c>
       <c r="G172" t="n">
-        <v>5.14160919189453</v>
+        <v>5.14160966873169</v>
       </c>
       <c r="H172" t="n">
         <v>9719</v>
@@ -5386,7 +5386,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G173" t="n">
-        <v>5.07901573181152</v>
+        <v>5.07901525497437</v>
       </c>
       <c r="H173" t="n">
         <v>8390</v>
@@ -5444,7 +5444,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G175" t="n">
-        <v>5.13266754150391</v>
+        <v>5.13266706466675</v>
       </c>
       <c r="H175" t="n">
         <v>26260</v>
@@ -5531,7 +5531,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G178" t="n">
-        <v>5.12372589111328</v>
+        <v>5.12372493743896</v>
       </c>
       <c r="H178" t="n">
         <v>13789</v>
@@ -5560,7 +5560,7 @@
         <v>5.90999984741211</v>
       </c>
       <c r="G179" t="n">
-        <v>5.28468036651611</v>
+        <v>5.28467988967896</v>
       </c>
       <c r="H179" t="n">
         <v>21763</v>
@@ -5705,7 +5705,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G184" t="n">
-        <v>5.67812490463257</v>
+        <v>5.67812442779541</v>
       </c>
       <c r="H184" t="n">
         <v>135409</v>
@@ -5937,7 +5937,7 @@
         <v>6.80999994277954</v>
       </c>
       <c r="G192" t="n">
-        <v>6.08945322036743</v>
+        <v>6.08945369720459</v>
       </c>
       <c r="H192" t="n">
         <v>86712</v>
@@ -5966,7 +5966,7 @@
         <v>7</v>
       </c>
       <c r="G193" t="n">
-        <v>6.25934982299805</v>
+        <v>6.25935029983521</v>
       </c>
       <c r="H193" t="n">
         <v>64859</v>
@@ -5995,7 +5995,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G194" t="n">
-        <v>6.18781471252441</v>
+        <v>6.18781518936157</v>
       </c>
       <c r="H194" t="n">
         <v>195087</v>
@@ -6082,7 +6082,7 @@
         <v>7</v>
       </c>
       <c r="G197" t="n">
-        <v>6.25934982299805</v>
+        <v>6.25935029983521</v>
       </c>
       <c r="H197" t="n">
         <v>92157</v>
@@ -6198,7 +6198,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G201" t="n">
-        <v>6.27723455429077</v>
+        <v>6.27723407745361</v>
       </c>
       <c r="H201" t="n">
         <v>56777</v>
@@ -6372,7 +6372,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G207" t="n">
-        <v>6.65279531478882</v>
+        <v>6.65279483795166</v>
       </c>
       <c r="H207" t="n">
         <v>179183</v>
@@ -6517,7 +6517,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G212" t="n">
-        <v>6.61702728271484</v>
+        <v>6.617027759552</v>
       </c>
       <c r="H212" t="n">
         <v>59738</v>
@@ -6575,7 +6575,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G214" t="n">
-        <v>6.79586601257324</v>
+        <v>6.79586553573608</v>
       </c>
       <c r="H214" t="n">
         <v>155309</v>
@@ -6749,7 +6749,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G220" t="n">
-        <v>6.60808563232422</v>
+        <v>6.60808515548706</v>
       </c>
       <c r="H220" t="n">
         <v>64845</v>
@@ -7155,7 +7155,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G234" t="n">
-        <v>7.77947807312012</v>
+        <v>7.77947854995728</v>
       </c>
       <c r="H234" t="n">
         <v>98556</v>
@@ -7184,7 +7184,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G235" t="n">
-        <v>7.65429210662842</v>
+        <v>7.65429162979126</v>
       </c>
       <c r="H235" t="n">
         <v>82796</v>
@@ -7213,7 +7213,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G236" t="n">
-        <v>7.35920667648315</v>
+        <v>7.35920715332031</v>
       </c>
       <c r="H236" t="n">
         <v>253702</v>
@@ -7242,7 +7242,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G237" t="n">
-        <v>7.35920667648315</v>
+        <v>7.35920715332031</v>
       </c>
       <c r="H237" t="n">
         <v>172849</v>
@@ -7271,7 +7271,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G238" t="n">
-        <v>7.73476839065552</v>
+        <v>7.73476791381836</v>
       </c>
       <c r="H238" t="n">
         <v>113648</v>
@@ -7300,7 +7300,7 @@
         <v>8.75</v>
       </c>
       <c r="G239" t="n">
-        <v>7.82418823242188</v>
+        <v>7.82418775558472</v>
       </c>
       <c r="H239" t="n">
         <v>92729</v>
@@ -7387,7 +7387,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G242" t="n">
-        <v>7.77947807312012</v>
+        <v>7.77947854995728</v>
       </c>
       <c r="H242" t="n">
         <v>118950</v>
@@ -7416,7 +7416,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G243" t="n">
-        <v>7.73476839065552</v>
+        <v>7.73476791381836</v>
       </c>
       <c r="H243" t="n">
         <v>250001</v>
@@ -7445,7 +7445,7 @@
         <v>8.60999965667725</v>
       </c>
       <c r="G244" t="n">
-        <v>7.6990008354187</v>
+        <v>7.69900035858154</v>
       </c>
       <c r="H244" t="n">
         <v>102832</v>
@@ -7474,7 +7474,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G245" t="n">
-        <v>7.77947807312012</v>
+        <v>7.77947854995728</v>
       </c>
       <c r="H245" t="n">
         <v>76403</v>
@@ -7503,7 +7503,7 @@
         <v>8.57999992370605</v>
       </c>
       <c r="G246" t="n">
-        <v>7.67217540740967</v>
+        <v>7.67217445373535</v>
       </c>
       <c r="H246" t="n">
         <v>44155</v>
@@ -7532,7 +7532,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G247" t="n">
-        <v>7.64534997940063</v>
+        <v>7.64534950256348</v>
       </c>
       <c r="H247" t="n">
         <v>105886</v>
@@ -7561,7 +7561,7 @@
         <v>8.63000011444092</v>
       </c>
       <c r="G248" t="n">
-        <v>7.71688461303711</v>
+        <v>7.71688508987427</v>
       </c>
       <c r="H248" t="n">
         <v>49730</v>
@@ -7590,7 +7590,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G249" t="n">
-        <v>7.73476839065552</v>
+        <v>7.73476791381836</v>
       </c>
       <c r="H249" t="n">
         <v>51008</v>
@@ -7735,7 +7735,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G254" t="n">
-        <v>7.81047248840332</v>
+        <v>7.81047344207764</v>
       </c>
       <c r="H254" t="n">
         <v>152971</v>
@@ -7793,7 +7793,7 @@
         <v>8.52999973297119</v>
       </c>
       <c r="G256" t="n">
-        <v>7.87509775161743</v>
+        <v>7.87509870529175</v>
       </c>
       <c r="H256" t="n">
         <v>99895</v>
@@ -7996,7 +7996,7 @@
         <v>8.60999965667725</v>
       </c>
       <c r="G263" t="n">
-        <v>7.94895648956299</v>
+        <v>7.94895553588867</v>
       </c>
       <c r="H263" t="n">
         <v>76537</v>
@@ -8141,7 +8141,7 @@
         <v>8.60999965667725</v>
       </c>
       <c r="G268" t="n">
-        <v>7.94895648956299</v>
+        <v>7.94895553588867</v>
       </c>
       <c r="H268" t="n">
         <v>61503</v>
@@ -8199,7 +8199,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G270" t="n">
-        <v>7.95818901062012</v>
+        <v>7.95818853378296</v>
       </c>
       <c r="H270" t="n">
         <v>77829</v>
@@ -8460,7 +8460,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G279" t="n">
-        <v>7.42271852493286</v>
+        <v>7.42271900177002</v>
       </c>
       <c r="H279" t="n">
         <v>56062</v>
@@ -8518,7 +8518,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G281" t="n">
-        <v>7.49657678604126</v>
+        <v>7.4965763092041</v>
       </c>
       <c r="H281" t="n">
         <v>39852</v>
@@ -8605,7 +8605,7 @@
         <v>7.80999994277954</v>
       </c>
       <c r="G284" t="n">
-        <v>7.21037721633911</v>
+        <v>7.21037769317627</v>
       </c>
       <c r="H284" t="n">
         <v>117674</v>
@@ -8634,7 +8634,7 @@
         <v>7.71000003814697</v>
       </c>
       <c r="G285" t="n">
-        <v>7.11805486679077</v>
+        <v>7.11805534362793</v>
       </c>
       <c r="H285" t="n">
         <v>57382</v>
@@ -8663,7 +8663,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G286" t="n">
-        <v>7.0534291267395</v>
+        <v>7.05342960357666</v>
       </c>
       <c r="H286" t="n">
         <v>74446</v>
@@ -8692,7 +8692,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G287" t="n">
-        <v>7.10882234573364</v>
+        <v>7.1088228225708</v>
       </c>
       <c r="H287" t="n">
         <v>108157</v>
@@ -8721,7 +8721,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G288" t="n">
-        <v>6.97033977508545</v>
+        <v>6.97033929824829</v>
       </c>
       <c r="H288" t="n">
         <v>37819</v>
@@ -8750,7 +8750,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G289" t="n">
-        <v>6.97033977508545</v>
+        <v>6.97033929824829</v>
       </c>
       <c r="H289" t="n">
         <v>41222</v>
@@ -8953,7 +8953,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G296" t="n">
-        <v>7.30270004272461</v>
+        <v>7.30269956588745</v>
       </c>
       <c r="H296" t="n">
         <v>83813</v>
@@ -8982,7 +8982,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G297" t="n">
-        <v>7.145751953125</v>
+        <v>7.14575147628784</v>
       </c>
       <c r="H297" t="n">
         <v>43493</v>
@@ -9069,7 +9069,7 @@
         <v>7.78999996185303</v>
       </c>
       <c r="G300" t="n">
-        <v>7.19191312789917</v>
+        <v>7.19191265106201</v>
       </c>
       <c r="H300" t="n">
         <v>50892</v>
@@ -9330,7 +9330,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G309" t="n">
-        <v>6.93341016769409</v>
+        <v>6.93341064453125</v>
       </c>
       <c r="H309" t="n">
         <v>19291</v>
@@ -9359,7 +9359,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G310" t="n">
-        <v>6.97033977508545</v>
+        <v>6.97033929824829</v>
       </c>
       <c r="H310" t="n">
         <v>22938</v>
@@ -9388,7 +9388,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G311" t="n">
-        <v>6.87801694869995</v>
+        <v>6.87801647186279</v>
       </c>
       <c r="H311" t="n">
         <v>39307</v>
@@ -9417,7 +9417,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G312" t="n">
-        <v>7.03496503829956</v>
+        <v>7.0349645614624</v>
       </c>
       <c r="H312" t="n">
         <v>19565</v>
@@ -9533,7 +9533,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G316" t="n">
-        <v>6.97033977508545</v>
+        <v>6.97033929824829</v>
       </c>
       <c r="H316" t="n">
         <v>31066</v>
@@ -9591,7 +9591,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G318" t="n">
-        <v>7.42271852493286</v>
+        <v>7.42271900177002</v>
       </c>
       <c r="H318" t="n">
         <v>77225</v>
@@ -9678,7 +9678,7 @@
         <v>7.78999996185303</v>
       </c>
       <c r="G321" t="n">
-        <v>7.19191312789917</v>
+        <v>7.19191265106201</v>
       </c>
       <c r="H321" t="n">
         <v>21141</v>
@@ -9823,7 +9823,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G326" t="n">
-        <v>7.10882234573364</v>
+        <v>7.1088228225708</v>
       </c>
       <c r="H326" t="n">
         <v>18088</v>
@@ -9852,7 +9852,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G327" t="n">
-        <v>6.97033977508545</v>
+        <v>6.97033929824829</v>
       </c>
       <c r="H327" t="n">
         <v>69708</v>
@@ -9881,7 +9881,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G328" t="n">
-        <v>7.13651990890503</v>
+        <v>7.13651943206787</v>
       </c>
       <c r="H328" t="n">
         <v>33278</v>
@@ -9910,7 +9910,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G329" t="n">
-        <v>7.0534291267395</v>
+        <v>7.05342960357666</v>
       </c>
       <c r="H329" t="n">
         <v>17493</v>
@@ -9997,7 +9997,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G332" t="n">
-        <v>6.93341016769409</v>
+        <v>6.93341064453125</v>
       </c>
       <c r="H332" t="n">
         <v>24732</v>
@@ -10026,7 +10026,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G333" t="n">
-        <v>7.0534291267395</v>
+        <v>7.05342960357666</v>
       </c>
       <c r="H333" t="n">
         <v>18353</v>
@@ -10084,7 +10084,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G335" t="n">
-        <v>7.0534291267395</v>
+        <v>7.05342960357666</v>
       </c>
       <c r="H335" t="n">
         <v>11054</v>
@@ -10345,7 +10345,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G344" t="n">
-        <v>6.97033977508545</v>
+        <v>6.97033929824829</v>
       </c>
       <c r="H344" t="n">
         <v>42139</v>
@@ -10403,7 +10403,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G346" t="n">
-        <v>7.145751953125</v>
+        <v>7.14575147628784</v>
       </c>
       <c r="H346" t="n">
         <v>47587</v>
@@ -10461,7 +10461,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G348" t="n">
-        <v>6.90571355819702</v>
+        <v>6.90571403503418</v>
       </c>
       <c r="H348" t="n">
         <v>60152</v>
@@ -10519,7 +10519,7 @@
         <v>7.53999996185303</v>
       </c>
       <c r="G350" t="n">
-        <v>6.96110677719116</v>
+        <v>6.96110725402832</v>
       </c>
       <c r="H350" t="n">
         <v>28852</v>
@@ -10548,7 +10548,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G351" t="n">
-        <v>6.77646207809448</v>
+        <v>6.77646255493164</v>
       </c>
       <c r="H351" t="n">
         <v>58129</v>
@@ -10664,7 +10664,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G355" t="n">
-        <v>6.53642416000366</v>
+        <v>6.5364236831665</v>
       </c>
       <c r="H355" t="n">
         <v>26264</v>
@@ -10809,7 +10809,7 @@
         <v>6.98999977111816</v>
       </c>
       <c r="G360" t="n">
-        <v>6.45333337783813</v>
+        <v>6.45333385467529</v>
       </c>
       <c r="H360" t="n">
         <v>50111</v>
@@ -10867,7 +10867,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G362" t="n">
-        <v>6.6472110748291</v>
+        <v>6.64721059799194</v>
       </c>
       <c r="H362" t="n">
         <v>58993</v>
@@ -10896,7 +10896,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G363" t="n">
-        <v>6.40717267990112</v>
+        <v>6.40717315673828</v>
       </c>
       <c r="H363" t="n">
         <v>39953</v>
@@ -10925,7 +10925,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G364" t="n">
-        <v>6.63797903060913</v>
+        <v>6.63797855377197</v>
       </c>
       <c r="H364" t="n">
         <v>33892</v>
@@ -11012,7 +11012,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G367" t="n">
-        <v>6.48103094100952</v>
+        <v>6.48103046417236</v>
       </c>
       <c r="H367" t="n">
         <v>37646</v>
@@ -11041,7 +11041,7 @@
         <v>7.09000015258789</v>
       </c>
       <c r="G368" t="n">
-        <v>6.54565668106079</v>
+        <v>6.54565620422363</v>
       </c>
       <c r="H368" t="n">
         <v>45957</v>
@@ -11099,7 +11099,7 @@
         <v>7.09000015258789</v>
       </c>
       <c r="G370" t="n">
-        <v>6.54565668106079</v>
+        <v>6.54565620422363</v>
       </c>
       <c r="H370" t="n">
         <v>28684</v>
@@ -11128,7 +11128,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G371" t="n">
-        <v>6.63797903060913</v>
+        <v>6.63797855377197</v>
       </c>
       <c r="H371" t="n">
         <v>24535</v>
@@ -11186,7 +11186,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G373" t="n">
-        <v>6.32408285140991</v>
+        <v>6.32408237457275</v>
       </c>
       <c r="H373" t="n">
         <v>47509</v>
@@ -11215,7 +11215,7 @@
         <v>7</v>
       </c>
       <c r="G374" t="n">
-        <v>6.46256589889526</v>
+        <v>6.46256637573242</v>
       </c>
       <c r="H374" t="n">
         <v>17115</v>
@@ -11476,7 +11476,7 @@
         <v>7.09000015258789</v>
       </c>
       <c r="G383" t="n">
-        <v>6.54565668106079</v>
+        <v>6.54565620422363</v>
       </c>
       <c r="H383" t="n">
         <v>39879</v>
@@ -11592,7 +11592,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G387" t="n">
-        <v>6.61028146743774</v>
+        <v>6.6102819442749</v>
       </c>
       <c r="H387" t="n">
         <v>59425</v>
@@ -11650,7 +11650,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G389" t="n">
-        <v>6.87801694869995</v>
+        <v>6.87801647186279</v>
       </c>
       <c r="H389" t="n">
         <v>91784</v>
@@ -11679,7 +11679,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G390" t="n">
-        <v>7.13651990890503</v>
+        <v>7.13651943206787</v>
       </c>
       <c r="H390" t="n">
         <v>203114</v>
@@ -11766,7 +11766,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G393" t="n">
-        <v>7.30270004272461</v>
+        <v>7.30269956588745</v>
       </c>
       <c r="H393" t="n">
         <v>167425</v>
@@ -11795,7 +11795,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G394" t="n">
-        <v>7.2011456489563</v>
+        <v>7.20114517211914</v>
       </c>
       <c r="H394" t="n">
         <v>191654</v>
@@ -11853,7 +11853,7 @@
         <v>7.86999988555908</v>
       </c>
       <c r="G396" t="n">
-        <v>7.26577043533325</v>
+        <v>7.26577091217041</v>
       </c>
       <c r="H396" t="n">
         <v>50620</v>
@@ -11911,7 +11911,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G398" t="n">
-        <v>7.30270004272461</v>
+        <v>7.30269956588745</v>
       </c>
       <c r="H398" t="n">
         <v>99717</v>
@@ -11940,7 +11940,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G399" t="n">
-        <v>7.36732530593872</v>
+        <v>7.36732578277588</v>
       </c>
       <c r="H399" t="n">
         <v>124059</v>
@@ -11969,7 +11969,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G400" t="n">
-        <v>7.24730634689331</v>
+        <v>7.24730587005615</v>
       </c>
       <c r="H400" t="n">
         <v>72121</v>
@@ -12114,7 +12114,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G405" t="n">
-        <v>7.30270004272461</v>
+        <v>7.30269956588745</v>
       </c>
       <c r="H405" t="n">
         <v>38438</v>
@@ -12636,7 +12636,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G423" t="n">
-        <v>7.40425491333008</v>
+        <v>7.40425443649292</v>
       </c>
       <c r="H423" t="n">
         <v>48656</v>
@@ -12752,7 +12752,7 @@
         <v>8.25</v>
       </c>
       <c r="G427" t="n">
-        <v>7.61659574508667</v>
+        <v>7.61659622192383</v>
       </c>
       <c r="H427" t="n">
         <v>55700</v>
@@ -12810,7 +12810,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G429" t="n">
-        <v>7.90279626846313</v>
+        <v>7.90279531478882</v>
       </c>
       <c r="H429" t="n">
         <v>122032</v>
@@ -12984,7 +12984,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G435" t="n">
-        <v>8.63214302062988</v>
+        <v>8.63214206695557</v>
       </c>
       <c r="H435" t="n">
         <v>236669</v>
@@ -13158,7 +13158,7 @@
         <v>9.6899995803833</v>
       </c>
       <c r="G441" t="n">
-        <v>8.94603824615479</v>
+        <v>8.94603729248047</v>
       </c>
       <c r="H441" t="n">
         <v>85296</v>
@@ -13216,7 +13216,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G443" t="n">
-        <v>8.9921989440918</v>
+        <v>8.99219989776611</v>
       </c>
       <c r="H443" t="n">
         <v>101160</v>
@@ -13477,7 +13477,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G452" t="n">
-        <v>9.52766799926758</v>
+        <v>9.52766895294189</v>
       </c>
       <c r="H452" t="n">
         <v>186778</v>
@@ -13506,7 +13506,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G453" t="n">
-        <v>9.61999225616455</v>
+        <v>9.61999130249023</v>
       </c>
       <c r="H453" t="n">
         <v>106036</v>
@@ -13535,7 +13535,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G454" t="n">
-        <v>9.4168815612793</v>
+        <v>9.41688251495361</v>
       </c>
       <c r="H454" t="n">
         <v>85544</v>
@@ -13593,7 +13593,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G456" t="n">
-        <v>9.25070285797119</v>
+        <v>9.25070190429688</v>
       </c>
       <c r="H456" t="n">
         <v>45013</v>
@@ -13651,7 +13651,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G458" t="n">
-        <v>9.26916694641113</v>
+        <v>9.26916599273682</v>
       </c>
       <c r="H458" t="n">
         <v>73523</v>
@@ -13825,7 +13825,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G464" t="n">
-        <v>9.26916694641113</v>
+        <v>9.26916599273682</v>
       </c>
       <c r="H464" t="n">
         <v>35262</v>
@@ -13883,7 +13883,7 @@
         <v>9.98999977111816</v>
       </c>
       <c r="G466" t="n">
-        <v>9.22300434112549</v>
+        <v>9.2230052947998</v>
       </c>
       <c r="H466" t="n">
         <v>90490</v>
@@ -13999,7 +13999,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G470" t="n">
-        <v>9.61999225616455</v>
+        <v>9.61999130249023</v>
       </c>
       <c r="H470" t="n">
         <v>91656</v>
@@ -14028,7 +14028,7 @@
         <v>10.4799995422363</v>
       </c>
       <c r="G471" t="n">
-        <v>9.67538452148438</v>
+        <v>9.67538356781006</v>
       </c>
       <c r="H471" t="n">
         <v>94908</v>
@@ -14173,7 +14173,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G476" t="n">
-        <v>9.61999225616455</v>
+        <v>9.61999130249023</v>
       </c>
       <c r="H476" t="n">
         <v>55619</v>
@@ -14202,7 +14202,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G477" t="n">
-        <v>9.58306312561035</v>
+        <v>9.58306217193604</v>
       </c>
       <c r="H477" t="n">
         <v>68414</v>
@@ -14289,7 +14289,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G480" t="n">
-        <v>10.247784614563</v>
+        <v>10.2477836608887</v>
       </c>
       <c r="H480" t="n">
         <v>121664</v>
@@ -14318,7 +14318,7 @@
         <v>11.1199998855591</v>
       </c>
       <c r="G481" t="n">
-        <v>10.2662487030029</v>
+        <v>10.2662477493286</v>
       </c>
       <c r="H481" t="n">
         <v>62344</v>
@@ -14347,7 +14347,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G482" t="n">
-        <v>8.93680667877197</v>
+        <v>8.93680572509766</v>
       </c>
       <c r="H482" t="n">
         <v>1087677</v>
@@ -14376,7 +14376,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G483" t="n">
-        <v>9.28763198852539</v>
+        <v>9.28763103485107</v>
       </c>
       <c r="H483" t="n">
         <v>332225</v>
@@ -14405,7 +14405,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G484" t="n">
-        <v>9.21377182006836</v>
+        <v>9.21377277374268</v>
       </c>
       <c r="H484" t="n">
         <v>153862</v>
@@ -14521,7 +14521,7 @@
         <v>9.63000011444092</v>
       </c>
       <c r="G488" t="n">
-        <v>8.89064407348633</v>
+        <v>8.89064502716064</v>
       </c>
       <c r="H488" t="n">
         <v>74178</v>
@@ -14695,7 +14695,7 @@
         <v>9.28999996185303</v>
       </c>
       <c r="G494" t="n">
-        <v>8.57674884796143</v>
+        <v>8.57674789428711</v>
       </c>
       <c r="H494" t="n">
         <v>136448</v>
@@ -14724,7 +14724,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G495" t="n">
-        <v>8.48442554473877</v>
+        <v>8.48442649841309</v>
       </c>
       <c r="H495" t="n">
         <v>37699</v>
@@ -14840,7 +14840,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G499" t="n">
-        <v>8.62291049957275</v>
+        <v>8.62290954589844</v>
       </c>
       <c r="H499" t="n">
         <v>120557</v>
@@ -14898,7 +14898,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G501" t="n">
-        <v>8.62291049957275</v>
+        <v>8.62290954589844</v>
       </c>
       <c r="H501" t="n">
         <v>49932</v>
@@ -14956,7 +14956,7 @@
         <v>9.6899995803833</v>
       </c>
       <c r="G503" t="n">
-        <v>8.94603824615479</v>
+        <v>8.94603729248047</v>
       </c>
       <c r="H503" t="n">
         <v>146163</v>
@@ -14985,7 +14985,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G504" t="n">
-        <v>8.86294746398926</v>
+        <v>8.86294841766357</v>
       </c>
       <c r="H504" t="n">
         <v>41942</v>
@@ -15188,7 +15188,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G511" t="n">
-        <v>8.78909015655518</v>
+        <v>8.78909111022949</v>
       </c>
       <c r="H511" t="n">
         <v>113583</v>
@@ -15246,7 +15246,7 @@
         <v>9.8100004196167</v>
       </c>
       <c r="G513" t="n">
-        <v>9.05682563781738</v>
+        <v>9.05682468414307</v>
       </c>
       <c r="H513" t="n">
         <v>107598</v>
@@ -15333,7 +15333,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G516" t="n">
-        <v>8.95527076721191</v>
+        <v>8.9552698135376</v>
       </c>
       <c r="H516" t="n">
         <v>76374</v>
@@ -33319,6 +33319,35 @@
         <v>534033</v>
       </c>
       <c r="I1136" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1137">
+      <c r="A1137" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1137" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C1137" t="n">
+        <v>0.720000028610229</v>
+      </c>
+      <c r="D1137" t="n">
+        <v>0.763000011444092</v>
+      </c>
+      <c r="E1137" t="n">
+        <v>0.695999979972839</v>
+      </c>
+      <c r="F1137" t="n">
+        <v>0.732999980449677</v>
+      </c>
+      <c r="G1137" t="n">
+        <v>0.732999980449677</v>
+      </c>
+      <c r="H1137" t="n">
+        <v>595587</v>
+      </c>
+      <c r="I1137" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/TISG.MI.xlsx
+++ b/data/TISG.MI.xlsx
@@ -427,7 +427,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G2" t="n">
-        <v>4.97171211242676</v>
+        <v>4.97171258926392</v>
       </c>
       <c r="H2" t="n">
         <v>20197</v>
@@ -456,7 +456,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G3" t="n">
-        <v>5.12372493743896</v>
+        <v>5.12372589111328</v>
       </c>
       <c r="H3" t="n">
         <v>28276</v>
@@ -543,7 +543,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G6" t="n">
-        <v>4.97171211242676</v>
+        <v>4.97171258926392</v>
       </c>
       <c r="H6" t="n">
         <v>18977</v>
@@ -688,7 +688,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G11" t="n">
-        <v>4.97171211242676</v>
+        <v>4.97171258926392</v>
       </c>
       <c r="H11" t="n">
         <v>12298</v>
@@ -978,7 +978,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G21" t="n">
-        <v>5.02536344528198</v>
+        <v>5.0253643989563</v>
       </c>
       <c r="H21" t="n">
         <v>16980</v>
@@ -1094,7 +1094,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G25" t="n">
-        <v>4.64086103439331</v>
+        <v>4.64086151123047</v>
       </c>
       <c r="H25" t="n">
         <v>38675</v>
@@ -1384,7 +1384,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G35" t="n">
-        <v>4.64086103439331</v>
+        <v>4.64086151123047</v>
       </c>
       <c r="H35" t="n">
         <v>71434</v>
@@ -1442,7 +1442,7 @@
         <v>4.78499984741211</v>
       </c>
       <c r="G37" t="n">
-        <v>4.27871322631836</v>
+        <v>4.2787127494812</v>
       </c>
       <c r="H37" t="n">
         <v>58880</v>
@@ -1529,7 +1529,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G40" t="n">
-        <v>4.3368353843689</v>
+        <v>4.33683586120605</v>
       </c>
       <c r="H40" t="n">
         <v>82262</v>
@@ -1587,7 +1587,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G42" t="n">
-        <v>4.40837097167969</v>
+        <v>4.40837049484253</v>
       </c>
       <c r="H42" t="n">
         <v>18554</v>
@@ -1674,7 +1674,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G45" t="n">
-        <v>4.39048671722412</v>
+        <v>4.39048719406128</v>
       </c>
       <c r="H45" t="n">
         <v>25487</v>
@@ -1703,7 +1703,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G46" t="n">
-        <v>4.41731309890747</v>
+        <v>4.41731262207031</v>
       </c>
       <c r="H46" t="n">
         <v>16689</v>
@@ -1732,7 +1732,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G47" t="n">
-        <v>4.3368353843689</v>
+        <v>4.33683586120605</v>
       </c>
       <c r="H47" t="n">
         <v>57150</v>
@@ -1935,7 +1935,7 @@
         <v>4.89499998092651</v>
       </c>
       <c r="G54" t="n">
-        <v>4.37707471847534</v>
+        <v>4.37707424163818</v>
       </c>
       <c r="H54" t="n">
         <v>13462</v>
@@ -2080,7 +2080,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G59" t="n">
-        <v>4.51567459106445</v>
+        <v>4.51567411422729</v>
       </c>
       <c r="H59" t="n">
         <v>22808</v>
@@ -2196,7 +2196,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G63" t="n">
-        <v>4.64980268478394</v>
+        <v>4.64980316162109</v>
       </c>
       <c r="H63" t="n">
         <v>36457</v>
@@ -2312,7 +2312,7 @@
         <v>5.25</v>
       </c>
       <c r="G67" t="n">
-        <v>4.69451236724854</v>
+        <v>4.69451284408569</v>
       </c>
       <c r="H67" t="n">
         <v>45084</v>
@@ -2341,7 +2341,7 @@
         <v>5.25</v>
       </c>
       <c r="G68" t="n">
-        <v>4.69451236724854</v>
+        <v>4.69451284408569</v>
       </c>
       <c r="H68" t="n">
         <v>32450</v>
@@ -2370,7 +2370,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G69" t="n">
-        <v>4.64980268478394</v>
+        <v>4.64980316162109</v>
       </c>
       <c r="H69" t="n">
         <v>10853</v>
@@ -2399,7 +2399,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G70" t="n">
-        <v>4.56038379669189</v>
+        <v>4.56038331985474</v>
       </c>
       <c r="H70" t="n">
         <v>18662</v>
@@ -2428,7 +2428,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G71" t="n">
-        <v>4.61403512954712</v>
+        <v>4.61403465270996</v>
       </c>
       <c r="H71" t="n">
         <v>5955</v>
@@ -2573,7 +2573,7 @@
         <v>4.85500001907349</v>
       </c>
       <c r="G76" t="n">
-        <v>4.34130620956421</v>
+        <v>4.34130668640137</v>
       </c>
       <c r="H76" t="n">
         <v>21022</v>
@@ -2892,7 +2892,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G87" t="n">
-        <v>4.23847389221191</v>
+        <v>4.23847436904907</v>
       </c>
       <c r="H87" t="n">
         <v>24828</v>
@@ -2921,7 +2921,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G88" t="n">
-        <v>4.49779033660889</v>
+        <v>4.49779081344604</v>
       </c>
       <c r="H88" t="n">
         <v>22654</v>
@@ -2979,7 +2979,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G90" t="n">
-        <v>4.4888482093811</v>
+        <v>4.48884868621826</v>
       </c>
       <c r="H90" t="n">
         <v>27075</v>
@@ -3008,7 +3008,7 @@
         <v>4.85500001907349</v>
       </c>
       <c r="G91" t="n">
-        <v>4.34130620956421</v>
+        <v>4.34130668640137</v>
       </c>
       <c r="H91" t="n">
         <v>28795</v>
@@ -3037,7 +3037,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G92" t="n">
-        <v>4.40837097167969</v>
+        <v>4.40837049484253</v>
       </c>
       <c r="H92" t="n">
         <v>28839</v>
@@ -3095,7 +3095,7 @@
         <v>4.75</v>
       </c>
       <c r="G94" t="n">
-        <v>4.24741649627686</v>
+        <v>4.2474160194397</v>
       </c>
       <c r="H94" t="n">
         <v>25723</v>
@@ -3182,7 +3182,7 @@
         <v>4.89499998092651</v>
       </c>
       <c r="G97" t="n">
-        <v>4.37707471847534</v>
+        <v>4.37707424163818</v>
       </c>
       <c r="H97" t="n">
         <v>41065</v>
@@ -3269,7 +3269,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G100" t="n">
-        <v>4.37260293960571</v>
+        <v>4.37260341644287</v>
       </c>
       <c r="H100" t="n">
         <v>25467</v>
@@ -3298,7 +3298,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G101" t="n">
-        <v>4.08646202087402</v>
+        <v>4.08646154403687</v>
       </c>
       <c r="H101" t="n">
         <v>93157</v>
@@ -3356,7 +3356,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G103" t="n">
-        <v>3.95233297348022</v>
+        <v>3.95233249664307</v>
       </c>
       <c r="H103" t="n">
         <v>122405</v>
@@ -3385,7 +3385,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G104" t="n">
-        <v>4.01492547988892</v>
+        <v>4.01492595672607</v>
       </c>
       <c r="H104" t="n">
         <v>12994</v>
@@ -3414,7 +3414,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G105" t="n">
-        <v>3.90762305259705</v>
+        <v>3.90762281417847</v>
       </c>
       <c r="H105" t="n">
         <v>8913</v>
@@ -3443,7 +3443,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G106" t="n">
-        <v>3.84502959251404</v>
+        <v>3.84502983093262</v>
       </c>
       <c r="H106" t="n">
         <v>39490</v>
@@ -3501,7 +3501,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G108" t="n">
-        <v>3.82714581489563</v>
+        <v>3.82714605331421</v>
       </c>
       <c r="H108" t="n">
         <v>26268</v>
@@ -3530,7 +3530,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G109" t="n">
-        <v>3.80926203727722</v>
+        <v>3.80926156044006</v>
       </c>
       <c r="H109" t="n">
         <v>5280</v>
@@ -3559,7 +3559,7 @@
         <v>4.2649998664856</v>
       </c>
       <c r="G110" t="n">
-        <v>3.81373262405396</v>
+        <v>3.81373238563538</v>
       </c>
       <c r="H110" t="n">
         <v>30391</v>
@@ -3588,7 +3588,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G111" t="n">
-        <v>3.69301700592041</v>
+        <v>3.69301676750183</v>
       </c>
       <c r="H111" t="n">
         <v>51138</v>
@@ -3675,7 +3675,7 @@
         <v>4.5</v>
       </c>
       <c r="G114" t="n">
-        <v>4.02386808395386</v>
+        <v>4.02386856079102</v>
       </c>
       <c r="H114" t="n">
         <v>51824</v>
@@ -3733,7 +3733,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G116" t="n">
-        <v>4.17588090896606</v>
+        <v>4.17588138580322</v>
       </c>
       <c r="H116" t="n">
         <v>27523</v>
@@ -3791,7 +3791,7 @@
         <v>4.78499984741211</v>
       </c>
       <c r="G118" t="n">
-        <v>4.27871322631836</v>
+        <v>4.2787127494812</v>
       </c>
       <c r="H118" t="n">
         <v>22444</v>
@@ -3820,7 +3820,7 @@
         <v>4.75</v>
       </c>
       <c r="G119" t="n">
-        <v>4.24741649627686</v>
+        <v>4.2474160194397</v>
       </c>
       <c r="H119" t="n">
         <v>12242</v>
@@ -3994,7 +3994,7 @@
         <v>4.70499992370605</v>
       </c>
       <c r="G125" t="n">
-        <v>4.20717716217041</v>
+        <v>4.20717763900757</v>
       </c>
       <c r="H125" t="n">
         <v>19005</v>
@@ -4110,7 +4110,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G129" t="n">
-        <v>4.56932592391968</v>
+        <v>4.56932544708252</v>
       </c>
       <c r="H129" t="n">
         <v>34023</v>
@@ -4226,7 +4226,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G133" t="n">
-        <v>4.82864141464233</v>
+        <v>4.82864189147949</v>
       </c>
       <c r="H133" t="n">
         <v>33414</v>
@@ -4342,7 +4342,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G137" t="n">
-        <v>4.83758306503296</v>
+        <v>4.83758354187012</v>
       </c>
       <c r="H137" t="n">
         <v>18118</v>
@@ -4371,7 +4371,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G138" t="n">
-        <v>4.81075763702393</v>
+        <v>4.81075811386108</v>
       </c>
       <c r="H138" t="n">
         <v>13168</v>
@@ -4603,7 +4603,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G146" t="n">
-        <v>5.13266706466675</v>
+        <v>5.13266754150391</v>
       </c>
       <c r="H146" t="n">
         <v>31662</v>
@@ -4632,7 +4632,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G147" t="n">
-        <v>5.02536344528198</v>
+        <v>5.0253643989563</v>
       </c>
       <c r="H147" t="n">
         <v>22523</v>
@@ -4719,7 +4719,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G150" t="n">
-        <v>5.06113195419312</v>
+        <v>5.06113147735596</v>
       </c>
       <c r="H150" t="n">
         <v>44995</v>
@@ -4835,7 +4835,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G154" t="n">
-        <v>5.13266706466675</v>
+        <v>5.13266754150391</v>
       </c>
       <c r="H154" t="n">
         <v>24494</v>
@@ -4951,7 +4951,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G158" t="n">
-        <v>5.02536344528198</v>
+        <v>5.0253643989563</v>
       </c>
       <c r="H158" t="n">
         <v>12170</v>
@@ -4980,7 +4980,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G159" t="n">
-        <v>4.95382881164551</v>
+        <v>4.95382833480835</v>
       </c>
       <c r="H159" t="n">
         <v>26457</v>
@@ -5009,7 +5009,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G160" t="n">
-        <v>5.09689950942993</v>
+        <v>5.09689903259277</v>
       </c>
       <c r="H160" t="n">
         <v>13151</v>
@@ -5067,7 +5067,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G162" t="n">
-        <v>5.09689950942993</v>
+        <v>5.09689903259277</v>
       </c>
       <c r="H162" t="n">
         <v>60968</v>
@@ -5125,7 +5125,7 @@
         <v>5.69000005722046</v>
       </c>
       <c r="G164" t="n">
-        <v>5.08795785903931</v>
+        <v>5.08795738220215</v>
       </c>
       <c r="H164" t="n">
         <v>9415</v>
@@ -5154,7 +5154,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G165" t="n">
-        <v>5.04324817657471</v>
+        <v>5.04324769973755</v>
       </c>
       <c r="H165" t="n">
         <v>16099</v>
@@ -5241,7 +5241,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G168" t="n">
-        <v>5.12372493743896</v>
+        <v>5.12372589111328</v>
       </c>
       <c r="H168" t="n">
         <v>13445</v>
@@ -5328,7 +5328,7 @@
         <v>5.75</v>
       </c>
       <c r="G171" t="n">
-        <v>5.14160966873169</v>
+        <v>5.14160919189453</v>
       </c>
       <c r="H171" t="n">
         <v>1538</v>
@@ -5357,7 +5357,7 @@
         <v>5.75</v>
       </c>
       <c r="G172" t="n">
-        <v>5.14160966873169</v>
+        <v>5.14160919189453</v>
       </c>
       <c r="H172" t="n">
         <v>9719</v>
@@ -5386,7 +5386,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G173" t="n">
-        <v>5.07901525497437</v>
+        <v>5.07901573181152</v>
       </c>
       <c r="H173" t="n">
         <v>8390</v>
@@ -5444,7 +5444,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G175" t="n">
-        <v>5.13266706466675</v>
+        <v>5.13266754150391</v>
       </c>
       <c r="H175" t="n">
         <v>26260</v>
@@ -5531,7 +5531,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G178" t="n">
-        <v>5.12372493743896</v>
+        <v>5.12372589111328</v>
       </c>
       <c r="H178" t="n">
         <v>13789</v>
@@ -5560,7 +5560,7 @@
         <v>5.90999984741211</v>
       </c>
       <c r="G179" t="n">
-        <v>5.28467988967896</v>
+        <v>5.28468036651611</v>
       </c>
       <c r="H179" t="n">
         <v>21763</v>
@@ -5705,7 +5705,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G184" t="n">
-        <v>5.67812442779541</v>
+        <v>5.67812490463257</v>
       </c>
       <c r="H184" t="n">
         <v>135409</v>
@@ -5937,7 +5937,7 @@
         <v>6.80999994277954</v>
       </c>
       <c r="G192" t="n">
-        <v>6.08945369720459</v>
+        <v>6.08945322036743</v>
       </c>
       <c r="H192" t="n">
         <v>86712</v>
@@ -5966,7 +5966,7 @@
         <v>7</v>
       </c>
       <c r="G193" t="n">
-        <v>6.25935029983521</v>
+        <v>6.25934982299805</v>
       </c>
       <c r="H193" t="n">
         <v>64859</v>
@@ -5995,7 +5995,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G194" t="n">
-        <v>6.18781518936157</v>
+        <v>6.18781471252441</v>
       </c>
       <c r="H194" t="n">
         <v>195087</v>
@@ -6082,7 +6082,7 @@
         <v>7</v>
       </c>
       <c r="G197" t="n">
-        <v>6.25935029983521</v>
+        <v>6.25934982299805</v>
       </c>
       <c r="H197" t="n">
         <v>92157</v>
@@ -6198,7 +6198,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G201" t="n">
-        <v>6.27723407745361</v>
+        <v>6.27723455429077</v>
       </c>
       <c r="H201" t="n">
         <v>56777</v>
@@ -6372,7 +6372,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G207" t="n">
-        <v>6.65279483795166</v>
+        <v>6.65279531478882</v>
       </c>
       <c r="H207" t="n">
         <v>179183</v>
@@ -6517,7 +6517,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G212" t="n">
-        <v>6.617027759552</v>
+        <v>6.61702728271484</v>
       </c>
       <c r="H212" t="n">
         <v>59738</v>
@@ -6575,7 +6575,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G214" t="n">
-        <v>6.79586553573608</v>
+        <v>6.79586601257324</v>
       </c>
       <c r="H214" t="n">
         <v>155309</v>
@@ -6749,7 +6749,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G220" t="n">
-        <v>6.60808515548706</v>
+        <v>6.60808563232422</v>
       </c>
       <c r="H220" t="n">
         <v>64845</v>
@@ -7155,7 +7155,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G234" t="n">
-        <v>7.77947854995728</v>
+        <v>7.77947807312012</v>
       </c>
       <c r="H234" t="n">
         <v>98556</v>
@@ -7184,7 +7184,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G235" t="n">
-        <v>7.65429162979126</v>
+        <v>7.65429210662842</v>
       </c>
       <c r="H235" t="n">
         <v>82796</v>
@@ -7213,7 +7213,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G236" t="n">
-        <v>7.35920715332031</v>
+        <v>7.35920667648315</v>
       </c>
       <c r="H236" t="n">
         <v>253702</v>
@@ -7242,7 +7242,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G237" t="n">
-        <v>7.35920715332031</v>
+        <v>7.35920667648315</v>
       </c>
       <c r="H237" t="n">
         <v>172849</v>
@@ -7271,7 +7271,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G238" t="n">
-        <v>7.73476791381836</v>
+        <v>7.73476839065552</v>
       </c>
       <c r="H238" t="n">
         <v>113648</v>
@@ -7300,7 +7300,7 @@
         <v>8.75</v>
       </c>
       <c r="G239" t="n">
-        <v>7.82418775558472</v>
+        <v>7.82418823242188</v>
       </c>
       <c r="H239" t="n">
         <v>92729</v>
@@ -7387,7 +7387,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G242" t="n">
-        <v>7.77947854995728</v>
+        <v>7.77947807312012</v>
       </c>
       <c r="H242" t="n">
         <v>118950</v>
@@ -7416,7 +7416,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G243" t="n">
-        <v>7.73476791381836</v>
+        <v>7.73476839065552</v>
       </c>
       <c r="H243" t="n">
         <v>250001</v>
@@ -7445,7 +7445,7 @@
         <v>8.60999965667725</v>
       </c>
       <c r="G244" t="n">
-        <v>7.69900035858154</v>
+        <v>7.6990008354187</v>
       </c>
       <c r="H244" t="n">
         <v>102832</v>
@@ -7474,7 +7474,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G245" t="n">
-        <v>7.77947854995728</v>
+        <v>7.77947807312012</v>
       </c>
       <c r="H245" t="n">
         <v>76403</v>
@@ -7503,7 +7503,7 @@
         <v>8.57999992370605</v>
       </c>
       <c r="G246" t="n">
-        <v>7.67217445373535</v>
+        <v>7.67217540740967</v>
       </c>
       <c r="H246" t="n">
         <v>44155</v>
@@ -7532,7 +7532,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G247" t="n">
-        <v>7.64534950256348</v>
+        <v>7.64534997940063</v>
       </c>
       <c r="H247" t="n">
         <v>105886</v>
@@ -7561,7 +7561,7 @@
         <v>8.63000011444092</v>
       </c>
       <c r="G248" t="n">
-        <v>7.71688508987427</v>
+        <v>7.71688461303711</v>
       </c>
       <c r="H248" t="n">
         <v>49730</v>
@@ -7590,7 +7590,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G249" t="n">
-        <v>7.73476791381836</v>
+        <v>7.73476839065552</v>
       </c>
       <c r="H249" t="n">
         <v>51008</v>
@@ -7735,7 +7735,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G254" t="n">
-        <v>7.81047344207764</v>
+        <v>7.81047248840332</v>
       </c>
       <c r="H254" t="n">
         <v>152971</v>
@@ -7793,7 +7793,7 @@
         <v>8.52999973297119</v>
       </c>
       <c r="G256" t="n">
-        <v>7.87509870529175</v>
+        <v>7.87509775161743</v>
       </c>
       <c r="H256" t="n">
         <v>99895</v>
@@ -7996,7 +7996,7 @@
         <v>8.60999965667725</v>
       </c>
       <c r="G263" t="n">
-        <v>7.94895553588867</v>
+        <v>7.94895648956299</v>
       </c>
       <c r="H263" t="n">
         <v>76537</v>
@@ -8141,7 +8141,7 @@
         <v>8.60999965667725</v>
       </c>
       <c r="G268" t="n">
-        <v>7.94895553588867</v>
+        <v>7.94895648956299</v>
       </c>
       <c r="H268" t="n">
         <v>61503</v>
@@ -8199,7 +8199,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G270" t="n">
-        <v>7.95818853378296</v>
+        <v>7.95818901062012</v>
       </c>
       <c r="H270" t="n">
         <v>77829</v>
@@ -8460,7 +8460,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G279" t="n">
-        <v>7.42271900177002</v>
+        <v>7.42271852493286</v>
       </c>
       <c r="H279" t="n">
         <v>56062</v>
@@ -8518,7 +8518,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G281" t="n">
-        <v>7.4965763092041</v>
+        <v>7.49657678604126</v>
       </c>
       <c r="H281" t="n">
         <v>39852</v>
@@ -8605,7 +8605,7 @@
         <v>7.80999994277954</v>
       </c>
       <c r="G284" t="n">
-        <v>7.21037769317627</v>
+        <v>7.21037721633911</v>
       </c>
       <c r="H284" t="n">
         <v>117674</v>
@@ -8634,7 +8634,7 @@
         <v>7.71000003814697</v>
       </c>
       <c r="G285" t="n">
-        <v>7.11805534362793</v>
+        <v>7.11805486679077</v>
       </c>
       <c r="H285" t="n">
         <v>57382</v>
@@ -8663,7 +8663,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G286" t="n">
-        <v>7.05342960357666</v>
+        <v>7.0534291267395</v>
       </c>
       <c r="H286" t="n">
         <v>74446</v>
@@ -8692,7 +8692,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G287" t="n">
-        <v>7.1088228225708</v>
+        <v>7.10882234573364</v>
       </c>
       <c r="H287" t="n">
         <v>108157</v>
@@ -8721,7 +8721,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G288" t="n">
-        <v>6.97033929824829</v>
+        <v>6.97033977508545</v>
       </c>
       <c r="H288" t="n">
         <v>37819</v>
@@ -8750,7 +8750,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G289" t="n">
-        <v>6.97033929824829</v>
+        <v>6.97033977508545</v>
       </c>
       <c r="H289" t="n">
         <v>41222</v>
@@ -8953,7 +8953,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G296" t="n">
-        <v>7.30269956588745</v>
+        <v>7.30270004272461</v>
       </c>
       <c r="H296" t="n">
         <v>83813</v>
@@ -8982,7 +8982,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G297" t="n">
-        <v>7.14575147628784</v>
+        <v>7.145751953125</v>
       </c>
       <c r="H297" t="n">
         <v>43493</v>
@@ -9069,7 +9069,7 @@
         <v>7.78999996185303</v>
       </c>
       <c r="G300" t="n">
-        <v>7.19191265106201</v>
+        <v>7.19191312789917</v>
       </c>
       <c r="H300" t="n">
         <v>50892</v>
@@ -9330,7 +9330,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G309" t="n">
-        <v>6.93341064453125</v>
+        <v>6.93341016769409</v>
       </c>
       <c r="H309" t="n">
         <v>19291</v>
@@ -9359,7 +9359,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G310" t="n">
-        <v>6.97033929824829</v>
+        <v>6.97033977508545</v>
       </c>
       <c r="H310" t="n">
         <v>22938</v>
@@ -9388,7 +9388,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G311" t="n">
-        <v>6.87801647186279</v>
+        <v>6.87801694869995</v>
       </c>
       <c r="H311" t="n">
         <v>39307</v>
@@ -9417,7 +9417,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G312" t="n">
-        <v>7.0349645614624</v>
+        <v>7.03496503829956</v>
       </c>
       <c r="H312" t="n">
         <v>19565</v>
@@ -9533,7 +9533,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G316" t="n">
-        <v>6.97033929824829</v>
+        <v>6.97033977508545</v>
       </c>
       <c r="H316" t="n">
         <v>31066</v>
@@ -9591,7 +9591,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G318" t="n">
-        <v>7.42271900177002</v>
+        <v>7.42271852493286</v>
       </c>
       <c r="H318" t="n">
         <v>77225</v>
@@ -9678,7 +9678,7 @@
         <v>7.78999996185303</v>
       </c>
       <c r="G321" t="n">
-        <v>7.19191265106201</v>
+        <v>7.19191312789917</v>
       </c>
       <c r="H321" t="n">
         <v>21141</v>
@@ -9823,7 +9823,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G326" t="n">
-        <v>7.1088228225708</v>
+        <v>7.10882234573364</v>
       </c>
       <c r="H326" t="n">
         <v>18088</v>
@@ -9852,7 +9852,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G327" t="n">
-        <v>6.97033929824829</v>
+        <v>6.97033977508545</v>
       </c>
       <c r="H327" t="n">
         <v>69708</v>
@@ -9881,7 +9881,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G328" t="n">
-        <v>7.13651943206787</v>
+        <v>7.13651990890503</v>
       </c>
       <c r="H328" t="n">
         <v>33278</v>
@@ -9910,7 +9910,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G329" t="n">
-        <v>7.05342960357666</v>
+        <v>7.0534291267395</v>
       </c>
       <c r="H329" t="n">
         <v>17493</v>
@@ -9997,7 +9997,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G332" t="n">
-        <v>6.93341064453125</v>
+        <v>6.93341016769409</v>
       </c>
       <c r="H332" t="n">
         <v>24732</v>
@@ -10026,7 +10026,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G333" t="n">
-        <v>7.05342960357666</v>
+        <v>7.0534291267395</v>
       </c>
       <c r="H333" t="n">
         <v>18353</v>
@@ -10084,7 +10084,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G335" t="n">
-        <v>7.05342960357666</v>
+        <v>7.0534291267395</v>
       </c>
       <c r="H335" t="n">
         <v>11054</v>
@@ -10345,7 +10345,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G344" t="n">
-        <v>6.97033929824829</v>
+        <v>6.97033977508545</v>
       </c>
       <c r="H344" t="n">
         <v>42139</v>
@@ -10403,7 +10403,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G346" t="n">
-        <v>7.14575147628784</v>
+        <v>7.145751953125</v>
       </c>
       <c r="H346" t="n">
         <v>47587</v>
@@ -10461,7 +10461,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G348" t="n">
-        <v>6.90571403503418</v>
+        <v>6.90571355819702</v>
       </c>
       <c r="H348" t="n">
         <v>60152</v>
@@ -10519,7 +10519,7 @@
         <v>7.53999996185303</v>
       </c>
       <c r="G350" t="n">
-        <v>6.96110725402832</v>
+        <v>6.96110677719116</v>
       </c>
       <c r="H350" t="n">
         <v>28852</v>
@@ -10548,7 +10548,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G351" t="n">
-        <v>6.77646255493164</v>
+        <v>6.77646207809448</v>
       </c>
       <c r="H351" t="n">
         <v>58129</v>
@@ -10664,7 +10664,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G355" t="n">
-        <v>6.5364236831665</v>
+        <v>6.53642416000366</v>
       </c>
       <c r="H355" t="n">
         <v>26264</v>
@@ -10809,7 +10809,7 @@
         <v>6.98999977111816</v>
       </c>
       <c r="G360" t="n">
-        <v>6.45333385467529</v>
+        <v>6.45333337783813</v>
       </c>
       <c r="H360" t="n">
         <v>50111</v>
@@ -10867,7 +10867,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G362" t="n">
-        <v>6.64721059799194</v>
+        <v>6.6472110748291</v>
       </c>
       <c r="H362" t="n">
         <v>58993</v>
@@ -10896,7 +10896,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G363" t="n">
-        <v>6.40717315673828</v>
+        <v>6.40717267990112</v>
       </c>
       <c r="H363" t="n">
         <v>39953</v>
@@ -10925,7 +10925,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G364" t="n">
-        <v>6.63797855377197</v>
+        <v>6.63797903060913</v>
       </c>
       <c r="H364" t="n">
         <v>33892</v>
@@ -11012,7 +11012,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G367" t="n">
-        <v>6.48103046417236</v>
+        <v>6.48103094100952</v>
       </c>
       <c r="H367" t="n">
         <v>37646</v>
@@ -11041,7 +11041,7 @@
         <v>7.09000015258789</v>
       </c>
       <c r="G368" t="n">
-        <v>6.54565620422363</v>
+        <v>6.54565668106079</v>
       </c>
       <c r="H368" t="n">
         <v>45957</v>
@@ -11099,7 +11099,7 @@
         <v>7.09000015258789</v>
       </c>
       <c r="G370" t="n">
-        <v>6.54565620422363</v>
+        <v>6.54565668106079</v>
       </c>
       <c r="H370" t="n">
         <v>28684</v>
@@ -11128,7 +11128,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G371" t="n">
-        <v>6.63797855377197</v>
+        <v>6.63797903060913</v>
       </c>
       <c r="H371" t="n">
         <v>24535</v>
@@ -11186,7 +11186,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G373" t="n">
-        <v>6.32408237457275</v>
+        <v>6.32408285140991</v>
       </c>
       <c r="H373" t="n">
         <v>47509</v>
@@ -11215,7 +11215,7 @@
         <v>7</v>
       </c>
       <c r="G374" t="n">
-        <v>6.46256637573242</v>
+        <v>6.46256589889526</v>
       </c>
       <c r="H374" t="n">
         <v>17115</v>
@@ -11476,7 +11476,7 @@
         <v>7.09000015258789</v>
       </c>
       <c r="G383" t="n">
-        <v>6.54565620422363</v>
+        <v>6.54565668106079</v>
       </c>
       <c r="H383" t="n">
         <v>39879</v>
@@ -11592,7 +11592,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G387" t="n">
-        <v>6.6102819442749</v>
+        <v>6.61028146743774</v>
       </c>
       <c r="H387" t="n">
         <v>59425</v>
@@ -11650,7 +11650,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G389" t="n">
-        <v>6.87801647186279</v>
+        <v>6.87801694869995</v>
       </c>
       <c r="H389" t="n">
         <v>91784</v>
@@ -11679,7 +11679,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G390" t="n">
-        <v>7.13651943206787</v>
+        <v>7.13651990890503</v>
       </c>
       <c r="H390" t="n">
         <v>203114</v>
@@ -11766,7 +11766,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G393" t="n">
-        <v>7.30269956588745</v>
+        <v>7.30270004272461</v>
       </c>
       <c r="H393" t="n">
         <v>167425</v>
@@ -11795,7 +11795,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G394" t="n">
-        <v>7.20114517211914</v>
+        <v>7.2011456489563</v>
       </c>
       <c r="H394" t="n">
         <v>191654</v>
@@ -11853,7 +11853,7 @@
         <v>7.86999988555908</v>
       </c>
       <c r="G396" t="n">
-        <v>7.26577091217041</v>
+        <v>7.26577043533325</v>
       </c>
       <c r="H396" t="n">
         <v>50620</v>
@@ -11911,7 +11911,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G398" t="n">
-        <v>7.30269956588745</v>
+        <v>7.30270004272461</v>
       </c>
       <c r="H398" t="n">
         <v>99717</v>
@@ -11940,7 +11940,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G399" t="n">
-        <v>7.36732578277588</v>
+        <v>7.36732530593872</v>
       </c>
       <c r="H399" t="n">
         <v>124059</v>
@@ -11969,7 +11969,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G400" t="n">
-        <v>7.24730587005615</v>
+        <v>7.24730634689331</v>
       </c>
       <c r="H400" t="n">
         <v>72121</v>
@@ -12114,7 +12114,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G405" t="n">
-        <v>7.30269956588745</v>
+        <v>7.30270004272461</v>
       </c>
       <c r="H405" t="n">
         <v>38438</v>
@@ -12636,7 +12636,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G423" t="n">
-        <v>7.40425443649292</v>
+        <v>7.40425491333008</v>
       </c>
       <c r="H423" t="n">
         <v>48656</v>
@@ -12752,7 +12752,7 @@
         <v>8.25</v>
       </c>
       <c r="G427" t="n">
-        <v>7.61659622192383</v>
+        <v>7.61659574508667</v>
       </c>
       <c r="H427" t="n">
         <v>55700</v>
@@ -12810,7 +12810,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G429" t="n">
-        <v>7.90279531478882</v>
+        <v>7.90279626846313</v>
       </c>
       <c r="H429" t="n">
         <v>122032</v>
@@ -12984,7 +12984,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G435" t="n">
-        <v>8.63214206695557</v>
+        <v>8.63214302062988</v>
       </c>
       <c r="H435" t="n">
         <v>236669</v>
@@ -13158,7 +13158,7 @@
         <v>9.6899995803833</v>
       </c>
       <c r="G441" t="n">
-        <v>8.94603729248047</v>
+        <v>8.94603824615479</v>
       </c>
       <c r="H441" t="n">
         <v>85296</v>
@@ -13216,7 +13216,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G443" t="n">
-        <v>8.99219989776611</v>
+        <v>8.9921989440918</v>
       </c>
       <c r="H443" t="n">
         <v>101160</v>
@@ -13477,7 +13477,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G452" t="n">
-        <v>9.52766895294189</v>
+        <v>9.52766799926758</v>
       </c>
       <c r="H452" t="n">
         <v>186778</v>
@@ -13506,7 +13506,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G453" t="n">
-        <v>9.61999130249023</v>
+        <v>9.61999225616455</v>
       </c>
       <c r="H453" t="n">
         <v>106036</v>
@@ -13535,7 +13535,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G454" t="n">
-        <v>9.41688251495361</v>
+        <v>9.4168815612793</v>
       </c>
       <c r="H454" t="n">
         <v>85544</v>
@@ -13593,7 +13593,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G456" t="n">
-        <v>9.25070190429688</v>
+        <v>9.25070285797119</v>
       </c>
       <c r="H456" t="n">
         <v>45013</v>
@@ -13651,7 +13651,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G458" t="n">
-        <v>9.26916599273682</v>
+        <v>9.26916694641113</v>
       </c>
       <c r="H458" t="n">
         <v>73523</v>
@@ -13825,7 +13825,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G464" t="n">
-        <v>9.26916599273682</v>
+        <v>9.26916694641113</v>
       </c>
       <c r="H464" t="n">
         <v>35262</v>
@@ -13883,7 +13883,7 @@
         <v>9.98999977111816</v>
       </c>
       <c r="G466" t="n">
-        <v>9.2230052947998</v>
+        <v>9.22300434112549</v>
       </c>
       <c r="H466" t="n">
         <v>90490</v>
@@ -13999,7 +13999,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G470" t="n">
-        <v>9.61999130249023</v>
+        <v>9.61999225616455</v>
       </c>
       <c r="H470" t="n">
         <v>91656</v>
@@ -14028,7 +14028,7 @@
         <v>10.4799995422363</v>
       </c>
       <c r="G471" t="n">
-        <v>9.67538356781006</v>
+        <v>9.67538452148438</v>
       </c>
       <c r="H471" t="n">
         <v>94908</v>
@@ -14173,7 +14173,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G476" t="n">
-        <v>9.61999130249023</v>
+        <v>9.61999225616455</v>
       </c>
       <c r="H476" t="n">
         <v>55619</v>
@@ -14202,7 +14202,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G477" t="n">
-        <v>9.58306217193604</v>
+        <v>9.58306312561035</v>
       </c>
       <c r="H477" t="n">
         <v>68414</v>
@@ -14289,7 +14289,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G480" t="n">
-        <v>10.2477836608887</v>
+        <v>10.247784614563</v>
       </c>
       <c r="H480" t="n">
         <v>121664</v>
@@ -14318,7 +14318,7 @@
         <v>11.1199998855591</v>
       </c>
       <c r="G481" t="n">
-        <v>10.2662477493286</v>
+        <v>10.2662487030029</v>
       </c>
       <c r="H481" t="n">
         <v>62344</v>
@@ -14347,7 +14347,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G482" t="n">
-        <v>8.93680572509766</v>
+        <v>8.93680667877197</v>
       </c>
       <c r="H482" t="n">
         <v>1087677</v>
@@ -14376,7 +14376,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G483" t="n">
-        <v>9.28763103485107</v>
+        <v>9.28763198852539</v>
       </c>
       <c r="H483" t="n">
         <v>332225</v>
@@ -14405,7 +14405,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G484" t="n">
-        <v>9.21377277374268</v>
+        <v>9.21377182006836</v>
       </c>
       <c r="H484" t="n">
         <v>153862</v>
@@ -14521,7 +14521,7 @@
         <v>9.63000011444092</v>
       </c>
       <c r="G488" t="n">
-        <v>8.89064502716064</v>
+        <v>8.89064407348633</v>
       </c>
       <c r="H488" t="n">
         <v>74178</v>
@@ -14695,7 +14695,7 @@
         <v>9.28999996185303</v>
       </c>
       <c r="G494" t="n">
-        <v>8.57674789428711</v>
+        <v>8.57674884796143</v>
       </c>
       <c r="H494" t="n">
         <v>136448</v>
@@ -14724,7 +14724,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G495" t="n">
-        <v>8.48442649841309</v>
+        <v>8.48442554473877</v>
       </c>
       <c r="H495" t="n">
         <v>37699</v>
@@ -14840,7 +14840,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G499" t="n">
-        <v>8.62290954589844</v>
+        <v>8.62291049957275</v>
       </c>
       <c r="H499" t="n">
         <v>120557</v>
@@ -14898,7 +14898,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G501" t="n">
-        <v>8.62290954589844</v>
+        <v>8.62291049957275</v>
       </c>
       <c r="H501" t="n">
         <v>49932</v>
@@ -14956,7 +14956,7 @@
         <v>9.6899995803833</v>
       </c>
       <c r="G503" t="n">
-        <v>8.94603729248047</v>
+        <v>8.94603824615479</v>
       </c>
       <c r="H503" t="n">
         <v>146163</v>
@@ -14985,7 +14985,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G504" t="n">
-        <v>8.86294841766357</v>
+        <v>8.86294746398926</v>
       </c>
       <c r="H504" t="n">
         <v>41942</v>
@@ -15188,7 +15188,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G511" t="n">
-        <v>8.78909111022949</v>
+        <v>8.78909015655518</v>
       </c>
       <c r="H511" t="n">
         <v>113583</v>
@@ -15246,7 +15246,7 @@
         <v>9.8100004196167</v>
       </c>
       <c r="G513" t="n">
-        <v>9.05682468414307</v>
+        <v>9.05682563781738</v>
       </c>
       <c r="H513" t="n">
         <v>107598</v>
@@ -15333,7 +15333,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G516" t="n">
-        <v>8.9552698135376</v>
+        <v>8.95527076721191</v>
       </c>
       <c r="H516" t="n">
         <v>76374</v>
@@ -33348,6 +33348,35 @@
         <v>595587</v>
       </c>
       <c r="I1137" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1138">
+      <c r="A1138" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1138" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C1138" t="n">
+        <v>0.726000010967255</v>
+      </c>
+      <c r="D1138" t="n">
+        <v>0.740000009536743</v>
+      </c>
+      <c r="E1138" t="n">
+        <v>0.616999983787537</v>
+      </c>
+      <c r="F1138" t="n">
+        <v>0.639999985694885</v>
+      </c>
+      <c r="G1138" t="n">
+        <v>0.639999985694885</v>
+      </c>
+      <c r="H1138" t="n">
+        <v>883396</v>
+      </c>
+      <c r="I1138" t="s">
         <v>9</v>
       </c>
     </row>
